--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1837"/>
+  <dimension ref="A1:A2252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13124,152 +13124,3057 @@
     <row r="1816">
       <c r="A1816" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap_23</t>
+          <t>OKVED_01_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1817">
       <c r="A1817" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap_24</t>
+          <t>OKVED_01_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1818">
       <c r="A1818" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap_23</t>
+          <t>OKVED_32_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1819">
       <c r="A1819" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap_24</t>
+          <t>OKVED_32_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1820">
       <c r="A1820" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap_23</t>
+          <t>OKVED_33_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1821">
       <c r="A1821" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap_24</t>
+          <t>OKVED_E_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1822">
       <c r="A1822" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap_23</t>
+          <t>OKVED_E_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1823">
       <c r="A1823" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap_24</t>
+          <t>OKVED_36_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1824">
       <c r="A1824" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap_23</t>
+          <t>OKVED_36_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1825">
       <c r="A1825" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap_24</t>
+          <t>OKVED_38_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1826">
       <c r="A1826" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_23</t>
+          <t>OKVED_38_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1827">
       <c r="A1827" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_24</t>
+          <t>OKVED_41_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1828">
       <c r="A1828" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_23</t>
+          <t>OKVED_43_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1829">
       <c r="A1829" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_24</t>
+          <t>OKVED_49_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1830">
       <c r="A1830" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap_23</t>
+          <t>OKVED_49_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1831">
       <c r="A1831" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap_24</t>
+          <t>OKVED_50_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1832">
       <c r="A1832" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap_23</t>
+          <t>OKVED_50_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1833">
       <c r="A1833" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap_24</t>
+          <t>OKVED_I_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1834">
       <c r="A1834" t="inlineStr">
         <is>
-          <t>OKVED_R_UstKap_23</t>
+          <t>OKVED_55_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1835">
       <c r="A1835" t="inlineStr">
         <is>
-          <t>OKVED_R_UstKap_24</t>
+          <t>OKVED_56_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1836">
       <c r="A1836" t="inlineStr">
         <is>
-          <t>OKVED_93_UstKap_23</t>
+          <t>OKVED_56_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1837">
       <c r="A1837" t="inlineStr">
+        <is>
+          <t>OKVED_J_OtProdDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="inlineStr">
+        <is>
+          <t>OKVED_J_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="inlineStr">
+        <is>
+          <t>OKVED_J_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="inlineStr">
+        <is>
+          <t>OKVED_63_OtProdDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="inlineStr">
+        <is>
+          <t>OKVED_63_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="inlineStr">
+        <is>
+          <t>OKVED_63_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="inlineStr">
+        <is>
+          <t>OKVED_K_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="inlineStr">
+        <is>
+          <t>OKVED_64_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="inlineStr">
+        <is>
+          <t>OKVED_69_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr">
+        <is>
+          <t>OKVED_69_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="inlineStr">
+        <is>
+          <t>OKVED_71_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="inlineStr">
+        <is>
+          <t>OKVED_74_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="inlineStr">
+        <is>
+          <t>OKVED_79_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="inlineStr">
+        <is>
+          <t>OKVED_79_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="inlineStr">
+        <is>
+          <t>OKVED_81_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="inlineStr">
+        <is>
+          <t>OKVED_81_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="inlineStr">
+        <is>
+          <t>OKVED_82_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr">
+        <is>
+          <t>OKVED_82_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="inlineStr">
+        <is>
+          <t>OKVED_O_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="inlineStr">
+        <is>
+          <t>OKVED_O_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="inlineStr">
+        <is>
+          <t>OKVED_84_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="inlineStr">
+        <is>
+          <t>OKVED_84_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="inlineStr">
+        <is>
+          <t>OKVED_85_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="inlineStr">
+        <is>
+          <t>OKVED_85_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="inlineStr">
+        <is>
+          <t>OKVED_85_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="inlineStr">
+        <is>
+          <t>OKVED_85_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="inlineStr">
+        <is>
+          <t>OKVED_Q_OtProdDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="inlineStr">
+        <is>
+          <t>OKVED_Q_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="inlineStr">
+        <is>
+          <t>OKVED_Q_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="inlineStr">
+        <is>
+          <t>OKVED_88_OtProdDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="inlineStr">
+        <is>
+          <t>OKVED_88_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="inlineStr">
+        <is>
+          <t>OKVED_88_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="inlineStr">
+        <is>
+          <t>OKVED_R_OtProdDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="inlineStr">
+        <is>
+          <t>OKVED_R_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="inlineStr">
+        <is>
+          <t>OKVED_R_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="inlineStr">
+        <is>
+          <t>OKVED_93_OtProdDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="inlineStr">
+        <is>
+          <t>OKVED_93_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="inlineStr">
+        <is>
+          <t>OKVED_93_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="inlineStr">
+        <is>
+          <t>OKVED_S_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="inlineStr">
+        <is>
+          <t>OKVED_S_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="inlineStr">
+        <is>
+          <t>OKVED_94_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="inlineStr">
+        <is>
+          <t>OKVED_94_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="inlineStr">
+        <is>
+          <t>OKVED_96_ArendPlDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="inlineStr">
+        <is>
+          <t>OKVED_96_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="inlineStr">
+        <is>
+          <t>OKVED_11_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="inlineStr">
+        <is>
+          <t>OKVED_32_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="inlineStr">
+        <is>
+          <t>OKVED_33_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="inlineStr">
+        <is>
+          <t>OKVED_36_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="inlineStr">
+        <is>
+          <t>OKVED_56_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="inlineStr">
+        <is>
+          <t>OKVED_J_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="inlineStr">
+        <is>
+          <t>OKVED_63_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="inlineStr">
+        <is>
+          <t>OKVED_69_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="inlineStr">
+        <is>
+          <t>OKVED_70_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="inlineStr">
+        <is>
+          <t>OKVED_74_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="inlineStr">
+        <is>
+          <t>OKVED_77_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="inlineStr">
+        <is>
+          <t>OKVED_81_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="inlineStr">
+        <is>
+          <t>OKVED_82_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="inlineStr">
+        <is>
+          <t>OKVED_O_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="inlineStr">
+        <is>
+          <t>OKVED_84_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="inlineStr">
+        <is>
+          <t>OKVED_85_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="inlineStr">
+        <is>
+          <t>OKVED_85_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="inlineStr">
+        <is>
+          <t>OKVED_Q_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="inlineStr">
+        <is>
+          <t>OKVED_86_PostPoTekDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="inlineStr">
+        <is>
+          <t>OKVED_86_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="inlineStr">
+        <is>
+          <t>OKVED_R_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="inlineStr">
+        <is>
+          <t>OKVED_93_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="inlineStr">
+        <is>
+          <t>OKVED_S_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="inlineStr">
+        <is>
+          <t>OKVED_94_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr">
+        <is>
+          <t>OKVED_96_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="inlineStr">
+        <is>
+          <t>OKVED_01_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="inlineStr">
+        <is>
+          <t>OKVED_01_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="inlineStr">
+        <is>
+          <t>OKVED_01_ProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="inlineStr">
+        <is>
+          <t>OKVED_01_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="inlineStr">
+        <is>
+          <t>OKVED_B_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="inlineStr">
+        <is>
+          <t>OKVED_07_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="inlineStr">
+        <is>
+          <t>OKVED_C_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="inlineStr">
+        <is>
+          <t>OKVED_10_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="inlineStr">
+        <is>
+          <t>OKVED_11_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="inlineStr">
+        <is>
+          <t>OKVED_11_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="inlineStr">
+        <is>
+          <t>OKVED_11_ProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="inlineStr">
+        <is>
+          <t>OKVED_33_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="inlineStr">
+        <is>
+          <t>OKVED_33_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="inlineStr">
+        <is>
+          <t>OKVED_33_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="inlineStr">
+        <is>
+          <t>OKVED_35_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="inlineStr">
+        <is>
+          <t>OKVED_35_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="inlineStr">
+        <is>
+          <t>OKVED_E_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
+        <is>
+          <t>OKVED_E_ProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="inlineStr">
+        <is>
+          <t>OKVED_E_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
+        <is>
+          <t>OKVED_36_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
+        <is>
+          <t>OKVED_36_ProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
+        <is>
+          <t>OKVED_36_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
+        <is>
+          <t>OKVED_38_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
+        <is>
+          <t>OKVED_38_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr">
+        <is>
+          <t>OKVED_38_ProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
+        <is>
+          <t>OKVED_38_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>OKVED_F_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="inlineStr">
+        <is>
+          <t>OKVED_F_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
+        <is>
+          <t>OKVED_41_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>OKVED_41_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
+        <is>
+          <t>OKVED_42_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
+        <is>
+          <t>OKVED_42_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
+        <is>
+          <t>OKVED_43_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
+        <is>
+          <t>OKVED_43_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
+        <is>
+          <t>OKVED_43_ProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
+        <is>
+          <t>OKVED_G_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
+        <is>
+          <t>OKVED_46_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
+        <is>
+          <t>OKVED_47_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
+        <is>
+          <t>OKVED_H_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
+        <is>
+          <t>OKVED_49_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
+        <is>
+          <t>OKVED_49_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
+        <is>
+          <t>OKVED_49_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
+        <is>
+          <t>OKVED_51_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
+        <is>
+          <t>OKVED_51_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
+        <is>
+          <t>OKVED_51_ProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
+        <is>
+          <t>OKVED_52_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
+        <is>
+          <t>OKVED_I_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
+        <is>
+          <t>OKVED_I_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
+        <is>
+          <t>OKVED_55_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
+        <is>
+          <t>OKVED_55_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
+        <is>
+          <t>OKVED_K_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
+        <is>
+          <t>OKVED_K_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
+        <is>
+          <t>OKVED_64_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
+        <is>
+          <t>OKVED_64_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
+        <is>
+          <t>OKVED_L_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
+        <is>
+          <t>OKVED_68_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
+        <is>
+          <t>OKVED_M_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
+        <is>
+          <t>OKVED_M_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
+        <is>
+          <t>OKVED_70_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
+        <is>
+          <t>OKVED_70_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
+        <is>
+          <t>OKVED_71_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
+        <is>
+          <t>OKVED_71_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="inlineStr">
+        <is>
+          <t>OKVED_71_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="inlineStr">
+        <is>
+          <t>OKVED_N_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="inlineStr">
+        <is>
+          <t>OKVED_N_ProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="inlineStr">
+        <is>
+          <t>OKVED_77_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="inlineStr">
+        <is>
+          <t>OKVED_77_ProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="inlineStr">
+        <is>
+          <t>OKVED_79_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="inlineStr">
+        <is>
+          <t>OKVED_79_ProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="inlineStr">
+        <is>
+          <t>OKVED_79_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="inlineStr">
+        <is>
+          <t>OKVED_S_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
+        <is>
+          <t>OKVED_S_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
+        <is>
+          <t>OKVED_S_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="inlineStr">
+        <is>
+          <t>OKVED_94_OtProdAkcOrgDolUch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
+        <is>
+          <t>OKVED_94_OtProdFinVlozh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
+        <is>
+          <t>OKVED_94_PrPostDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
+        <is>
+          <t>OKVED_01_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
+        <is>
+          <t>OKVED_B_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
+        <is>
+          <t>OKVED_07_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
+        <is>
+          <t>OKVED_C_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>OKVED_10_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
+        <is>
+          <t>OKVED_11_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
+        <is>
+          <t>OKVED_11_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
+        <is>
+          <t>OKVED_33_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>OKVED_33_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
+        <is>
+          <t>OKVED_E_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
+        <is>
+          <t>OKVED_36_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>OKVED_36_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
+        <is>
+          <t>OKVED_38_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
+        <is>
+          <t>OKVED_F_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
+        <is>
+          <t>OKVED_41_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
+        <is>
+          <t>OKVED_42_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
+        <is>
+          <t>OKVED_43_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
+        <is>
+          <t>OKVED_47_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
+        <is>
+          <t>OKVED_H_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>OKVED_49_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>OKVED_50_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
+          <t>OKVED_51_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
+        <is>
+          <t>OKVED_52_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>OKVED_K_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
+        <is>
+          <t>OKVED_64_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
+        <is>
+          <t>OKVED_M_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>OKVED_70_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
+        <is>
+          <t>OKVED_70_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
+        <is>
+          <t>OKVED_71_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
+        <is>
+          <t>OKVED_N_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
+        <is>
+          <t>OKVED_77_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
+        <is>
+          <t>OKVED_77_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
+        <is>
+          <t>OKVED_79_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
+        <is>
+          <t>OKVED_S_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
+        <is>
+          <t>OKVED_S_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
+        <is>
+          <t>OKVED_94_PrCenBum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
+        <is>
+          <t>OKVED_94_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
+        <is>
+          <t>OKVED_01_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
+        <is>
+          <t>OKVED_B_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
+        <is>
+          <t>OKVED_B_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
+        <is>
+          <t>OKVED_07_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
+        <is>
+          <t>OKVED_07_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
+        <is>
+          <t>OKVED_C_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
+        <is>
+          <t>OKVED_10_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>OKVED_32_PlCredit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
+        <is>
+          <t>OKVED_32_PostDeyt1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
+        <is>
+          <t>OKVED_32_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
+        <is>
+          <t>OKVED_32_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
+        <is>
+          <t>OKVED_33_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
+        <is>
+          <t>OKVED_33_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
+        <is>
+          <t>OKVED_35_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>OKVED_35_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
+        <is>
+          <t>OKVED_E_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
+        <is>
+          <t>OKVED_38_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
+        <is>
+          <t>OKVED_F_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
+        <is>
+          <t>OKVED_41_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
+        <is>
+          <t>OKVED_41_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
+        <is>
+          <t>OKVED_42_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
+        <is>
+          <t>OKVED_42_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
+        <is>
+          <t>OKVED_43_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
+        <is>
+          <t>OKVED_G_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
+        <is>
+          <t>OKVED_G_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
+        <is>
+          <t>OKVED_46_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
+        <is>
+          <t>OKVED_46_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
+        <is>
+          <t>OKVED_47_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
+        <is>
+          <t>OKVED_47_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
+        <is>
+          <t>OKVED_H_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
+        <is>
+          <t>OKVED_49_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
+        <is>
+          <t>OKVED_49_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
+        <is>
+          <t>OKVED_50_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
+        <is>
+          <t>OKVED_50_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
+        <is>
+          <t>OKVED_51_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
+        <is>
+          <t>OKVED_51_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
+        <is>
+          <t>OKVED_52_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
+        <is>
+          <t>OKVED_I_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
+        <is>
+          <t>OKVED_55_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
+        <is>
+          <t>OKVED_K_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
+        <is>
+          <t>OKVED_K_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
+        <is>
+          <t>OKVED_64_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
+        <is>
+          <t>OKVED_64_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
+        <is>
+          <t>OKVED_L_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
+        <is>
+          <t>OKVED_68_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
+        <is>
+          <t>OKVED_M_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
+        <is>
+          <t>OKVED_70_PostDeyt1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
+        <is>
+          <t>OKVED_70_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
+        <is>
+          <t>OKVED_71_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
+        <is>
+          <t>OKVED_74_PlCredit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
+        <is>
+          <t>OKVED_74_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
+        <is>
+          <t>OKVED_74_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
+        <is>
+          <t>OKVED_N_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
+        <is>
+          <t>OKVED_N_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
+        <is>
+          <t>OKVED_79_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
+        <is>
+          <t>OKVED_79_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
+        <is>
+          <t>OKVED_81_PlCredit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
+        <is>
+          <t>OKVED_81_PostDeyt1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
+        <is>
+          <t>OKVED_81_PostDeyt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
+        <is>
+          <t>OKVED_81_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
+        <is>
+          <t>OKVED_S_PostDeyt1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
+        <is>
+          <t>OKVED_S_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
+        <is>
+          <t>OKVED_94_PostDeyt1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
+        <is>
+          <t>OKVED_94_DrPost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
+        <is>
+          <t>OKVED_01_PlPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
+        <is>
+          <t>OKVED_01_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
+        <is>
+          <t>OKVED_01_PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
+        <is>
+          <t>OKVED_B_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
+        <is>
+          <t>OKVED_07_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
+        <is>
+          <t>OKVED_32_PlPoFin1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
+        <is>
+          <t>OKVED_32_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
+        <is>
+          <t>OKVED_32_PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
+        <is>
+          <t>OKVED_32_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
+        <is>
+          <t>OKVED_32_SaldoDenPot</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
+        <is>
+          <t>OKVED_33_PlPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
+        <is>
+          <t>OKVED_33_PlPoFin1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
+        <is>
+          <t>OKVED_33_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
+        <is>
+          <t>OKVED_33_PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
+        <is>
+          <t>OKVED_33_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
+        <is>
+          <t>OKVED_33_SaldoDenPot</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
+        <is>
+          <t>OKVED_35_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
+        <is>
+          <t>OKVED_35_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
+        <is>
+          <t>OKVED_E_PlPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
+        <is>
+          <t>OKVED_E_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
+        <is>
+          <t>OKVED_E_PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
+        <is>
+          <t>OKVED_38_PlPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
+        <is>
+          <t>OKVED_38_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
+        <is>
+          <t>OKVED_38_PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
+        <is>
+          <t>OKVED_F_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
+        <is>
+          <t>OKVED_41_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
+        <is>
+          <t>OKVED_42_PlPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
+        <is>
+          <t>OKVED_42_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
+        <is>
+          <t>OKVED_43_PlPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
+        <is>
+          <t>OKVED_43_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
+        <is>
+          <t>OKVED_43_PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
+        <is>
+          <t>OKVED_43_SaldoDenPot</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
+        <is>
+          <t>OKVED_G_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
+        <is>
+          <t>OKVED_46_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
+        <is>
+          <t>OKVED_47_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
+        <is>
+          <t>OKVED_H_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
+        <is>
+          <t>OKVED_49_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
+        <is>
+          <t>OKVED_49_PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
+        <is>
+          <t>OKVED_49_SaldoDenPot</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
+        <is>
+          <t>OKVED_50_PlPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
+        <is>
+          <t>OKVED_50_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
+        <is>
+          <t>OKVED_50_SaldoDenPot</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
+        <is>
+          <t>OKVED_51_PlPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
+        <is>
+          <t>OKVED_51_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
+        <is>
+          <t>OKVED_51_PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
+        <is>
+          <t>OKVED_52_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
+        <is>
+          <t>OKVED_I_PlPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
+        <is>
+          <t>OKVED_I_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
+        <is>
+          <t>OKVED_I_PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
+        <is>
+          <t>OKVED_I_SaldoDenPot</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
+        <is>
+          <t>OKVED_55_PlPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
+        <is>
+          <t>OKVED_55_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
+        <is>
+          <t>OKVED_55_PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
+        <is>
+          <t>OKVED_55_SaldoDenPot</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
+        <is>
+          <t>OKVED_K_PlPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
+        <is>
+          <t>OKVED_K_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
+        <is>
+          <t>OKVED_K_SaldoDenPot</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
+        <is>
+          <t>OKVED_64_PlPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
+        <is>
+          <t>OKVED_64_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
+        <is>
+          <t>OKVED_64_SaldoDenPot</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
+        <is>
+          <t>OKVED_L_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
+        <is>
+          <t>OKVED_68_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
+        <is>
+          <t>OKVED_M_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
+        <is>
+          <t>OKVED_70_PlPoFin1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>OKVED_70_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>OKVED_70_PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
+        <is>
+          <t>OKVED_70_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
+        <is>
+          <t>OKVED_70_SaldoDenPot</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>OKVED_71_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
+        <is>
+          <t>OKVED_74_PlPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
+        <is>
+          <t>OKVED_74_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
+        <is>
+          <t>OKVED_74_PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
+        <is>
+          <t>OKVED_74_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
+        <is>
+          <t>OKVED_N_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
+        <is>
+          <t>OKVED_N_PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
+        <is>
+          <t>OKVED_79_PlPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
+        <is>
+          <t>OKVED_79_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
+        <is>
+          <t>OKVED_79_PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
+        <is>
+          <t>OKVED_79_SaldoDenPot</t>
+        </is>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="inlineStr">
+        <is>
+          <t>OKVED_81_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="inlineStr">
+        <is>
+          <t>OKVED_81_PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="inlineStr">
+        <is>
+          <t>OKVED_81_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>OKVED_S_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="inlineStr">
+        <is>
+          <t>OKVED_S_PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>OKVED_S_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" t="inlineStr">
+        <is>
+          <t>OKVED_94_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
+        <is>
+          <t>OKVED_94_PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" t="inlineStr">
+        <is>
+          <t>OKVED_94_PrPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" t="inlineStr">
+        <is>
+          <t>OKVED_01_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" t="inlineStr">
+        <is>
+          <t>OKVED_11_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
+        <is>
+          <t>OKVED_11_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" t="inlineStr">
+        <is>
+          <t>OKVED_32_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
+        <is>
+          <t>OKVED_33_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" t="inlineStr">
+        <is>
+          <t>OKVED_E_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="inlineStr">
+        <is>
+          <t>OKVED_36_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" t="inlineStr">
+        <is>
+          <t>OKVED_36_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="inlineStr">
+        <is>
+          <t>OKVED_38_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" t="inlineStr">
+        <is>
+          <t>OKVED_F_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="inlineStr">
+        <is>
+          <t>OKVED_41_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" t="inlineStr">
+        <is>
+          <t>OKVED_42_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" t="inlineStr">
+        <is>
+          <t>OKVED_43_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" t="inlineStr">
+        <is>
+          <t>OKVED_47_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" t="inlineStr">
+        <is>
+          <t>OKVED_49_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2186">
+      <c r="A2186" t="inlineStr">
+        <is>
+          <t>OKVED_I_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" t="inlineStr">
+        <is>
+          <t>OKVED_55_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" t="inlineStr">
+        <is>
+          <t>OKVED_56_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" t="inlineStr">
+        <is>
+          <t>OKVED_56_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" t="inlineStr">
+        <is>
+          <t>OKVED_J_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" t="inlineStr">
+        <is>
+          <t>OKVED_J_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" t="inlineStr">
+        <is>
+          <t>OKVED_63_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" t="inlineStr">
+        <is>
+          <t>OKVED_63_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" t="inlineStr">
+        <is>
+          <t>OKVED_L_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" t="inlineStr">
+        <is>
+          <t>OKVED_68_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" t="inlineStr">
+        <is>
+          <t>OKVED_M_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" t="inlineStr">
+        <is>
+          <t>OKVED_69_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" t="inlineStr">
+        <is>
+          <t>OKVED_69_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" t="inlineStr">
+        <is>
+          <t>OKVED_70_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" t="inlineStr">
+        <is>
+          <t>OKVED_71_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" t="inlineStr">
+        <is>
+          <t>OKVED_74_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" t="inlineStr">
+        <is>
+          <t>OKVED_74_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" t="inlineStr">
+        <is>
+          <t>OKVED_N_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" t="inlineStr">
+        <is>
+          <t>OKVED_77_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" t="inlineStr">
+        <is>
+          <t>OKVED_77_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" t="inlineStr">
+        <is>
+          <t>OKVED_79_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="inlineStr">
+        <is>
+          <t>OKVED_81_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" t="inlineStr">
+        <is>
+          <t>OKVED_81_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" t="inlineStr">
+        <is>
+          <t>OKVED_82_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" t="inlineStr">
+        <is>
+          <t>OKVED_82_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="inlineStr">
+        <is>
+          <t>OKVED_O_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" t="inlineStr">
+        <is>
+          <t>OKVED_O_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" t="inlineStr">
+        <is>
+          <t>OKVED_84_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" t="inlineStr">
+        <is>
+          <t>OKVED_84_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" t="inlineStr">
+        <is>
+          <t>OKVED_85_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" t="inlineStr">
+        <is>
+          <t>OKVED_85_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" t="inlineStr">
+        <is>
+          <t>OKVED_85_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" t="inlineStr">
+        <is>
+          <t>OKVED_85_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
+        <is>
+          <t>OKVED_Q_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" t="inlineStr">
+        <is>
+          <t>OKVED_Q_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" t="inlineStr">
+        <is>
+          <t>OKVED_88_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" t="inlineStr">
+        <is>
+          <t>OKVED_88_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" t="inlineStr">
+        <is>
+          <t>OKVED_R_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" t="inlineStr">
+        <is>
+          <t>OKVED_R_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="A2225" t="inlineStr">
+        <is>
+          <t>OKVED_93_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" t="inlineStr">
+        <is>
+          <t>OKVED_93_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" t="inlineStr">
+        <is>
+          <t>OKVED_S_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" t="inlineStr">
+        <is>
+          <t>OKVED_94_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" t="inlineStr">
+        <is>
+          <t>OKVED_96_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" t="inlineStr">
+        <is>
+          <t>OKVED_96_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" t="inlineStr">
+        <is>
+          <t>OKVED_J_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" t="inlineStr">
+        <is>
+          <t>OKVED_J_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" t="inlineStr">
+        <is>
+          <t>OKVED_63_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" t="inlineStr">
+        <is>
+          <t>OKVED_63_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" t="inlineStr">
+        <is>
+          <t>OKVED_69_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" t="inlineStr">
+        <is>
+          <t>OKVED_69_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" t="inlineStr">
+        <is>
+          <t>OKVED_O_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" t="inlineStr">
+        <is>
+          <t>OKVED_O_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" t="inlineStr">
+        <is>
+          <t>OKVED_84_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" t="inlineStr">
+        <is>
+          <t>OKVED_84_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" t="inlineStr">
+        <is>
+          <t>OKVED_Q_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" t="inlineStr">
+        <is>
+          <t>OKVED_Q_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" t="inlineStr">
+        <is>
+          <t>OKVED_88_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" t="inlineStr">
+        <is>
+          <t>OKVED_88_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" t="inlineStr">
+        <is>
+          <t>OKVED_R_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" t="inlineStr">
+        <is>
+          <t>OKVED_R_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" t="inlineStr">
+        <is>
+          <t>OKVED_93_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" t="inlineStr">
         <is>
           <t>OKVED_93_UstKap_24</t>
         </is>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1645"/>
+  <dimension ref="A1:A1694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9729,2203 +9729,2546 @@
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_01_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>OKVED_01_ProdAkcOrgDolUch</t>
+          <t>OKVED_01_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>OKVED_B_PrCenBum</t>
+          <t>OKVED_01_ProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>OKVED_B_Saldo</t>
+          <t>OKVED_B_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>OKVED_07_PrCenBum</t>
+          <t>OKVED_B_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>OKVED_07_Saldo</t>
+          <t>OKVED_B_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>OKVED_C_PrCenBum</t>
+          <t>OKVED_07_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>OKVED_C_Saldo</t>
+          <t>OKVED_07_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>OKVED_10_PrCenBum</t>
+          <t>OKVED_07_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>OKVED_10_Saldo</t>
+          <t>OKVED_C_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>OKVED_11_PrCenBum</t>
+          <t>OKVED_C_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>OKVED_11_ProdAkcOrgDolUch</t>
+          <t>OKVED_10_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPoFin</t>
+          <t>OKVED_10_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>OKVED_11_Saldo</t>
+          <t>OKVED_11_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>OKVED_33_PrCenBum</t>
+          <t>OKVED_11_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_11_ProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>OKVED_33_Saldo</t>
+          <t>OKVED_11_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>OKVED_E_PrCenBum</t>
+          <t>OKVED_11_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>OKVED_E_ProdAkcOrgDolUch</t>
+          <t>OKVED_33_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>OKVED_E_Saldo</t>
+          <t>OKVED_33_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>OKVED_36_PrCenBum</t>
+          <t>OKVED_33_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>OKVED_36_ProdAkcOrgDolUch</t>
+          <t>OKVED_33_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>OKVED_36_PrPoFin</t>
+          <t>OKVED_35_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>OKVED_36_Saldo</t>
+          <t>OKVED_35_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>OKVED_38_PrCenBum</t>
+          <t>OKVED_E_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>OKVED_38_ProdAkcOrgDolUch</t>
+          <t>OKVED_E_ProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>OKVED_38_Saldo</t>
+          <t>OKVED_E_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>OKVED_F_PrCenBum</t>
+          <t>OKVED_36_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>OKVED_F_Saldo</t>
+          <t>OKVED_36_ProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>OKVED_41_PrCenBum</t>
+          <t>OKVED_36_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>OKVED_41_Saldo</t>
+          <t>OKVED_36_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>OKVED_42_PrCenBum</t>
+          <t>OKVED_38_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>OKVED_42_Saldo</t>
+          <t>OKVED_38_ProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>OKVED_43_PrCenBum</t>
+          <t>OKVED_38_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>OKVED_43_ProdAkcOrgDolUch</t>
+          <t>OKVED_F_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>OKVED_43_Saldo</t>
+          <t>OKVED_F_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>OKVED_46_Saldo</t>
+          <t>OKVED_41_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>OKVED_47_PrCenBum</t>
+          <t>OKVED_41_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>OKVED_H_PrCenBum</t>
+          <t>OKVED_42_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>OKVED_H_Saldo</t>
+          <t>OKVED_42_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>OKVED_49_PrCenBum</t>
+          <t>OKVED_43_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>OKVED_49_Saldo</t>
+          <t>OKVED_43_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>OKVED_50_PrCenBum</t>
+          <t>OKVED_43_ProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>OKVED_50_ProdAkcOrgDolUch</t>
+          <t>OKVED_43_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>OKVED_50_Saldo</t>
+          <t>OKVED_G_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>OKVED_51_PrCenBum</t>
+          <t>OKVED_46_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>OKVED_51_ProdAkcOrgDolUch</t>
+          <t>OKVED_46_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>OKVED_51_Saldo</t>
+          <t>OKVED_47_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>OKVED_52_PrCenBum</t>
+          <t>OKVED_47_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>OKVED_52_Saldo</t>
+          <t>OKVED_H_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>OKVED_I_Saldo</t>
+          <t>OKVED_H_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>OKVED_55_Saldo</t>
+          <t>OKVED_H_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>OKVED_K_PrCenBum</t>
+          <t>OKVED_49_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>OKVED_K_Saldo</t>
+          <t>OKVED_49_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>OKVED_64_PrCenBum</t>
+          <t>OKVED_49_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>OKVED_64_Saldo</t>
+          <t>OKVED_50_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>OKVED_M_PrCenBum</t>
+          <t>OKVED_50_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>OKVED_70_PrCenBum</t>
+          <t>OKVED_50_ProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPoFin</t>
+          <t>OKVED_50_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>OKVED_70_Saldo</t>
+          <t>OKVED_51_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>OKVED_71_PrCenBum</t>
+          <t>OKVED_51_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>OKVED_N_PrCenBum</t>
+          <t>OKVED_51_ProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>OKVED_N_ProdAkcOrgDolUch</t>
+          <t>OKVED_51_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>OKVED_77_PrCenBum</t>
+          <t>OKVED_52_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>OKVED_77_ProdAkcOrgDolUch</t>
+          <t>OKVED_52_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>OKVED_77_PrPoFin</t>
+          <t>OKVED_52_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>OKVED_77_Saldo</t>
+          <t>OKVED_I_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>OKVED_79_PrCenBum</t>
+          <t>OKVED_55_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>OKVED_79_ProdAkcOrgDolUch</t>
+          <t>OKVED_K_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>OKVED_S_DolUch</t>
+          <t>OKVED_K_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>OKVED_S_PrCenBum</t>
+          <t>OKVED_K_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>OKVED_S_PrPoFin</t>
+          <t>OKVED_64_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>OKVED_S_Saldo</t>
+          <t>OKVED_64_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>OKVED_94_DolUch</t>
+          <t>OKVED_64_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>OKVED_94_PrCenBum</t>
+          <t>OKVED_M_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>OKVED_94_PrPoFin</t>
+          <t>OKVED_M_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>OKVED_94_Saldo</t>
+          <t>OKVED_70_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_70_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>OKVED_01_ProdAkcOrgDolUch</t>
+          <t>OKVED_70_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>OKVED_B_PrCenBum</t>
+          <t>OKVED_70_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>OKVED_B_Saldo</t>
+          <t>OKVED_71_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>OKVED_07_PrCenBum</t>
+          <t>OKVED_71_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>OKVED_07_Saldo</t>
+          <t>OKVED_N_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>OKVED_C_PrCenBum</t>
+          <t>OKVED_N_ProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>OKVED_C_Saldo</t>
+          <t>OKVED_77_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>OKVED_10_PrCenBum</t>
+          <t>OKVED_77_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>OKVED_10_Saldo</t>
+          <t>OKVED_77_ProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>OKVED_32_DolUch</t>
+          <t>OKVED_77_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>OKVED_32_PrCenBum</t>
+          <t>OKVED_77_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>OKVED_32_ProdAkcOrgDolUch</t>
+          <t>OKVED_79_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>OKVED_32_PrPoFin</t>
+          <t>OKVED_79_ProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>OKVED_32_Saldo</t>
+          <t>OKVED_S_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>OKVED_33_PrCenBum</t>
+          <t>OKVED_S_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_S_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>OKVED_33_Saldo</t>
+          <t>OKVED_S_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>OKVED_E_DrPost</t>
+          <t>OKVED_94_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>OKVED_38_DrPost</t>
+          <t>OKVED_94_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>OKVED_F_DrPost</t>
+          <t>OKVED_94_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt2</t>
+          <t>OKVED_94_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>OKVED_41_DrPost</t>
+          <t>OKVED_01_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt2</t>
+          <t>OKVED_01_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>OKVED_42_DrPost</t>
+          <t>OKVED_01_ProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>OKVED_43_DrPost</t>
+          <t>OKVED_B_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt2</t>
+          <t>OKVED_B_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>OKVED_G_DrPost</t>
+          <t>OKVED_B_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt2</t>
+          <t>OKVED_07_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>OKVED_46_DrPost</t>
+          <t>OKVED_07_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt2</t>
+          <t>OKVED_07_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>OKVED_47_DrPost</t>
+          <t>OKVED_C_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>OKVED_H_DrPost</t>
+          <t>OKVED_C_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>OKVED_49_PostDeyt2</t>
+          <t>OKVED_10_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>OKVED_49_DrPost</t>
+          <t>OKVED_10_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt2</t>
+          <t>OKVED_32_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>OKVED_50_DrPost</t>
+          <t>OKVED_32_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt2</t>
+          <t>OKVED_32_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>OKVED_51_DrPost</t>
+          <t>OKVED_32_ProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>OKVED_52_DrPost</t>
+          <t>OKVED_32_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>OKVED_I_DrPost</t>
+          <t>OKVED_32_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>OKVED_55_DrPost</t>
+          <t>OKVED_33_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt2</t>
+          <t>OKVED_33_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>OKVED_K_DrPost</t>
+          <t>OKVED_33_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt2</t>
+          <t>OKVED_33_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>OKVED_64_DrPost</t>
+          <t>OKVED_35_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>OKVED_L_DrPost</t>
+          <t>OKVED_35_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>OKVED_68_DrPost</t>
+          <t>OKVED_E_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>OKVED_M_PostDeyt2</t>
+          <t>OKVED_E_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>OKVED_70_PostDeyt1</t>
+          <t>OKVED_38_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>OKVED_70_PostDeyt2</t>
+          <t>OKVED_38_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>OKVED_71_PostDeyt2</t>
+          <t>OKVED_F_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>OKVED_74_PlCredit</t>
+          <t>OKVED_F_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt2</t>
+          <t>OKVED_41_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>OKVED_74_DrPost</t>
+          <t>OKVED_41_PostDeyt2</t>
         </is>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt2</t>
+          <t>OKVED_41_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>OKVED_N_DrPost</t>
+          <t>OKVED_42_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt2</t>
+          <t>OKVED_42_PostDeyt2</t>
         </is>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>OKVED_79_DrPost</t>
+          <t>OKVED_42_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>OKVED_81_PlCredit</t>
+          <t>OKVED_43_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt1</t>
+          <t>OKVED_43_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt2</t>
+          <t>OKVED_G_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>OKVED_81_DrPost</t>
+          <t>OKVED_G_PostDeyt2</t>
         </is>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>OKVED_S_PostDeyt1</t>
+          <t>OKVED_G_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>OKVED_S_DrPost</t>
+          <t>OKVED_46_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>OKVED_94_PostDeyt1</t>
+          <t>OKVED_46_PostDeyt2</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>OKVED_94_DrPost</t>
+          <t>OKVED_46_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin</t>
+          <t>OKVED_47_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin2</t>
+          <t>OKVED_47_PostDeyt2</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin3</t>
+          <t>OKVED_47_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>OKVED_B_PlPoFin2</t>
+          <t>OKVED_H_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>OKVED_07_PlPoFin2</t>
+          <t>OKVED_H_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin1</t>
+          <t>OKVED_49_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin2</t>
+          <t>OKVED_49_PostDeyt2</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin3</t>
+          <t>OKVED_49_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>OKVED_32_PrPoFin</t>
+          <t>OKVED_50_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>OKVED_32_SaldoDenPot</t>
+          <t>OKVED_50_PostDeyt2</t>
         </is>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin</t>
+          <t>OKVED_50_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin1</t>
+          <t>OKVED_51_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin2</t>
+          <t>OKVED_51_PostDeyt2</t>
         </is>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin3</t>
+          <t>OKVED_51_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_52_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>OKVED_33_SaldoDenPot</t>
+          <t>OKVED_52_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin2</t>
+          <t>OKVED_I_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin2</t>
+          <t>OKVED_55_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin</t>
+          <t>OKVED_K_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin2</t>
+          <t>OKVED_K_PostDeyt2</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin3</t>
+          <t>OKVED_K_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin</t>
+          <t>OKVED_64_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin2</t>
+          <t>OKVED_64_PostDeyt2</t>
         </is>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin3</t>
+          <t>OKVED_64_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>OKVED_F_PlPoFin2</t>
+          <t>OKVED_L_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>OKVED_41_PlPoFin2</t>
+          <t>OKVED_68_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>OKVED_42_PlPoFin</t>
+          <t>OKVED_M_PostDeyt2</t>
         </is>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>OKVED_42_PlPoFin2</t>
+          <t>OKVED_70_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin</t>
+          <t>OKVED_70_PostDeyt2</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin2</t>
+          <t>OKVED_71_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin3</t>
+          <t>OKVED_71_PostDeyt2</t>
         </is>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>OKVED_43_SaldoDenPot</t>
+          <t>OKVED_74_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>OKVED_G_PlPoFin2</t>
+          <t>OKVED_74_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>OKVED_46_PlPoFin2</t>
+          <t>OKVED_74_PostDeyt2</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>OKVED_47_PlPoFin2</t>
+          <t>OKVED_74_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>OKVED_H_PlPoFin2</t>
+          <t>OKVED_N_PostDeyt2</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin2</t>
+          <t>OKVED_N_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin3</t>
+          <t>OKVED_79_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>OKVED_49_SaldoDenPot</t>
+          <t>OKVED_79_PostDeyt2</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoFin</t>
+          <t>OKVED_79_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoFin2</t>
+          <t>OKVED_81_PostFin</t>
         </is>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>OKVED_50_SaldoDenPot</t>
+          <t>OKVED_81_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>OKVED_51_PlPoFin</t>
+          <t>OKVED_81_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>OKVED_51_PlPoFin2</t>
+          <t>OKVED_81_PostDeyt2</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>OKVED_51_PlPoFin3</t>
+          <t>OKVED_81_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>OKVED_52_PlPoFin2</t>
+          <t>OKVED_S_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin</t>
+          <t>OKVED_S_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin2</t>
+          <t>OKVED_94_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin3</t>
+          <t>OKVED_94_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>OKVED_I_SaldoDenPot</t>
+          <t>OKVED_01_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin</t>
+          <t>OKVED_01_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin2</t>
+          <t>OKVED_01_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin3</t>
+          <t>OKVED_B_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>OKVED_55_SaldoDenPot</t>
+          <t>OKVED_07_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoFin</t>
+          <t>OKVED_32_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoFin2</t>
+          <t>OKVED_32_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>OKVED_K_SaldoDenPot</t>
+          <t>OKVED_32_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoFin</t>
+          <t>OKVED_32_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoFin2</t>
+          <t>OKVED_32_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>OKVED_64_SaldoDenPot</t>
+          <t>OKVED_33_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>OKVED_L_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>OKVED_68_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>OKVED_M_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin1</t>
+          <t>OKVED_33_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin2</t>
+          <t>OKVED_33_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin3</t>
+          <t>OKVED_35_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPoFin</t>
+          <t>OKVED_35_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>OKVED_70_SaldoDenPot</t>
+          <t>OKVED_E_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>OKVED_71_PlPoFin2</t>
+          <t>OKVED_E_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin</t>
+          <t>OKVED_E_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin2</t>
+          <t>OKVED_38_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin3</t>
+          <t>OKVED_38_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>OKVED_74_PrPoFin</t>
+          <t>OKVED_38_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>OKVED_N_PlPoFin2</t>
+          <t>OKVED_F_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>OKVED_N_PlPoFin3</t>
+          <t>OKVED_41_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin</t>
+          <t>OKVED_42_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin2</t>
+          <t>OKVED_42_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin3</t>
+          <t>OKVED_43_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>OKVED_79_SaldoDenPot</t>
+          <t>OKVED_43_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin2</t>
+          <t>OKVED_43_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin3</t>
+          <t>OKVED_43_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>OKVED_81_PrPoFin</t>
+          <t>OKVED_G_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin2</t>
+          <t>OKVED_46_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin3</t>
+          <t>OKVED_47_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>OKVED_S_PrPoFin</t>
+          <t>OKVED_H_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin2</t>
+          <t>OKVED_49_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin3</t>
+          <t>OKVED_49_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>OKVED_94_PrPoFin</t>
+          <t>OKVED_49_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>OKVED_01_PostSredst</t>
+          <t>OKVED_50_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>OKVED_11_SaldoDenPotOtch</t>
+          <t>OKVED_50_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>OKVED_11_PostSredst</t>
+          <t>OKVED_50_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>OKVED_32_PostSredst</t>
+          <t>OKVED_51_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>OKVED_33_PostSredst</t>
+          <t>OKVED_51_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>OKVED_E_PostSredst</t>
+          <t>OKVED_51_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>OKVED_36_SaldoDenPotOtch</t>
+          <t>OKVED_52_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>OKVED_36_PostSredst</t>
+          <t>OKVED_I_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>OKVED_38_PostSredst</t>
+          <t>OKVED_I_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>OKVED_F_PostSredst</t>
+          <t>OKVED_I_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>OKVED_41_PostSredst</t>
+          <t>OKVED_I_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>OKVED_42_PostSredst</t>
+          <t>OKVED_55_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>OKVED_43_PostSredst</t>
+          <t>OKVED_55_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>OKVED_47_PostSredst</t>
+          <t>OKVED_55_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>OKVED_49_PostSredst</t>
+          <t>OKVED_55_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>OKVED_I_PostSredst</t>
+          <t>OKVED_K_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>OKVED_55_PostSredst</t>
+          <t>OKVED_K_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>OKVED_56_SaldoDenPotOtch</t>
+          <t>OKVED_K_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>OKVED_56_PostSredst</t>
+          <t>OKVED_64_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>OKVED_J_SaldoDenPotOtch</t>
+          <t>OKVED_64_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>OKVED_J_PostSredst</t>
+          <t>OKVED_64_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>OKVED_63_SaldoDenPotOtch</t>
+          <t>OKVED_L_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>OKVED_63_PostSredst</t>
+          <t>OKVED_68_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>OKVED_L_PostSredst</t>
+          <t>OKVED_M_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>OKVED_68_PostSredst</t>
+          <t>OKVED_70_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>OKVED_M_PostSredst</t>
+          <t>OKVED_70_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>OKVED_69_SaldoDenPotOtch</t>
+          <t>OKVED_70_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>OKVED_69_PostSredst</t>
+          <t>OKVED_70_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>OKVED_70_PostSredst</t>
+          <t>OKVED_70_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>OKVED_71_PostSredst</t>
+          <t>OKVED_71_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>OKVED_74_SaldoDenPotOtch</t>
+          <t>OKVED_74_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>OKVED_74_PostSredst</t>
+          <t>OKVED_74_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>OKVED_N_PostSredst</t>
+          <t>OKVED_74_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>OKVED_77_SaldoDenPotOtch</t>
+          <t>OKVED_74_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>OKVED_77_PostSredst</t>
+          <t>OKVED_N_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>OKVED_79_PostSredst</t>
+          <t>OKVED_N_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>OKVED_81_SaldoDenPotOtch</t>
+          <t>OKVED_79_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>OKVED_81_PostSredst</t>
+          <t>OKVED_79_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>OKVED_82_SaldoDenPotOtch</t>
+          <t>OKVED_79_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>OKVED_82_PostSredst</t>
+          <t>OKVED_79_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>OKVED_O_SaldoDenPotOtch</t>
+          <t>OKVED_81_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>OKVED_O_PostSredst</t>
+          <t>OKVED_81_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>OKVED_84_SaldoDenPotOtch</t>
+          <t>OKVED_81_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>OKVED_84_PostSredst</t>
+          <t>OKVED_S_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>OKVED_85_SaldoDenPotOtch</t>
+          <t>OKVED_S_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>OKVED_85_PostSredst</t>
+          <t>OKVED_S_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>OKVED_85_SaldoDenPotOtch</t>
+          <t>OKVED_94_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>OKVED_85_PostSredst</t>
+          <t>OKVED_94_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>OKVED_Q_SaldoDenPotOtch</t>
+          <t>OKVED_94_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>OKVED_Q_PostSredst</t>
+          <t>OKVED_01_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>OKVED_88_SaldoDenPotOtch</t>
+          <t>OKVED_11_SaldoDenPotOtch</t>
         </is>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>OKVED_88_PostSredst</t>
+          <t>OKVED_11_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>OKVED_R_SaldoDenPotOtch</t>
+          <t>OKVED_32_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>OKVED_R_PostSredst</t>
+          <t>OKVED_33_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>OKVED_93_SaldoDenPotOtch</t>
+          <t>OKVED_E_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>OKVED_93_PostSredst</t>
+          <t>OKVED_36_SaldoDenPotOtch</t>
         </is>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>OKVED_S_PostSredst</t>
+          <t>OKVED_36_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>OKVED_94_PostSredst</t>
+          <t>OKVED_38_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
         <is>
-          <t>OKVED_96_SaldoDenPotOtch</t>
+          <t>OKVED_F_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>OKVED_96_PostSredst</t>
+          <t>OKVED_41_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>OKVED_43_UstKap_23</t>
+          <t>OKVED_42_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>OKVED_43_ChiAkt_23</t>
+          <t>OKVED_43_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap_23</t>
+          <t>OKVED_47_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap_24</t>
+          <t>OKVED_49_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap_23</t>
+          <t>OKVED_I_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap_24</t>
+          <t>OKVED_55_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap_23</t>
+          <t>OKVED_56_SaldoDenPotOtch</t>
         </is>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap_24</t>
+          <t>OKVED_56_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>OKVED_69_ChiAkt_23</t>
+          <t>OKVED_J_SaldoDenPotOtch</t>
         </is>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap_23</t>
+          <t>OKVED_J_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap_24</t>
+          <t>OKVED_63_SaldoDenPotOtch</t>
         </is>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap_23</t>
+          <t>OKVED_63_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap_24</t>
+          <t>OKVED_L_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_23</t>
+          <t>OKVED_68_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_24</t>
+          <t>OKVED_M_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_23</t>
+          <t>OKVED_69_SaldoDenPotOtch</t>
         </is>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_24</t>
+          <t>OKVED_69_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap_23</t>
+          <t>OKVED_70_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap_24</t>
+          <t>OKVED_71_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap_23</t>
+          <t>OKVED_74_SaldoDenPotOtch</t>
         </is>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap_24</t>
+          <t>OKVED_74_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>OKVED_R_UstKap_24</t>
+          <t>OKVED_N_PostSredst</t>
         </is>
       </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
+        <is>
+          <t>OKVED_77_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>OKVED_77_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>OKVED_79_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>OKVED_81_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>OKVED_81_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>OKVED_82_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>OKVED_82_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>OKVED_O_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>OKVED_O_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>OKVED_84_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>OKVED_84_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>OKVED_85_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>OKVED_85_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>OKVED_85_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>OKVED_85_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>OKVED_Q_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>OKVED_Q_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>OKVED_88_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>OKVED_88_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>OKVED_R_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>OKVED_R_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>OKVED_93_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>OKVED_93_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>OKVED_S_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>OKVED_94_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>OKVED_96_SaldoDenPotOtch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>OKVED_96_PostSredst</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>OKVED_43_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>OKVED_43_ChiAkt_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>OKVED_J_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>OKVED_J_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>OKVED_63_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>OKVED_63_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>OKVED_69_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>OKVED_69_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>OKVED_69_ChiAkt_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>OKVED_O_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>OKVED_O_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>OKVED_84_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>OKVED_84_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>OKVED_Q_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>OKVED_Q_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>OKVED_88_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>OKVED_88_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>OKVED_R_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
         <is>
           <t>OKVED_93_UstKap_24</t>
         </is>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1694"/>
+  <dimension ref="A1:A1714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8581,3694 +8581,3834 @@
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>OKVED_32_ArendPlDeVsego</t>
+          <t>OKVED_B_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>OKVED_32_PrPostDeyt</t>
+          <t>OKVED_07_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPostDeyt</t>
+          <t>OKVED_11_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>OKVED_E_ArendPlDeVsego</t>
+          <t>OKVED_32_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>OKVED_E_PrPostDeyt</t>
+          <t>OKVED_32_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>OKVED_36_ArendPlDeVsego</t>
+          <t>OKVED_33_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>OKVED_36_PrPostDeyt</t>
+          <t>OKVED_35_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>OKVED_38_ArendPlDeVsego</t>
+          <t>OKVED_35_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>OKVED_38_PrPostDeyt</t>
+          <t>OKVED_E_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>OKVED_41_ArendPlDeVsego</t>
+          <t>OKVED_36_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>OKVED_43_ArendPlDeVsego</t>
+          <t>OKVED_38_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>OKVED_49_ArendPlDeVsego</t>
+          <t>OKVED_41_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPostDeyt</t>
+          <t>OKVED_43_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>OKVED_50_ArendPlDeVsego</t>
+          <t>OKVED_43_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>OKVED_50_PrPostDeyt</t>
+          <t>OKVED_G_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>OKVED_I_ArendPlDeVsego</t>
+          <t>OKVED_46_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>OKVED_55_ArendPlDeVsego</t>
+          <t>OKVED_47_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>OKVED_56_ArendPlDeVsego</t>
+          <t>OKVED_H_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>OKVED_56_PrPostDeyt</t>
+          <t>OKVED_49_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>OKVED_J_OtProdDeVsego</t>
+          <t>OKVED_49_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>OKVED_J_ArendPlDeVsego</t>
+          <t>OKVED_50_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>OKVED_J_PrPostDeyt</t>
+          <t>OKVED_50_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>OKVED_63_OtProdDeVsego</t>
+          <t>OKVED_51_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>OKVED_63_ArendPlDeVsego</t>
+          <t>OKVED_52_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>OKVED_63_PrPostDeyt</t>
+          <t>OKVED_I_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>OKVED_K_ArendPlDeVsego</t>
+          <t>OKVED_55_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>OKVED_64_ArendPlDeVsego</t>
+          <t>OKVED_56_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>OKVED_69_ArendPlDeVsego</t>
+          <t>OKVED_56_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>OKVED_69_PrPostDeyt</t>
+          <t>OKVED_J_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>OKVED_71_PrPostDeyt</t>
+          <t>OKVED_J_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>OKVED_74_PrPostDeyt</t>
+          <t>OKVED_J_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>OKVED_79_ArendPlDeVsego</t>
+          <t>OKVED_63_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>OKVED_79_PrPostDeyt</t>
+          <t>OKVED_63_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>OKVED_81_ArendPlDeVsego</t>
+          <t>OKVED_63_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t>OKVED_81_PrPostDeyt</t>
+          <t>OKVED_K_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t>OKVED_82_ArendPlDeVsego</t>
+          <t>OKVED_K_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t>OKVED_82_PrPostDeyt</t>
+          <t>OKVED_64_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>OKVED_O_ArendPlDeVsego</t>
+          <t>OKVED_64_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t>OKVED_O_PrPostDeyt</t>
+          <t>OKVED_M_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>OKVED_84_ArendPlDeVsego</t>
+          <t>OKVED_69_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>OKVED_84_PrPostDeyt</t>
+          <t>OKVED_69_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_70_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPostDeyt</t>
+          <t>OKVED_71_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_74_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPostDeyt</t>
+          <t>OKVED_77_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>OKVED_Q_OtProdDeVsego</t>
+          <t>OKVED_79_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
-          <t>OKVED_Q_ArendPlDeVsego</t>
+          <t>OKVED_81_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>OKVED_Q_PrPostDeyt</t>
+          <t>OKVED_81_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>OKVED_88_OtProdDeVsego</t>
+          <t>OKVED_82_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t>OKVED_88_ArendPlDeVsego</t>
+          <t>OKVED_82_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>OKVED_88_PrPostDeyt</t>
+          <t>OKVED_O_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>OKVED_R_OtProdDeVsego</t>
+          <t>OKVED_O_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>OKVED_R_ArendPlDeVsego</t>
+          <t>OKVED_84_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>OKVED_R_PrPostDeyt</t>
+          <t>OKVED_84_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>OKVED_93_OtProdDeVsego</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>OKVED_93_ArendPlDeVsego</t>
+          <t>OKVED_85_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>OKVED_93_PrPostDeyt</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="inlineStr">
         <is>
-          <t>OKVED_S_ArendPlDeVsego</t>
+          <t>OKVED_85_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
         <is>
-          <t>OKVED_S_PrPostDeyt</t>
+          <t>OKVED_Q_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>OKVED_94_ArendPlDeVsego</t>
+          <t>OKVED_Q_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="inlineStr">
         <is>
-          <t>OKVED_94_PrPostDeyt</t>
+          <t>OKVED_Q_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>OKVED_96_ArendPlDeVsego</t>
+          <t>OKVED_88_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>OKVED_96_PrPostDeyt</t>
+          <t>OKVED_88_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPoFin</t>
+          <t>OKVED_88_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>OKVED_32_PrPoFin</t>
+          <t>OKVED_R_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_R_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>OKVED_36_PrPoFin</t>
+          <t>OKVED_R_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>OKVED_56_PrPoFin</t>
+          <t>OKVED_93_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>OKVED_J_PrPoFin</t>
+          <t>OKVED_93_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>OKVED_63_PrPoFin</t>
+          <t>OKVED_93_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>OKVED_69_PrPoFin</t>
+          <t>OKVED_S_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPoFin</t>
+          <t>OKVED_94_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>OKVED_74_PrPoFin</t>
+          <t>OKVED_96_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>OKVED_77_PrPoFin</t>
+          <t>OKVED_96_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>OKVED_81_PrPoFin</t>
+          <t>OKVED_11_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>OKVED_82_PrPoFin</t>
+          <t>OKVED_11_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>OKVED_O_PrPoFin</t>
+          <t>OKVED_32_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>OKVED_84_PrPoFin</t>
+          <t>OKVED_32_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPoFin</t>
+          <t>OKVED_32_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPoFin</t>
+          <t>OKVED_33_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>OKVED_Q_PrPoFin</t>
+          <t>OKVED_33_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>OKVED_86_PostPoTekDeyt</t>
+          <t>OKVED_36_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>OKVED_86_PrPoFin</t>
+          <t>OKVED_36_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>OKVED_R_PrPoFin</t>
+          <t>OKVED_38_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>OKVED_93_PrPoFin</t>
+          <t>OKVED_43_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>OKVED_S_PrPoFin</t>
+          <t>OKVED_49_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>OKVED_94_PrPoFin</t>
+          <t>OKVED_49_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="inlineStr">
         <is>
-          <t>OKVED_96_PrPoFin</t>
+          <t>OKVED_50_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdAkcOrgDolUch</t>
+          <t>OKVED_I_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdFinVlozh</t>
+          <t>OKVED_55_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>OKVED_01_ProdAkcOrgDolUch</t>
+          <t>OKVED_56_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>OKVED_01_PrPostDeyt</t>
+          <t>OKVED_56_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>OKVED_B_OtProdFinVlozh</t>
+          <t>OKVED_56_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
         <is>
-          <t>OKVED_07_OtProdFinVlozh</t>
+          <t>OKVED_J_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>OKVED_C_OtProdFinVlozh</t>
+          <t>OKVED_J_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>OKVED_10_OtProdFinVlozh</t>
+          <t>OKVED_J_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdAkcOrgDolUch</t>
+          <t>OKVED_63_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdFinVlozh</t>
+          <t>OKVED_63_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>OKVED_11_ProdAkcOrgDolUch</t>
+          <t>OKVED_63_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>OKVED_33_OtProdAkcOrgDolUch</t>
+          <t>OKVED_K_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>OKVED_33_OtProdFinVlozh</t>
+          <t>OKVED_64_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPostDeyt</t>
+          <t>OKVED_M_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdFinVlozh</t>
+          <t>OKVED_69_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdFinVlozh</t>
+          <t>OKVED_69_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdFinVlozh</t>
+          <t>OKVED_69_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>OKVED_E_ProdAkcOrgDolUch</t>
+          <t>OKVED_70_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>OKVED_E_PrPostDeyt</t>
+          <t>OKVED_70_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdFinVlozh</t>
+          <t>OKVED_71_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>OKVED_36_ProdAkcOrgDolUch</t>
+          <t>OKVED_71_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>OKVED_36_PrPostDeyt</t>
+          <t>OKVED_74_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdAkcOrgDolUch</t>
+          <t>OKVED_77_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdFinVlozh</t>
+          <t>OKVED_77_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>OKVED_38_ProdAkcOrgDolUch</t>
+          <t>OKVED_79_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>OKVED_38_PrPostDeyt</t>
+          <t>OKVED_79_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdAkcOrgDolUch</t>
+          <t>OKVED_81_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdFinVlozh</t>
+          <t>OKVED_82_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdAkcOrgDolUch</t>
+          <t>OKVED_82_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdFinVlozh</t>
+          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>OKVED_42_OtProdAkcOrgDolUch</t>
+          <t>OKVED_O_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>OKVED_42_OtProdFinVlozh</t>
+          <t>OKVED_O_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdAkcOrgDolUch</t>
+          <t>OKVED_O_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdFinVlozh</t>
+          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>OKVED_43_ProdAkcOrgDolUch</t>
+          <t>OKVED_84_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>OKVED_G_OtProdFinVlozh</t>
+          <t>OKVED_84_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>OKVED_46_OtProdFinVlozh</t>
+          <t>OKVED_84_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>OKVED_47_OtProdFinVlozh</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>OKVED_H_OtProdFinVlozh</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdAkcOrgDolUch</t>
+          <t>OKVED_85_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdFinVlozh</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPostDeyt</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>OKVED_51_OtProdAkcOrgDolUch</t>
+          <t>OKVED_85_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>OKVED_51_OtProdFinVlozh</t>
+          <t>OKVED_Q_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>OKVED_51_ProdAkcOrgDolUch</t>
+          <t>OKVED_Q_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>OKVED_52_OtProdFinVlozh</t>
+          <t>OKVED_Q_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdAkcOrgDolUch</t>
+          <t>OKVED_86_PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdFinVlozh</t>
+          <t>OKVED_86_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdAkcOrgDolUch</t>
+          <t>OKVED_86_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdFinVlozh</t>
+          <t>OKVED_86_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdAkcOrgDolUch</t>
+          <t>OKVED_86_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdFinVlozh</t>
+          <t>OKVED_86_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdAkcOrgDolUch</t>
+          <t>OKVED_86_SaldoDenPotTekOper</t>
         </is>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdFinVlozh</t>
+          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>OKVED_L_OtProdFinVlozh</t>
+          <t>OKVED_R_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>OKVED_68_OtProdFinVlozh</t>
+          <t>OKVED_R_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdAkcOrgDolUch</t>
+          <t>OKVED_R_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdFinVlozh</t>
+          <t>OKVED_R_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdFinVlozh</t>
+          <t>OKVED_93_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdFinVlozh</t>
+          <t>OKVED_93_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>OKVED_71_PrPostDeyt</t>
+          <t>OKVED_93_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdFinVlozh</t>
+          <t>OKVED_96_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>OKVED_N_ProdAkcOrgDolUch</t>
+          <t>OKVED_96_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdFinVlozh</t>
+          <t>OKVED_96_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>OKVED_77_ProdAkcOrgDolUch</t>
+          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>OKVED_79_OtProdFinVlozh</t>
+          <t>OKVED_01_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>OKVED_79_ProdAkcOrgDolUch</t>
+          <t>OKVED_01_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>OKVED_79_PrPostDeyt</t>
+          <t>OKVED_01_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdAkcOrgDolUch</t>
+          <t>OKVED_B_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdFinVlozh</t>
+          <t>OKVED_B_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>OKVED_S_PrPostDeyt</t>
+          <t>OKVED_07_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdAkcOrgDolUch</t>
+          <t>OKVED_07_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdFinVlozh</t>
+          <t>OKVED_C_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>OKVED_94_PrPostDeyt</t>
+          <t>OKVED_10_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoInvDeyt</t>
+          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_11_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>OKVED_01_ProdAkcOrgDolUch</t>
+          <t>OKVED_11_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>OKVED_B_PlPoInvDeyt</t>
+          <t>OKVED_11_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>OKVED_B_PrCenBum</t>
+          <t>OKVED_33_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>OKVED_B_Saldo</t>
+          <t>OKVED_33_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>OKVED_07_PlPoInvDeyt</t>
+          <t>OKVED_33_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>OKVED_07_PrCenBum</t>
+          <t>OKVED_33_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>OKVED_07_Saldo</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>OKVED_C_PrCenBum</t>
+          <t>OKVED_35_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>OKVED_C_Saldo</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>OKVED_10_PrCenBum</t>
+          <t>OKVED_35_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>OKVED_10_Saldo</t>
+          <t>OKVED_E_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>OKVED_11_PlPoInvDeyt</t>
+          <t>OKVED_E_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>OKVED_11_PrCenBum</t>
+          <t>OKVED_E_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>OKVED_11_ProdAkcOrgDolUch</t>
+          <t>OKVED_36_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPoFin</t>
+          <t>OKVED_36_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>OKVED_11_Saldo</t>
+          <t>OKVED_36_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoInvDeyt</t>
+          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>OKVED_33_PrCenBum</t>
+          <t>OKVED_38_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_38_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>OKVED_33_Saldo</t>
+          <t>OKVED_38_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoInvDeyt</t>
+          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoInvDeyt</t>
+          <t>OKVED_F_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>OKVED_E_PrCenBum</t>
+          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>OKVED_E_ProdAkcOrgDolUch</t>
+          <t>OKVED_41_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>OKVED_E_Saldo</t>
+          <t>OKVED_42_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>OKVED_36_PrCenBum</t>
+          <t>OKVED_42_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>OKVED_36_ProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>OKVED_36_PrPoFin</t>
+          <t>OKVED_43_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>OKVED_36_Saldo</t>
+          <t>OKVED_43_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>OKVED_38_PrCenBum</t>
+          <t>OKVED_43_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>OKVED_38_ProdAkcOrgDolUch</t>
+          <t>OKVED_G_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>OKVED_38_Saldo</t>
+          <t>OKVED_G_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>OKVED_F_PrCenBum</t>
+          <t>OKVED_46_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>OKVED_F_Saldo</t>
+          <t>OKVED_46_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>OKVED_41_PrCenBum</t>
+          <t>OKVED_47_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>OKVED_41_Saldo</t>
+          <t>OKVED_47_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>OKVED_42_PrCenBum</t>
+          <t>OKVED_H_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>OKVED_42_Saldo</t>
+          <t>OKVED_H_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoInvDeyt</t>
+          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>OKVED_43_PrCenBum</t>
+          <t>OKVED_49_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>OKVED_43_ProdAkcOrgDolUch</t>
+          <t>OKVED_49_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>OKVED_43_Saldo</t>
+          <t>OKVED_49_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>OKVED_G_PlPoInvDeyt</t>
+          <t>OKVED_51_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>OKVED_46_PlPoInvDeyt</t>
+          <t>OKVED_51_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>OKVED_46_Saldo</t>
+          <t>OKVED_51_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>OKVED_47_PlPoInvDeyt</t>
+          <t>OKVED_52_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>OKVED_47_PrCenBum</t>
+          <t>OKVED_52_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>OKVED_H_PlPoInvDeyt</t>
+          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>OKVED_H_PrCenBum</t>
+          <t>OKVED_I_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>OKVED_H_Saldo</t>
+          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoInvDeyt</t>
+          <t>OKVED_55_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>OKVED_49_PrCenBum</t>
+          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>OKVED_49_Saldo</t>
+          <t>OKVED_K_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoInvDeyt</t>
+          <t>OKVED_K_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>OKVED_50_PrCenBum</t>
+          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>OKVED_50_ProdAkcOrgDolUch</t>
+          <t>OKVED_64_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>OKVED_50_Saldo</t>
+          <t>OKVED_64_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>OKVED_51_PlPoInvDeyt</t>
+          <t>OKVED_L_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>OKVED_51_PrCenBum</t>
+          <t>OKVED_68_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>OKVED_51_ProdAkcOrgDolUch</t>
+          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>OKVED_51_Saldo</t>
+          <t>OKVED_M_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>OKVED_52_PlPoInvDeyt</t>
+          <t>OKVED_M_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>OKVED_52_PrCenBum</t>
+          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>OKVED_52_Saldo</t>
+          <t>OKVED_70_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>OKVED_I_Saldo</t>
+          <t>OKVED_70_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>OKVED_55_Saldo</t>
+          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoInvDeyt</t>
+          <t>OKVED_71_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>OKVED_K_PrCenBum</t>
+          <t>OKVED_71_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>OKVED_K_Saldo</t>
+          <t>OKVED_71_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoInvDeyt</t>
+          <t>OKVED_N_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>OKVED_64_PrCenBum</t>
+          <t>OKVED_N_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>OKVED_64_Saldo</t>
+          <t>OKVED_77_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>OKVED_M_PlPoInvDeyt</t>
+          <t>OKVED_77_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>OKVED_M_PrCenBum</t>
+          <t>OKVED_77_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoInvDeyt</t>
+          <t>OKVED_79_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>OKVED_70_PrCenBum</t>
+          <t>OKVED_79_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPoFin</t>
+          <t>OKVED_79_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>OKVED_70_Saldo</t>
+          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>OKVED_71_PlPoInvDeyt</t>
+          <t>OKVED_S_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>OKVED_71_PrCenBum</t>
+          <t>OKVED_S_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>OKVED_N_PrCenBum</t>
+          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>OKVED_N_ProdAkcOrgDolUch</t>
+          <t>OKVED_94_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>OKVED_77_PlPoInvDeyt</t>
+          <t>OKVED_94_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>OKVED_77_PrCenBum</t>
+          <t>OKVED_01_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>OKVED_77_ProdAkcOrgDolUch</t>
+          <t>OKVED_01_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>OKVED_77_PrPoFin</t>
+          <t>OKVED_B_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>OKVED_77_Saldo</t>
+          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>OKVED_79_PrCenBum</t>
+          <t>OKVED_07_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>OKVED_79_ProdAkcOrgDolUch</t>
+          <t>OKVED_07_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>OKVED_S_DolUch</t>
+          <t>OKVED_C_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>OKVED_S_PrCenBum</t>
+          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>OKVED_S_PrPoFin</t>
+          <t>OKVED_10_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>OKVED_S_Saldo</t>
+          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>OKVED_94_DolUch</t>
+          <t>OKVED_11_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>OKVED_94_PrCenBum</t>
+          <t>OKVED_11_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>OKVED_94_PrPoFin</t>
+          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>OKVED_94_Saldo</t>
+          <t>OKVED_11_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoInvDeyt</t>
+          <t>OKVED_33_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>OKVED_01_ProdAkcOrgDolUch</t>
+          <t>OKVED_33_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>OKVED_B_PlPoInvDeyt</t>
+          <t>OKVED_E_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>OKVED_B_PrCenBum</t>
+          <t>OKVED_E_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>OKVED_B_Saldo</t>
+          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>OKVED_07_PlPoInvDeyt</t>
+          <t>OKVED_36_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>OKVED_07_PrCenBum</t>
+          <t>OKVED_36_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>OKVED_07_Saldo</t>
+          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>OKVED_C_PrCenBum</t>
+          <t>OKVED_36_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>OKVED_C_Saldo</t>
+          <t>OKVED_38_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>OKVED_10_PrCenBum</t>
+          <t>OKVED_38_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>OKVED_10_Saldo</t>
+          <t>OKVED_38_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoInvDeyt</t>
+          <t>OKVED_F_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>OKVED_32_DolUch</t>
+          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>OKVED_32_PrCenBum</t>
+          <t>OKVED_41_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>OKVED_32_ProdAkcOrgDolUch</t>
+          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>OKVED_32_PrPoFin</t>
+          <t>OKVED_42_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>OKVED_32_Saldo</t>
+          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoInvDeyt</t>
+          <t>OKVED_43_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>OKVED_33_PrCenBum</t>
+          <t>OKVED_43_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>OKVED_33_Saldo</t>
+          <t>OKVED_43_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoInvDeyt</t>
+          <t>OKVED_46_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoInvDeyt</t>
+          <t>OKVED_47_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>OKVED_E_PostFin</t>
+          <t>OKVED_H_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>OKVED_E_DrPost</t>
+          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>OKVED_38_PostFin</t>
+          <t>OKVED_49_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>OKVED_38_DrPost</t>
+          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>OKVED_F_PostFin</t>
+          <t>OKVED_49_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>OKVED_F_DrPost</t>
+          <t>OKVED_50_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>OKVED_41_PostFin</t>
+          <t>OKVED_50_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt2</t>
+          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>OKVED_41_DrPost</t>
+          <t>OKVED_50_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>OKVED_42_PostFin</t>
+          <t>OKVED_51_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt2</t>
+          <t>OKVED_51_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>OKVED_42_DrPost</t>
+          <t>OKVED_51_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>OKVED_43_PostFin</t>
+          <t>OKVED_52_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>OKVED_43_DrPost</t>
+          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>OKVED_G_PostFin</t>
+          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt2</t>
+          <t>OKVED_I_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>OKVED_G_DrPost</t>
+          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>OKVED_46_PostFin</t>
+          <t>OKVED_55_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt2</t>
+          <t>OKVED_K_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>OKVED_46_DrPost</t>
+          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>OKVED_47_PostFin</t>
+          <t>OKVED_K_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt2</t>
+          <t>OKVED_64_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>OKVED_47_DrPost</t>
+          <t>OKVED_64_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>OKVED_H_PostFin</t>
+          <t>OKVED_64_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>OKVED_H_DrPost</t>
+          <t>OKVED_M_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>OKVED_49_PostFin</t>
+          <t>OKVED_70_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>OKVED_49_PostDeyt2</t>
+          <t>OKVED_70_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>OKVED_49_DrPost</t>
+          <t>OKVED_70_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>OKVED_50_PostFin</t>
+          <t>OKVED_71_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt2</t>
+          <t>OKVED_N_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>OKVED_50_DrPost</t>
+          <t>OKVED_N_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>OKVED_51_PostFin</t>
+          <t>OKVED_77_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt2</t>
+          <t>OKVED_77_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>OKVED_51_DrPost</t>
+          <t>OKVED_77_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>OKVED_52_PostFin</t>
+          <t>OKVED_77_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>OKVED_52_DrPost</t>
+          <t>OKVED_79_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>OKVED_I_DrPost</t>
+          <t>OKVED_79_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>OKVED_55_DrPost</t>
+          <t>OKVED_79_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>OKVED_K_PostFin</t>
+          <t>OKVED_S_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt2</t>
+          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>OKVED_K_DrPost</t>
+          <t>OKVED_94_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>OKVED_64_PostFin</t>
+          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt2</t>
+          <t>OKVED_01_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>OKVED_64_DrPost</t>
+          <t>OKVED_01_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>OKVED_L_DrPost</t>
+          <t>OKVED_B_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>OKVED_68_DrPost</t>
+          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>OKVED_M_PostDeyt2</t>
+          <t>OKVED_07_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>OKVED_70_PostDeyt1</t>
+          <t>OKVED_07_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>OKVED_70_PostDeyt2</t>
+          <t>OKVED_C_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>OKVED_71_PostFin</t>
+          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>OKVED_71_PostDeyt2</t>
+          <t>OKVED_10_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>OKVED_74_PostFin</t>
+          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>OKVED_74_PlCredit</t>
+          <t>OKVED_32_PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt2</t>
+          <t>OKVED_32_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>OKVED_74_DrPost</t>
+          <t>OKVED_32_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt2</t>
+          <t>OKVED_32_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>OKVED_N_DrPost</t>
+          <t>OKVED_32_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>OKVED_79_PostFin</t>
+          <t>OKVED_32_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt2</t>
+          <t>OKVED_33_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>OKVED_79_DrPost</t>
+          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>OKVED_81_PostFin</t>
+          <t>OKVED_33_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>OKVED_81_PlCredit</t>
+          <t>OKVED_E_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt1</t>
+          <t>OKVED_E_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt2</t>
+          <t>OKVED_38_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>OKVED_81_DrPost</t>
+          <t>OKVED_38_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>OKVED_S_PostDeyt1</t>
+          <t>OKVED_F_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>OKVED_S_DrPost</t>
+          <t>OKVED_41_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>OKVED_94_PostDeyt1</t>
+          <t>OKVED_41_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>OKVED_94_DrPost</t>
+          <t>OKVED_42_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin</t>
+          <t>OKVED_42_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin2</t>
+          <t>OKVED_42_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin3</t>
+          <t>OKVED_43_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>OKVED_B_PlPoFin2</t>
+          <t>OKVED_43_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>OKVED_07_PlPoFin2</t>
+          <t>OKVED_G_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin1</t>
+          <t>OKVED_G_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin2</t>
+          <t>OKVED_46_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin3</t>
+          <t>OKVED_46_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>OKVED_32_PrPoFin</t>
+          <t>OKVED_47_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>OKVED_32_SaldoDenPot</t>
+          <t>OKVED_47_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin</t>
+          <t>OKVED_H_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin1</t>
+          <t>OKVED_49_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin2</t>
+          <t>OKVED_49_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin3</t>
+          <t>OKVED_50_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_50_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>OKVED_33_SaldoDenPot</t>
+          <t>OKVED_50_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin2</t>
+          <t>OKVED_51_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin2</t>
+          <t>OKVED_51_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin</t>
+          <t>OKVED_51_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin2</t>
+          <t>OKVED_52_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin3</t>
+          <t>OKVED_I_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin</t>
+          <t>OKVED_I_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin2</t>
+          <t>OKVED_55_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin3</t>
+          <t>OKVED_55_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>OKVED_F_PlPoFin2</t>
+          <t>OKVED_K_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>OKVED_41_PlPoFin2</t>
+          <t>OKVED_K_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>OKVED_42_PlPoFin</t>
+          <t>OKVED_K_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>OKVED_42_PlPoFin2</t>
+          <t>OKVED_64_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin</t>
+          <t>OKVED_64_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin2</t>
+          <t>OKVED_64_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin3</t>
+          <t>OKVED_L_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>OKVED_43_SaldoDenPot</t>
+          <t>OKVED_68_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>OKVED_G_PlPoFin2</t>
+          <t>OKVED_M_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>OKVED_46_PlPoFin2</t>
+          <t>OKVED_70_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>OKVED_47_PlPoFin2</t>
+          <t>OKVED_70_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>OKVED_H_PlPoFin2</t>
+          <t>OKVED_71_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin2</t>
+          <t>OKVED_74_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin3</t>
+          <t>OKVED_74_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>OKVED_49_SaldoDenPot</t>
+          <t>OKVED_74_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoFin</t>
+          <t>OKVED_N_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoFin2</t>
+          <t>OKVED_N_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>OKVED_50_SaldoDenPot</t>
+          <t>OKVED_79_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>OKVED_51_PlPoFin</t>
+          <t>OKVED_79_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>OKVED_51_PlPoFin2</t>
+          <t>OKVED_79_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>OKVED_51_PlPoFin3</t>
+          <t>OKVED_81_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>OKVED_52_PlPoFin2</t>
+          <t>OKVED_81_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin</t>
+          <t>OKVED_81_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin2</t>
+          <t>OKVED_S_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin3</t>
+          <t>OKVED_S_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>OKVED_I_SaldoDenPot</t>
+          <t>OKVED_94_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin</t>
+          <t>OKVED_94_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin2</t>
+          <t>OKVED_01_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin3</t>
+          <t>OKVED_01_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>OKVED_55_SaldoDenPot</t>
+          <t>OKVED_B_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoFin</t>
+          <t>OKVED_07_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoFin2</t>
+          <t>OKVED_32_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>OKVED_K_SaldoDenPot</t>
+          <t>OKVED_32_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoFin</t>
+          <t>OKVED_32_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoFin2</t>
+          <t>OKVED_32_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>OKVED_64_SaldoDenPot</t>
+          <t>OKVED_32_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>OKVED_L_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>OKVED_68_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>OKVED_M_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin2</t>
+          <t>OKVED_33_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin3</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPoFin</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>OKVED_70_SaldoDenPot</t>
+          <t>OKVED_E_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>OKVED_71_PlPoFin2</t>
+          <t>OKVED_E_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin</t>
+          <t>OKVED_38_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin2</t>
+          <t>OKVED_38_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin3</t>
+          <t>OKVED_F_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>OKVED_74_PrPoFin</t>
+          <t>OKVED_41_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>OKVED_N_PlPoFin2</t>
+          <t>OKVED_42_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>OKVED_N_PlPoFin3</t>
+          <t>OKVED_43_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin</t>
+          <t>OKVED_43_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin2</t>
+          <t>OKVED_43_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin3</t>
+          <t>OKVED_G_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>OKVED_79_SaldoDenPot</t>
+          <t>OKVED_46_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin2</t>
+          <t>OKVED_47_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin3</t>
+          <t>OKVED_H_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>OKVED_81_PrPoFin</t>
+          <t>OKVED_49_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin2</t>
+          <t>OKVED_49_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin3</t>
+          <t>OKVED_49_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>OKVED_S_PrPoFin</t>
+          <t>OKVED_50_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin2</t>
+          <t>OKVED_50_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin3</t>
+          <t>OKVED_51_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>OKVED_94_PrPoFin</t>
+          <t>OKVED_51_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>OKVED_01_PostSredst</t>
+          <t>OKVED_52_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>OKVED_11_SaldoDenPotOtch</t>
+          <t>OKVED_I_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>OKVED_11_PostSredst</t>
+          <t>OKVED_I_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>OKVED_32_PostSredst</t>
+          <t>OKVED_I_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>OKVED_33_PostSredst</t>
+          <t>OKVED_55_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>OKVED_E_PostSredst</t>
+          <t>OKVED_55_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>OKVED_36_SaldoDenPotOtch</t>
+          <t>OKVED_55_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>OKVED_36_PostSredst</t>
+          <t>OKVED_K_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>OKVED_38_PostSredst</t>
+          <t>OKVED_K_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
         <is>
-          <t>OKVED_F_PostSredst</t>
+          <t>OKVED_64_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>OKVED_41_PostSredst</t>
+          <t>OKVED_64_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>OKVED_42_PostSredst</t>
+          <t>OKVED_L_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>OKVED_43_PostSredst</t>
+          <t>OKVED_68_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>OKVED_47_PostSredst</t>
+          <t>OKVED_M_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>OKVED_49_PostSredst</t>
+          <t>OKVED_70_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>OKVED_I_PostSredst</t>
+          <t>OKVED_70_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>OKVED_55_PostSredst</t>
+          <t>OKVED_70_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>OKVED_56_SaldoDenPotOtch</t>
+          <t>OKVED_70_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>OKVED_56_PostSredst</t>
+          <t>OKVED_70_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>OKVED_J_SaldoDenPotOtch</t>
+          <t>OKVED_71_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>OKVED_J_PostSredst</t>
+          <t>OKVED_74_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>OKVED_63_SaldoDenPotOtch</t>
+          <t>OKVED_74_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>OKVED_63_PostSredst</t>
+          <t>OKVED_74_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
         <is>
-          <t>OKVED_L_PostSredst</t>
+          <t>OKVED_74_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>OKVED_68_PostSredst</t>
+          <t>OKVED_N_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>OKVED_M_PostSredst</t>
+          <t>OKVED_N_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>OKVED_69_SaldoDenPotOtch</t>
+          <t>OKVED_79_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>OKVED_69_PostSredst</t>
+          <t>OKVED_79_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>OKVED_70_PostSredst</t>
+          <t>OKVED_79_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>OKVED_71_PostSredst</t>
+          <t>OKVED_81_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>OKVED_74_SaldoDenPotOtch</t>
+          <t>OKVED_81_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>OKVED_74_PostSredst</t>
+          <t>OKVED_81_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>OKVED_N_PostSredst</t>
+          <t>OKVED_81_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>OKVED_77_SaldoDenPotOtch</t>
+          <t>OKVED_S_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
         <is>
-          <t>OKVED_77_PostSredst</t>
+          <t>OKVED_S_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>OKVED_79_PostSredst</t>
+          <t>OKVED_S_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>OKVED_81_SaldoDenPotOtch</t>
+          <t>OKVED_94_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>OKVED_81_PostSredst</t>
+          <t>OKVED_94_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
         <is>
-          <t>OKVED_82_SaldoDenPotOtch</t>
+          <t>OKVED_94_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
         <is>
-          <t>OKVED_82_PostSredst</t>
+          <t>OKVED_01_Velch</t>
         </is>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>OKVED_O_SaldoDenPotOtch</t>
+          <t>OKVED_11_Velch</t>
         </is>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
         <is>
-          <t>OKVED_O_PostSredst</t>
+          <t>OKVED_32_Velch</t>
         </is>
       </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
         <is>
-          <t>OKVED_84_SaldoDenPotOtch</t>
+          <t>OKVED_33_Velch</t>
         </is>
       </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
         <is>
-          <t>OKVED_84_PostSredst</t>
+          <t>OKVED_E_Velch</t>
         </is>
       </c>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
         <is>
-          <t>OKVED_85_SaldoDenPotOtch</t>
+          <t>OKVED_36_Velch</t>
         </is>
       </c>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
         <is>
-          <t>OKVED_85_PostSredst</t>
+          <t>OKVED_38_Velch</t>
         </is>
       </c>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
         <is>
-          <t>OKVED_85_SaldoDenPotOtch</t>
+          <t>OKVED_F_Velch</t>
         </is>
       </c>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
         <is>
-          <t>OKVED_85_PostSredst</t>
+          <t>OKVED_41_Velch</t>
         </is>
       </c>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
         <is>
-          <t>OKVED_Q_SaldoDenPotOtch</t>
+          <t>OKVED_42_Velch</t>
         </is>
       </c>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
         <is>
-          <t>OKVED_Q_PostSredst</t>
+          <t>OKVED_43_Velch</t>
         </is>
       </c>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
         <is>
-          <t>OKVED_88_SaldoDenPotOtch</t>
+          <t>OKVED_47_Velch</t>
         </is>
       </c>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
         <is>
-          <t>OKVED_88_PostSredst</t>
+          <t>OKVED_49_Velch</t>
         </is>
       </c>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
         <is>
-          <t>OKVED_R_SaldoDenPotOtch</t>
+          <t>OKVED_I_Velch</t>
         </is>
       </c>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
         <is>
-          <t>OKVED_R_PostSredst</t>
+          <t>OKVED_55_Velch</t>
         </is>
       </c>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>OKVED_93_SaldoDenPotOtch</t>
+          <t>OKVED_56_Velch</t>
         </is>
       </c>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>OKVED_93_PostSredst</t>
+          <t>OKVED_J_Velch</t>
         </is>
       </c>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
         <is>
-          <t>OKVED_S_PostSredst</t>
+          <t>OKVED_63_Velch</t>
         </is>
       </c>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
         <is>
-          <t>OKVED_94_PostSredst</t>
+          <t>OKVED_L_Velch</t>
         </is>
       </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>OKVED_96_SaldoDenPotOtch</t>
+          <t>OKVED_68_Velch</t>
         </is>
       </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>OKVED_96_PostSredst</t>
+          <t>OKVED_M_Velch</t>
         </is>
       </c>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>OKVED_43_UstKap_23</t>
+          <t>OKVED_69_Velch</t>
         </is>
       </c>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>OKVED_43_ChiAkt_23</t>
+          <t>OKVED_70_Velch</t>
         </is>
       </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap_23</t>
+          <t>OKVED_71_Velch</t>
         </is>
       </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap_24</t>
+          <t>OKVED_74_Velch</t>
         </is>
       </c>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap_23</t>
+          <t>OKVED_N_Velch</t>
         </is>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap_24</t>
+          <t>OKVED_77_Velch</t>
         </is>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap_23</t>
+          <t>OKVED_79_Velch</t>
         </is>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap_24</t>
+          <t>OKVED_81_Velch</t>
         </is>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
         <is>
-          <t>OKVED_69_ChiAkt_23</t>
+          <t>OKVED_82_Velch</t>
         </is>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap_23</t>
+          <t>OKVED_O_Velch</t>
         </is>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap_24</t>
+          <t>OKVED_84_Velch</t>
         </is>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap_23</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap_24</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_23</t>
+          <t>OKVED_Q_Velch</t>
         </is>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_24</t>
+          <t>OKVED_88_Velch</t>
         </is>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_23</t>
+          <t>OKVED_R_Velch</t>
         </is>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_24</t>
+          <t>OKVED_93_Velch</t>
         </is>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap_23</t>
+          <t>OKVED_S_Velch</t>
         </is>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap_24</t>
+          <t>OKVED_94_Velch</t>
         </is>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap_23</t>
+          <t>OKVED_96_Velch</t>
         </is>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap_24</t>
+          <t>OKVED_43_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
-          <t>OKVED_R_UstKap_24</t>
+          <t>OKVED_43_ChiAkt_23</t>
         </is>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
+        <is>
+          <t>OKVED_J_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>OKVED_J_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>OKVED_63_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>OKVED_63_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>OKVED_69_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>OKVED_69_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>OKVED_69_ChiAkt_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>OKVED_O_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>OKVED_O_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>OKVED_84_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>OKVED_84_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>OKVED_Q_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>OKVED_Q_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>OKVED_88_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>OKVED_88_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>OKVED_R_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
         <is>
           <t>OKVED_93_UstKap_24</t>
         </is>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1714"/>
+  <dimension ref="A1:A1713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10961,574 +10961,574 @@
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoInvDeyt</t>
+          <t>OKVED_32_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>OKVED_32_DolUch</t>
+          <t>OKVED_32_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>OKVED_32_PrCenBum</t>
+          <t>OKVED_32_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>OKVED_32_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_32_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>OKVED_32_PrPoFin</t>
+          <t>OKVED_32_Saldo</t>
         </is>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>OKVED_32_Saldo</t>
+          <t>OKVED_33_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>OKVED_33_DolUch</t>
+          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_33_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_E_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>OKVED_E_PostDeyt1</t>
+          <t>OKVED_E_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>OKVED_E_DrPost</t>
+          <t>OKVED_38_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>OKVED_38_PostDeyt1</t>
+          <t>OKVED_38_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>OKVED_38_DrPost</t>
+          <t>OKVED_F_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>OKVED_F_PostDeyt1</t>
+          <t>OKVED_41_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt</t>
+          <t>OKVED_41_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt1</t>
+          <t>OKVED_42_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt</t>
+          <t>OKVED_42_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt1</t>
+          <t>OKVED_42_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>OKVED_42_DrPost</t>
+          <t>OKVED_43_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>OKVED_43_PostDeyt1</t>
+          <t>OKVED_43_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>OKVED_43_DrPost</t>
+          <t>OKVED_G_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt</t>
+          <t>OKVED_G_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt1</t>
+          <t>OKVED_46_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt</t>
+          <t>OKVED_46_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt1</t>
+          <t>OKVED_47_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt</t>
+          <t>OKVED_47_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt1</t>
+          <t>OKVED_H_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>OKVED_H_PostDeyt1</t>
+          <t>OKVED_49_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>OKVED_49_PostDeyt</t>
+          <t>OKVED_49_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>OKVED_49_PostDeyt1</t>
+          <t>OKVED_50_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt</t>
+          <t>OKVED_50_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt1</t>
+          <t>OKVED_50_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>OKVED_50_DrPost</t>
+          <t>OKVED_51_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt</t>
+          <t>OKVED_51_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt1</t>
+          <t>OKVED_51_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>OKVED_51_DrPost</t>
+          <t>OKVED_52_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>OKVED_52_PostDeyt1</t>
+          <t>OKVED_I_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>OKVED_I_PostDeyt1</t>
+          <t>OKVED_I_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>OKVED_I_DrPost</t>
+          <t>OKVED_55_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>OKVED_55_PostDeyt1</t>
+          <t>OKVED_55_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>OKVED_55_DrPost</t>
+          <t>OKVED_K_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt</t>
+          <t>OKVED_K_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt1</t>
+          <t>OKVED_K_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>OKVED_K_DrPost</t>
+          <t>OKVED_64_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt</t>
+          <t>OKVED_64_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt1</t>
+          <t>OKVED_64_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>OKVED_64_DrPost</t>
+          <t>OKVED_L_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>OKVED_L_PostDeyt1</t>
+          <t>OKVED_68_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>OKVED_68_PostDeyt1</t>
+          <t>OKVED_M_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>OKVED_M_PostDeyt</t>
+          <t>OKVED_70_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>OKVED_70_PlCredit</t>
+          <t>OKVED_70_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>OKVED_70_PostDeyt</t>
+          <t>OKVED_71_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>OKVED_71_PostDeyt</t>
+          <t>OKVED_74_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt</t>
+          <t>OKVED_74_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt1</t>
+          <t>OKVED_74_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>OKVED_74_DrPost</t>
+          <t>OKVED_N_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt</t>
+          <t>OKVED_N_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt1</t>
+          <t>OKVED_79_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt</t>
+          <t>OKVED_79_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt1</t>
+          <t>OKVED_79_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>OKVED_79_DrPost</t>
+          <t>OKVED_81_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>OKVED_81_PlCredit</t>
+          <t>OKVED_81_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt</t>
+          <t>OKVED_81_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt1</t>
+          <t>OKVED_S_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>OKVED_S_PlCredit</t>
+          <t>OKVED_S_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>OKVED_S_PostDeyt1</t>
+          <t>OKVED_94_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>OKVED_94_PlCredit</t>
+          <t>OKVED_94_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>OKVED_94_PostDeyt1</t>
+          <t>OKVED_01_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin1</t>
+          <t>OKVED_01_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin2</t>
+          <t>OKVED_B_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>OKVED_B_PlPoFin1</t>
+          <t>OKVED_07_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>OKVED_07_PlPoFin1</t>
+          <t>OKVED_32_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin</t>
+          <t>OKVED_32_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin1</t>
+          <t>OKVED_32_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin2</t>
+          <t>OKVED_32_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin3</t>
+          <t>OKVED_32_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>OKVED_32_PrPoFin</t>
+          <t>OKVED_33_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin</t>
+          <t>OKVED_33_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin3</t>
+          <t>OKVED_33_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
@@ -11542,651 +11542,651 @@
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_E_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin1</t>
+          <t>OKVED_E_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin2</t>
+          <t>OKVED_38_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin1</t>
+          <t>OKVED_38_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin2</t>
+          <t>OKVED_F_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>OKVED_F_PlPoFin1</t>
+          <t>OKVED_41_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>OKVED_41_PlPoFin1</t>
+          <t>OKVED_42_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>OKVED_42_PlPoFin1</t>
+          <t>OKVED_43_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin1</t>
+          <t>OKVED_43_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin2</t>
+          <t>OKVED_43_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPoFin</t>
+          <t>OKVED_G_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>OKVED_G_PlPoFin1</t>
+          <t>OKVED_46_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>OKVED_46_PlPoFin1</t>
+          <t>OKVED_47_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>OKVED_47_PlPoFin1</t>
+          <t>OKVED_H_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>OKVED_H_PlPoFin1</t>
+          <t>OKVED_49_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin1</t>
+          <t>OKVED_49_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin2</t>
+          <t>OKVED_49_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPoFin</t>
+          <t>OKVED_50_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoFin1</t>
+          <t>OKVED_50_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>OKVED_50_PrPoFin</t>
+          <t>OKVED_51_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>OKVED_51_PlPoFin1</t>
+          <t>OKVED_51_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>OKVED_51_PlPoFin2</t>
+          <t>OKVED_52_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>OKVED_52_PlPoFin1</t>
+          <t>OKVED_I_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin1</t>
+          <t>OKVED_I_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin2</t>
+          <t>OKVED_I_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>OKVED_I_PrPoFin</t>
+          <t>OKVED_55_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin1</t>
+          <t>OKVED_55_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin2</t>
+          <t>OKVED_55_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>OKVED_55_PrPoFin</t>
+          <t>OKVED_K_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoFin1</t>
+          <t>OKVED_K_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPoFin</t>
+          <t>OKVED_64_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoFin1</t>
+          <t>OKVED_64_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPoFin</t>
+          <t>OKVED_L_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>OKVED_L_PlPoFin1</t>
+          <t>OKVED_68_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>OKVED_68_PlPoFin1</t>
+          <t>OKVED_M_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>OKVED_M_PlPoFin1</t>
+          <t>OKVED_70_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin</t>
+          <t>OKVED_70_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin1</t>
+          <t>OKVED_70_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin2</t>
+          <t>OKVED_70_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin3</t>
+          <t>OKVED_70_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPoFin</t>
+          <t>OKVED_71_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>OKVED_71_PlPoFin1</t>
+          <t>OKVED_74_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin1</t>
+          <t>OKVED_74_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin2</t>
+          <t>OKVED_74_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin3</t>
+          <t>OKVED_74_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
         <is>
-          <t>OKVED_74_SaldoDenPot</t>
+          <t>OKVED_N_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>OKVED_N_PlPoFin1</t>
+          <t>OKVED_N_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>OKVED_N_PlPoFin2</t>
+          <t>OKVED_79_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin1</t>
+          <t>OKVED_79_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin2</t>
+          <t>OKVED_79_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>OKVED_79_PrPoFin</t>
+          <t>OKVED_81_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin1</t>
+          <t>OKVED_81_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin2</t>
+          <t>OKVED_81_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin3</t>
+          <t>OKVED_81_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>OKVED_81_SaldoDenPot</t>
+          <t>OKVED_S_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin1</t>
+          <t>OKVED_S_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin2</t>
+          <t>OKVED_S_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin3</t>
+          <t>OKVED_94_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin1</t>
+          <t>OKVED_94_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin2</t>
+          <t>OKVED_94_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin3</t>
+          <t>OKVED_01_Velch</t>
         </is>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
         <is>
-          <t>OKVED_01_Velch</t>
+          <t>OKVED_11_Velch</t>
         </is>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>OKVED_11_Velch</t>
+          <t>OKVED_32_Velch</t>
         </is>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
         <is>
-          <t>OKVED_32_Velch</t>
+          <t>OKVED_33_Velch</t>
         </is>
       </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
         <is>
-          <t>OKVED_33_Velch</t>
+          <t>OKVED_E_Velch</t>
         </is>
       </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
         <is>
-          <t>OKVED_E_Velch</t>
+          <t>OKVED_36_Velch</t>
         </is>
       </c>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
         <is>
-          <t>OKVED_36_Velch</t>
+          <t>OKVED_38_Velch</t>
         </is>
       </c>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
         <is>
-          <t>OKVED_38_Velch</t>
+          <t>OKVED_F_Velch</t>
         </is>
       </c>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
         <is>
-          <t>OKVED_F_Velch</t>
+          <t>OKVED_41_Velch</t>
         </is>
       </c>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
         <is>
-          <t>OKVED_41_Velch</t>
+          <t>OKVED_42_Velch</t>
         </is>
       </c>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
         <is>
-          <t>OKVED_42_Velch</t>
+          <t>OKVED_43_Velch</t>
         </is>
       </c>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
         <is>
-          <t>OKVED_43_Velch</t>
+          <t>OKVED_47_Velch</t>
         </is>
       </c>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
         <is>
-          <t>OKVED_47_Velch</t>
+          <t>OKVED_49_Velch</t>
         </is>
       </c>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
         <is>
-          <t>OKVED_49_Velch</t>
+          <t>OKVED_I_Velch</t>
         </is>
       </c>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
         <is>
-          <t>OKVED_I_Velch</t>
+          <t>OKVED_55_Velch</t>
         </is>
       </c>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
         <is>
-          <t>OKVED_55_Velch</t>
+          <t>OKVED_56_Velch</t>
         </is>
       </c>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>OKVED_56_Velch</t>
+          <t>OKVED_J_Velch</t>
         </is>
       </c>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>OKVED_J_Velch</t>
+          <t>OKVED_63_Velch</t>
         </is>
       </c>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
         <is>
-          <t>OKVED_63_Velch</t>
+          <t>OKVED_L_Velch</t>
         </is>
       </c>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
         <is>
-          <t>OKVED_L_Velch</t>
+          <t>OKVED_68_Velch</t>
         </is>
       </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>OKVED_68_Velch</t>
+          <t>OKVED_M_Velch</t>
         </is>
       </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>OKVED_M_Velch</t>
+          <t>OKVED_69_Velch</t>
         </is>
       </c>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>OKVED_69_Velch</t>
+          <t>OKVED_70_Velch</t>
         </is>
       </c>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>OKVED_70_Velch</t>
+          <t>OKVED_71_Velch</t>
         </is>
       </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
         <is>
-          <t>OKVED_71_Velch</t>
+          <t>OKVED_74_Velch</t>
         </is>
       </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
         <is>
-          <t>OKVED_74_Velch</t>
+          <t>OKVED_N_Velch</t>
         </is>
       </c>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>OKVED_N_Velch</t>
+          <t>OKVED_77_Velch</t>
         </is>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
         <is>
-          <t>OKVED_77_Velch</t>
+          <t>OKVED_79_Velch</t>
         </is>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
         <is>
-          <t>OKVED_79_Velch</t>
+          <t>OKVED_81_Velch</t>
         </is>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
         <is>
-          <t>OKVED_81_Velch</t>
+          <t>OKVED_82_Velch</t>
         </is>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
         <is>
-          <t>OKVED_82_Velch</t>
+          <t>OKVED_O_Velch</t>
         </is>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>OKVED_O_Velch</t>
+          <t>OKVED_84_Velch</t>
         </is>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
         <is>
-          <t>OKVED_84_Velch</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
@@ -12200,215 +12200,208 @@
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_Q_Velch</t>
         </is>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>OKVED_Q_Velch</t>
+          <t>OKVED_88_Velch</t>
         </is>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>OKVED_88_Velch</t>
+          <t>OKVED_R_Velch</t>
         </is>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>OKVED_R_Velch</t>
+          <t>OKVED_93_Velch</t>
         </is>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>OKVED_93_Velch</t>
+          <t>OKVED_S_Velch</t>
         </is>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>OKVED_S_Velch</t>
+          <t>OKVED_94_Velch</t>
         </is>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>OKVED_94_Velch</t>
+          <t>OKVED_96_Velch</t>
         </is>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>OKVED_96_Velch</t>
+          <t>OKVED_43_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>OKVED_43_UstKap_23</t>
+          <t>OKVED_43_ChiAkt_23</t>
         </is>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
-          <t>OKVED_43_ChiAkt_23</t>
+          <t>OKVED_J_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap_23</t>
+          <t>OKVED_J_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap_24</t>
+          <t>OKVED_63_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1696">
       <c r="A1696" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap_23</t>
+          <t>OKVED_63_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1697">
       <c r="A1697" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap_24</t>
+          <t>OKVED_69_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1698">
       <c r="A1698" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap_23</t>
+          <t>OKVED_69_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1699">
       <c r="A1699" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap_24</t>
+          <t>OKVED_69_ChiAkt_23</t>
         </is>
       </c>
     </row>
     <row r="1700">
       <c r="A1700" t="inlineStr">
         <is>
-          <t>OKVED_69_ChiAkt_23</t>
+          <t>OKVED_O_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1701">
       <c r="A1701" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap_23</t>
+          <t>OKVED_O_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1702">
       <c r="A1702" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap_24</t>
+          <t>OKVED_84_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1703">
       <c r="A1703" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap_23</t>
+          <t>OKVED_84_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1704">
       <c r="A1704" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap_24</t>
+          <t>OKVED_85_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1705">
       <c r="A1705" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_23</t>
+          <t>OKVED_85_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1706">
       <c r="A1706" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_24</t>
+          <t>OKVED_85_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1707">
       <c r="A1707" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_23</t>
+          <t>OKVED_85_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1708">
       <c r="A1708" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_24</t>
+          <t>OKVED_Q_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1709">
       <c r="A1709" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap_23</t>
+          <t>OKVED_Q_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1710">
       <c r="A1710" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap_24</t>
+          <t>OKVED_88_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1711">
       <c r="A1711" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap_23</t>
+          <t>OKVED_88_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1712">
       <c r="A1712" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap_24</t>
+          <t>OKVED_R_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1713">
       <c r="A1713" t="inlineStr">
-        <is>
-          <t>OKVED_R_UstKap_24</t>
-        </is>
-      </c>
-    </row>
-    <row r="1714">
-      <c r="A1714" t="inlineStr">
         <is>
           <t>OKVED_93_UstKap_24</t>
         </is>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -5620,525 +5620,525 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>OKVED_11_ZayIKre_1_23</t>
+          <t>OKVED_11_OtsOby_1_23</t>
         </is>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>OKVED_11_DohBudPer_23</t>
+          <t>OKVED_11_ProKraOby_23</t>
         </is>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>OKVED_32_ZayIKre_1_23</t>
+          <t>OKVED_11_ProKraOby_24</t>
         </is>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>OKVED_32_DohBudPer_23</t>
+          <t>OKVED_32_ProKraOby_23</t>
         </is>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>OKVED_33_ZayIKre_1_23</t>
+          <t>OKVED_32_ProKraOby_24</t>
         </is>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>OKVED_33_DohBudPer_23</t>
+          <t>OKVED_36_ProKraOby_23</t>
         </is>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>OKVED_36_ZayIKre_1_23</t>
+          <t>OKVED_36_ProKraOby_24</t>
         </is>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>OKVED_F_DohBudPer_23</t>
+          <t>OKVED_F_ProKraOby_24</t>
         </is>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>OKVED_41_DohBudPer_23</t>
+          <t>OKVED_41_ProKraOby_24</t>
         </is>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>OKVED_42_ZayIKre_1_23</t>
+          <t>OKVED_42_ProKraOby_23</t>
         </is>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>OKVED_42_DohBudPer_23</t>
+          <t>OKVED_42_ProKraOby_24</t>
         </is>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>OKVED_43_ZayIKre_1_23</t>
+          <t>OKVED_43_OtsOby_1_23</t>
         </is>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>OKVED_43_KreZad_23</t>
+          <t>OKVED_43_ProKraOby_23</t>
         </is>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>OKVED_43_DohBudPer_23</t>
+          <t>OKVED_43_ProKraOby_24</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>OKVED_G_DohBudPer_23</t>
+          <t>OKVED_I_ProKraOby_23</t>
         </is>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>OKVED_46_DohBudPer_23</t>
+          <t>OKVED_55_ProKraOby_23</t>
         </is>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>OKVED_47_DohBudPer_23</t>
+          <t>OKVED_K_ProKraOby_23</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>OKVED_49_DohBudPer_23</t>
+          <t>OKVED_K_ProKraOby_24</t>
         </is>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>OKVED_50_DohBudPer_23</t>
+          <t>OKVED_64_ProKraOby_23</t>
         </is>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>OKVED_51_DohBudPer_23</t>
+          <t>OKVED_64_ProKraOby_24</t>
         </is>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>OKVED_K_DohBudPer_23</t>
+          <t>OKVED_74_OtsOby_1_24</t>
         </is>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>OKVED_64_DohBudPer_23</t>
+          <t>OKVED_74_ProKraOby_24</t>
         </is>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>OKVED_70_ZayIKre_1_23</t>
+          <t>OKVED_77_ProKraOby_23</t>
         </is>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>OKVED_74_ZayIKre_1_23</t>
+          <t>OKVED_77_ProKraOby_24</t>
         </is>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>OKVED_74_DohBudPer_23</t>
+          <t>OKVED_79_OtsOby_1_23</t>
         </is>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>OKVED_N_DohBudPer_23</t>
+          <t>OKVED_79_OtsOby_1_24</t>
         </is>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>OKVED_77_DohBudPer_23</t>
+          <t>OKVED_79_ProKraOby_23</t>
         </is>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>OKVED_79_ZayIKre_1_23</t>
+          <t>OKVED_82_OtsOby_1_23</t>
         </is>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>OKVED_79_DohBudPer_23</t>
+          <t>OKVED_82_OtsOby_1_24</t>
         </is>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>OKVED_82_ZayIKre_1_23</t>
+          <t>OKVED_O_ProKraOby_23</t>
         </is>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>OKVED_82_DohBudPer_23</t>
+          <t>OKVED_O_ProKraOby_24</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>OKVED_O_ZayIKre_1_23</t>
+          <t>OKVED_84_ProKraOby_23</t>
         </is>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>OKVED_84_ZayIKre_1_23</t>
+          <t>OKVED_84_ProKraOby_24</t>
         </is>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>OKVED_S_ZayIKre_1_23</t>
+          <t>OKVED_S_ProKraOby_23</t>
         </is>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>OKVED_94_ZayIKre_1_23</t>
+          <t>OKVED_S_ProKraOby_24</t>
         </is>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>OKVED_43_SooZaeISobSre(noOgrMenLiRav100_23</t>
+          <t>OKVED_94_ProKraOby_23</t>
         </is>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>OKVED_43_KoeAvt(doSobSreVValBal(noOgrBolLiRav50%)_23</t>
+          <t>OKVED_94_ProKraOby_24</t>
         </is>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>OKVED_43_KoeMan(doSobOboSreKIstSobSre_23</t>
+          <t>OKVED_43_SooZaeISobSre(noOgrMenLiRav100_23</t>
         </is>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>OKVED_43_DolImuProNazVValBal_23</t>
+          <t>OKVED_43_KoeAvt(doSobSreVValBal(noOgrBolLiRav50%)_23</t>
         </is>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>OKVED_J_DolImuProNazVValBal_23</t>
+          <t>OKVED_43_KoeMan(doSobOboSreKIstSobSre_23</t>
         </is>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>OKVED_J_DolImuProNazVValBal_24</t>
+          <t>OKVED_43_DolImuProNazVValBal_23</t>
         </is>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>OKVED_63_DolImuProNazVValBal_23</t>
+          <t>OKVED_J_DolImuProNazVValBal_23</t>
         </is>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>OKVED_63_DolImuProNazVValBal_24</t>
+          <t>OKVED_J_DolImuProNazVValBal_24</t>
         </is>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>OKVED_69_SooZaeISobSre(noOgrMenLiRav100_23</t>
+          <t>OKVED_63_DolImuProNazVValBal_23</t>
         </is>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeAvt(doSobSreVValBal(noOgrBolLiRav50%)_23</t>
+          <t>OKVED_63_DolImuProNazVValBal_24</t>
         </is>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeMan(doSobOboSreKIstSobSre_23</t>
+          <t>OKVED_69_SooZaeISobSre(noOgrMenLiRav100_23</t>
         </is>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>OKVED_69_DolImuProNazVValBal_23</t>
+          <t>OKVED_69_KoeAvt(doSobSreVValBal(noOgrBolLiRav50%)_23</t>
         </is>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>OKVED_69_DolImuProNazVValBal_24</t>
+          <t>OKVED_69_KoeMan(doSobOboSreKIstSobSre_23</t>
         </is>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>OKVED_R_DolImuProNazVValBal_23</t>
+          <t>OKVED_69_DolImuProNazVValBal_23</t>
         </is>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>OKVED_R_DolImuProNazVValBal_24</t>
+          <t>OKVED_69_DolImuProNazVValBal_24</t>
         </is>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>OKVED_93_DolImuProNazVValBal_23</t>
+          <t>OKVED_R_DolImuProNazVValBal_23</t>
         </is>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>OKVED_93_DolImuProNazVValBal_24</t>
+          <t>OKVED_R_DolImuProNazVValBal_24</t>
         </is>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>OKVED_32_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_93_DolImuProNazVValBal_23</t>
         </is>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>OKVED_43_KoeObeSobOboSre_23</t>
+          <t>OKVED_93_DolImuProNazVValBal_24</t>
         </is>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>OKVED_43_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_32_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>OKVED_43_DolIstFin(isSobSreIDolObyVValBal_23</t>
+          <t>OKVED_43_KoeObeSobOboSre_23</t>
         </is>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>OKVED_43_SooSobIZaeSre_23</t>
+          <t>OKVED_43_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>OKVED_56_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_43_DolIstFin(isSobSreIDolObyVValBal_23</t>
         </is>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>OKVED_56_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_43_SooSobIZaeSre_23</t>
         </is>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>OKVED_J_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_56_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>OKVED_J_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_56_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>OKVED_63_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_J_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>OKVED_63_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_J_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeObeSobOboSre_23</t>
+          <t>OKVED_63_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>OKVED_69_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_63_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>OKVED_69_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_69_KoeObeSobOboSre_23</t>
         </is>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>OKVED_69_DolIstFin(isSobSreIDolObyVValBal_23</t>
+          <t>OKVED_69_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>OKVED_69_SooSobIZaeSre_23</t>
+          <t>OKVED_69_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>OKVED_81_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_69_DolIstFin(isSobSreIDolObyVValBal_23</t>
         </is>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>OKVED_82_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_69_SooSobIZaeSre_23</t>
         </is>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>OKVED_82_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_81_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>OKVED_O_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_82_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>OKVED_84_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_82_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>OKVED_85_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_O_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>OKVED_85_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_84_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
@@ -6159,588 +6159,588 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>OKVED_Q_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_85_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>OKVED_Q_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_85_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>OKVED_88_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_Q_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>OKVED_88_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_Q_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>OKVED_R_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_88_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>OKVED_R_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_88_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>OKVED_93_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_R_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>OKVED_93_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_R_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>OKVED_96_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_93_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>OKVED_96_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_93_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>OKVED_43_KoeAbsLik(noOgr20%)_23</t>
+          <t>OKVED_96_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>OKVED_43_KoeLik(noOgr80%)_23</t>
+          <t>OKVED_96_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>OKVED_43_KoeTekLik(po(noOgr20%)_23</t>
+          <t>OKVED_43_KoeAbsLik(noOgr20%)_23</t>
         </is>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeAbsLik(noOgr20%)_23</t>
+          <t>OKVED_43_KoeLik(noOgr80%)_23</t>
         </is>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeLik(noOgr80%)_23</t>
+          <t>OKVED_43_KoeTekLik(po(noOgr20%)_23</t>
         </is>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeTekLik(po(noOgr20%)_23</t>
+          <t>OKVED_69_KoeAbsLik(noOgr20%)_23</t>
         </is>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>MO_30510_SooZaeISobSre(noOgrMenLiRav100_1_24</t>
+          <t>OKVED_69_KoeLik(noOgr80%)_23</t>
         </is>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>MO_30501_DolDolObyKIstSobSreIDolOby_1_23</t>
+          <t>OKVED_69_KoeTekLik(po(noOgr20%)_23</t>
         </is>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>MO_30501_DolDolObyKIstSobSreIDolOby_1_24</t>
+          <t>MO_30510_SooZaeISobSre(noOgrMenLiRav100_1_24</t>
         </is>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>MO_30510_DolDolObyKIstSobSreIDolOby_1_23</t>
+          <t>MO_30501_DolDolObyKIstSobSreIDolOby_1_23</t>
         </is>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>MO_30510_DolDolObyKIstSobSreIDolOby_1_24</t>
+          <t>MO_30501_DolDolObyKIstSobSreIDolOby_1_24</t>
         </is>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>MO_30604_DolDolObyKIstSobSreIDolOby_1_23</t>
+          <t>MO_30510_DolDolObyKIstSobSreIDolOby_1_23</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>MO_30604_DolDolObyKIstSobSreIDolOby_1_24</t>
+          <t>MO_30510_DolDolObyKIstSobSreIDolOby_1_24</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>OKVED_56_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>MO_30604_DolDolObyKIstSobSreIDolOby_1_23</t>
         </is>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>OKVED_K_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>MO_30604_DolDolObyKIstSobSreIDolOby_1_24</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>OKVED_64_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_56_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>OKVED_69_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_K_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>OKVED_74_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_64_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>OKVED_81_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_69_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>OKVED_82_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_74_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>OKVED_O_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_81_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>OKVED_84_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_82_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_O_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_84_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas</t>
+          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas</t>
+          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>OKVED_11_OtcGoPro</t>
+          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>OKVED_32_OtcGoOtlNalNaPri</t>
+          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>OKVED_33_OtcGoPro</t>
+          <t>OKVED_11_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoOtlNalNaPri</t>
+          <t>OKVED_32_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoPro</t>
+          <t>OKVED_33_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>OKVED_42_OtcGoPro</t>
+          <t>OKVED_38_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>OKVED_43_OtcGoPro</t>
+          <t>OKVED_38_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>OKVED_50_OtcGoPro</t>
+          <t>OKVED_42_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>OKVED_56_OtcGoOtlNalNaPri</t>
+          <t>OKVED_43_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoOtlNalNaPri</t>
+          <t>OKVED_50_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoPro</t>
+          <t>OKVED_56_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>OKVED_74_OtcGoPro</t>
+          <t>OKVED_69_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>OKVED_77_OtcGoPro</t>
+          <t>OKVED_69_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>OKVED_79_OtcGoPro</t>
+          <t>OKVED_74_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>OKVED_82_OtcGoOtlNalNaPri</t>
+          <t>OKVED_77_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>OKVED_82_OtcGoPro</t>
+          <t>OKVED_79_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>OKVED_O_OtcGoOtlNalNaPri</t>
+          <t>OKVED_82_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>OKVED_O_OtcGoPro</t>
+          <t>OKVED_82_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>OKVED_84_OtcGoOtlNalNaPri</t>
+          <t>OKVED_O_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>OKVED_84_OtcGoPro</t>
+          <t>OKVED_O_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoPro</t>
+          <t>OKVED_84_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoPro</t>
+          <t>OKVED_84_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoSalProDohIRas</t>
+          <t>OKVED_85_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoOtlNalNaPri</t>
+          <t>OKVED_85_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoPro</t>
+          <t>OKVED_R_OtcGoSalProDohIRas</t>
         </is>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoSalProDohIRas</t>
+          <t>OKVED_R_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoOtlNalNaPri</t>
+          <t>OKVED_R_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoPro</t>
+          <t>OKVED_93_OtcGoSalProDohIRas</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>OKVED_S_OtcGoPro</t>
+          <t>OKVED_93_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>OKVED_94_OtcGoPro</t>
+          <t>OKVED_93_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>OKVED_96_OtcGoPro</t>
+          <t>OKVED_S_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>OKVED_01_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_94_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>OKVED_B_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_96_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>OKVED_B_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_01_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>OKVED_07_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_B_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>OKVED_07_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_B_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>OKVED_10_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_07_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>OKVED_11_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_07_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>OKVED_11_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_10_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>OKVED_32_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_11_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>OKVED_33_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_11_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>OKVED_33_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_32_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>OKVED_35_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_33_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>OKVED_35_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_33_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
@@ -6761,448 +6761,448 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>OKVED_E_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_35_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>OKVED_E_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_35_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>OKVED_36_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_E_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>OKVED_36_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_E_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_36_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_36_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>OKVED_F_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_38_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>OKVED_41_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_38_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>OKVED_41_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_F_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>OKVED_42_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_41_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>OKVED_43_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_41_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>OKVED_43_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_42_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>OKVED_G_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_43_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>OKVED_G_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_43_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>OKVED_46_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_G_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>OKVED_46_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_G_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>OKVED_47_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_46_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>OKVED_47_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_46_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>OKVED_50_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_47_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>OKVED_50_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_47_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>OKVED_51_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_50_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>OKVED_51_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_50_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>OKVED_52_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_51_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>OKVED_52_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_51_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>OKVED_I_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_52_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>OKVED_I_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_52_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>OKVED_55_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_I_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>OKVED_55_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_I_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>OKVED_56_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_55_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>OKVED_56_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_55_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>OKVED_K_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_56_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>OKVED_K_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_56_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>OKVED_64_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_K_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>OKVED_64_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_K_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>OKVED_L_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_64_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>OKVED_L_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_64_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>OKVED_68_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_L_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>OKVED_68_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_L_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>OKVED_M_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_68_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>OKVED_M_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_68_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_M_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_M_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>OKVED_70_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_69_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>OKVED_70_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_69_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>OKVED_71_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_70_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>OKVED_71_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_70_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>OKVED_74_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_71_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>OKVED_74_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_71_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>OKVED_N_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_74_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>OKVED_N_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_74_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>OKVED_77_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_N_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>OKVED_77_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_N_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>OKVED_79_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_77_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>OKVED_79_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_77_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>OKVED_81_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_79_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>OKVED_81_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_79_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>OKVED_82_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_81_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>OKVED_82_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_81_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>OKVED_O_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_82_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>OKVED_O_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_82_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>OKVED_84_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_O_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>OKVED_84_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_O_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_84_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_84_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
@@ -7223,1274 +7223,1274 @@
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_85_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_85_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_R_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_R_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>OKVED_S_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_93_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>OKVED_S_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_93_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>OKVED_94_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_S_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>OKVED_94_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_S_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>OKVED_96_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_94_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>OKVED_96_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_94_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerVyr_1</t>
+          <t>OKVED_96_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerKomIUprRas_1</t>
+          <t>OKVED_96_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>MO_30851_OtcGoPro_1</t>
+          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerVyr_1</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>MO_30501_OtcGoOtlNalNaPri_1</t>
+          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerKomIUprRas_1</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>MO_30501_OtcGoPro_1</t>
+          <t>MO_30851_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>MO_30510_OtcGoSalProDohIRas_1</t>
+          <t>MO_30501_OtcGoOtlNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>MO_30510_OtcGoOtlNalNaPri_1</t>
+          <t>MO_30501_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>MO_30510_OtcGoPro_1</t>
+          <t>MO_30510_OtcGoSalProDohIRas_1</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>MO_30604_OtcGoPri(ubDoNal_1</t>
+          <t>MO_30510_OtcGoOtlNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>MO_30604_OtcGoOtlNalNaPri_1</t>
+          <t>MO_30510_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>MO_30604_OtcGoPro_1</t>
+          <t>MO_30604_OtcGoPri(ubDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>MO_30832_OtcGoPro_1</t>
+          <t>MO_30604_OtcGoOtlNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-DoNal</t>
+          <t>MO_30604_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-DoNal</t>
+          <t>MO_30832_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-DoNal</t>
+          <t>OKVED_J_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-DoNal</t>
+          <t>OKVED_63_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>OKVED_01_TeRosPriV%</t>
+          <t>OKVED_Q_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>OKVED_10_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_88_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>OKVED_11_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_01_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>OKVED_11_TeRosUbyV%</t>
+          <t>OKVED_10_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>OKVED_32_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_11_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>OKVED_32_TeRosUbyV%</t>
+          <t>OKVED_11_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>OKVED_38_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_32_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>OKVED_F_TeRosPriV%</t>
+          <t>OKVED_32_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>OKVED_41_TeRosPriV%</t>
+          <t>OKVED_38_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>OKVED_41_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_F_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>OKVED_42_TeRosPriV%</t>
+          <t>OKVED_41_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>OKVED_42_TeRosSumPriV%</t>
+          <t>OKVED_41_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>OKVED_43_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_42_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>OKVED_43_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_42_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>OKVED_43_SumPriZaSooPerPreGo</t>
+          <t>OKVED_43_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>OKVED_43_TeRosUbyV%</t>
+          <t>OKVED_43_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>OKVED_49_TeRosUbyV%</t>
+          <t>OKVED_43_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>OKVED_50_TeRosPriV%</t>
+          <t>OKVED_43_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>OKVED_50_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_49_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>OKVED_50_TeRosSumPriV%</t>
+          <t>OKVED_50_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>OKVED_51_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_50_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>OKVED_51_TeRosUbyV%</t>
+          <t>OKVED_50_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>OKVED_I_TeRosPriV%</t>
+          <t>OKVED_51_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>OKVED_55_TeRosPriV%</t>
+          <t>OKVED_51_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>OKVED_55_SumPriZaSooPerPreGo</t>
+          <t>OKVED_I_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>OKVED_56_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_55_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>OKVED_56_TeRosUbyV%</t>
+          <t>OKVED_55_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>OKVED_L_TeRosPriV%</t>
+          <t>OKVED_56_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>OKVED_68_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_56_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>OKVED_68_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_L_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>OKVED_68_SumPriZaSooPerPreGo</t>
+          <t>OKVED_68_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>OKVED_68_TeRosUbyV%</t>
+          <t>OKVED_68_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>OKVED_M_TeRosPriV%</t>
+          <t>OKVED_68_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>OKVED_69_TeRosPriV%</t>
+          <t>OKVED_68_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>OKVED_70_TeRosPriV%</t>
+          <t>OKVED_M_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>OKVED_70_SumPriZaSooPerPreGo</t>
+          <t>OKVED_69_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>OKVED_70_TeRosSumPriV%</t>
+          <t>OKVED_70_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>OKVED_71_TeRosPriV%</t>
+          <t>OKVED_70_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>OKVED_74_TeRosPriV%</t>
+          <t>OKVED_70_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>OKVED_N_TeRosPriV%</t>
+          <t>OKVED_71_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>OKVED_N_SumPriZaSooPerPreGo</t>
+          <t>OKVED_74_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>OKVED_N_TeRosSumPriV%</t>
+          <t>OKVED_N_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>OKVED_77_TeRosPriV%</t>
+          <t>OKVED_N_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>OKVED_77_SumPriZaSooPerPreGo</t>
+          <t>OKVED_N_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>OKVED_77_TeRosUbyV%</t>
+          <t>OKVED_77_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>OKVED_79_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_77_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>OKVED_79_TeRosUbyV%</t>
+          <t>OKVED_77_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>OKVED_81_TeRosPriV%</t>
+          <t>OKVED_79_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>OKVED_81_SumPriZaSooPerPreGo</t>
+          <t>OKVED_79_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>OKVED_81_TeRosUbyV%</t>
+          <t>OKVED_81_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>OKVED_82_TeRosPriV%</t>
+          <t>OKVED_81_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>OKVED_82_SumPriZaSooPerPreGo</t>
+          <t>OKVED_81_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>OKVED_82_TeRosUbyV%</t>
+          <t>OKVED_82_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>OKVED_O_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_82_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>OKVED_O_TeRosUbyV%</t>
+          <t>OKVED_82_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>OKVED_84_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_O_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>OKVED_84_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_O_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>OKVED_84_TeRosUbyV%</t>
+          <t>OKVED_84_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_84_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosPriV%</t>
+          <t>OKVED_84_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_85_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>OKVED_85_SumPriZaSooPerPreGo</t>
+          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosUbyV%</t>
+          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosSumPriV%</t>
+          <t>OKVED_85_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_85_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosPriV%</t>
+          <t>OKVED_85_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_85_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>OKVED_85_SumPriZaSooPerPreGo</t>
+          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosUbyV%</t>
+          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosSumPriV%</t>
+          <t>OKVED_85_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>OKVED_93_TeRosUbyV%</t>
+          <t>OKVED_85_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>OKVED_S_TeRosPriV%</t>
+          <t>OKVED_85_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>OKVED_94_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_93_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosPriV%</t>
+          <t>OKVED_S_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>OKVED_94_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_94_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>OKVED_94_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_94_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>OKVED_94_SumPriZaSooPerPreGo</t>
+          <t>OKVED_94_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosUbyV%</t>
+          <t>OKVED_94_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosSumPriV%</t>
+          <t>OKVED_94_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>OKVED_96_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_94_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosPriV%</t>
+          <t>OKVED_94_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>OKVED_96_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_96_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>OKVED_96_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_96_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>OKVED_96_SumPriZaSooPerPreGo</t>
+          <t>OKVED_96_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosUbyV%</t>
+          <t>OKVED_96_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosSumPriV%</t>
+          <t>OKVED_96_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>MO_30604_PriUby(-DoNal_1</t>
+          <t>OKVED_96_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>MO_30851_SumUbyZaSooPerPreGo_1</t>
+          <t>OKVED_96_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>MO_30851_TeRosUbyV%_1</t>
+          <t>MO_30604_PriUby(-DoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>MO_30501_TeRosPriV%_1</t>
+          <t>MO_30851_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>MO_30501_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30851_TeRosUbyV%_1</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>MO_30501_TeRosSumPriV%_1</t>
+          <t>MO_30501_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>MO_30510_TeRosPriV%_1</t>
+          <t>MO_30501_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>MO_30510_SumPriZaSooPerPreGo_1</t>
+          <t>MO_30501_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>MO_30510_TeRosSumPriV%_1</t>
+          <t>MO_30510_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>MO_30604_PriUby(-DoNalZaAnaPerPreGo_1</t>
+          <t>MO_30510_SumPriZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosPriV%_1</t>
+          <t>MO_30510_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>MO_30604_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30604_PriUby(-DoNalZaAnaPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>MO_30604_SumPriZaSooPerPreGo_1</t>
+          <t>MO_30604_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosUbyV%_1</t>
+          <t>MO_30604_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosSumPriV%_1</t>
+          <t>MO_30604_SumPriZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>MO_30616_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30604_TeRosUbyV%_1</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>MO_30619_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30604_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>MO_30832_TeRosPriV%_1</t>
+          <t>MO_30616_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>OKVED_101_АГ_KolOrgEdi_1</t>
+          <t>MO_30619_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>OKVED_101_АГ_PriUby(-DoNal_1</t>
+          <t>MO_30832_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>OKVED_56_VToChiKomIUprRas</t>
+          <t>OKVED_101_АГ_KolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-OtPro</t>
+          <t>OKVED_101_АГ_PriUby(-DoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>OKVED_J_SebProSUchKomIUprRas</t>
+          <t>OKVED_56_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>OKVED_J_VToChiKomIUprRas</t>
+          <t>OKVED_J_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-OtPro</t>
+          <t>OKVED_J_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>OKVED_63_SebProSUchKomIUprRas</t>
+          <t>OKVED_J_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>OKVED_63_VToChiKomIUprRas</t>
+          <t>OKVED_63_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>OKVED_74_VToChiKomIUprRas</t>
+          <t>OKVED_63_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>OKVED_81_VToChiKomIUprRas</t>
+          <t>OKVED_63_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>OKVED_82_VToChiKomIUprRas</t>
+          <t>OKVED_74_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>OKVED_O_VToChiKomIUprRas</t>
+          <t>OKVED_81_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>OKVED_84_VToChiKomIUprRas</t>
+          <t>OKVED_82_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>OKVED_85_VToChiKomIUprRas</t>
+          <t>OKVED_O_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>OKVED_85_VToChiKomIUprRas</t>
+          <t>OKVED_84_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-OtPro</t>
+          <t>OKVED_85_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>OKVED_Q_SebProSUchKomIUprRas</t>
+          <t>OKVED_85_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>OKVED_Q_VToChiKomIUprRas</t>
+          <t>OKVED_Q_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-OtPro</t>
+          <t>OKVED_Q_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>OKVED_88_SebProSUchKomIUprRas</t>
+          <t>OKVED_Q_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>OKVED_88_VToChiKomIUprRas</t>
+          <t>OKVED_88_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>OKVED_R_SebProSUchKomIUprRas</t>
+          <t>OKVED_88_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>OKVED_R_VToChiKomIUprRas</t>
+          <t>OKVED_88_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>OKVED_93_SebProSUchKomIUprRas</t>
+          <t>OKVED_R_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>OKVED_93_VToChiKomIUprRas</t>
+          <t>OKVED_R_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>OKVED_56_VToChiKomIUprRas</t>
+          <t>OKVED_93_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>OKVED_O_VToChiKomIUprRas</t>
+          <t>OKVED_93_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>OKVED_84_VToChiKomIUprRas</t>
+          <t>OKVED_56_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>OKVED_11_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_O_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>OKVED_32_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_84_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>OKVED_32_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_11_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>OKVED_43_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_32_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>OKVED_49_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_32_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>OKVED_51_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_43_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>OKVED_56_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_49_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>OKVED_56_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_51_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>OKVED_69_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_56_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>OKVED_69_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_56_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>OKVED_74_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_69_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>OKVED_81_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_69_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>OKVED_81_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_74_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>OKVED_82_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_81_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>OKVED_82_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_81_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>OKVED_O_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_82_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>OKVED_O_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_82_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>OKVED_84_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_O_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>OKVED_84_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_O_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_84_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_84_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
@@ -8511,462 +8511,462 @@
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>OKVED_R_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>OKVED_R_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>OKVED_93_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_R_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>OKVED_93_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_R_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>OKVED_94_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_93_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>OKVED_96_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_93_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>OKVED_32_KoeTekLikDo&lt;10KolOrg(ed</t>
+          <t>OKVED_94_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
+          <t>OKVED_96_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>OKVED_01_ArendPlDeVsego</t>
+          <t>OKVED_32_KoeTekLikDo&lt;10KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>OKVED_01_PrPostDeyt</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>OKVED_B_PrPostDeyt</t>
+          <t>OKVED_01_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>OKVED_07_PrPostDeyt</t>
+          <t>OKVED_01_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPostDeyt</t>
+          <t>OKVED_B_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>OKVED_32_ArendPlDeVsego</t>
+          <t>OKVED_07_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>OKVED_32_PrPostDeyt</t>
+          <t>OKVED_11_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPostDeyt</t>
+          <t>OKVED_32_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>OKVED_35_PrPostDeyt</t>
+          <t>OKVED_32_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>OKVED_35_PrPostDeyt</t>
+          <t>OKVED_33_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>OKVED_E_ArendPlDeVsego</t>
+          <t>OKVED_35_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>OKVED_36_ArendPlDeVsego</t>
+          <t>OKVED_35_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>OKVED_38_ArendPlDeVsego</t>
+          <t>OKVED_E_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>OKVED_41_ArendPlDeVsego</t>
+          <t>OKVED_36_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>OKVED_43_ArendPlDeVsego</t>
+          <t>OKVED_38_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPostDeyt</t>
+          <t>OKVED_41_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>OKVED_G_PrPostDeyt</t>
+          <t>OKVED_43_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>OKVED_46_PrPostDeyt</t>
+          <t>OKVED_43_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>OKVED_47_PrPostDeyt</t>
+          <t>OKVED_G_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>OKVED_H_PrPostDeyt</t>
+          <t>OKVED_46_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>OKVED_49_ArendPlDeVsego</t>
+          <t>OKVED_47_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPostDeyt</t>
+          <t>OKVED_H_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>OKVED_50_ArendPlDeVsego</t>
+          <t>OKVED_49_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>OKVED_50_PrPostDeyt</t>
+          <t>OKVED_49_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>OKVED_51_PrPostDeyt</t>
+          <t>OKVED_50_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>OKVED_52_PrPostDeyt</t>
+          <t>OKVED_50_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>OKVED_I_ArendPlDeVsego</t>
+          <t>OKVED_51_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>OKVED_55_ArendPlDeVsego</t>
+          <t>OKVED_52_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>OKVED_56_ArendPlDeVsego</t>
+          <t>OKVED_I_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>OKVED_56_PrPostDeyt</t>
+          <t>OKVED_55_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>OKVED_J_OtProdDeVsego</t>
+          <t>OKVED_56_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>OKVED_J_ArendPlDeVsego</t>
+          <t>OKVED_56_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>OKVED_J_PrPostDeyt</t>
+          <t>OKVED_J_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>OKVED_63_OtProdDeVsego</t>
+          <t>OKVED_J_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>OKVED_63_ArendPlDeVsego</t>
+          <t>OKVED_J_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>OKVED_63_PrPostDeyt</t>
+          <t>OKVED_63_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t>OKVED_K_ArendPlDeVsego</t>
+          <t>OKVED_63_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPostDeyt</t>
+          <t>OKVED_63_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t>OKVED_64_ArendPlDeVsego</t>
+          <t>OKVED_K_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPostDeyt</t>
+          <t>OKVED_K_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t>OKVED_M_PrPostDeyt</t>
+          <t>OKVED_64_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>OKVED_69_ArendPlDeVsego</t>
+          <t>OKVED_64_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>OKVED_69_PrPostDeyt</t>
+          <t>OKVED_M_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPostDeyt</t>
+          <t>OKVED_69_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t>OKVED_71_PrPostDeyt</t>
+          <t>OKVED_69_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>OKVED_74_PrPostDeyt</t>
+          <t>OKVED_70_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>OKVED_77_PrPostDeyt</t>
+          <t>OKVED_71_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>OKVED_79_ArendPlDeVsego</t>
+          <t>OKVED_74_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
-          <t>OKVED_81_ArendPlDeVsego</t>
+          <t>OKVED_77_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>OKVED_81_PrPostDeyt</t>
+          <t>OKVED_79_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>OKVED_82_ArendPlDeVsego</t>
+          <t>OKVED_81_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t>OKVED_82_PrPostDeyt</t>
+          <t>OKVED_81_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>OKVED_O_ArendPlDeVsego</t>
+          <t>OKVED_82_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>OKVED_O_PrPostDeyt</t>
+          <t>OKVED_82_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>OKVED_84_ArendPlDeVsego</t>
+          <t>OKVED_O_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>OKVED_84_PrPostDeyt</t>
+          <t>OKVED_O_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_84_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPostDeyt</t>
+          <t>OKVED_84_PrPostDeyt</t>
         </is>
       </c>
     </row>
@@ -8987,812 +8987,812 @@
     <row r="1225">
       <c r="A1225" t="inlineStr">
         <is>
-          <t>OKVED_Q_OtProdDeVsego</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>OKVED_Q_ArendPlDeVsego</t>
+          <t>OKVED_85_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="inlineStr">
         <is>
-          <t>OKVED_Q_PrPostDeyt</t>
+          <t>OKVED_Q_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>OKVED_88_OtProdDeVsego</t>
+          <t>OKVED_Q_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>OKVED_88_ArendPlDeVsego</t>
+          <t>OKVED_Q_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>OKVED_88_PrPostDeyt</t>
+          <t>OKVED_88_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>OKVED_R_OtProdDeVsego</t>
+          <t>OKVED_88_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>OKVED_R_ArendPlDeVsego</t>
+          <t>OKVED_88_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>OKVED_R_PrPostDeyt</t>
+          <t>OKVED_R_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>OKVED_93_OtProdDeVsego</t>
+          <t>OKVED_R_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>OKVED_93_ArendPlDeVsego</t>
+          <t>OKVED_R_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>OKVED_93_PrPostDeyt</t>
+          <t>OKVED_93_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>OKVED_S_ArendPlDeVsego</t>
+          <t>OKVED_93_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>OKVED_94_ArendPlDeVsego</t>
+          <t>OKVED_93_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>OKVED_96_ArendPlDeVsego</t>
+          <t>OKVED_S_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>OKVED_96_PrPostDeyt</t>
+          <t>OKVED_94_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcPoDolgObyaz</t>
+          <t>OKVED_96_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPoFin</t>
+          <t>OKVED_96_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>OKVED_32_ProcPoDolgObyaz</t>
+          <t>OKVED_11_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>OKVED_32_NalogNaPri</t>
+          <t>OKVED_11_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>OKVED_32_PrPoFin</t>
+          <t>OKVED_32_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>OKVED_33_NalogNaPri</t>
+          <t>OKVED_32_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_32_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcPoDolgObyaz</t>
+          <t>OKVED_33_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>OKVED_36_PrPoFin</t>
+          <t>OKVED_33_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>OKVED_38_NalogNaPri</t>
+          <t>OKVED_36_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPoFin</t>
+          <t>OKVED_36_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcPoDolgObyaz</t>
+          <t>OKVED_38_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPoFin</t>
+          <t>OKVED_43_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="inlineStr">
         <is>
-          <t>OKVED_50_PrPoFin</t>
+          <t>OKVED_49_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="inlineStr">
         <is>
-          <t>OKVED_I_PrPoFin</t>
+          <t>OKVED_49_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>OKVED_55_PrPoFin</t>
+          <t>OKVED_50_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>OKVED_56_ProcPoDolgObyaz</t>
+          <t>OKVED_I_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>OKVED_56_NalogNaPri</t>
+          <t>OKVED_55_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>OKVED_56_PrPoFin</t>
+          <t>OKVED_56_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
         <is>
-          <t>OKVED_J_ProcPoDolgObyaz</t>
+          <t>OKVED_56_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>OKVED_J_NalogNaPri</t>
+          <t>OKVED_56_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>OKVED_J_PrPoFin</t>
+          <t>OKVED_J_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>OKVED_63_ProcPoDolgObyaz</t>
+          <t>OKVED_J_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>OKVED_63_NalogNaPri</t>
+          <t>OKVED_J_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>OKVED_63_PrPoFin</t>
+          <t>OKVED_63_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPoFin</t>
+          <t>OKVED_63_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPoFin</t>
+          <t>OKVED_63_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>OKVED_M_ProcPoDolgObyaz</t>
+          <t>OKVED_K_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>OKVED_69_ProcPoDolgObyaz</t>
+          <t>OKVED_64_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>OKVED_69_NalogNaPri</t>
+          <t>OKVED_M_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>OKVED_69_PrPoFin</t>
+          <t>OKVED_69_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>OKVED_70_ProcPoDolgObyaz</t>
+          <t>OKVED_69_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPoFin</t>
+          <t>OKVED_69_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>OKVED_71_ProcPoDolgObyaz</t>
+          <t>OKVED_70_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>OKVED_71_NalogNaPri</t>
+          <t>OKVED_70_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>OKVED_74_ProcPoDolgObyaz</t>
+          <t>OKVED_71_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcPoDolgObyaz</t>
+          <t>OKVED_71_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>OKVED_77_PrPoFin</t>
+          <t>OKVED_74_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>OKVED_79_NalogNaPri</t>
+          <t>OKVED_77_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>OKVED_79_PrPoFin</t>
+          <t>OKVED_77_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>OKVED_81_NalogNaPri</t>
+          <t>OKVED_79_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>OKVED_82_ProcPoDolgObyaz</t>
+          <t>OKVED_79_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>OKVED_82_PrPoFin</t>
+          <t>OKVED_81_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_82_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>OKVED_O_VSvyaziSOplTrudRab</t>
+          <t>OKVED_82_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>OKVED_O_ProcPoDolgObyaz</t>
+          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>OKVED_O_PrPoFin</t>
+          <t>OKVED_O_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_O_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>OKVED_84_VSvyaziSOplTrudRab</t>
+          <t>OKVED_O_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>OKVED_84_ProcPoDolgObyaz</t>
+          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>OKVED_84_PrPoFin</t>
+          <t>OKVED_84_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_84_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_84_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPoFin</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_85_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPoFin</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>OKVED_Q_ProcPoDolgObyaz</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>OKVED_Q_NalogNaPri</t>
+          <t>OKVED_85_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>OKVED_Q_PrPoFin</t>
+          <t>OKVED_Q_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>OKVED_86_PlatPoTekDeVsego</t>
+          <t>OKVED_Q_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>OKVED_86_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_Q_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>OKVED_86_VSvyaziSOplTrudRab</t>
+          <t>OKVED_86_PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>OKVED_86_ProcPoDolgObyaz</t>
+          <t>OKVED_86_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>OKVED_86_NalogNaPri</t>
+          <t>OKVED_86_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>OKVED_86_PrPoFin</t>
+          <t>OKVED_86_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>OKVED_86_SaldoDenPotTekOper</t>
+          <t>OKVED_86_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_86_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>OKVED_R_VSvyaziSOplTrudRab</t>
+          <t>OKVED_86_SaldoDenPotTekOper</t>
         </is>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>OKVED_R_ProcPoDolgObyaz</t>
+          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>OKVED_R_NalogNaPri</t>
+          <t>OKVED_R_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>OKVED_R_PrPoFin</t>
+          <t>OKVED_R_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_R_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>OKVED_93_VSvyaziSOplTrudRab</t>
+          <t>OKVED_R_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>OKVED_93_ProcPoDolgObyaz</t>
+          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>OKVED_93_NalogNaPri</t>
+          <t>OKVED_93_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>OKVED_93_PrPoFin</t>
+          <t>OKVED_93_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>OKVED_96_ProcPoDolgObyaz</t>
+          <t>OKVED_93_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>OKVED_96_NalogNaPri</t>
+          <t>OKVED_93_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>OKVED_96_PrPoFin</t>
+          <t>OKVED_96_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_96_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdAkcOrgDolUch</t>
+          <t>OKVED_96_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>OKVED_01_DivProcDolgFinVlozh</t>
+          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>OKVED_01_PrPostDeyt</t>
+          <t>OKVED_01_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>OKVED_B_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>OKVED_B_PrPostDeyt</t>
+          <t>OKVED_01_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>OKVED_07_OtProdAkcOrgDolUch</t>
+          <t>OKVED_B_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>OKVED_07_PrPostDeyt</t>
+          <t>OKVED_B_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>OKVED_C_OtProdAkcOrgDolUch</t>
+          <t>OKVED_07_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>OKVED_10_OtProdAkcOrgDolUch</t>
+          <t>OKVED_07_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_C_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdAkcOrgDolUch</t>
+          <t>OKVED_10_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdFinVlozh</t>
+          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPostDeyt</t>
+          <t>OKVED_11_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>OKVED_33_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_11_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>OKVED_33_OtProdAkcOrgDolUch</t>
+          <t>OKVED_11_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>OKVED_33_DivProcDolgFinVlozh</t>
+          <t>OKVED_33_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPostDeyt</t>
+          <t>OKVED_33_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_33_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>OKVED_35_PrPostDeyt</t>
+          <t>OKVED_33_PrPostDeyt</t>
         </is>
       </c>
     </row>
@@ -9813,1204 +9813,1204 @@
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdAkcOrgDolUch</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdFinVlozh</t>
+          <t>OKVED_35_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>OKVED_E_DivProcDolgFinVlozh</t>
+          <t>OKVED_E_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdAkcOrgDolUch</t>
+          <t>OKVED_E_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdFinVlozh</t>
+          <t>OKVED_E_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>OKVED_36_DivProcDolgFinVlozh</t>
+          <t>OKVED_36_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_36_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdAkcOrgDolUch</t>
+          <t>OKVED_36_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdFinVlozh</t>
+          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>OKVED_38_DivProcDolgFinVlozh</t>
+          <t>OKVED_38_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_38_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdAkcOrgDolUch</t>
+          <t>OKVED_F_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>OKVED_42_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>OKVED_42_OtProdAkcOrgDolUch</t>
+          <t>OKVED_41_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_42_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdAkcOrgDolUch</t>
+          <t>OKVED_42_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdFinVlozh</t>
+          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPostDeyt</t>
+          <t>OKVED_43_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>OKVED_G_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>OKVED_G_PrPostDeyt</t>
+          <t>OKVED_43_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>OKVED_46_OtProdAkcOrgDolUch</t>
+          <t>OKVED_G_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>OKVED_46_PrPostDeyt</t>
+          <t>OKVED_G_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>OKVED_47_OtProdAkcOrgDolUch</t>
+          <t>OKVED_46_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>OKVED_47_PrPostDeyt</t>
+          <t>OKVED_46_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>OKVED_H_OtProdAkcOrgDolUch</t>
+          <t>OKVED_47_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>OKVED_H_PrPostDeyt</t>
+          <t>OKVED_47_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_H_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdAkcOrgDolUch</t>
+          <t>OKVED_H_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>OKVED_49_DivProcDolgFinVlozh</t>
+          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPostDeyt</t>
+          <t>OKVED_49_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>OKVED_51_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_49_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>OKVED_51_OtProdAkcOrgDolUch</t>
+          <t>OKVED_49_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>OKVED_51_PrPostDeyt</t>
+          <t>OKVED_51_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>OKVED_52_OtProdAkcOrgDolUch</t>
+          <t>OKVED_51_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>OKVED_52_PrPostDeyt</t>
+          <t>OKVED_51_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_52_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdAkcOrgDolUch</t>
+          <t>OKVED_52_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdAkcOrgDolUch</t>
+          <t>OKVED_I_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdAkcOrgDolUch</t>
+          <t>OKVED_55_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPostDeyt</t>
+          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_K_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdAkcOrgDolUch</t>
+          <t>OKVED_K_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPostDeyt</t>
+          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>OKVED_L_OtProdAkcOrgDolUch</t>
+          <t>OKVED_64_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>OKVED_68_OtProdAkcOrgDolUch</t>
+          <t>OKVED_64_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_L_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdAkcOrgDolUch</t>
+          <t>OKVED_68_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>OKVED_M_PrPostDeyt</t>
+          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_M_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdAkcOrgDolUch</t>
+          <t>OKVED_M_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPostDeyt</t>
+          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_70_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdAkcOrgDolUch</t>
+          <t>OKVED_70_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>OKVED_71_DivProcDolgFinVlozh</t>
+          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>OKVED_71_PrPostDeyt</t>
+          <t>OKVED_71_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdAkcOrgDolUch</t>
+          <t>OKVED_71_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdFinVlozh</t>
+          <t>OKVED_71_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdAkcOrgDolUch</t>
+          <t>OKVED_N_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdFinVlozh</t>
+          <t>OKVED_N_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>OKVED_77_PrPostDeyt</t>
+          <t>OKVED_77_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>OKVED_79_OtProdAkcOrgDolUch</t>
+          <t>OKVED_77_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>OKVED_79_OtProdFinVlozh</t>
+          <t>OKVED_77_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>OKVED_79_DivProcDolgFinVlozh</t>
+          <t>OKVED_79_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_79_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdAkcOrgDolUch</t>
+          <t>OKVED_79_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>OKVED_S_DivProcDolgFinVlozh</t>
+          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_S_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdAkcOrgDolUch</t>
+          <t>OKVED_S_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>OKVED_94_DivProcDolgFinVlozh</t>
+          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>OKVED_01_DolUch</t>
+          <t>OKVED_94_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_94_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>OKVED_B_DolUch</t>
+          <t>OKVED_01_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_01_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>OKVED_07_DolUch</t>
+          <t>OKVED_B_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>OKVED_07_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>OKVED_C_DolUch</t>
+          <t>OKVED_07_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_07_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>OKVED_10_DolUch</t>
+          <t>OKVED_C_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>OKVED_11_DolUch</t>
+          <t>OKVED_10_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>OKVED_11_PrCenBum</t>
+          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_11_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPoFin</t>
+          <t>OKVED_11_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>OKVED_33_DolUch</t>
+          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_11_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_33_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>OKVED_E_DolUch</t>
+          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>OKVED_E_PrCenBum</t>
+          <t>OKVED_33_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_E_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>OKVED_36_DolUch</t>
+          <t>OKVED_E_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>OKVED_36_PrCenBum</t>
+          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_36_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>OKVED_36_PrPoFin</t>
+          <t>OKVED_36_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>OKVED_38_DolUch</t>
+          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>OKVED_38_PrCenBum</t>
+          <t>OKVED_36_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>OKVED_38_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_38_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>OKVED_F_DolUch</t>
+          <t>OKVED_38_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_38_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>OKVED_41_DolUch</t>
+          <t>OKVED_F_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>OKVED_42_DolUch</t>
+          <t>OKVED_41_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>OKVED_43_DolUch</t>
+          <t>OKVED_42_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>OKVED_43_PrCenBum</t>
+          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_43_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPoFin</t>
+          <t>OKVED_43_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>OKVED_46_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>OKVED_47_DolUch</t>
+          <t>OKVED_43_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>OKVED_H_DolUch</t>
+          <t>OKVED_46_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_47_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>OKVED_49_DolUch</t>
+          <t>OKVED_H_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPoFin</t>
+          <t>OKVED_49_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>OKVED_50_DolUch</t>
+          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>OKVED_50_PrCenBum</t>
+          <t>OKVED_49_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_50_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>OKVED_50_PrPoFin</t>
+          <t>OKVED_50_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>OKVED_51_DolUch</t>
+          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>OKVED_51_PrCenBum</t>
+          <t>OKVED_50_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>OKVED_51_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_51_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>OKVED_52_DolUch</t>
+          <t>OKVED_51_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_51_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_52_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>OKVED_I_PrPoFin</t>
+          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>OKVED_55_PrPoFin</t>
+          <t>OKVED_I_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>OKVED_K_DolUch</t>
+          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_55_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPoFin</t>
+          <t>OKVED_K_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>OKVED_64_DolUch</t>
+          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>OKVED_64_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_K_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPoFin</t>
+          <t>OKVED_64_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>OKVED_M_DolUch</t>
+          <t>OKVED_64_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>OKVED_70_DolUch</t>
+          <t>OKVED_64_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>OKVED_70_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_M_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPoFin</t>
+          <t>OKVED_70_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>OKVED_71_DolUch</t>
+          <t>OKVED_70_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>OKVED_N_DolUch</t>
+          <t>OKVED_70_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>OKVED_N_PrCenBum</t>
+          <t>OKVED_71_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>OKVED_77_DolUch</t>
+          <t>OKVED_N_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>OKVED_77_PrCenBum</t>
+          <t>OKVED_N_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_77_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>OKVED_77_PrPoFin</t>
+          <t>OKVED_77_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>OKVED_79_DolUch</t>
+          <t>OKVED_77_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>OKVED_79_PrCenBum</t>
+          <t>OKVED_77_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>OKVED_79_PrPoFin</t>
+          <t>OKVED_79_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>OKVED_S_DolUch</t>
+          <t>OKVED_79_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_79_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>OKVED_94_DolUch</t>
+          <t>OKVED_S_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>OKVED_01_DolUch</t>
+          <t>OKVED_94_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>OKVED_B_DolUch</t>
+          <t>OKVED_01_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_01_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>OKVED_07_DolUch</t>
+          <t>OKVED_B_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>OKVED_07_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_B_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>OKVED_C_DolUch</t>
+          <t>OKVED_07_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_07_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>OKVED_10_DolUch</t>
+          <t>OKVED_C_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_10_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>OKVED_32_DolUch</t>
+          <t>OKVED_32_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>OKVED_32_PrCenBum</t>
+          <t>OKVED_32_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>OKVED_32_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_32_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>OKVED_32_PrPoFin</t>
+          <t>OKVED_33_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>OKVED_32_Saldo</t>
+          <t>OKVED_33_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>OKVED_33_DolUch</t>
+          <t>OKVED_33_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1713"/>
+  <dimension ref="A1:A1710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,7 +2491,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>OKVED_Q_DebZadSreSrPog</t>
+          <t>OKVED_69_FinIDruAkt(deNdPoPriTseKraFinVloSreSrPog</t>
         </is>
       </c>
     </row>
@@ -6334,5670 +6334,5670 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>OKVED_56_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_B_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>OKVED_K_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_07_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>OKVED_64_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_33_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>OKVED_69_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_E_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>OKVED_74_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_36_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>OKVED_81_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_38_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>OKVED_82_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_42_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>OKVED_O_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_43_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>OKVED_84_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_49_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_52_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_56_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_56_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_K_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas</t>
+          <t>OKVED_K_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_64_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_64_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas</t>
+          <t>OKVED_69_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>OKVED_11_OtcGoPro</t>
+          <t>OKVED_69_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>OKVED_32_OtcGoOtlNalNaPri</t>
+          <t>OKVED_71_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>OKVED_33_OtcGoPro</t>
+          <t>OKVED_74_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoOtlNalNaPri</t>
+          <t>OKVED_74_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoPro</t>
+          <t>OKVED_79_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>OKVED_42_OtcGoPro</t>
+          <t>OKVED_81_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>OKVED_43_OtcGoPro</t>
+          <t>OKVED_81_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>OKVED_50_OtcGoPro</t>
+          <t>OKVED_82_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>OKVED_56_OtcGoOtlNalNaPri</t>
+          <t>OKVED_82_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoOtlNalNaPri</t>
+          <t>OKVED_O_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoPro</t>
+          <t>OKVED_O_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>OKVED_74_OtcGoPro</t>
+          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>OKVED_77_OtcGoPro</t>
+          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>OKVED_79_OtcGoPro</t>
+          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>OKVED_82_OtcGoOtlNalNaPri</t>
+          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>OKVED_82_OtcGoPro</t>
+          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>OKVED_O_OtcGoOtlNalNaPri</t>
+          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>OKVED_O_OtcGoPro</t>
+          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>OKVED_84_OtcGoOtlNalNaPri</t>
+          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>OKVED_84_OtcGoPro</t>
+          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoPro</t>
+          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoPro</t>
+          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoSalProDohIRas</t>
+          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoOtlNalNaPri</t>
+          <t>OKVED_S_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoPro</t>
+          <t>OKVED_94_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoSalProDohIRas</t>
+          <t>OKVED_96_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoOtlNalNaPri</t>
+          <t>OKVED_11_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoPro</t>
+          <t>OKVED_32_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>OKVED_S_OtcGoPro</t>
+          <t>OKVED_33_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>OKVED_94_OtcGoPro</t>
+          <t>OKVED_38_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>OKVED_96_OtcGoPro</t>
+          <t>OKVED_38_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>OKVED_01_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_42_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>OKVED_B_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_43_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>OKVED_B_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_50_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>OKVED_07_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_56_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>OKVED_07_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_69_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>OKVED_10_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_69_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>OKVED_11_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_74_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>OKVED_11_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_77_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>OKVED_32_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_79_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>OKVED_33_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_O_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>OKVED_33_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_O_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>OKVED_35_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_84_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>OKVED_35_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_84_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>OKVED_35_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_85_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>OKVED_35_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_85_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>OKVED_E_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_R_OtcGoSalProDohIRas</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>OKVED_E_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_R_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>OKVED_36_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_R_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>OKVED_36_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_93_OtcGoSalProDohIRas</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_93_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_93_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>OKVED_F_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_S_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>OKVED_41_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_94_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>OKVED_41_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_96_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>OKVED_42_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_01_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>OKVED_43_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_B_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>OKVED_43_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_B_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>OKVED_G_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_07_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>OKVED_G_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_07_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>OKVED_46_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_10_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>OKVED_46_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_11_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>OKVED_47_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_11_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>OKVED_47_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_32_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>OKVED_50_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_33_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>OKVED_50_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_33_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>OKVED_51_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_35_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>OKVED_51_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_35_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>OKVED_52_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_35_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>OKVED_52_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_35_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>OKVED_I_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_36_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>OKVED_I_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_36_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>OKVED_55_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_38_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>OKVED_55_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_38_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>OKVED_56_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_F_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>OKVED_56_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_41_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>OKVED_K_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_41_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>OKVED_K_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_42_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>OKVED_64_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_43_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>OKVED_64_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_43_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>OKVED_L_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_G_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>OKVED_L_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_G_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>OKVED_68_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_46_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>OKVED_68_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_46_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>OKVED_M_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_47_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>OKVED_M_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_47_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_50_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_50_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>OKVED_70_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_52_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>OKVED_70_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_52_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>OKVED_71_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_I_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>OKVED_71_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_I_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>OKVED_74_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_55_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>OKVED_74_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_55_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>OKVED_N_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_56_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>OKVED_N_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_56_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>OKVED_77_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_K_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>OKVED_77_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_K_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>OKVED_79_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_64_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>OKVED_79_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_64_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>OKVED_81_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_L_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>OKVED_81_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_L_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>OKVED_82_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_68_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>OKVED_82_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_68_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>OKVED_O_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_M_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>OKVED_O_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_M_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>OKVED_84_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_69_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>OKVED_84_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_69_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_71_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_71_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_74_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_74_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_N_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_N_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_77_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_77_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>OKVED_S_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_79_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>OKVED_S_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_79_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>OKVED_94_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_81_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>OKVED_94_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_81_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>OKVED_96_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_82_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>OKVED_96_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_82_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerVyr_1</t>
+          <t>OKVED_84_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerKomIUprRas_1</t>
+          <t>OKVED_84_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>MO_30851_OtcGoPro_1</t>
+          <t>OKVED_85_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>MO_30501_OtcGoOtlNalNaPri_1</t>
+          <t>OKVED_85_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>MO_30501_OtcGoPro_1</t>
+          <t>OKVED_85_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>MO_30510_OtcGoSalProDohIRas_1</t>
+          <t>OKVED_85_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>MO_30510_OtcGoOtlNalNaPri_1</t>
+          <t>OKVED_R_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>MO_30510_OtcGoPro_1</t>
+          <t>OKVED_R_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>MO_30604_OtcGoPri(ubDoNal_1</t>
+          <t>OKVED_93_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>MO_30604_OtcGoOtlNalNaPri_1</t>
+          <t>OKVED_93_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>MO_30604_OtcGoPro_1</t>
+          <t>OKVED_S_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>MO_30832_OtcGoPro_1</t>
+          <t>OKVED_S_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-DoNal</t>
+          <t>OKVED_94_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-DoNal</t>
+          <t>OKVED_94_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-DoNal</t>
+          <t>OKVED_96_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-DoNal</t>
+          <t>OKVED_96_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>OKVED_01_TeRosPriV%</t>
+          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerVyr_1</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>OKVED_10_SumUbyZaSooPerPreGo</t>
+          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerKomIUprRas_1</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>OKVED_11_SumUbyZaSooPerPreGo</t>
+          <t>MO_30851_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>OKVED_11_TeRosUbyV%</t>
+          <t>MO_30501_OtcGoOtlNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>OKVED_32_SumUbyZaSooPerPreGo</t>
+          <t>MO_30501_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>OKVED_32_TeRosUbyV%</t>
+          <t>MO_30510_OtcGoSalProDohIRas_1</t>
         </is>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>OKVED_38_SumUbyZaSooPerPreGo</t>
+          <t>MO_30510_OtcGoOtlNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>OKVED_F_TeRosPriV%</t>
+          <t>MO_30510_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>OKVED_41_TeRosPriV%</t>
+          <t>MO_30604_OtcGoPri(ubDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>OKVED_41_SumUbyZaSooPerPreGo</t>
+          <t>MO_30604_OtcGoOtlNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>OKVED_42_TeRosPriV%</t>
+          <t>MO_30604_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>OKVED_42_TeRosSumPriV%</t>
+          <t>MO_30832_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>OKVED_43_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_11_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>OKVED_43_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_32_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>OKVED_43_SumPriZaSooPerPreGo</t>
+          <t>OKVED_42_OrgPolPriKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>OKVED_43_TeRosUbyV%</t>
+          <t>OKVED_42_OrgPolPriV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>OKVED_49_TeRosUbyV%</t>
+          <t>OKVED_42_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>OKVED_50_TeRosPriV%</t>
+          <t>OKVED_43_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>OKVED_50_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_43_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>OKVED_50_TeRosSumPriV%</t>
+          <t>OKVED_43_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>OKVED_51_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_49_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>OKVED_51_TeRosUbyV%</t>
+          <t>OKVED_49_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>OKVED_I_TeRosPriV%</t>
+          <t>OKVED_49_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>OKVED_55_TeRosPriV%</t>
+          <t>OKVED_50_OrgPolPriKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>OKVED_55_SumPriZaSooPerPreGo</t>
+          <t>OKVED_50_OrgPolPriV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>OKVED_56_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_50_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>OKVED_56_TeRosUbyV%</t>
+          <t>OKVED_51_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>OKVED_L_TeRosPriV%</t>
+          <t>OKVED_51_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>OKVED_68_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_51_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>OKVED_68_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_56_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>OKVED_68_SumPriZaSooPerPreGo</t>
+          <t>OKVED_56_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>OKVED_68_TeRosUbyV%</t>
+          <t>OKVED_56_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>OKVED_M_TeRosPriV%</t>
+          <t>OKVED_J_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>OKVED_69_TeRosPriV%</t>
+          <t>OKVED_J_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>OKVED_70_TeRosPriV%</t>
+          <t>OKVED_J_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>OKVED_70_SumPriZaSooPerPreGo</t>
+          <t>OKVED_J_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>OKVED_70_TeRosSumPriV%</t>
+          <t>OKVED_J_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>OKVED_71_TeRosPriV%</t>
+          <t>OKVED_63_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>OKVED_74_TeRosPriV%</t>
+          <t>OKVED_63_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>OKVED_N_TeRosPriV%</t>
+          <t>OKVED_63_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>OKVED_N_SumPriZaSooPerPreGo</t>
+          <t>OKVED_63_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>OKVED_N_TeRosSumPriV%</t>
+          <t>OKVED_63_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>OKVED_77_TeRosPriV%</t>
+          <t>OKVED_69_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>OKVED_77_SumPriZaSooPerPreGo</t>
+          <t>OKVED_69_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>OKVED_77_TeRosUbyV%</t>
+          <t>OKVED_69_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>OKVED_79_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_74_OrgPolPriKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>OKVED_79_TeRosUbyV%</t>
+          <t>OKVED_74_OrgPolPriV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>OKVED_81_TeRosPriV%</t>
+          <t>OKVED_74_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>OKVED_81_SumPriZaSooPerPreGo</t>
+          <t>OKVED_79_OrgPolPriKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>OKVED_81_TeRosUbyV%</t>
+          <t>OKVED_79_OrgPolPriV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>OKVED_82_TeRosPriV%</t>
+          <t>OKVED_79_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>OKVED_82_SumPriZaSooPerPreGo</t>
+          <t>OKVED_81_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>OKVED_82_TeRosUbyV%</t>
+          <t>OKVED_81_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>OKVED_O_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_81_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>OKVED_O_TeRosUbyV%</t>
+          <t>OKVED_O_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>OKVED_84_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_O_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>OKVED_84_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_O_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>OKVED_84_TeRosUbyV%</t>
+          <t>OKVED_84_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_84_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosPriV%</t>
+          <t>OKVED_84_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_85_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_85_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>OKVED_85_SumPriZaSooPerPreGo</t>
+          <t>OKVED_85_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosUbyV%</t>
+          <t>OKVED_85_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosSumPriV%</t>
+          <t>OKVED_85_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_85_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosPriV%</t>
+          <t>OKVED_Q_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_Q_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_Q_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>OKVED_85_SumPriZaSooPerPreGo</t>
+          <t>OKVED_Q_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosUbyV%</t>
+          <t>OKVED_Q_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosSumPriV%</t>
+          <t>OKVED_88_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>OKVED_93_TeRosUbyV%</t>
+          <t>OKVED_88_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>OKVED_S_TeRosPriV%</t>
+          <t>OKVED_88_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>OKVED_94_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_88_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosPriV%</t>
+          <t>OKVED_88_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>OKVED_94_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_93_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>OKVED_94_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_93_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>OKVED_94_SumPriZaSooPerPreGo</t>
+          <t>OKVED_93_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosUbyV%</t>
+          <t>OKVED_94_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosSumPriV%</t>
+          <t>OKVED_94_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>OKVED_96_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_94_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosPriV%</t>
+          <t>OKVED_01_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>OKVED_96_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_10_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>OKVED_96_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_11_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>OKVED_96_SumPriZaSooPerPreGo</t>
+          <t>OKVED_11_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosUbyV%</t>
+          <t>OKVED_32_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosSumPriV%</t>
+          <t>OKVED_32_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>MO_30604_PriUby(-DoNal_1</t>
+          <t>OKVED_38_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>MO_30851_SumUbyZaSooPerPreGo_1</t>
+          <t>OKVED_F_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>MO_30851_TeRosUbyV%_1</t>
+          <t>OKVED_41_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>MO_30501_TeRosPriV%_1</t>
+          <t>OKVED_41_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>MO_30501_SumUbyZaSooPerPreGo_1</t>
+          <t>OKVED_42_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>MO_30501_TeRosSumPriV%_1</t>
+          <t>OKVED_42_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>MO_30510_TeRosPriV%_1</t>
+          <t>OKVED_43_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>MO_30510_SumPriZaSooPerPreGo_1</t>
+          <t>OKVED_43_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>MO_30510_TeRosSumPriV%_1</t>
+          <t>OKVED_43_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>MO_30604_PriUby(-DoNalZaAnaPerPreGo_1</t>
+          <t>OKVED_43_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosPriV%_1</t>
+          <t>OKVED_49_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>MO_30604_SumUbyZaSooPerPreGo_1</t>
+          <t>OKVED_50_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>MO_30604_SumPriZaSooPerPreGo_1</t>
+          <t>OKVED_50_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosUbyV%_1</t>
+          <t>OKVED_50_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosSumPriV%_1</t>
+          <t>OKVED_51_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>MO_30616_SumUbyZaSooPerPreGo_1</t>
+          <t>OKVED_51_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>MO_30619_SumUbyZaSooPerPreGo_1</t>
+          <t>OKVED_I_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>MO_30832_TeRosPriV%_1</t>
+          <t>OKVED_55_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>OKVED_101_АГ_KolOrgEdi_1</t>
+          <t>OKVED_55_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>OKVED_101_АГ_PriUby(-DoNal_1</t>
+          <t>OKVED_56_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>OKVED_56_VToChiKomIUprRas</t>
+          <t>OKVED_56_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-OtPro</t>
+          <t>OKVED_L_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>OKVED_J_SebProSUchKomIUprRas</t>
+          <t>OKVED_68_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>OKVED_J_VToChiKomIUprRas</t>
+          <t>OKVED_68_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-OtPro</t>
+          <t>OKVED_68_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>OKVED_63_SebProSUchKomIUprRas</t>
+          <t>OKVED_68_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>OKVED_63_VToChiKomIUprRas</t>
+          <t>OKVED_M_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>OKVED_74_VToChiKomIUprRas</t>
+          <t>OKVED_69_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>OKVED_81_VToChiKomIUprRas</t>
+          <t>OKVED_70_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>OKVED_82_VToChiKomIUprRas</t>
+          <t>OKVED_70_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>OKVED_O_VToChiKomIUprRas</t>
+          <t>OKVED_70_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>OKVED_84_VToChiKomIUprRas</t>
+          <t>OKVED_71_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>OKVED_85_VToChiKomIUprRas</t>
+          <t>OKVED_74_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>OKVED_85_VToChiKomIUprRas</t>
+          <t>OKVED_77_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-OtPro</t>
+          <t>OKVED_77_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>OKVED_Q_SebProSUchKomIUprRas</t>
+          <t>OKVED_77_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>OKVED_Q_VToChiKomIUprRas</t>
+          <t>OKVED_79_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-OtPro</t>
+          <t>OKVED_79_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>OKVED_88_SebProSUchKomIUprRas</t>
+          <t>OKVED_81_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>OKVED_88_VToChiKomIUprRas</t>
+          <t>OKVED_81_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>OKVED_R_SebProSUchKomIUprRas</t>
+          <t>OKVED_81_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>OKVED_R_VToChiKomIUprRas</t>
+          <t>OKVED_82_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>OKVED_93_SebProSUchKomIUprRas</t>
+          <t>OKVED_82_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>OKVED_93_VToChiKomIUprRas</t>
+          <t>OKVED_82_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>OKVED_56_VToChiKomIUprRas</t>
+          <t>OKVED_O_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>OKVED_O_VToChiKomIUprRas</t>
+          <t>OKVED_O_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>OKVED_84_VToChiKomIUprRas</t>
+          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>OKVED_11_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_85_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>OKVED_32_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>OKVED_32_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>OKVED_43_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_85_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>OKVED_49_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_85_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>OKVED_51_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_85_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>OKVED_56_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>OKVED_56_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_85_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>OKVED_69_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>OKVED_69_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>OKVED_74_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_85_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>OKVED_81_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_85_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>OKVED_81_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_85_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>OKVED_82_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_93_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>OKVED_82_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_S_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>OKVED_O_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_94_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>OKVED_O_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_94_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>OKVED_84_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_94_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>OKVED_84_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_94_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_94_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_94_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_94_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_96_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>OKVED_R_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_96_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>OKVED_R_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_96_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>OKVED_93_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_96_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>OKVED_93_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_96_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>OKVED_94_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_96_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>OKVED_96_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_96_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>OKVED_32_KoeTekLikDo&lt;10KolOrg(ed</t>
+          <t>MO_30851_OrgPolUbyKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
+          <t>MO_30604_PriUby(-DoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>OKVED_01_ArendPlDeVsego</t>
+          <t>MO_30604_OrgPolUbyKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>OKVED_01_PrPostDeyt</t>
+          <t>MO_30851_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>OKVED_B_PrPostDeyt</t>
+          <t>MO_30851_TeRosUbyV%_1</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>OKVED_07_PrPostDeyt</t>
+          <t>MO_30501_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPostDeyt</t>
+          <t>MO_30501_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>OKVED_32_ArendPlDeVsego</t>
+          <t>MO_30501_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>OKVED_32_PrPostDeyt</t>
+          <t>MO_30510_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPostDeyt</t>
+          <t>MO_30510_SumPriZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>OKVED_35_PrPostDeyt</t>
+          <t>MO_30510_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>OKVED_35_PrPostDeyt</t>
+          <t>MO_30604_PriUby(-DoNalZaAnaPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>OKVED_E_ArendPlDeVsego</t>
+          <t>MO_30604_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>OKVED_36_ArendPlDeVsego</t>
+          <t>MO_30604_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>OKVED_38_ArendPlDeVsego</t>
+          <t>MO_30604_SumPriZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>OKVED_41_ArendPlDeVsego</t>
+          <t>MO_30604_TeRosUbyV%_1</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>OKVED_43_ArendPlDeVsego</t>
+          <t>MO_30604_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPostDeyt</t>
+          <t>MO_30616_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>OKVED_G_PrPostDeyt</t>
+          <t>MO_30619_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>OKVED_46_PrPostDeyt</t>
+          <t>MO_30832_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>OKVED_47_PrPostDeyt</t>
+          <t>OKVED_56_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>OKVED_H_PrPostDeyt</t>
+          <t>OKVED_J_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>OKVED_49_ArendPlDeVsego</t>
+          <t>OKVED_J_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPostDeyt</t>
+          <t>OKVED_J_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>OKVED_50_ArendPlDeVsego</t>
+          <t>OKVED_63_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>OKVED_50_PrPostDeyt</t>
+          <t>OKVED_63_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>OKVED_51_PrPostDeyt</t>
+          <t>OKVED_63_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>OKVED_52_PrPostDeyt</t>
+          <t>OKVED_74_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>OKVED_I_ArendPlDeVsego</t>
+          <t>OKVED_81_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>OKVED_55_ArendPlDeVsego</t>
+          <t>OKVED_82_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>OKVED_56_ArendPlDeVsego</t>
+          <t>OKVED_O_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>OKVED_56_PrPostDeyt</t>
+          <t>OKVED_84_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>OKVED_J_OtProdDeVsego</t>
+          <t>OKVED_85_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>OKVED_J_ArendPlDeVsego</t>
+          <t>OKVED_Q_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>OKVED_J_PrPostDeyt</t>
+          <t>OKVED_Q_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>OKVED_63_OtProdDeVsego</t>
+          <t>OKVED_Q_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t>OKVED_63_ArendPlDeVsego</t>
+          <t>OKVED_88_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t>OKVED_63_PrPostDeyt</t>
+          <t>OKVED_88_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t>OKVED_K_ArendPlDeVsego</t>
+          <t>OKVED_88_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPostDeyt</t>
+          <t>OKVED_R_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t>OKVED_64_ArendPlDeVsego</t>
+          <t>OKVED_R_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPostDeyt</t>
+          <t>OKVED_93_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>OKVED_M_PrPostDeyt</t>
+          <t>OKVED_93_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>OKVED_69_ArendPlDeVsego</t>
+          <t>OKVED_56_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t>OKVED_69_PrPostDeyt</t>
+          <t>OKVED_O_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPostDeyt</t>
+          <t>OKVED_84_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>OKVED_71_PrPostDeyt</t>
+          <t>OKVED_11_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>OKVED_74_PrPostDeyt</t>
+          <t>OKVED_43_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
-          <t>OKVED_77_PrPostDeyt</t>
+          <t>OKVED_49_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>OKVED_79_ArendPlDeVsego</t>
+          <t>OKVED_56_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>OKVED_81_ArendPlDeVsego</t>
+          <t>OKVED_56_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t>OKVED_81_PrPostDeyt</t>
+          <t>OKVED_69_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>OKVED_82_ArendPlDeVsego</t>
+          <t>OKVED_69_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>OKVED_82_PrPostDeyt</t>
+          <t>OKVED_74_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>OKVED_O_ArendPlDeVsego</t>
+          <t>OKVED_81_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>OKVED_O_PrPostDeyt</t>
+          <t>OKVED_81_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>OKVED_84_ArendPlDeVsego</t>
+          <t>OKVED_82_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>OKVED_84_PrPostDeyt</t>
+          <t>OKVED_82_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_O_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPostDeyt</t>
+          <t>OKVED_O_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPostDeyt</t>
+          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="inlineStr">
         <is>
-          <t>OKVED_Q_OtProdDeVsego</t>
+          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>OKVED_Q_ArendPlDeVsego</t>
+          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>OKVED_Q_PrPostDeyt</t>
+          <t>OKVED_R_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>OKVED_88_OtProdDeVsego</t>
+          <t>OKVED_R_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>OKVED_88_ArendPlDeVsego</t>
+          <t>OKVED_93_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>OKVED_88_PrPostDeyt</t>
+          <t>OKVED_93_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>OKVED_R_OtProdDeVsego</t>
+          <t>OKVED_94_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>OKVED_R_ArendPlDeVsego</t>
+          <t>OKVED_96_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>OKVED_R_PrPostDeyt</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>OKVED_93_OtProdDeVsego</t>
+          <t>OKVED_01_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>OKVED_93_ArendPlDeVsego</t>
+          <t>OKVED_01_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>OKVED_93_PrPostDeyt</t>
+          <t>OKVED_B_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>OKVED_S_ArendPlDeVsego</t>
+          <t>OKVED_07_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>OKVED_94_ArendPlDeVsego</t>
+          <t>OKVED_11_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>OKVED_96_ArendPlDeVsego</t>
+          <t>OKVED_32_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>OKVED_96_PrPostDeyt</t>
+          <t>OKVED_32_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcPoDolgObyaz</t>
+          <t>OKVED_33_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPoFin</t>
+          <t>OKVED_35_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>OKVED_32_ProcPoDolgObyaz</t>
+          <t>OKVED_E_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>OKVED_32_NalogNaPri</t>
+          <t>OKVED_36_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>OKVED_32_PrPoFin</t>
+          <t>OKVED_38_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>OKVED_33_NalogNaPri</t>
+          <t>OKVED_41_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_43_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcPoDolgObyaz</t>
+          <t>OKVED_43_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>OKVED_36_PrPoFin</t>
+          <t>OKVED_G_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>OKVED_38_NalogNaPri</t>
+          <t>OKVED_46_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPoFin</t>
+          <t>OKVED_H_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcPoDolgObyaz</t>
+          <t>OKVED_49_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPoFin</t>
+          <t>OKVED_49_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>OKVED_50_PrPoFin</t>
+          <t>OKVED_50_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>OKVED_I_PrPoFin</t>
+          <t>OKVED_50_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>OKVED_55_PrPoFin</t>
+          <t>OKVED_51_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>OKVED_56_ProcPoDolgObyaz</t>
+          <t>OKVED_52_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
         <is>
-          <t>OKVED_56_NalogNaPri</t>
+          <t>OKVED_I_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>OKVED_56_PrPoFin</t>
+          <t>OKVED_55_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>OKVED_J_ProcPoDolgObyaz</t>
+          <t>OKVED_56_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>OKVED_J_NalogNaPri</t>
+          <t>OKVED_56_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>OKVED_J_PrPoFin</t>
+          <t>OKVED_J_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>OKVED_63_ProcPoDolgObyaz</t>
+          <t>OKVED_J_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>OKVED_63_NalogNaPri</t>
+          <t>OKVED_J_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>OKVED_63_PrPoFin</t>
+          <t>OKVED_63_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPoFin</t>
+          <t>OKVED_63_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPoFin</t>
+          <t>OKVED_63_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>OKVED_M_ProcPoDolgObyaz</t>
+          <t>OKVED_64_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>OKVED_69_ProcPoDolgObyaz</t>
+          <t>OKVED_64_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>OKVED_69_NalogNaPri</t>
+          <t>OKVED_M_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>OKVED_69_PrPoFin</t>
+          <t>OKVED_69_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>OKVED_70_ProcPoDolgObyaz</t>
+          <t>OKVED_69_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPoFin</t>
+          <t>OKVED_70_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>OKVED_71_ProcPoDolgObyaz</t>
+          <t>OKVED_71_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>OKVED_71_NalogNaPri</t>
+          <t>OKVED_74_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>OKVED_74_ProcPoDolgObyaz</t>
+          <t>OKVED_79_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcPoDolgObyaz</t>
+          <t>OKVED_81_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>OKVED_77_PrPoFin</t>
+          <t>OKVED_81_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>OKVED_79_NalogNaPri</t>
+          <t>OKVED_82_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>OKVED_79_PrPoFin</t>
+          <t>OKVED_82_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>OKVED_81_NalogNaPri</t>
+          <t>OKVED_O_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>OKVED_82_ProcPoDolgObyaz</t>
+          <t>OKVED_O_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>OKVED_82_PrPoFin</t>
+          <t>OKVED_84_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_84_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>OKVED_O_VSvyaziSOplTrudRab</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>OKVED_O_ProcPoDolgObyaz</t>
+          <t>OKVED_85_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>OKVED_O_PrPoFin</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_85_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>OKVED_84_VSvyaziSOplTrudRab</t>
+          <t>OKVED_88_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>OKVED_84_ProcPoDolgObyaz</t>
+          <t>OKVED_88_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>OKVED_84_PrPoFin</t>
+          <t>OKVED_88_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_R_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_R_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPoFin</t>
+          <t>OKVED_R_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_93_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_93_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPoFin</t>
+          <t>OKVED_93_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>OKVED_Q_ProcPoDolgObyaz</t>
+          <t>OKVED_S_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>OKVED_Q_NalogNaPri</t>
+          <t>OKVED_94_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>OKVED_Q_PrPoFin</t>
+          <t>OKVED_96_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>OKVED_86_PlatPoTekDeVsego</t>
+          <t>OKVED_96_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>OKVED_86_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_11_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>OKVED_86_VSvyaziSOplTrudRab</t>
+          <t>OKVED_11_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>OKVED_86_ProcPoDolgObyaz</t>
+          <t>OKVED_32_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>OKVED_86_NalogNaPri</t>
+          <t>OKVED_32_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>OKVED_86_PrPoFin</t>
+          <t>OKVED_32_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>OKVED_86_SaldoDenPotTekOper</t>
+          <t>OKVED_33_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_33_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>OKVED_R_VSvyaziSOplTrudRab</t>
+          <t>OKVED_36_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>OKVED_R_ProcPoDolgObyaz</t>
+          <t>OKVED_36_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>OKVED_R_NalogNaPri</t>
+          <t>OKVED_38_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>OKVED_R_PrPoFin</t>
+          <t>OKVED_43_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_49_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>OKVED_93_VSvyaziSOplTrudRab</t>
+          <t>OKVED_49_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>OKVED_93_ProcPoDolgObyaz</t>
+          <t>OKVED_50_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>OKVED_93_NalogNaPri</t>
+          <t>OKVED_I_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>OKVED_93_PrPoFin</t>
+          <t>OKVED_56_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>OKVED_96_ProcPoDolgObyaz</t>
+          <t>OKVED_56_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>OKVED_96_NalogNaPri</t>
+          <t>OKVED_56_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>OKVED_96_PrPoFin</t>
+          <t>OKVED_J_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_J_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdAkcOrgDolUch</t>
+          <t>OKVED_J_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>OKVED_01_DivProcDolgFinVlozh</t>
+          <t>OKVED_63_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>OKVED_01_PrPostDeyt</t>
+          <t>OKVED_63_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>OKVED_B_OtProdAkcOrgDolUch</t>
+          <t>OKVED_63_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>OKVED_B_PrPostDeyt</t>
+          <t>OKVED_K_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>OKVED_07_OtProdAkcOrgDolUch</t>
+          <t>OKVED_64_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>OKVED_07_PrPostDeyt</t>
+          <t>OKVED_M_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>OKVED_C_OtProdAkcOrgDolUch</t>
+          <t>OKVED_69_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>OKVED_10_OtProdAkcOrgDolUch</t>
+          <t>OKVED_69_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_69_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdAkcOrgDolUch</t>
+          <t>OKVED_71_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdFinVlozh</t>
+          <t>OKVED_71_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPostDeyt</t>
+          <t>OKVED_74_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>OKVED_33_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_77_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>OKVED_33_OtProdAkcOrgDolUch</t>
+          <t>OKVED_77_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>OKVED_33_DivProcDolgFinVlozh</t>
+          <t>OKVED_79_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPostDeyt</t>
+          <t>OKVED_79_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_81_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>OKVED_35_PrPostDeyt</t>
+          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_O_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>OKVED_35_PrPostDeyt</t>
+          <t>OKVED_O_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdAkcOrgDolUch</t>
+          <t>OKVED_O_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdFinVlozh</t>
+          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>OKVED_E_DivProcDolgFinVlozh</t>
+          <t>OKVED_84_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdAkcOrgDolUch</t>
+          <t>OKVED_84_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdFinVlozh</t>
+          <t>OKVED_84_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>OKVED_36_DivProcDolgFinVlozh</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdAkcOrgDolUch</t>
+          <t>OKVED_85_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdFinVlozh</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>OKVED_38_DivProcDolgFinVlozh</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_85_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdAkcOrgDolUch</t>
+          <t>OKVED_Q_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_Q_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdAkcOrgDolUch</t>
+          <t>OKVED_Q_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>OKVED_42_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>OKVED_42_OtProdAkcOrgDolUch</t>
+          <t>OKVED_R_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_R_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdAkcOrgDolUch</t>
+          <t>OKVED_R_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdFinVlozh</t>
+          <t>OKVED_R_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPostDeyt</t>
+          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>OKVED_G_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>OKVED_G_PrPostDeyt</t>
+          <t>OKVED_93_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>OKVED_46_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>OKVED_46_PrPostDeyt</t>
+          <t>OKVED_93_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>OKVED_47_OtProdAkcOrgDolUch</t>
+          <t>OKVED_96_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>OKVED_47_PrPostDeyt</t>
+          <t>OKVED_96_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>OKVED_H_OtProdAkcOrgDolUch</t>
+          <t>OKVED_96_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>OKVED_H_PrPostDeyt</t>
+          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_01_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>OKVED_49_DivProcDolgFinVlozh</t>
+          <t>OKVED_01_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPostDeyt</t>
+          <t>OKVED_B_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>OKVED_51_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_B_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>OKVED_51_OtProdAkcOrgDolUch</t>
+          <t>OKVED_07_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>OKVED_51_PrPostDeyt</t>
+          <t>OKVED_07_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>OKVED_52_OtProdAkcOrgDolUch</t>
+          <t>OKVED_C_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>OKVED_52_PrPostDeyt</t>
+          <t>OKVED_10_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdAkcOrgDolUch</t>
+          <t>OKVED_11_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_11_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdAkcOrgDolUch</t>
+          <t>OKVED_11_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdAkcOrgDolUch</t>
+          <t>OKVED_35_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPostDeyt</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_35_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdAkcOrgDolUch</t>
+          <t>OKVED_E_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPostDeyt</t>
+          <t>OKVED_E_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>OKVED_L_OtProdAkcOrgDolUch</t>
+          <t>OKVED_E_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>OKVED_68_OtProdAkcOrgDolUch</t>
+          <t>OKVED_36_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_36_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdAkcOrgDolUch</t>
+          <t>OKVED_36_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>OKVED_M_PrPostDeyt</t>
+          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_38_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPostDeyt</t>
+          <t>OKVED_38_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdAkcOrgDolUch</t>
+          <t>OKVED_F_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>OKVED_71_DivProcDolgFinVlozh</t>
+          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>OKVED_71_PrPostDeyt</t>
+          <t>OKVED_41_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdFinVlozh</t>
+          <t>OKVED_43_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdFinVlozh</t>
+          <t>OKVED_43_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>OKVED_77_PrPostDeyt</t>
+          <t>OKVED_G_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>OKVED_79_OtProdAkcOrgDolUch</t>
+          <t>OKVED_G_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>OKVED_79_OtProdFinVlozh</t>
+          <t>OKVED_46_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>OKVED_79_DivProcDolgFinVlozh</t>
+          <t>OKVED_46_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_47_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdAkcOrgDolUch</t>
+          <t>OKVED_47_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>OKVED_S_DivProcDolgFinVlozh</t>
+          <t>OKVED_H_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_H_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdAkcOrgDolUch</t>
+          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>OKVED_94_DivProcDolgFinVlozh</t>
+          <t>OKVED_49_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>OKVED_01_DolUch</t>
+          <t>OKVED_49_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_49_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>OKVED_B_DolUch</t>
+          <t>OKVED_52_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_52_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>OKVED_07_DolUch</t>
+          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>OKVED_07_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_I_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>OKVED_C_DolUch</t>
+          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_55_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>OKVED_10_DolUch</t>
+          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_K_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>OKVED_11_DolUch</t>
+          <t>OKVED_K_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>OKVED_11_PrCenBum</t>
+          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_64_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPoFin</t>
+          <t>OKVED_64_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>OKVED_33_DolUch</t>
+          <t>OKVED_L_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_M_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>OKVED_E_DolUch</t>
+          <t>OKVED_M_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>OKVED_E_PrCenBum</t>
+          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_70_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>OKVED_36_DolUch</t>
+          <t>OKVED_70_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>OKVED_36_PrCenBum</t>
+          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_71_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>OKVED_36_PrPoFin</t>
+          <t>OKVED_71_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>OKVED_38_DolUch</t>
+          <t>OKVED_71_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>OKVED_38_PrCenBum</t>
+          <t>OKVED_N_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>OKVED_38_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_N_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>OKVED_F_DolUch</t>
+          <t>OKVED_77_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_77_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>OKVED_41_DolUch</t>
+          <t>OKVED_77_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>OKVED_42_DolUch</t>
+          <t>OKVED_S_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_S_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>OKVED_43_DolUch</t>
+          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>OKVED_43_PrCenBum</t>
+          <t>OKVED_94_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_94_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPoFin</t>
+          <t>OKVED_01_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>OKVED_46_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_01_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>OKVED_47_DolUch</t>
+          <t>OKVED_B_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>OKVED_H_DolUch</t>
+          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_C_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>OKVED_49_DolUch</t>
+          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_10_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPoFin</t>
+          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>OKVED_50_DolUch</t>
+          <t>OKVED_11_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>OKVED_50_PrCenBum</t>
+          <t>OKVED_11_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>OKVED_50_PrPoFin</t>
+          <t>OKVED_11_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>OKVED_51_DolUch</t>
+          <t>OKVED_33_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>OKVED_51_PrCenBum</t>
+          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>OKVED_51_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_33_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>OKVED_52_DolUch</t>
+          <t>OKVED_E_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_E_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>OKVED_I_PrPoFin</t>
+          <t>OKVED_36_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_36_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>OKVED_55_PrPoFin</t>
+          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>OKVED_K_DolUch</t>
+          <t>OKVED_36_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_F_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPoFin</t>
+          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>OKVED_64_DolUch</t>
+          <t>OKVED_41_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>OKVED_64_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPoFin</t>
+          <t>OKVED_42_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>OKVED_M_DolUch</t>
+          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>OKVED_70_DolUch</t>
+          <t>OKVED_43_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>OKVED_70_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_43_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPoFin</t>
+          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>OKVED_71_DolUch</t>
+          <t>OKVED_43_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>OKVED_N_DolUch</t>
+          <t>OKVED_47_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>OKVED_N_PrCenBum</t>
+          <t>OKVED_H_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>OKVED_77_DolUch</t>
+          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>OKVED_77_PrCenBum</t>
+          <t>OKVED_49_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>OKVED_77_PrPoFin</t>
+          <t>OKVED_49_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>OKVED_79_DolUch</t>
+          <t>OKVED_50_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>OKVED_79_PrCenBum</t>
+          <t>OKVED_50_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>OKVED_79_PrPoFin</t>
+          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>OKVED_S_DolUch</t>
+          <t>OKVED_50_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_52_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>OKVED_94_DolUch</t>
+          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>OKVED_01_PostDeyt1</t>
+          <t>OKVED_I_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>OKVED_01_DrPost</t>
+          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt</t>
+          <t>OKVED_55_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt1</t>
+          <t>OKVED_K_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt</t>
+          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt1</t>
+          <t>OKVED_K_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>OKVED_C_PostDeyt1</t>
+          <t>OKVED_M_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>OKVED_10_PostDeyt1</t>
+          <t>OKVED_71_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>OKVED_32_PlCredit</t>
+          <t>OKVED_N_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt</t>
+          <t>OKVED_N_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt1</t>
+          <t>OKVED_79_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt</t>
+          <t>OKVED_79_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt1</t>
+          <t>OKVED_79_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>OKVED_33_DrPost</t>
+          <t>OKVED_S_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_94_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>OKVED_E_PostDeyt1</t>
+          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>OKVED_E_DrPost</t>
+          <t>OKVED_01_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>OKVED_38_PostDeyt1</t>
+          <t>OKVED_01_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>OKVED_38_DrPost</t>
+          <t>OKVED_B_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>OKVED_F_PostDeyt1</t>
+          <t>OKVED_B_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt</t>
+          <t>OKVED_07_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt1</t>
+          <t>OKVED_07_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt</t>
+          <t>OKVED_C_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt1</t>
+          <t>OKVED_10_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>OKVED_42_DrPost</t>
+          <t>OKVED_32_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>OKVED_43_PostDeyt1</t>
+          <t>OKVED_32_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>OKVED_43_DrPost</t>
+          <t>OKVED_32_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt</t>
+          <t>OKVED_33_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt1</t>
+          <t>OKVED_33_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt</t>
+          <t>OKVED_33_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt1</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt1</t>
+          <t>OKVED_38_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>OKVED_H_PostDeyt1</t>
+          <t>OKVED_38_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>OKVED_49_PostDeyt</t>
+          <t>OKVED_F_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>OKVED_49_PostDeyt1</t>
+          <t>OKVED_41_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt</t>
+          <t>OKVED_41_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt1</t>
+          <t>OKVED_42_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>OKVED_50_DrPost</t>
+          <t>OKVED_42_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt</t>
+          <t>OKVED_42_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt1</t>
+          <t>OKVED_43_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>OKVED_51_DrPost</t>
+          <t>OKVED_43_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>OKVED_52_PostDeyt1</t>
+          <t>OKVED_G_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>OKVED_I_PostDeyt1</t>
+          <t>OKVED_G_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>OKVED_I_DrPost</t>
+          <t>OKVED_46_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>OKVED_55_PostDeyt1</t>
+          <t>OKVED_46_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>OKVED_55_DrPost</t>
+          <t>OKVED_47_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt</t>
+          <t>OKVED_47_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt1</t>
+          <t>OKVED_H_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>OKVED_K_DrPost</t>
+          <t>OKVED_50_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt</t>
+          <t>OKVED_50_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt1</t>
+          <t>OKVED_50_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>OKVED_64_DrPost</t>
+          <t>OKVED_51_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>OKVED_L_PostDeyt1</t>
+          <t>OKVED_51_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>OKVED_68_PostDeyt1</t>
+          <t>OKVED_51_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>OKVED_M_PostDeyt</t>
+          <t>OKVED_52_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>OKVED_70_PlCredit</t>
+          <t>OKVED_I_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>OKVED_70_PostDeyt</t>
+          <t>OKVED_I_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>OKVED_71_PostDeyt</t>
+          <t>OKVED_55_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt</t>
+          <t>OKVED_55_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt1</t>
+          <t>OKVED_K_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>OKVED_74_DrPost</t>
+          <t>OKVED_K_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt</t>
+          <t>OKVED_K_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt1</t>
+          <t>OKVED_64_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt</t>
+          <t>OKVED_64_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt1</t>
+          <t>OKVED_64_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>OKVED_79_DrPost</t>
+          <t>OKVED_L_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>OKVED_81_PlCredit</t>
+          <t>OKVED_68_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt</t>
+          <t>OKVED_70_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt1</t>
+          <t>OKVED_70_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>OKVED_S_PlCredit</t>
+          <t>OKVED_71_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>OKVED_S_PostDeyt1</t>
+          <t>OKVED_74_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>OKVED_94_PlCredit</t>
+          <t>OKVED_74_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>OKVED_94_PostDeyt1</t>
+          <t>OKVED_74_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin1</t>
+          <t>OKVED_N_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin2</t>
+          <t>OKVED_N_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>OKVED_B_PlPoFin1</t>
+          <t>OKVED_79_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>OKVED_07_PlPoFin1</t>
+          <t>OKVED_79_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin</t>
+          <t>OKVED_79_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin1</t>
+          <t>OKVED_81_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin2</t>
+          <t>OKVED_81_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin3</t>
+          <t>OKVED_81_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>OKVED_32_PrPoFin</t>
+          <t>OKVED_S_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin</t>
+          <t>OKVED_S_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin1</t>
+          <t>OKVED_94_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin2</t>
+          <t>OKVED_94_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin3</t>
+          <t>OKVED_01_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_01_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_B_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_07_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>OKVED_F_PlPoFin1</t>
+          <t>OKVED_33_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>OKVED_41_PlPoFin1</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>OKVED_42_PlPoFin1</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin1</t>
+          <t>OKVED_E_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin2</t>
+          <t>OKVED_E_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPoFin</t>
+          <t>OKVED_38_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>OKVED_G_PlPoFin1</t>
+          <t>OKVED_38_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>OKVED_46_PlPoFin1</t>
+          <t>OKVED_F_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>OKVED_47_PlPoFin1</t>
+          <t>OKVED_41_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>OKVED_H_PlPoFin1</t>
+          <t>OKVED_43_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin1</t>
+          <t>OKVED_43_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin2</t>
+          <t>OKVED_43_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPoFin</t>
+          <t>OKVED_G_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoFin1</t>
+          <t>OKVED_46_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>OKVED_50_PrPoFin</t>
+          <t>OKVED_47_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>OKVED_51_PlPoFin1</t>
+          <t>OKVED_H_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>OKVED_51_PlPoFin2</t>
+          <t>OKVED_49_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>OKVED_52_PlPoFin1</t>
+          <t>OKVED_49_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin1</t>
+          <t>OKVED_49_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin2</t>
+          <t>OKVED_50_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>OKVED_I_PrPoFin</t>
+          <t>OKVED_50_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin1</t>
+          <t>OKVED_52_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin2</t>
+          <t>OKVED_I_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>OKVED_55_PrPoFin</t>
+          <t>OKVED_I_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoFin1</t>
+          <t>OKVED_I_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPoFin</t>
+          <t>OKVED_55_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoFin1</t>
+          <t>OKVED_55_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPoFin</t>
+          <t>OKVED_55_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>OKVED_L_PlPoFin1</t>
+          <t>OKVED_K_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>OKVED_68_PlPoFin1</t>
+          <t>OKVED_K_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>OKVED_M_PlPoFin1</t>
+          <t>OKVED_64_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin</t>
+          <t>OKVED_64_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin1</t>
+          <t>OKVED_68_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin2</t>
+          <t>OKVED_M_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin3</t>
+          <t>OKVED_70_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPoFin</t>
+          <t>OKVED_70_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>OKVED_71_PlPoFin1</t>
+          <t>OKVED_70_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin1</t>
+          <t>OKVED_70_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin2</t>
+          <t>OKVED_70_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin3</t>
+          <t>OKVED_71_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>OKVED_74_SaldoDenPot</t>
+          <t>OKVED_74_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
         <is>
-          <t>OKVED_N_PlPoFin1</t>
+          <t>OKVED_74_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>OKVED_N_PlPoFin2</t>
+          <t>OKVED_74_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin1</t>
+          <t>OKVED_74_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin2</t>
+          <t>OKVED_79_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>OKVED_79_PrPoFin</t>
+          <t>OKVED_79_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin1</t>
+          <t>OKVED_79_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin2</t>
+          <t>OKVED_81_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin3</t>
+          <t>OKVED_81_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>OKVED_81_SaldoDenPot</t>
+          <t>OKVED_81_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin1</t>
+          <t>OKVED_81_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin2</t>
+          <t>OKVED_S_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin3</t>
+          <t>OKVED_S_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin1</t>
+          <t>OKVED_S_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin2</t>
+          <t>OKVED_94_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin3</t>
+          <t>OKVED_94_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
         <is>
-          <t>OKVED_01_Velch</t>
+          <t>OKVED_94_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
         <is>
-          <t>OKVED_11_Velch</t>
+          <t>OKVED_01_Velch</t>
         </is>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>OKVED_32_Velch</t>
+          <t>OKVED_11_Velch</t>
         </is>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
         <is>
-          <t>OKVED_33_Velch</t>
+          <t>OKVED_32_Velch</t>
         </is>
       </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
         <is>
-          <t>OKVED_E_Velch</t>
+          <t>OKVED_33_Velch</t>
         </is>
       </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
         <is>
-          <t>OKVED_36_Velch</t>
+          <t>OKVED_E_Velch</t>
         </is>
       </c>
     </row>
@@ -12060,350 +12060,329 @@
     <row r="1664">
       <c r="A1664" t="inlineStr">
         <is>
-          <t>OKVED_55_Velch</t>
+          <t>OKVED_56_Velch</t>
         </is>
       </c>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
         <is>
-          <t>OKVED_56_Velch</t>
+          <t>OKVED_J_Velch</t>
         </is>
       </c>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>OKVED_J_Velch</t>
+          <t>OKVED_63_Velch</t>
         </is>
       </c>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>OKVED_63_Velch</t>
+          <t>OKVED_L_Velch</t>
         </is>
       </c>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
         <is>
-          <t>OKVED_L_Velch</t>
+          <t>OKVED_68_Velch</t>
         </is>
       </c>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
         <is>
-          <t>OKVED_68_Velch</t>
+          <t>OKVED_M_Velch</t>
         </is>
       </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>OKVED_M_Velch</t>
+          <t>OKVED_69_Velch</t>
         </is>
       </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>OKVED_69_Velch</t>
+          <t>OKVED_70_Velch</t>
         </is>
       </c>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>OKVED_70_Velch</t>
+          <t>OKVED_71_Velch</t>
         </is>
       </c>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>OKVED_71_Velch</t>
+          <t>OKVED_N_Velch</t>
         </is>
       </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
         <is>
-          <t>OKVED_74_Velch</t>
+          <t>OKVED_77_Velch</t>
         </is>
       </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
         <is>
-          <t>OKVED_N_Velch</t>
+          <t>OKVED_79_Velch</t>
         </is>
       </c>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>OKVED_77_Velch</t>
+          <t>OKVED_81_Velch</t>
         </is>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
         <is>
-          <t>OKVED_79_Velch</t>
+          <t>OKVED_82_Velch</t>
         </is>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
         <is>
-          <t>OKVED_81_Velch</t>
+          <t>OKVED_O_Velch</t>
         </is>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
         <is>
-          <t>OKVED_82_Velch</t>
+          <t>OKVED_84_Velch</t>
         </is>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
         <is>
-          <t>OKVED_O_Velch</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>OKVED_84_Velch</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_88_Velch</t>
         </is>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_R_Velch</t>
         </is>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>OKVED_Q_Velch</t>
+          <t>OKVED_93_Velch</t>
         </is>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>OKVED_88_Velch</t>
+          <t>OKVED_S_Velch</t>
         </is>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>OKVED_R_Velch</t>
+          <t>OKVED_94_Velch</t>
         </is>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>OKVED_93_Velch</t>
+          <t>OKVED_96_Velch</t>
         </is>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>OKVED_S_Velch</t>
+          <t>OKVED_43_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>OKVED_94_Velch</t>
+          <t>OKVED_43_ChiAkt</t>
         </is>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>OKVED_96_Velch</t>
+          <t>OKVED_J_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>OKVED_43_UstKap_23</t>
+          <t>OKVED_J_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>OKVED_43_ChiAkt_23</t>
+          <t>OKVED_J_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap_23</t>
+          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap_24</t>
+          <t>OKVED_63_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap_23</t>
+          <t>OKVED_63_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1696">
       <c r="A1696" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap_24</t>
+          <t>OKVED_63_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1697">
       <c r="A1697" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap_23</t>
+          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1698">
       <c r="A1698" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap_24</t>
+          <t>OKVED_69_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1699">
       <c r="A1699" t="inlineStr">
         <is>
-          <t>OKVED_69_ChiAkt_23</t>
+          <t>OKVED_69_ChiAkt</t>
         </is>
       </c>
     </row>
     <row r="1700">
       <c r="A1700" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap_23</t>
+          <t>OKVED_O_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1701">
       <c r="A1701" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap_24</t>
+          <t>OKVED_84_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1702">
       <c r="A1702" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap_23</t>
+          <t>OKVED_85_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1703">
       <c r="A1703" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap_24</t>
+          <t>OKVED_Q_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1704">
       <c r="A1704" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_23</t>
+          <t>OKVED_Q_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1705">
       <c r="A1705" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_24</t>
+          <t>OKVED_Q_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1706">
       <c r="A1706" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_23</t>
+          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1707">
       <c r="A1707" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_24</t>
+          <t>OKVED_88_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1708">
       <c r="A1708" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap_23</t>
+          <t>OKVED_88_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1709">
       <c r="A1709" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap_24</t>
+          <t>OKVED_88_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1710">
       <c r="A1710" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap_23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1711">
-      <c r="A1711" t="inlineStr">
-        <is>
-          <t>OKVED_88_UstKap_24</t>
-        </is>
-      </c>
-    </row>
-    <row r="1712">
-      <c r="A1712" t="inlineStr">
-        <is>
-          <t>OKVED_R_UstKap_24</t>
-        </is>
-      </c>
-    </row>
-    <row r="1713">
-      <c r="A1713" t="inlineStr">
-        <is>
-          <t>OKVED_93_UstKap_24</t>
+          <t>OKVED_88_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1710"/>
+  <dimension ref="A1:A1758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7510,4877 +7510,5213 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>OKVED_32_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_11_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>OKVED_42_OrgPolPriKolOrgEdi</t>
+          <t>OKVED_11_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>OKVED_42_OrgPolPriV%KObsKol</t>
+          <t>OKVED_32_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>OKVED_42_OrgPolPriPriDoNal</t>
+          <t>OKVED_32_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>OKVED_43_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_32_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>OKVED_43_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_42_OrgPolPriKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>OKVED_43_OrgPolUbyUby</t>
+          <t>OKVED_42_OrgPolPriV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>OKVED_49_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_42_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>OKVED_49_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_43_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>OKVED_49_OrgPolUbyUby</t>
+          <t>OKVED_43_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>OKVED_50_OrgPolPriKolOrgEdi</t>
+          <t>OKVED_43_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>OKVED_50_OrgPolPriV%KObsKol</t>
+          <t>OKVED_49_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>OKVED_50_OrgPolPriPriDoNal</t>
+          <t>OKVED_49_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>OKVED_51_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_49_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>OKVED_51_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_51_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>OKVED_51_OrgPolUbyUby</t>
+          <t>OKVED_51_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>OKVED_56_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_51_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>OKVED_56_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_56_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>OKVED_56_OrgPolUbyUby</t>
+          <t>OKVED_56_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-DoNal</t>
+          <t>OKVED_56_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>OKVED_J_OrgPolPriPriDoNal</t>
+          <t>OKVED_J_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>OKVED_J_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_J_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>OKVED_J_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_J_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>OKVED_J_OrgPolUbyUby</t>
+          <t>OKVED_J_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-DoNal</t>
+          <t>OKVED_J_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>OKVED_63_OrgPolPriPriDoNal</t>
+          <t>OKVED_63_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>OKVED_63_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_63_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>OKVED_63_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_63_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>OKVED_63_OrgPolUbyUby</t>
+          <t>OKVED_63_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>OKVED_69_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_63_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>OKVED_69_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_69_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>OKVED_69_OrgPolUbyUby</t>
+          <t>OKVED_69_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>OKVED_74_OrgPolPriKolOrgEdi</t>
+          <t>OKVED_69_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>OKVED_74_OrgPolPriV%KObsKol</t>
+          <t>OKVED_74_OrgPolPriKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>OKVED_74_OrgPolPriPriDoNal</t>
+          <t>OKVED_74_OrgPolPriV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>OKVED_79_OrgPolPriKolOrgEdi</t>
+          <t>OKVED_74_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>OKVED_79_OrgPolPriV%KObsKol</t>
+          <t>OKVED_79_OrgPolPriKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>OKVED_79_OrgPolPriPriDoNal</t>
+          <t>OKVED_79_OrgPolPriV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>OKVED_81_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_79_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>OKVED_81_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_81_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>OKVED_81_OrgPolUbyUby</t>
+          <t>OKVED_81_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>OKVED_O_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_81_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>OKVED_O_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_O_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>OKVED_O_OrgPolUbyUby</t>
+          <t>OKVED_O_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>OKVED_84_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_O_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>OKVED_84_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_84_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>OKVED_84_OrgPolUbyUby</t>
+          <t>OKVED_84_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_84_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_85_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyUby</t>
+          <t>OKVED_85_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_85_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_85_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyUby</t>
+          <t>OKVED_85_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-DoNal</t>
+          <t>OKVED_85_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>OKVED_Q_OrgPolPriPriDoNal</t>
+          <t>OKVED_Q_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>OKVED_Q_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_Q_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>OKVED_Q_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_Q_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>OKVED_Q_OrgPolUbyUby</t>
+          <t>OKVED_Q_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-DoNal</t>
+          <t>OKVED_Q_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>OKVED_88_OrgPolPriPriDoNal</t>
+          <t>OKVED_88_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>OKVED_88_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_88_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>OKVED_88_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_88_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>OKVED_88_OrgPolUbyUby</t>
+          <t>OKVED_88_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>OKVED_93_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_88_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>OKVED_93_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_93_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>OKVED_93_OrgPolUbyUby</t>
+          <t>OKVED_93_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>OKVED_94_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_93_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>OKVED_94_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_94_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>OKVED_94_OrgPolUbyUby</t>
+          <t>OKVED_94_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>OKVED_01_TeRosPriV%</t>
+          <t>OKVED_94_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>OKVED_10_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_01_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>OKVED_11_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_10_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>OKVED_11_TeRosUbyV%</t>
+          <t>OKVED_11_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>OKVED_32_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_11_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>OKVED_32_TeRosUbyV%</t>
+          <t>OKVED_32_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>OKVED_38_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_32_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>OKVED_F_TeRosPriV%</t>
+          <t>OKVED_38_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>OKVED_41_TeRosPriV%</t>
+          <t>OKVED_F_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>OKVED_41_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_41_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>OKVED_42_TeRosPriV%</t>
+          <t>OKVED_41_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>OKVED_42_TeRosSumPriV%</t>
+          <t>OKVED_42_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>OKVED_43_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_42_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>OKVED_43_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_43_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>OKVED_43_SumPriZaSooPerPreGo</t>
+          <t>OKVED_43_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>OKVED_43_TeRosUbyV%</t>
+          <t>OKVED_43_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>OKVED_49_TeRosUbyV%</t>
+          <t>OKVED_43_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>OKVED_50_TeRosPriV%</t>
+          <t>OKVED_49_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>OKVED_50_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_50_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>OKVED_50_TeRosSumPriV%</t>
+          <t>OKVED_50_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>OKVED_51_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_50_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>OKVED_51_TeRosUbyV%</t>
+          <t>OKVED_51_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>OKVED_I_TeRosPriV%</t>
+          <t>OKVED_51_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>OKVED_55_TeRosPriV%</t>
+          <t>OKVED_I_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>OKVED_55_SumPriZaSooPerPreGo</t>
+          <t>OKVED_55_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>OKVED_56_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_55_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>OKVED_56_TeRosUbyV%</t>
+          <t>OKVED_56_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>OKVED_L_TeRosPriV%</t>
+          <t>OKVED_56_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>OKVED_68_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_L_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>OKVED_68_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_68_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>OKVED_68_SumPriZaSooPerPreGo</t>
+          <t>OKVED_68_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>OKVED_68_TeRosUbyV%</t>
+          <t>OKVED_68_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>OKVED_M_TeRosPriV%</t>
+          <t>OKVED_68_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>OKVED_69_TeRosPriV%</t>
+          <t>OKVED_M_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>OKVED_70_TeRosPriV%</t>
+          <t>OKVED_69_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>OKVED_70_SumPriZaSooPerPreGo</t>
+          <t>OKVED_70_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>OKVED_70_TeRosSumPriV%</t>
+          <t>OKVED_70_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>OKVED_71_TeRosPriV%</t>
+          <t>OKVED_70_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>OKVED_74_TeRosPriV%</t>
+          <t>OKVED_71_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>OKVED_77_TeRosPriV%</t>
+          <t>OKVED_74_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>OKVED_77_SumPriZaSooPerPreGo</t>
+          <t>OKVED_77_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>OKVED_77_TeRosUbyV%</t>
+          <t>OKVED_77_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>OKVED_79_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_77_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>OKVED_79_TeRosUbyV%</t>
+          <t>OKVED_79_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>OKVED_81_TeRosPriV%</t>
+          <t>OKVED_79_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>OKVED_81_SumPriZaSooPerPreGo</t>
+          <t>OKVED_81_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>OKVED_81_TeRosUbyV%</t>
+          <t>OKVED_81_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>OKVED_82_TeRosPriV%</t>
+          <t>OKVED_81_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>OKVED_82_SumPriZaSooPerPreGo</t>
+          <t>OKVED_82_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>OKVED_82_TeRosUbyV%</t>
+          <t>OKVED_82_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>OKVED_O_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_82_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>OKVED_O_TeRosUbyV%</t>
+          <t>OKVED_O_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_O_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosPriV%</t>
+          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_85_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>OKVED_85_SumPriZaSooPerPreGo</t>
+          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosUbyV%</t>
+          <t>OKVED_85_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosSumPriV%</t>
+          <t>OKVED_85_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_85_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosPriV%</t>
+          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_85_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>OKVED_85_SumPriZaSooPerPreGo</t>
+          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosUbyV%</t>
+          <t>OKVED_85_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosSumPriV%</t>
+          <t>OKVED_85_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>OKVED_93_TeRosUbyV%</t>
+          <t>OKVED_85_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>OKVED_S_TeRosPriV%</t>
+          <t>OKVED_93_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>OKVED_94_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_S_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosPriV%</t>
+          <t>OKVED_94_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>OKVED_94_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_94_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>OKVED_94_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_94_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>OKVED_94_SumPriZaSooPerPreGo</t>
+          <t>OKVED_94_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosUbyV%</t>
+          <t>OKVED_94_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosSumPriV%</t>
+          <t>OKVED_94_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>OKVED_96_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_94_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosPriV%</t>
+          <t>OKVED_96_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>OKVED_96_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_96_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>OKVED_96_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_96_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>OKVED_96_SumPriZaSooPerPreGo</t>
+          <t>OKVED_96_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosUbyV%</t>
+          <t>OKVED_96_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosSumPriV%</t>
+          <t>OKVED_96_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>MO_30851_OrgPolUbyKolOrgEdi_1</t>
+          <t>OKVED_96_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>MO_30604_PriUby(-DoNal_1</t>
+          <t>MO_30851_OrgPolUbyKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolUbyKolOrgEdi_1</t>
+          <t>MO_30851_OrgPolUbyV%KObsKol_1</t>
         </is>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>MO_30851_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30851_OrgPolUbyUby_1</t>
         </is>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>MO_30851_TeRosUbyV%_1</t>
+          <t>MO_30501_OrgPolPriKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>MO_30501_TeRosPriV%_1</t>
+          <t>MO_30501_OrgPolPriV%KObsKol_1</t>
         </is>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>MO_30501_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30501_OrgPolPriPriDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>MO_30501_TeRosSumPriV%_1</t>
+          <t>MO_30510_OrgPolPriPriDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>MO_30510_TeRosPriV%_1</t>
+          <t>MO_30604_PriUby(-DoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>MO_30510_SumPriZaSooPerPreGo_1</t>
+          <t>MO_30604_OrgPolPriPriDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>MO_30510_TeRosSumPriV%_1</t>
+          <t>MO_30604_OrgPolUbyKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>MO_30604_PriUby(-DoNalZaAnaPerPreGo_1</t>
+          <t>MO_30604_OrgPolUbyV%KObsKol_1</t>
         </is>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosPriV%_1</t>
+          <t>MO_30604_OrgPolUbyUby_1</t>
         </is>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>MO_30604_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30851_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>MO_30604_SumPriZaSooPerPreGo_1</t>
+          <t>MO_30851_TeRosUbyV%_1</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosUbyV%_1</t>
+          <t>MO_30501_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosSumPriV%_1</t>
+          <t>MO_30501_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>MO_30616_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30501_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>MO_30619_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30510_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>MO_30832_TeRosPriV%_1</t>
+          <t>MO_30510_SumPriZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>OKVED_56_VToChiKomIUprRas</t>
+          <t>MO_30510_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-OtPro</t>
+          <t>MO_30604_PriUby(-DoNalZaAnaPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>OKVED_J_SebProSUchKomIUprRas</t>
+          <t>MO_30604_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>OKVED_J_VToChiKomIUprRas</t>
+          <t>MO_30604_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-OtPro</t>
+          <t>MO_30604_SumPriZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>OKVED_63_SebProSUchKomIUprRas</t>
+          <t>MO_30604_TeRosUbyV%_1</t>
         </is>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>OKVED_63_VToChiKomIUprRas</t>
+          <t>MO_30604_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>OKVED_74_VToChiKomIUprRas</t>
+          <t>MO_30616_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>OKVED_81_VToChiKomIUprRas</t>
+          <t>MO_30619_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>OKVED_82_VToChiKomIUprRas</t>
+          <t>MO_30832_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>OKVED_O_VToChiKomIUprRas</t>
+          <t>OKVED_56_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>OKVED_84_VToChiKomIUprRas</t>
+          <t>OKVED_J_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>OKVED_85_VToChiKomIUprRas</t>
+          <t>OKVED_J_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-OtPro</t>
+          <t>OKVED_J_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>OKVED_Q_SebProSUchKomIUprRas</t>
+          <t>OKVED_J_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>OKVED_Q_VToChiKomIUprRas</t>
+          <t>OKVED_J_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-OtPro</t>
+          <t>OKVED_J_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t>OKVED_88_SebProSUchKomIUprRas</t>
+          <t>OKVED_J_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t>OKVED_88_VToChiKomIUprRas</t>
+          <t>OKVED_63_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>OKVED_R_SebProSUchKomIUprRas</t>
+          <t>OKVED_63_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t>OKVED_R_VToChiKomIUprRas</t>
+          <t>OKVED_63_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>OKVED_93_SebProSUchKomIUprRas</t>
+          <t>OKVED_63_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>OKVED_93_VToChiKomIUprRas</t>
+          <t>OKVED_63_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>OKVED_56_VToChiKomIUprRas</t>
+          <t>OKVED_63_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t>OKVED_O_VToChiKomIUprRas</t>
+          <t>OKVED_63_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>OKVED_84_VToChiKomIUprRas</t>
+          <t>OKVED_74_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>OKVED_11_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_81_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>OKVED_43_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_82_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
-          <t>OKVED_49_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_O_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>OKVED_56_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_84_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>OKVED_56_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_85_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t>OKVED_69_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_Q_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>OKVED_69_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_Q_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>OKVED_74_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_Q_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>OKVED_81_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_Q_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>OKVED_81_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_Q_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>OKVED_82_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_Q_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>OKVED_82_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_Q_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>OKVED_O_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_88_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="inlineStr">
         <is>
-          <t>OKVED_O_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_88_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
         <is>
-          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_88_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_88_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="inlineStr">
         <is>
-          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_88_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_88_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>OKVED_R_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_88_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>OKVED_R_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_R_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>OKVED_93_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_R_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>OKVED_93_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_93_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>OKVED_94_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_93_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>OKVED_96_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_56_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
+          <t>OKVED_O_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>OKVED_01_ArendPlDeVsego</t>
+          <t>OKVED_84_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>OKVED_01_PrPostDeyt</t>
+          <t>OKVED_11_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>OKVED_B_PrPostDeyt</t>
+          <t>OKVED_43_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>OKVED_07_PrPostDeyt</t>
+          <t>OKVED_49_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPostDeyt</t>
+          <t>OKVED_56_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>OKVED_32_ArendPlDeVsego</t>
+          <t>OKVED_56_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>OKVED_32_PrPostDeyt</t>
+          <t>OKVED_69_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPostDeyt</t>
+          <t>OKVED_69_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>OKVED_35_PrPostDeyt</t>
+          <t>OKVED_74_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>OKVED_E_ArendPlDeVsego</t>
+          <t>OKVED_81_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>OKVED_36_ArendPlDeVsego</t>
+          <t>OKVED_81_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>OKVED_38_ArendPlDeVsego</t>
+          <t>OKVED_82_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>OKVED_41_ArendPlDeVsego</t>
+          <t>OKVED_82_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>OKVED_43_ArendPlDeVsego</t>
+          <t>OKVED_O_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPostDeyt</t>
+          <t>OKVED_O_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>OKVED_G_PrPostDeyt</t>
+          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>OKVED_46_PrPostDeyt</t>
+          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>OKVED_H_PrPostDeyt</t>
+          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="inlineStr">
         <is>
-          <t>OKVED_49_ArendPlDeVsego</t>
+          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPostDeyt</t>
+          <t>OKVED_R_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>OKVED_50_ArendPlDeVsego</t>
+          <t>OKVED_R_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>OKVED_50_PrPostDeyt</t>
+          <t>OKVED_93_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>OKVED_51_PrPostDeyt</t>
+          <t>OKVED_93_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>OKVED_52_PrPostDeyt</t>
+          <t>OKVED_94_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
         <is>
-          <t>OKVED_I_ArendPlDeVsego</t>
+          <t>OKVED_96_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>OKVED_55_ArendPlDeVsego</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>OKVED_56_ArendPlDeVsego</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>OKVED_56_PrPostDeyt</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>OKVED_J_OtProdDeVsego</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10DebZad</t>
         </is>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>OKVED_J_ArendPlDeVsego</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>OKVED_J_PrPostDeyt</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>OKVED_63_OtProdDeVsego</t>
+          <t>OKVED_70_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>OKVED_63_ArendPlDeVsego</t>
+          <t>OKVED_R_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>OKVED_63_PrPostDeyt</t>
+          <t>OKVED_93_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>OKVED_64_ArendPlDeVsego</t>
+          <t>OKVED_94_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPostDeyt</t>
+          <t>OKVED_96_KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>OKVED_M_PrPostDeyt</t>
+          <t>OKVED_96_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>OKVED_69_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>OKVED_69_PrPostDeyt</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPostDeyt</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>OKVED_71_PrPostDeyt</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>OKVED_74_PrPostDeyt</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KreZad</t>
         </is>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>OKVED_79_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>OKVED_81_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>OKVED_81_PrPostDeyt</t>
+          <t>OKVED_69_KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>OKVED_82_ArendPlDeVsego</t>
+          <t>OKVED_69_KoeTekLikOt&gt;=20V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>OKVED_82_PrPostDeyt</t>
+          <t>OKVED_01_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>OKVED_O_ArendPlDeVsego</t>
+          <t>OKVED_01_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>OKVED_O_PrPostDeyt</t>
+          <t>OKVED_B_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>OKVED_84_ArendPlDeVsego</t>
+          <t>OKVED_07_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>OKVED_84_PrPostDeyt</t>
+          <t>OKVED_11_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_32_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPostDeyt</t>
+          <t>OKVED_32_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_33_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPostDeyt</t>
+          <t>OKVED_35_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>OKVED_88_OtProdDeVsego</t>
+          <t>OKVED_E_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>OKVED_88_ArendPlDeVsego</t>
+          <t>OKVED_36_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>OKVED_88_PrPostDeyt</t>
+          <t>OKVED_38_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>OKVED_R_OtProdDeVsego</t>
+          <t>OKVED_41_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>OKVED_R_ArendPlDeVsego</t>
+          <t>OKVED_43_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>OKVED_R_PrPostDeyt</t>
+          <t>OKVED_43_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>OKVED_93_OtProdDeVsego</t>
+          <t>OKVED_G_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>OKVED_93_ArendPlDeVsego</t>
+          <t>OKVED_46_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>OKVED_93_PrPostDeyt</t>
+          <t>OKVED_H_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>OKVED_S_ArendPlDeVsego</t>
+          <t>OKVED_49_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>OKVED_94_ArendPlDeVsego</t>
+          <t>OKVED_49_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>OKVED_96_ArendPlDeVsego</t>
+          <t>OKVED_50_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>OKVED_96_PrPostDeyt</t>
+          <t>OKVED_50_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcPoDolgObyaz</t>
+          <t>OKVED_51_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPoFin</t>
+          <t>OKVED_52_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>OKVED_32_ProcPoDolgObyaz</t>
+          <t>OKVED_I_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>OKVED_32_NalogNaPri</t>
+          <t>OKVED_55_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>OKVED_32_PrPoFin</t>
+          <t>OKVED_56_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>OKVED_33_NalogNaPri</t>
+          <t>OKVED_56_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_J_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcPoDolgObyaz</t>
+          <t>OKVED_J_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>OKVED_36_PrPoFin</t>
+          <t>OKVED_J_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>OKVED_38_NalogNaPri</t>
+          <t>OKVED_63_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPoFin</t>
+          <t>OKVED_63_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcPoDolgObyaz</t>
+          <t>OKVED_63_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPoFin</t>
+          <t>OKVED_64_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>OKVED_50_PrPoFin</t>
+          <t>OKVED_64_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>OKVED_I_PrPoFin</t>
+          <t>OKVED_M_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>OKVED_56_ProcPoDolgObyaz</t>
+          <t>OKVED_69_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>OKVED_56_NalogNaPri</t>
+          <t>OKVED_69_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>OKVED_56_PrPoFin</t>
+          <t>OKVED_70_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>OKVED_J_ProcPoDolgObyaz</t>
+          <t>OKVED_71_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>OKVED_J_NalogNaPri</t>
+          <t>OKVED_74_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>OKVED_J_PrPoFin</t>
+          <t>OKVED_79_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>OKVED_63_ProcPoDolgObyaz</t>
+          <t>OKVED_81_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>OKVED_63_NalogNaPri</t>
+          <t>OKVED_81_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>OKVED_63_PrPoFin</t>
+          <t>OKVED_82_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPoFin</t>
+          <t>OKVED_82_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPoFin</t>
+          <t>OKVED_O_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>OKVED_M_ProcPoDolgObyaz</t>
+          <t>OKVED_O_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>OKVED_69_ProcPoDolgObyaz</t>
+          <t>OKVED_84_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>OKVED_69_NalogNaPri</t>
+          <t>OKVED_84_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>OKVED_69_PrPoFin</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>OKVED_71_ProcPoDolgObyaz</t>
+          <t>OKVED_85_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>OKVED_71_NalogNaPri</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>OKVED_74_ProcPoDolgObyaz</t>
+          <t>OKVED_85_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcPoDolgObyaz</t>
+          <t>OKVED_88_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>OKVED_77_PrPoFin</t>
+          <t>OKVED_88_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>OKVED_79_NalogNaPri</t>
+          <t>OKVED_88_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>OKVED_79_PrPoFin</t>
+          <t>OKVED_R_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>OKVED_81_NalogNaPri</t>
+          <t>OKVED_R_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_R_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>OKVED_O_VSvyaziSOplTrudRab</t>
+          <t>OKVED_93_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>OKVED_O_ProcPoDolgObyaz</t>
+          <t>OKVED_93_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>OKVED_O_PrPoFin</t>
+          <t>OKVED_93_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_S_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>OKVED_84_VSvyaziSOplTrudRab</t>
+          <t>OKVED_94_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>OKVED_84_ProcPoDolgObyaz</t>
+          <t>OKVED_96_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>OKVED_84_PrPoFin</t>
+          <t>OKVED_96_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_11_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_11_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPoFin</t>
+          <t>OKVED_32_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_32_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_32_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPoFin</t>
+          <t>OKVED_33_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>OKVED_Q_ProcPoDolgObyaz</t>
+          <t>OKVED_33_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>OKVED_Q_NalogNaPri</t>
+          <t>OKVED_36_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>OKVED_Q_PrPoFin</t>
+          <t>OKVED_36_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_38_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>OKVED_R_VSvyaziSOplTrudRab</t>
+          <t>OKVED_43_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>OKVED_R_ProcPoDolgObyaz</t>
+          <t>OKVED_49_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>OKVED_R_NalogNaPri</t>
+          <t>OKVED_49_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>OKVED_R_PrPoFin</t>
+          <t>OKVED_50_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_I_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>OKVED_93_VSvyaziSOplTrudRab</t>
+          <t>OKVED_56_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>OKVED_93_ProcPoDolgObyaz</t>
+          <t>OKVED_56_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>OKVED_93_NalogNaPri</t>
+          <t>OKVED_56_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>OKVED_93_PrPoFin</t>
+          <t>OKVED_J_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>OKVED_96_ProcPoDolgObyaz</t>
+          <t>OKVED_J_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>OKVED_96_NalogNaPri</t>
+          <t>OKVED_J_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>OKVED_96_PrPoFin</t>
+          <t>OKVED_63_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_63_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdAkcOrgDolUch</t>
+          <t>OKVED_63_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>OKVED_01_DivProcDolgFinVlozh</t>
+          <t>OKVED_K_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>OKVED_01_PrPostDeyt</t>
+          <t>OKVED_64_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>OKVED_B_OtProdAkcOrgDolUch</t>
+          <t>OKVED_M_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>OKVED_B_PrPostDeyt</t>
+          <t>OKVED_69_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>OKVED_07_OtProdAkcOrgDolUch</t>
+          <t>OKVED_69_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>OKVED_07_PrPostDeyt</t>
+          <t>OKVED_69_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>OKVED_C_OtProdAkcOrgDolUch</t>
+          <t>OKVED_71_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>OKVED_10_OtProdAkcOrgDolUch</t>
+          <t>OKVED_71_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_74_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdAkcOrgDolUch</t>
+          <t>OKVED_77_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdFinVlozh</t>
+          <t>OKVED_77_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPostDeyt</t>
+          <t>OKVED_79_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_79_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>OKVED_35_PrPostDeyt</t>
+          <t>OKVED_81_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>OKVED_35_PrPostDeyt</t>
+          <t>OKVED_O_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdAkcOrgDolUch</t>
+          <t>OKVED_O_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdFinVlozh</t>
+          <t>OKVED_O_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>OKVED_E_DivProcDolgFinVlozh</t>
+          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdAkcOrgDolUch</t>
+          <t>OKVED_84_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdFinVlozh</t>
+          <t>OKVED_84_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>OKVED_36_DivProcDolgFinVlozh</t>
+          <t>OKVED_84_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdAkcOrgDolUch</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdFinVlozh</t>
+          <t>OKVED_85_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>OKVED_38_DivProcDolgFinVlozh</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdAkcOrgDolUch</t>
+          <t>OKVED_85_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_Q_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdAkcOrgDolUch</t>
+          <t>OKVED_Q_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_Q_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdAkcOrgDolUch</t>
+          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdFinVlozh</t>
+          <t>OKVED_R_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPostDeyt</t>
+          <t>OKVED_R_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>OKVED_G_OtProdAkcOrgDolUch</t>
+          <t>OKVED_R_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>OKVED_G_PrPostDeyt</t>
+          <t>OKVED_R_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>OKVED_46_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>OKVED_46_PrPostDeyt</t>
+          <t>OKVED_93_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>OKVED_47_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>OKVED_47_PrPostDeyt</t>
+          <t>OKVED_93_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>OKVED_H_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>OKVED_H_PrPostDeyt</t>
+          <t>OKVED_96_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_96_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdAkcOrgDolUch</t>
+          <t>OKVED_96_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>OKVED_49_DivProcDolgFinVlozh</t>
+          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPostDeyt</t>
+          <t>OKVED_01_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>OKVED_52_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>OKVED_52_PrPostDeyt</t>
+          <t>OKVED_01_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_B_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdAkcOrgDolUch</t>
+          <t>OKVED_B_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_07_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdAkcOrgDolUch</t>
+          <t>OKVED_07_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_C_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdAkcOrgDolUch</t>
+          <t>OKVED_10_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPostDeyt</t>
+          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_11_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdAkcOrgDolUch</t>
+          <t>OKVED_11_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPostDeyt</t>
+          <t>OKVED_11_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>OKVED_L_OtProdAkcOrgDolUch</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_35_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdAkcOrgDolUch</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>OKVED_M_PrPostDeyt</t>
+          <t>OKVED_35_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_E_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdAkcOrgDolUch</t>
+          <t>OKVED_E_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPostDeyt</t>
+          <t>OKVED_E_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_36_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdAkcOrgDolUch</t>
+          <t>OKVED_36_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>OKVED_71_DivProcDolgFinVlozh</t>
+          <t>OKVED_36_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>OKVED_71_PrPostDeyt</t>
+          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdFinVlozh</t>
+          <t>OKVED_38_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdFinVlozh</t>
+          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>OKVED_77_PrPostDeyt</t>
+          <t>OKVED_F_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdAkcOrgDolUch</t>
+          <t>OKVED_41_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>OKVED_S_DivProcDolgFinVlozh</t>
+          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_43_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>OKVED_94_DivProcDolgFinVlozh</t>
+          <t>OKVED_43_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>OKVED_01_DolUch</t>
+          <t>OKVED_G_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_G_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>OKVED_B_DolUch</t>
+          <t>OKVED_46_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_46_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>OKVED_C_DolUch</t>
+          <t>OKVED_47_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_47_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>OKVED_10_DolUch</t>
+          <t>OKVED_H_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_H_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>OKVED_11_DolUch</t>
+          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>OKVED_11_PrCenBum</t>
+          <t>OKVED_49_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_49_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPoFin</t>
+          <t>OKVED_49_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>OKVED_33_DolUch</t>
+          <t>OKVED_52_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_52_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>OKVED_E_DolUch</t>
+          <t>OKVED_I_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>OKVED_E_PrCenBum</t>
+          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_55_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>OKVED_36_DolUch</t>
+          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>OKVED_36_PrCenBum</t>
+          <t>OKVED_K_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_K_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>OKVED_36_PrPoFin</t>
+          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>OKVED_F_DolUch</t>
+          <t>OKVED_64_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_64_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>OKVED_41_DolUch</t>
+          <t>OKVED_L_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>OKVED_42_DolUch</t>
+          <t>OKVED_M_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_M_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>OKVED_43_DolUch</t>
+          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>OKVED_43_PrCenBum</t>
+          <t>OKVED_70_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_70_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPoFin</t>
+          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>OKVED_47_DolUch</t>
+          <t>OKVED_71_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>OKVED_H_DolUch</t>
+          <t>OKVED_71_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_71_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>OKVED_49_DolUch</t>
+          <t>OKVED_N_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_N_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPoFin</t>
+          <t>OKVED_77_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>OKVED_50_DolUch</t>
+          <t>OKVED_77_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>OKVED_50_PrCenBum</t>
+          <t>OKVED_77_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>OKVED_50_PrPoFin</t>
+          <t>OKVED_S_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>OKVED_52_DolUch</t>
+          <t>OKVED_S_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_94_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>OKVED_I_PrPoFin</t>
+          <t>OKVED_94_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_01_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>OKVED_55_PrPoFin</t>
+          <t>OKVED_01_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>OKVED_K_DolUch</t>
+          <t>OKVED_B_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPoFin</t>
+          <t>OKVED_C_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>OKVED_M_DolUch</t>
+          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>OKVED_71_DolUch</t>
+          <t>OKVED_10_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>OKVED_N_DolUch</t>
+          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>OKVED_N_PrCenBum</t>
+          <t>OKVED_11_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>OKVED_79_DolUch</t>
+          <t>OKVED_11_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>OKVED_79_PrCenBum</t>
+          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>OKVED_79_PrPoFin</t>
+          <t>OKVED_11_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>OKVED_S_DolUch</t>
+          <t>OKVED_33_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>OKVED_94_DolUch</t>
+          <t>OKVED_33_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_E_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>OKVED_01_PostDeyt1</t>
+          <t>OKVED_E_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>OKVED_01_DrPost</t>
+          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt</t>
+          <t>OKVED_36_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt1</t>
+          <t>OKVED_36_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt</t>
+          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt1</t>
+          <t>OKVED_36_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>OKVED_C_PostDeyt1</t>
+          <t>OKVED_F_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>OKVED_10_PostDeyt1</t>
+          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>OKVED_32_PlCredit</t>
+          <t>OKVED_41_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt</t>
+          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt1</t>
+          <t>OKVED_42_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt</t>
+          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt1</t>
+          <t>OKVED_43_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>OKVED_33_DrPost</t>
+          <t>OKVED_43_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_43_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>OKVED_38_PostDeyt1</t>
+          <t>OKVED_47_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>OKVED_38_DrPost</t>
+          <t>OKVED_H_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>OKVED_F_PostDeyt1</t>
+          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt</t>
+          <t>OKVED_49_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt1</t>
+          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt</t>
+          <t>OKVED_49_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt1</t>
+          <t>OKVED_50_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>OKVED_42_DrPost</t>
+          <t>OKVED_50_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>OKVED_43_PostDeyt1</t>
+          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>OKVED_43_DrPost</t>
+          <t>OKVED_50_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt</t>
+          <t>OKVED_52_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt1</t>
+          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt</t>
+          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt1</t>
+          <t>OKVED_I_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt</t>
+          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt1</t>
+          <t>OKVED_55_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>OKVED_H_PostDeyt1</t>
+          <t>OKVED_K_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt</t>
+          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt1</t>
+          <t>OKVED_K_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>OKVED_50_DrPost</t>
+          <t>OKVED_M_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt</t>
+          <t>OKVED_71_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt1</t>
+          <t>OKVED_N_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>OKVED_51_DrPost</t>
+          <t>OKVED_N_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>OKVED_52_PostDeyt1</t>
+          <t>OKVED_79_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>OKVED_I_PostDeyt1</t>
+          <t>OKVED_79_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>OKVED_I_DrPost</t>
+          <t>OKVED_79_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>OKVED_55_PostDeyt1</t>
+          <t>OKVED_S_Modern</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>OKVED_55_DrPost</t>
+          <t>OKVED_S_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt</t>
+          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt1</t>
+          <t>OKVED_94_Modern</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>OKVED_K_DrPost</t>
+          <t>OKVED_94_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt</t>
+          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt1</t>
+          <t>OKVED_01_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>OKVED_64_DrPost</t>
+          <t>OKVED_01_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>OKVED_L_PostDeyt1</t>
+          <t>OKVED_B_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>OKVED_68_PostDeyt1</t>
+          <t>OKVED_B_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>OKVED_70_PlCredit</t>
+          <t>OKVED_07_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>OKVED_70_PostDeyt</t>
+          <t>OKVED_07_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>OKVED_71_PostDeyt</t>
+          <t>OKVED_C_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt</t>
+          <t>OKVED_10_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt1</t>
+          <t>OKVED_32_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>OKVED_74_DrPost</t>
+          <t>OKVED_32_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt</t>
+          <t>OKVED_32_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt1</t>
+          <t>OKVED_33_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt</t>
+          <t>OKVED_33_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt1</t>
+          <t>OKVED_33_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>OKVED_79_DrPost</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>OKVED_81_PlCredit</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt</t>
+          <t>OKVED_38_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt1</t>
+          <t>OKVED_38_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>OKVED_S_PlCredit</t>
+          <t>OKVED_F_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>OKVED_S_PostDeyt1</t>
+          <t>OKVED_41_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>OKVED_94_PlCredit</t>
+          <t>OKVED_41_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>OKVED_94_PostDeyt1</t>
+          <t>OKVED_42_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin1</t>
+          <t>OKVED_42_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin2</t>
+          <t>OKVED_42_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>OKVED_B_PlPoFin1</t>
+          <t>OKVED_43_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>OKVED_07_PlPoFin1</t>
+          <t>OKVED_43_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin</t>
+          <t>OKVED_G_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin1</t>
+          <t>OKVED_G_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin2</t>
+          <t>OKVED_46_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin3</t>
+          <t>OKVED_46_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_47_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_47_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_H_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin1</t>
+          <t>OKVED_50_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin2</t>
+          <t>OKVED_50_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin1</t>
+          <t>OKVED_50_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin2</t>
+          <t>OKVED_51_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>OKVED_F_PlPoFin1</t>
+          <t>OKVED_51_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>OKVED_41_PlPoFin1</t>
+          <t>OKVED_51_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin1</t>
+          <t>OKVED_52_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin2</t>
+          <t>OKVED_I_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPoFin</t>
+          <t>OKVED_I_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>OKVED_G_PlPoFin1</t>
+          <t>OKVED_55_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>OKVED_46_PlPoFin1</t>
+          <t>OKVED_55_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>OKVED_47_PlPoFin1</t>
+          <t>OKVED_K_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>OKVED_H_PlPoFin1</t>
+          <t>OKVED_K_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin1</t>
+          <t>OKVED_K_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin2</t>
+          <t>OKVED_64_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPoFin</t>
+          <t>OKVED_64_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoFin1</t>
+          <t>OKVED_64_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>OKVED_50_PrPoFin</t>
+          <t>OKVED_L_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>OKVED_52_PlPoFin1</t>
+          <t>OKVED_68_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin1</t>
+          <t>OKVED_70_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin2</t>
+          <t>OKVED_70_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>OKVED_I_PrPoFin</t>
+          <t>OKVED_71_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin1</t>
+          <t>OKVED_74_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin2</t>
+          <t>OKVED_74_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
         <is>
-          <t>OKVED_55_PrPoFin</t>
+          <t>OKVED_74_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoFin1</t>
+          <t>OKVED_N_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPoFin</t>
+          <t>OKVED_N_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoFin1</t>
+          <t>OKVED_79_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPoFin</t>
+          <t>OKVED_79_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>OKVED_68_PlPoFin1</t>
+          <t>OKVED_79_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>OKVED_M_PlPoFin1</t>
+          <t>OKVED_81_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin</t>
+          <t>OKVED_81_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin1</t>
+          <t>OKVED_81_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin2</t>
+          <t>OKVED_S_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin3</t>
+          <t>OKVED_S_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPoFin</t>
+          <t>OKVED_94_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>OKVED_71_PlPoFin1</t>
+          <t>OKVED_94_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin1</t>
+          <t>OKVED_01_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin2</t>
+          <t>OKVED_01_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin3</t>
+          <t>OKVED_B_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>OKVED_74_SaldoDenPot</t>
+          <t>OKVED_07_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>OKVED_79_PrPoFin</t>
+          <t>OKVED_33_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin2</t>
+          <t>OKVED_33_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin3</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>OKVED_81_SaldoDenPot</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin1</t>
+          <t>OKVED_E_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin2</t>
+          <t>OKVED_E_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin3</t>
+          <t>OKVED_38_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin1</t>
+          <t>OKVED_38_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin2</t>
+          <t>OKVED_F_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin3</t>
+          <t>OKVED_41_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
         <is>
-          <t>OKVED_01_Velch</t>
+          <t>OKVED_43_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>OKVED_11_Velch</t>
+          <t>OKVED_43_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
         <is>
-          <t>OKVED_32_Velch</t>
+          <t>OKVED_43_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
         <is>
-          <t>OKVED_33_Velch</t>
+          <t>OKVED_G_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
         <is>
-          <t>OKVED_E_Velch</t>
+          <t>OKVED_46_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
         <is>
-          <t>OKVED_38_Velch</t>
+          <t>OKVED_47_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
         <is>
-          <t>OKVED_F_Velch</t>
+          <t>OKVED_H_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
         <is>
-          <t>OKVED_41_Velch</t>
+          <t>OKVED_49_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
         <is>
-          <t>OKVED_42_Velch</t>
+          <t>OKVED_49_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
         <is>
-          <t>OKVED_43_Velch</t>
+          <t>OKVED_49_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
         <is>
-          <t>OKVED_47_Velch</t>
+          <t>OKVED_50_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
         <is>
-          <t>OKVED_49_Velch</t>
+          <t>OKVED_50_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
         <is>
-          <t>OKVED_I_Velch</t>
+          <t>OKVED_52_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
         <is>
-          <t>OKVED_56_Velch</t>
+          <t>OKVED_I_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
         <is>
-          <t>OKVED_J_Velch</t>
+          <t>OKVED_I_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>OKVED_63_Velch</t>
+          <t>OKVED_I_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>OKVED_L_Velch</t>
+          <t>OKVED_55_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
         <is>
-          <t>OKVED_68_Velch</t>
+          <t>OKVED_55_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
         <is>
-          <t>OKVED_M_Velch</t>
+          <t>OKVED_55_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>OKVED_69_Velch</t>
+          <t>OKVED_K_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>OKVED_70_Velch</t>
+          <t>OKVED_K_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>OKVED_71_Velch</t>
+          <t>OKVED_64_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>OKVED_N_Velch</t>
+          <t>OKVED_64_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
         <is>
-          <t>OKVED_77_Velch</t>
+          <t>OKVED_68_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
         <is>
-          <t>OKVED_79_Velch</t>
+          <t>OKVED_M_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>OKVED_81_Velch</t>
+          <t>OKVED_70_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
         <is>
-          <t>OKVED_82_Velch</t>
+          <t>OKVED_70_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
         <is>
-          <t>OKVED_O_Velch</t>
+          <t>OKVED_70_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
         <is>
-          <t>OKVED_84_Velch</t>
+          <t>OKVED_70_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_70_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_71_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
         <is>
-          <t>OKVED_88_Velch</t>
+          <t>OKVED_74_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>OKVED_R_Velch</t>
+          <t>OKVED_74_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>OKVED_93_Velch</t>
+          <t>OKVED_74_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>OKVED_S_Velch</t>
+          <t>OKVED_74_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>OKVED_94_Velch</t>
+          <t>OKVED_79_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>OKVED_96_Velch</t>
+          <t>OKVED_79_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>OKVED_43_UstKap</t>
+          <t>OKVED_79_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>OKVED_43_ChiAkt</t>
+          <t>OKVED_81_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap</t>
+          <t>OKVED_81_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>OKVED_J_Pri(ubOtPro</t>
+          <t>OKVED_81_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>OKVED_J_ChiPri(ubOtcPer</t>
+          <t>OKVED_81_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_S_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap</t>
+          <t>OKVED_S_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>OKVED_63_Pri(ubOtPro</t>
+          <t>OKVED_S_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1696">
       <c r="A1696" t="inlineStr">
         <is>
-          <t>OKVED_63_ChiPri(ubOtcPer</t>
+          <t>OKVED_94_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1697">
       <c r="A1697" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_94_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1698">
       <c r="A1698" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap</t>
+          <t>OKVED_94_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1699">
       <c r="A1699" t="inlineStr">
         <is>
-          <t>OKVED_69_ChiAkt</t>
+          <t>OKVED_01_Velch</t>
         </is>
       </c>
     </row>
     <row r="1700">
       <c r="A1700" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap</t>
+          <t>OKVED_11_Velch</t>
         </is>
       </c>
     </row>
     <row r="1701">
       <c r="A1701" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap</t>
+          <t>OKVED_32_Velch</t>
         </is>
       </c>
     </row>
     <row r="1702">
       <c r="A1702" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap</t>
+          <t>OKVED_33_Velch</t>
         </is>
       </c>
     </row>
     <row r="1703">
       <c r="A1703" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap</t>
+          <t>OKVED_E_Velch</t>
         </is>
       </c>
     </row>
     <row r="1704">
       <c r="A1704" t="inlineStr">
         <is>
-          <t>OKVED_Q_Pri(ubOtPro</t>
+          <t>OKVED_38_Velch</t>
         </is>
       </c>
     </row>
     <row r="1705">
       <c r="A1705" t="inlineStr">
         <is>
-          <t>OKVED_Q_ChiPri(ubOtcPer</t>
+          <t>OKVED_F_Velch</t>
         </is>
       </c>
     </row>
     <row r="1706">
       <c r="A1706" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_41_Velch</t>
         </is>
       </c>
     </row>
     <row r="1707">
       <c r="A1707" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap</t>
+          <t>OKVED_42_Velch</t>
         </is>
       </c>
     </row>
     <row r="1708">
       <c r="A1708" t="inlineStr">
         <is>
-          <t>OKVED_88_Pri(ubOtPro</t>
+          <t>OKVED_43_Velch</t>
         </is>
       </c>
     </row>
     <row r="1709">
       <c r="A1709" t="inlineStr">
         <is>
-          <t>OKVED_88_ChiPri(ubOtcPer</t>
+          <t>OKVED_47_Velch</t>
         </is>
       </c>
     </row>
     <row r="1710">
       <c r="A1710" t="inlineStr">
+        <is>
+          <t>OKVED_49_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>OKVED_I_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>OKVED_56_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>OKVED_J_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>OKVED_63_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>OKVED_L_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>OKVED_68_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>OKVED_M_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>OKVED_69_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>OKVED_70_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>OKVED_71_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>OKVED_N_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>OKVED_77_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>OKVED_79_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>OKVED_81_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>OKVED_82_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>OKVED_O_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>OKVED_84_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>OKVED_85_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>OKVED_85_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>OKVED_88_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>OKVED_R_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>OKVED_93_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>OKVED_S_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>OKVED_94_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>OKVED_96_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>OKVED_43_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>OKVED_43_ChiAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>OKVED_J_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>OKVED_J_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>OKVED_J_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>OKVED_63_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>OKVED_63_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>OKVED_63_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>OKVED_69_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>OKVED_69_ChiAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>OKVED_O_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>OKVED_84_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>OKVED_Q_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>OKVED_Q_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>OKVED_Q_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>OKVED_88_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>OKVED_88_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>OKVED_88_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr">
         <is>
           <t>OKVED_88_PriUby(-DoNalKChiAktV%</t>
         </is>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1758"/>
+  <dimension ref="A1:A1714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9869,2854 +9869,2546 @@
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPoFin</t>
+          <t>OKVED_32_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>OKVED_32_ProcPoDolgObyaz</t>
+          <t>OKVED_32_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>OKVED_32_NalogNaPri</t>
+          <t>OKVED_33_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>OKVED_32_PrPoFin</t>
+          <t>OKVED_36_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>OKVED_33_NalogNaPri</t>
+          <t>OKVED_38_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_49_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcPoDolgObyaz</t>
+          <t>OKVED_56_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>OKVED_36_PrPoFin</t>
+          <t>OKVED_56_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>OKVED_38_NalogNaPri</t>
+          <t>OKVED_J_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPoFin</t>
+          <t>OKVED_J_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcPoDolgObyaz</t>
+          <t>OKVED_63_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPoFin</t>
+          <t>OKVED_63_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>OKVED_50_PrPoFin</t>
+          <t>OKVED_M_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>OKVED_I_PrPoFin</t>
+          <t>OKVED_69_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>OKVED_56_ProcPoDolgObyaz</t>
+          <t>OKVED_69_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>OKVED_56_NalogNaPri</t>
+          <t>OKVED_71_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>OKVED_56_PrPoFin</t>
+          <t>OKVED_71_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>OKVED_J_ProcPoDolgObyaz</t>
+          <t>OKVED_74_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>OKVED_J_NalogNaPri</t>
+          <t>OKVED_77_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>OKVED_J_PrPoFin</t>
+          <t>OKVED_79_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>OKVED_63_ProcPoDolgObyaz</t>
+          <t>OKVED_81_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>OKVED_63_NalogNaPri</t>
+          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>OKVED_63_PrPoFin</t>
+          <t>OKVED_O_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPoFin</t>
+          <t>OKVED_O_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPoFin</t>
+          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>OKVED_M_ProcPoDolgObyaz</t>
+          <t>OKVED_84_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>OKVED_69_ProcPoDolgObyaz</t>
+          <t>OKVED_84_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>OKVED_69_NalogNaPri</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>OKVED_69_PrPoFin</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>OKVED_71_ProcPoDolgObyaz</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>OKVED_71_NalogNaPri</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>OKVED_74_ProcPoDolgObyaz</t>
+          <t>OKVED_Q_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcPoDolgObyaz</t>
+          <t>OKVED_Q_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>OKVED_77_PrPoFin</t>
+          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>OKVED_79_NalogNaPri</t>
+          <t>OKVED_R_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>OKVED_79_PrPoFin</t>
+          <t>OKVED_R_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>OKVED_81_NalogNaPri</t>
+          <t>OKVED_R_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>OKVED_O_VSvyaziSOplTrudRab</t>
+          <t>OKVED_93_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>OKVED_O_ProcPoDolgObyaz</t>
+          <t>OKVED_93_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>OKVED_O_PrPoFin</t>
+          <t>OKVED_93_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_96_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>OKVED_84_VSvyaziSOplTrudRab</t>
+          <t>OKVED_96_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>OKVED_84_ProcPoDolgObyaz</t>
+          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>OKVED_84_PrPoFin</t>
+          <t>OKVED_01_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_01_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_01_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPoFin</t>
+          <t>OKVED_B_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_B_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_07_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPoFin</t>
+          <t>OKVED_07_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>OKVED_Q_ProcPoDolgObyaz</t>
+          <t>OKVED_C_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>OKVED_Q_NalogNaPri</t>
+          <t>OKVED_10_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>OKVED_Q_PrPoFin</t>
+          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_11_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>OKVED_R_VSvyaziSOplTrudRab</t>
+          <t>OKVED_11_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>OKVED_R_ProcPoDolgObyaz</t>
+          <t>OKVED_11_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>OKVED_R_NalogNaPri</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>OKVED_R_PrPoFin</t>
+          <t>OKVED_35_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>OKVED_93_VSvyaziSOplTrudRab</t>
+          <t>OKVED_35_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>OKVED_93_ProcPoDolgObyaz</t>
+          <t>OKVED_E_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>OKVED_93_NalogNaPri</t>
+          <t>OKVED_E_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>OKVED_93_PrPoFin</t>
+          <t>OKVED_E_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>OKVED_96_ProcPoDolgObyaz</t>
+          <t>OKVED_36_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>OKVED_96_NalogNaPri</t>
+          <t>OKVED_36_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>OKVED_96_PrPoFin</t>
+          <t>OKVED_36_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>OKVED_01_DivProcDolgFinVlozh</t>
+          <t>OKVED_38_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>OKVED_01_PrPostDeyt</t>
+          <t>OKVED_38_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>OKVED_B_OtProdAkcOrgDolUch</t>
+          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>OKVED_B_PrPostDeyt</t>
+          <t>OKVED_F_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>OKVED_07_OtProdAkcOrgDolUch</t>
+          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>OKVED_07_PrPostDeyt</t>
+          <t>OKVED_41_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>OKVED_C_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>OKVED_10_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_43_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdFinVlozh</t>
+          <t>OKVED_G_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPostDeyt</t>
+          <t>OKVED_G_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_46_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>OKVED_35_PrPostDeyt</t>
+          <t>OKVED_46_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_47_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>OKVED_35_PrPostDeyt</t>
+          <t>OKVED_47_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdAkcOrgDolUch</t>
+          <t>OKVED_H_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdFinVlozh</t>
+          <t>OKVED_H_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>OKVED_E_DivProcDolgFinVlozh</t>
+          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdAkcOrgDolUch</t>
+          <t>OKVED_49_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdFinVlozh</t>
+          <t>OKVED_49_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>OKVED_36_DivProcDolgFinVlozh</t>
+          <t>OKVED_49_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_52_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdAkcOrgDolUch</t>
+          <t>OKVED_52_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdFinVlozh</t>
+          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>OKVED_38_DivProcDolgFinVlozh</t>
+          <t>OKVED_I_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdAkcOrgDolUch</t>
+          <t>OKVED_55_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdAkcOrgDolUch</t>
+          <t>OKVED_K_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_K_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdAkcOrgDolUch</t>
+          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdFinVlozh</t>
+          <t>OKVED_64_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPostDeyt</t>
+          <t>OKVED_64_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>OKVED_G_OtProdAkcOrgDolUch</t>
+          <t>OKVED_L_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>OKVED_G_PrPostDeyt</t>
+          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>OKVED_46_OtProdAkcOrgDolUch</t>
+          <t>OKVED_M_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>OKVED_46_PrPostDeyt</t>
+          <t>OKVED_M_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>OKVED_47_OtProdAkcOrgDolUch</t>
+          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>OKVED_47_PrPostDeyt</t>
+          <t>OKVED_70_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>OKVED_H_OtProdAkcOrgDolUch</t>
+          <t>OKVED_70_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>OKVED_H_PrPostDeyt</t>
+          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_71_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdAkcOrgDolUch</t>
+          <t>OKVED_71_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>OKVED_49_DivProcDolgFinVlozh</t>
+          <t>OKVED_71_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPostDeyt</t>
+          <t>OKVED_N_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>OKVED_52_OtProdAkcOrgDolUch</t>
+          <t>OKVED_N_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>OKVED_52_PrPostDeyt</t>
+          <t>OKVED_77_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_77_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdAkcOrgDolUch</t>
+          <t>OKVED_77_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdAkcOrgDolUch</t>
+          <t>OKVED_S_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_S_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdAkcOrgDolUch</t>
+          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPostDeyt</t>
+          <t>OKVED_94_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_94_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPostDeyt</t>
+          <t>OKVED_01_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>OKVED_L_OtProdAkcOrgDolUch</t>
+          <t>OKVED_B_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdAkcOrgDolUch</t>
+          <t>OKVED_C_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>OKVED_M_PrPostDeyt</t>
+          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_10_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdAkcOrgDolUch</t>
+          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPostDeyt</t>
+          <t>OKVED_11_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_11_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdAkcOrgDolUch</t>
+          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>OKVED_71_DivProcDolgFinVlozh</t>
+          <t>OKVED_33_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>OKVED_71_PrPostDeyt</t>
+          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdAkcOrgDolUch</t>
+          <t>OKVED_E_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdFinVlozh</t>
+          <t>OKVED_E_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdAkcOrgDolUch</t>
+          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdFinVlozh</t>
+          <t>OKVED_36_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>OKVED_77_PrPostDeyt</t>
+          <t>OKVED_36_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdAkcOrgDolUch</t>
+          <t>OKVED_F_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>OKVED_S_DivProcDolgFinVlozh</t>
+          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_41_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdAkcOrgDolUch</t>
+          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>OKVED_94_DivProcDolgFinVlozh</t>
+          <t>OKVED_42_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>OKVED_01_DolUch</t>
+          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_43_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>OKVED_B_DolUch</t>
+          <t>OKVED_43_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>OKVED_C_DolUch</t>
+          <t>OKVED_47_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_H_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>OKVED_10_DolUch</t>
+          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_49_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>OKVED_11_DolUch</t>
+          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>OKVED_11_PrCenBum</t>
+          <t>OKVED_50_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_50_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPoFin</t>
+          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>OKVED_33_DolUch</t>
+          <t>OKVED_52_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>OKVED_E_DolUch</t>
+          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>OKVED_E_PrCenBum</t>
+          <t>OKVED_K_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>OKVED_36_DolUch</t>
+          <t>OKVED_M_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>OKVED_36_PrCenBum</t>
+          <t>OKVED_71_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_N_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>OKVED_36_PrPoFin</t>
+          <t>OKVED_N_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>OKVED_F_DolUch</t>
+          <t>OKVED_79_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_79_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>OKVED_41_DolUch</t>
+          <t>OKVED_S_Modern</t>
         </is>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_S_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>OKVED_42_DolUch</t>
+          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_94_Modern</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>OKVED_43_DolUch</t>
+          <t>OKVED_94_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>OKVED_43_PrCenBum</t>
+          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_01_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPoFin</t>
+          <t>OKVED_01_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>OKVED_47_DolUch</t>
+          <t>OKVED_B_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>OKVED_H_DolUch</t>
+          <t>OKVED_B_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_07_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>OKVED_49_DolUch</t>
+          <t>OKVED_07_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_C_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPoFin</t>
+          <t>OKVED_10_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>OKVED_50_DolUch</t>
+          <t>OKVED_32_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>OKVED_50_PrCenBum</t>
+          <t>OKVED_32_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_32_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>OKVED_50_PrPoFin</t>
+          <t>OKVED_33_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>OKVED_52_DolUch</t>
+          <t>OKVED_33_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_33_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>OKVED_I_PrPoFin</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_38_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>OKVED_55_PrPoFin</t>
+          <t>OKVED_38_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>OKVED_K_DolUch</t>
+          <t>OKVED_F_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_41_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPoFin</t>
+          <t>OKVED_41_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>OKVED_M_DolUch</t>
+          <t>OKVED_42_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>OKVED_71_DolUch</t>
+          <t>OKVED_42_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>OKVED_N_DolUch</t>
+          <t>OKVED_42_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>OKVED_N_PrCenBum</t>
+          <t>OKVED_43_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>OKVED_79_DolUch</t>
+          <t>OKVED_43_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>OKVED_79_PrCenBum</t>
+          <t>OKVED_G_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>OKVED_79_PrPoFin</t>
+          <t>OKVED_G_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>OKVED_S_Modern</t>
+          <t>OKVED_46_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>OKVED_S_DolUch</t>
+          <t>OKVED_46_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_47_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>OKVED_94_Modern</t>
+          <t>OKVED_47_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>OKVED_94_DolUch</t>
+          <t>OKVED_H_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_50_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>OKVED_01_PostDeyt1</t>
+          <t>OKVED_50_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>OKVED_01_DrPost</t>
+          <t>OKVED_50_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt</t>
+          <t>OKVED_51_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt1</t>
+          <t>OKVED_51_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt</t>
+          <t>OKVED_51_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt1</t>
+          <t>OKVED_52_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>OKVED_C_PostDeyt1</t>
+          <t>OKVED_I_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>OKVED_10_PostDeyt1</t>
+          <t>OKVED_I_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>OKVED_32_PlCredit</t>
+          <t>OKVED_55_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt</t>
+          <t>OKVED_55_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt1</t>
+          <t>OKVED_K_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt</t>
+          <t>OKVED_K_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt1</t>
+          <t>OKVED_K_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>OKVED_33_DrPost</t>
+          <t>OKVED_64_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_64_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_64_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>OKVED_38_PostDeyt1</t>
+          <t>OKVED_L_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>OKVED_38_DrPost</t>
+          <t>OKVED_68_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>OKVED_F_PostDeyt1</t>
+          <t>OKVED_70_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt</t>
+          <t>OKVED_70_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt1</t>
+          <t>OKVED_71_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt</t>
+          <t>OKVED_74_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt1</t>
+          <t>OKVED_74_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>OKVED_42_DrPost</t>
+          <t>OKVED_74_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>OKVED_43_PostDeyt1</t>
+          <t>OKVED_N_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>OKVED_43_DrPost</t>
+          <t>OKVED_N_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt</t>
+          <t>OKVED_79_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt1</t>
+          <t>OKVED_79_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt</t>
+          <t>OKVED_79_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt1</t>
+          <t>OKVED_81_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt</t>
+          <t>OKVED_81_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt1</t>
+          <t>OKVED_81_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>OKVED_H_PostDeyt1</t>
+          <t>OKVED_S_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt</t>
+          <t>OKVED_S_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt1</t>
+          <t>OKVED_94_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>OKVED_50_DrPost</t>
+          <t>OKVED_94_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt</t>
+          <t>OKVED_01_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt1</t>
+          <t>OKVED_01_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>OKVED_51_DrPost</t>
+          <t>OKVED_B_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>OKVED_52_PostDeyt1</t>
+          <t>OKVED_07_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>OKVED_I_PostDeyt1</t>
+          <t>OKVED_33_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>OKVED_I_DrPost</t>
+          <t>OKVED_33_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>OKVED_55_PostDeyt1</t>
+          <t>OKVED_33_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>OKVED_55_DrPost</t>
+          <t>OKVED_33_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt1</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>OKVED_K_DrPost</t>
+          <t>OKVED_E_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt</t>
+          <t>OKVED_E_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt1</t>
+          <t>OKVED_38_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>OKVED_64_DrPost</t>
+          <t>OKVED_38_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>OKVED_L_PostDeyt1</t>
+          <t>OKVED_F_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>OKVED_68_PostDeyt1</t>
+          <t>OKVED_41_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>OKVED_70_PlCredit</t>
+          <t>OKVED_43_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>OKVED_70_PostDeyt</t>
+          <t>OKVED_43_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>OKVED_71_PostDeyt</t>
+          <t>OKVED_G_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt</t>
+          <t>OKVED_46_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt1</t>
+          <t>OKVED_47_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
         <is>
-          <t>OKVED_74_DrPost</t>
+          <t>OKVED_H_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt</t>
+          <t>OKVED_49_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt1</t>
+          <t>OKVED_49_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt</t>
+          <t>OKVED_50_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt1</t>
+          <t>OKVED_52_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>OKVED_79_DrPost</t>
+          <t>OKVED_I_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>OKVED_81_PlCredit</t>
+          <t>OKVED_I_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt</t>
+          <t>OKVED_55_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt1</t>
+          <t>OKVED_55_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>OKVED_S_PlCredit</t>
+          <t>OKVED_K_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>OKVED_S_PostDeyt1</t>
+          <t>OKVED_64_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>OKVED_94_PlCredit</t>
+          <t>OKVED_68_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>OKVED_94_PostDeyt1</t>
+          <t>OKVED_M_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin1</t>
+          <t>OKVED_70_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin2</t>
+          <t>OKVED_70_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>OKVED_B_PlPoFin1</t>
+          <t>OKVED_70_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>OKVED_07_PlPoFin1</t>
+          <t>OKVED_70_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin</t>
+          <t>OKVED_71_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin1</t>
+          <t>OKVED_74_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin2</t>
+          <t>OKVED_74_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin3</t>
+          <t>OKVED_74_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPoFin</t>
+          <t>OKVED_74_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_79_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_79_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin1</t>
+          <t>OKVED_81_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin2</t>
+          <t>OKVED_81_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin1</t>
+          <t>OKVED_81_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin2</t>
+          <t>OKVED_81_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>OKVED_F_PlPoFin1</t>
+          <t>OKVED_S_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
         <is>
-          <t>OKVED_41_PlPoFin1</t>
+          <t>OKVED_S_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin1</t>
+          <t>OKVED_S_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin2</t>
+          <t>OKVED_94_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPoFin</t>
+          <t>OKVED_94_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
         <is>
-          <t>OKVED_G_PlPoFin1</t>
+          <t>OKVED_94_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
         <is>
-          <t>OKVED_46_PlPoFin1</t>
+          <t>OKVED_01_Velch</t>
         </is>
       </c>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
         <is>
-          <t>OKVED_47_PlPoFin1</t>
+          <t>OKVED_11_Velch</t>
         </is>
       </c>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
         <is>
-          <t>OKVED_H_PlPoFin1</t>
+          <t>OKVED_32_Velch</t>
         </is>
       </c>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin1</t>
+          <t>OKVED_33_Velch</t>
         </is>
       </c>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin2</t>
+          <t>OKVED_E_Velch</t>
         </is>
       </c>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPoFin</t>
+          <t>OKVED_38_Velch</t>
         </is>
       </c>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoFin1</t>
+          <t>OKVED_F_Velch</t>
         </is>
       </c>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
         <is>
-          <t>OKVED_50_PrPoFin</t>
+          <t>OKVED_41_Velch</t>
         </is>
       </c>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
         <is>
-          <t>OKVED_52_PlPoFin1</t>
+          <t>OKVED_42_Velch</t>
         </is>
       </c>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin1</t>
+          <t>OKVED_43_Velch</t>
         </is>
       </c>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin2</t>
+          <t>OKVED_47_Velch</t>
         </is>
       </c>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>OKVED_I_PrPoFin</t>
+          <t>OKVED_49_Velch</t>
         </is>
       </c>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin1</t>
+          <t>OKVED_I_Velch</t>
         </is>
       </c>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin2</t>
+          <t>OKVED_56_Velch</t>
         </is>
       </c>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
         <is>
-          <t>OKVED_55_PrPoFin</t>
+          <t>OKVED_J_Velch</t>
         </is>
       </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoFin1</t>
+          <t>OKVED_63_Velch</t>
         </is>
       </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPoFin</t>
+          <t>OKVED_L_Velch</t>
         </is>
       </c>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoFin1</t>
+          <t>OKVED_68_Velch</t>
         </is>
       </c>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPoFin</t>
+          <t>OKVED_M_Velch</t>
         </is>
       </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
         <is>
-          <t>OKVED_68_PlPoFin1</t>
+          <t>OKVED_69_Velch</t>
         </is>
       </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
         <is>
-          <t>OKVED_M_PlPoFin1</t>
+          <t>OKVED_70_Velch</t>
         </is>
       </c>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin</t>
+          <t>OKVED_71_Velch</t>
         </is>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin1</t>
+          <t>OKVED_N_Velch</t>
         </is>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin2</t>
+          <t>OKVED_77_Velch</t>
         </is>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin3</t>
+          <t>OKVED_79_Velch</t>
         </is>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPoFin</t>
+          <t>OKVED_81_Velch</t>
         </is>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>OKVED_71_PlPoFin1</t>
+          <t>OKVED_82_Velch</t>
         </is>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin1</t>
+          <t>OKVED_O_Velch</t>
         </is>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin2</t>
+          <t>OKVED_84_Velch</t>
         </is>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin3</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>OKVED_74_SaldoDenPot</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin1</t>
+          <t>OKVED_88_Velch</t>
         </is>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin2</t>
+          <t>OKVED_R_Velch</t>
         </is>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>OKVED_79_PrPoFin</t>
+          <t>OKVED_93_Velch</t>
         </is>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin1</t>
+          <t>OKVED_S_Velch</t>
         </is>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin2</t>
+          <t>OKVED_94_Velch</t>
         </is>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin3</t>
+          <t>OKVED_96_Velch</t>
         </is>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>OKVED_81_SaldoDenPot</t>
+          <t>OKVED_43_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin1</t>
+          <t>OKVED_43_ChiAkt</t>
         </is>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin2</t>
+          <t>OKVED_J_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin3</t>
+          <t>OKVED_J_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1696">
       <c r="A1696" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin1</t>
+          <t>OKVED_J_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1697">
       <c r="A1697" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin2</t>
+          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1698">
       <c r="A1698" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin3</t>
+          <t>OKVED_63_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1699">
       <c r="A1699" t="inlineStr">
         <is>
-          <t>OKVED_01_Velch</t>
+          <t>OKVED_63_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1700">
       <c r="A1700" t="inlineStr">
         <is>
-          <t>OKVED_11_Velch</t>
+          <t>OKVED_63_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1701">
       <c r="A1701" t="inlineStr">
         <is>
-          <t>OKVED_32_Velch</t>
+          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1702">
       <c r="A1702" t="inlineStr">
         <is>
-          <t>OKVED_33_Velch</t>
+          <t>OKVED_69_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1703">
       <c r="A1703" t="inlineStr">
         <is>
-          <t>OKVED_E_Velch</t>
+          <t>OKVED_69_ChiAkt</t>
         </is>
       </c>
     </row>
     <row r="1704">
       <c r="A1704" t="inlineStr">
         <is>
-          <t>OKVED_38_Velch</t>
+          <t>OKVED_O_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1705">
       <c r="A1705" t="inlineStr">
         <is>
-          <t>OKVED_F_Velch</t>
+          <t>OKVED_84_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1706">
       <c r="A1706" t="inlineStr">
         <is>
-          <t>OKVED_41_Velch</t>
+          <t>OKVED_85_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1707">
       <c r="A1707" t="inlineStr">
         <is>
-          <t>OKVED_42_Velch</t>
+          <t>OKVED_Q_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1708">
       <c r="A1708" t="inlineStr">
         <is>
-          <t>OKVED_43_Velch</t>
+          <t>OKVED_Q_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1709">
       <c r="A1709" t="inlineStr">
         <is>
-          <t>OKVED_47_Velch</t>
+          <t>OKVED_Q_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1710">
       <c r="A1710" t="inlineStr">
         <is>
-          <t>OKVED_49_Velch</t>
+          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1711">
       <c r="A1711" t="inlineStr">
         <is>
-          <t>OKVED_I_Velch</t>
+          <t>OKVED_88_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1712">
       <c r="A1712" t="inlineStr">
         <is>
-          <t>OKVED_56_Velch</t>
+          <t>OKVED_88_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1713">
       <c r="A1713" t="inlineStr">
         <is>
-          <t>OKVED_J_Velch</t>
+          <t>OKVED_88_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1714">
       <c r="A1714" t="inlineStr">
-        <is>
-          <t>OKVED_63_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1715">
-      <c r="A1715" t="inlineStr">
-        <is>
-          <t>OKVED_L_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1716">
-      <c r="A1716" t="inlineStr">
-        <is>
-          <t>OKVED_68_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1717">
-      <c r="A1717" t="inlineStr">
-        <is>
-          <t>OKVED_M_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1718">
-      <c r="A1718" t="inlineStr">
-        <is>
-          <t>OKVED_69_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1719">
-      <c r="A1719" t="inlineStr">
-        <is>
-          <t>OKVED_70_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1720">
-      <c r="A1720" t="inlineStr">
-        <is>
-          <t>OKVED_71_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1721">
-      <c r="A1721" t="inlineStr">
-        <is>
-          <t>OKVED_N_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1722">
-      <c r="A1722" t="inlineStr">
-        <is>
-          <t>OKVED_77_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1723">
-      <c r="A1723" t="inlineStr">
-        <is>
-          <t>OKVED_79_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1724">
-      <c r="A1724" t="inlineStr">
-        <is>
-          <t>OKVED_81_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1725">
-      <c r="A1725" t="inlineStr">
-        <is>
-          <t>OKVED_82_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1726">
-      <c r="A1726" t="inlineStr">
-        <is>
-          <t>OKVED_O_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1727">
-      <c r="A1727" t="inlineStr">
-        <is>
-          <t>OKVED_84_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1728">
-      <c r="A1728" t="inlineStr">
-        <is>
-          <t>OKVED_85_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1729">
-      <c r="A1729" t="inlineStr">
-        <is>
-          <t>OKVED_85_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1730">
-      <c r="A1730" t="inlineStr">
-        <is>
-          <t>OKVED_88_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1731">
-      <c r="A1731" t="inlineStr">
-        <is>
-          <t>OKVED_R_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1732">
-      <c r="A1732" t="inlineStr">
-        <is>
-          <t>OKVED_93_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1733">
-      <c r="A1733" t="inlineStr">
-        <is>
-          <t>OKVED_S_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1734">
-      <c r="A1734" t="inlineStr">
-        <is>
-          <t>OKVED_94_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1735">
-      <c r="A1735" t="inlineStr">
-        <is>
-          <t>OKVED_96_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1736">
-      <c r="A1736" t="inlineStr">
-        <is>
-          <t>OKVED_43_UstKap</t>
-        </is>
-      </c>
-    </row>
-    <row r="1737">
-      <c r="A1737" t="inlineStr">
-        <is>
-          <t>OKVED_43_ChiAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="1738">
-      <c r="A1738" t="inlineStr">
-        <is>
-          <t>OKVED_J_UstKap</t>
-        </is>
-      </c>
-    </row>
-    <row r="1739">
-      <c r="A1739" t="inlineStr">
-        <is>
-          <t>OKVED_J_Pri(ubOtPro</t>
-        </is>
-      </c>
-    </row>
-    <row r="1740">
-      <c r="A1740" t="inlineStr">
-        <is>
-          <t>OKVED_J_ChiPri(ubOtcPer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1741">
-      <c r="A1741" t="inlineStr">
-        <is>
-          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
-        </is>
-      </c>
-    </row>
-    <row r="1742">
-      <c r="A1742" t="inlineStr">
-        <is>
-          <t>OKVED_63_UstKap</t>
-        </is>
-      </c>
-    </row>
-    <row r="1743">
-      <c r="A1743" t="inlineStr">
-        <is>
-          <t>OKVED_63_Pri(ubOtPro</t>
-        </is>
-      </c>
-    </row>
-    <row r="1744">
-      <c r="A1744" t="inlineStr">
-        <is>
-          <t>OKVED_63_ChiPri(ubOtcPer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1745">
-      <c r="A1745" t="inlineStr">
-        <is>
-          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
-        </is>
-      </c>
-    </row>
-    <row r="1746">
-      <c r="A1746" t="inlineStr">
-        <is>
-          <t>OKVED_69_UstKap</t>
-        </is>
-      </c>
-    </row>
-    <row r="1747">
-      <c r="A1747" t="inlineStr">
-        <is>
-          <t>OKVED_69_ChiAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="1748">
-      <c r="A1748" t="inlineStr">
-        <is>
-          <t>OKVED_O_UstKap</t>
-        </is>
-      </c>
-    </row>
-    <row r="1749">
-      <c r="A1749" t="inlineStr">
-        <is>
-          <t>OKVED_84_UstKap</t>
-        </is>
-      </c>
-    </row>
-    <row r="1750">
-      <c r="A1750" t="inlineStr">
-        <is>
-          <t>OKVED_85_UstKap</t>
-        </is>
-      </c>
-    </row>
-    <row r="1751">
-      <c r="A1751" t="inlineStr">
-        <is>
-          <t>OKVED_Q_UstKap</t>
-        </is>
-      </c>
-    </row>
-    <row r="1752">
-      <c r="A1752" t="inlineStr">
-        <is>
-          <t>OKVED_Q_Pri(ubOtPro</t>
-        </is>
-      </c>
-    </row>
-    <row r="1753">
-      <c r="A1753" t="inlineStr">
-        <is>
-          <t>OKVED_Q_ChiPri(ubOtcPer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1754">
-      <c r="A1754" t="inlineStr">
-        <is>
-          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
-        </is>
-      </c>
-    </row>
-    <row r="1755">
-      <c r="A1755" t="inlineStr">
-        <is>
-          <t>OKVED_88_UstKap</t>
-        </is>
-      </c>
-    </row>
-    <row r="1756">
-      <c r="A1756" t="inlineStr">
-        <is>
-          <t>OKVED_88_Pri(ubOtPro</t>
-        </is>
-      </c>
-    </row>
-    <row r="1757">
-      <c r="A1757" t="inlineStr">
-        <is>
-          <t>OKVED_88_ChiPri(ubOtcPer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1758">
-      <c r="A1758" t="inlineStr">
         <is>
           <t>OKVED_88_PriUby(-DoNalKChiAktV%</t>
         </is>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1714"/>
+  <dimension ref="A1:A1661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9393,3022 +9393,2651 @@
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>OKVED_01_PrPostDeyt</t>
+          <t>OKVED_32_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>OKVED_B_PrPostDeyt</t>
+          <t>OKVED_E_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>OKVED_07_PrPostDeyt</t>
+          <t>OKVED_36_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPostDeyt</t>
+          <t>OKVED_38_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>OKVED_32_ArendPlDeVsego</t>
+          <t>OKVED_41_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>OKVED_32_PrPostDeyt</t>
+          <t>OKVED_43_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>OKVED_33_PrPostDeyt</t>
+          <t>OKVED_49_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>OKVED_35_PrPostDeyt</t>
+          <t>OKVED_50_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>OKVED_E_ArendPlDeVsego</t>
+          <t>OKVED_I_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>OKVED_36_ArendPlDeVsego</t>
+          <t>OKVED_55_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>OKVED_38_ArendPlDeVsego</t>
+          <t>OKVED_56_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>OKVED_41_ArendPlDeVsego</t>
+          <t>OKVED_J_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>OKVED_43_ArendPlDeVsego</t>
+          <t>OKVED_J_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPostDeyt</t>
+          <t>OKVED_63_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>OKVED_G_PrPostDeyt</t>
+          <t>OKVED_63_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>OKVED_46_PrPostDeyt</t>
+          <t>OKVED_64_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>OKVED_H_PrPostDeyt</t>
+          <t>OKVED_69_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>OKVED_49_ArendPlDeVsego</t>
+          <t>OKVED_79_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPostDeyt</t>
+          <t>OKVED_81_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>OKVED_50_ArendPlDeVsego</t>
+          <t>OKVED_82_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>OKVED_50_PrPostDeyt</t>
+          <t>OKVED_O_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>OKVED_51_PrPostDeyt</t>
+          <t>OKVED_84_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>OKVED_52_PrPostDeyt</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>OKVED_I_ArendPlDeVsego</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>OKVED_55_ArendPlDeVsego</t>
+          <t>OKVED_88_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>OKVED_56_ArendPlDeVsego</t>
+          <t>OKVED_88_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>OKVED_56_PrPostDeyt</t>
+          <t>OKVED_R_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>OKVED_J_OtProdDeVsego</t>
+          <t>OKVED_R_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>OKVED_J_ArendPlDeVsego</t>
+          <t>OKVED_93_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>OKVED_J_PrPostDeyt</t>
+          <t>OKVED_93_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>OKVED_63_OtProdDeVsego</t>
+          <t>OKVED_S_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>OKVED_63_ArendPlDeVsego</t>
+          <t>OKVED_94_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>OKVED_63_PrPostDeyt</t>
+          <t>OKVED_96_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>OKVED_64_ArendPlDeVsego</t>
+          <t>OKVED_11_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPostDeyt</t>
+          <t>OKVED_32_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>OKVED_M_PrPostDeyt</t>
+          <t>OKVED_32_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>OKVED_69_ArendPlDeVsego</t>
+          <t>OKVED_33_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>OKVED_69_PrPostDeyt</t>
+          <t>OKVED_36_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPostDeyt</t>
+          <t>OKVED_38_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>OKVED_71_PrPostDeyt</t>
+          <t>OKVED_49_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>OKVED_74_PrPostDeyt</t>
+          <t>OKVED_56_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>OKVED_79_ArendPlDeVsego</t>
+          <t>OKVED_56_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>OKVED_81_ArendPlDeVsego</t>
+          <t>OKVED_J_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>OKVED_81_PrPostDeyt</t>
+          <t>OKVED_J_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>OKVED_82_ArendPlDeVsego</t>
+          <t>OKVED_63_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>OKVED_82_PrPostDeyt</t>
+          <t>OKVED_63_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>OKVED_O_ArendPlDeVsego</t>
+          <t>OKVED_M_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>OKVED_O_PrPostDeyt</t>
+          <t>OKVED_69_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>OKVED_84_ArendPlDeVsego</t>
+          <t>OKVED_69_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>OKVED_84_PrPostDeyt</t>
+          <t>OKVED_71_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_71_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPostDeyt</t>
+          <t>OKVED_74_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_77_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>OKVED_85_PrPostDeyt</t>
+          <t>OKVED_79_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>OKVED_88_OtProdDeVsego</t>
+          <t>OKVED_81_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>OKVED_88_ArendPlDeVsego</t>
+          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>OKVED_88_PrPostDeyt</t>
+          <t>OKVED_O_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>OKVED_R_OtProdDeVsego</t>
+          <t>OKVED_O_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>OKVED_R_ArendPlDeVsego</t>
+          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>OKVED_R_PrPostDeyt</t>
+          <t>OKVED_84_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>OKVED_93_OtProdDeVsego</t>
+          <t>OKVED_84_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>OKVED_93_ArendPlDeVsego</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>OKVED_93_PrPostDeyt</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>OKVED_S_ArendPlDeVsego</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>OKVED_94_ArendPlDeVsego</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>OKVED_96_ArendPlDeVsego</t>
+          <t>OKVED_Q_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>OKVED_96_PrPostDeyt</t>
+          <t>OKVED_Q_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcPoDolgObyaz</t>
+          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>OKVED_32_ProcPoDolgObyaz</t>
+          <t>OKVED_R_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>OKVED_32_NalogNaPri</t>
+          <t>OKVED_R_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>OKVED_33_NalogNaPri</t>
+          <t>OKVED_R_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcPoDolgObyaz</t>
+          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>OKVED_38_NalogNaPri</t>
+          <t>OKVED_93_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcPoDolgObyaz</t>
+          <t>OKVED_93_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>OKVED_56_ProcPoDolgObyaz</t>
+          <t>OKVED_93_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>OKVED_56_NalogNaPri</t>
+          <t>OKVED_96_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>OKVED_J_ProcPoDolgObyaz</t>
+          <t>OKVED_96_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>OKVED_J_NalogNaPri</t>
+          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>OKVED_63_ProcPoDolgObyaz</t>
+          <t>OKVED_01_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>OKVED_63_NalogNaPri</t>
+          <t>OKVED_01_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>OKVED_M_ProcPoDolgObyaz</t>
+          <t>OKVED_B_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>OKVED_69_ProcPoDolgObyaz</t>
+          <t>OKVED_07_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>OKVED_69_NalogNaPri</t>
+          <t>OKVED_C_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>OKVED_71_ProcPoDolgObyaz</t>
+          <t>OKVED_10_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>OKVED_71_NalogNaPri</t>
+          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>OKVED_74_ProcPoDolgObyaz</t>
+          <t>OKVED_11_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcPoDolgObyaz</t>
+          <t>OKVED_11_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>OKVED_79_NalogNaPri</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>OKVED_81_NalogNaPri</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_E_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>OKVED_O_VSvyaziSOplTrudRab</t>
+          <t>OKVED_E_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>OKVED_O_ProcPoDolgObyaz</t>
+          <t>OKVED_E_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_36_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>OKVED_84_VSvyaziSOplTrudRab</t>
+          <t>OKVED_36_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>OKVED_84_ProcPoDolgObyaz</t>
+          <t>OKVED_36_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_38_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_38_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_38_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>OKVED_Q_ProcPoDolgObyaz</t>
+          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>OKVED_Q_NalogNaPri</t>
+          <t>OKVED_F_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>OKVED_R_VSvyaziSOplTrudRab</t>
+          <t>OKVED_41_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>OKVED_R_ProcPoDolgObyaz</t>
+          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>OKVED_R_NalogNaPri</t>
+          <t>OKVED_43_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_43_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>OKVED_93_VSvyaziSOplTrudRab</t>
+          <t>OKVED_G_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>OKVED_93_ProcPoDolgObyaz</t>
+          <t>OKVED_46_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>OKVED_93_NalogNaPri</t>
+          <t>OKVED_47_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>OKVED_96_ProcPoDolgObyaz</t>
+          <t>OKVED_H_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>OKVED_96_NalogNaPri</t>
+          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_49_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdAkcOrgDolUch</t>
+          <t>OKVED_49_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>OKVED_01_DivProcDolgFinVlozh</t>
+          <t>OKVED_52_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>OKVED_01_PrPostDeyt</t>
+          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>OKVED_B_OtProdAkcOrgDolUch</t>
+          <t>OKVED_I_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>OKVED_B_PrPostDeyt</t>
+          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>OKVED_07_OtProdAkcOrgDolUch</t>
+          <t>OKVED_55_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>OKVED_07_PrPostDeyt</t>
+          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>OKVED_C_OtProdAkcOrgDolUch</t>
+          <t>OKVED_K_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>OKVED_10_OtProdAkcOrgDolUch</t>
+          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_64_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdAkcOrgDolUch</t>
+          <t>OKVED_L_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdFinVlozh</t>
+          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>OKVED_11_PrPostDeyt</t>
+          <t>OKVED_M_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>OKVED_35_PrPostDeyt</t>
+          <t>OKVED_70_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>OKVED_35_PrPostDeyt</t>
+          <t>OKVED_71_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdAkcOrgDolUch</t>
+          <t>OKVED_71_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdFinVlozh</t>
+          <t>OKVED_N_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>OKVED_E_DivProcDolgFinVlozh</t>
+          <t>OKVED_N_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdAkcOrgDolUch</t>
+          <t>OKVED_77_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdFinVlozh</t>
+          <t>OKVED_77_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>OKVED_36_DivProcDolgFinVlozh</t>
+          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_S_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdAkcOrgDolUch</t>
+          <t>OKVED_S_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdFinVlozh</t>
+          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>OKVED_38_DivProcDolgFinVlozh</t>
+          <t>OKVED_94_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_94_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_01_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdAkcOrgDolUch</t>
+          <t>OKVED_B_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdAkcOrgDolUch</t>
+          <t>OKVED_C_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdFinVlozh</t>
+          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>OKVED_43_PrPostDeyt</t>
+          <t>OKVED_10_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>OKVED_G_OtProdAkcOrgDolUch</t>
+          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>OKVED_G_PrPostDeyt</t>
+          <t>OKVED_11_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>OKVED_46_OtProdAkcOrgDolUch</t>
+          <t>OKVED_11_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>OKVED_46_PrPostDeyt</t>
+          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>OKVED_47_OtProdAkcOrgDolUch</t>
+          <t>OKVED_33_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>OKVED_47_PrPostDeyt</t>
+          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>OKVED_H_OtProdAkcOrgDolUch</t>
+          <t>OKVED_E_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>OKVED_H_PrPostDeyt</t>
+          <t>OKVED_E_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdAkcOrgDolUch</t>
+          <t>OKVED_36_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>OKVED_49_DivProcDolgFinVlozh</t>
+          <t>OKVED_36_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>OKVED_49_PrPostDeyt</t>
+          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>OKVED_52_OtProdAkcOrgDolUch</t>
+          <t>OKVED_F_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>OKVED_52_PrPostDeyt</t>
+          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_41_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdAkcOrgDolUch</t>
+          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_42_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdAkcOrgDolUch</t>
+          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_43_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>OKVED_K_PrPostDeyt</t>
+          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_47_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdAkcOrgDolUch</t>
+          <t>OKVED_H_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>OKVED_64_PrPostDeyt</t>
+          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>OKVED_L_OtProdAkcOrgDolUch</t>
+          <t>OKVED_49_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdAkcOrgDolUch</t>
+          <t>OKVED_50_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>OKVED_M_PrPostDeyt</t>
+          <t>OKVED_50_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdAkcOrgDolUch</t>
+          <t>OKVED_52_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>OKVED_70_PrPostDeyt</t>
+          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdAkcOrgDolUch</t>
+          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>OKVED_71_DivProcDolgFinVlozh</t>
+          <t>OKVED_K_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>OKVED_71_PrPostDeyt</t>
+          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdAkcOrgDolUch</t>
+          <t>OKVED_M_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdFinVlozh</t>
+          <t>OKVED_71_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdAkcOrgDolUch</t>
+          <t>OKVED_N_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdFinVlozh</t>
+          <t>OKVED_N_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>OKVED_77_PrPostDeyt</t>
+          <t>OKVED_79_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_79_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdAkcOrgDolUch</t>
+          <t>OKVED_S_Modern</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>OKVED_S_DivProcDolgFinVlozh</t>
+          <t>OKVED_S_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdAkcOrgDolUch</t>
+          <t>OKVED_94_Modern</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>OKVED_94_DivProcDolgFinVlozh</t>
+          <t>OKVED_94_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>OKVED_01_DolUch</t>
+          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_01_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>OKVED_B_DolUch</t>
+          <t>OKVED_01_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_B_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>OKVED_C_DolUch</t>
+          <t>OKVED_B_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_07_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>OKVED_10_DolUch</t>
+          <t>OKVED_07_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_C_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>OKVED_11_DolUch</t>
+          <t>OKVED_10_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>OKVED_11_PrCenBum</t>
+          <t>OKVED_32_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_32_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>OKVED_33_DolUch</t>
+          <t>OKVED_32_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_33_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>OKVED_E_DolUch</t>
+          <t>OKVED_33_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>OKVED_E_PrCenBum</t>
+          <t>OKVED_33_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>OKVED_36_DolUch</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>OKVED_36_PrCenBum</t>
+          <t>OKVED_38_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_38_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>OKVED_F_DolUch</t>
+          <t>OKVED_F_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_41_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>OKVED_41_DolUch</t>
+          <t>OKVED_41_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_42_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>OKVED_42_DolUch</t>
+          <t>OKVED_42_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_42_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>OKVED_43_DolUch</t>
+          <t>OKVED_43_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>OKVED_43_PrCenBum</t>
+          <t>OKVED_43_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_G_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>OKVED_47_DolUch</t>
+          <t>OKVED_G_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>OKVED_H_DolUch</t>
+          <t>OKVED_46_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_46_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>OKVED_49_DolUch</t>
+          <t>OKVED_47_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_47_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>OKVED_50_DolUch</t>
+          <t>OKVED_H_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>OKVED_50_PrCenBum</t>
+          <t>OKVED_50_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_50_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>OKVED_52_DolUch</t>
+          <t>OKVED_50_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_51_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_51_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_51_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>OKVED_K_DolUch</t>
+          <t>OKVED_52_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_I_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>OKVED_M_DolUch</t>
+          <t>OKVED_I_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>OKVED_71_DolUch</t>
+          <t>OKVED_55_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>OKVED_N_DolUch</t>
+          <t>OKVED_55_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>OKVED_N_PrCenBum</t>
+          <t>OKVED_K_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>OKVED_79_DolUch</t>
+          <t>OKVED_K_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>OKVED_79_PrCenBum</t>
+          <t>OKVED_K_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>OKVED_S_Modern</t>
+          <t>OKVED_64_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>OKVED_S_DolUch</t>
+          <t>OKVED_64_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_64_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>OKVED_94_Modern</t>
+          <t>OKVED_L_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>OKVED_94_DolUch</t>
+          <t>OKVED_68_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_70_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>OKVED_01_PostDeyt1</t>
+          <t>OKVED_70_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>OKVED_01_DrPost</t>
+          <t>OKVED_71_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt</t>
+          <t>OKVED_74_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt1</t>
+          <t>OKVED_74_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt</t>
+          <t>OKVED_74_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt1</t>
+          <t>OKVED_N_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>OKVED_C_PostDeyt1</t>
+          <t>OKVED_N_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>OKVED_10_PostDeyt1</t>
+          <t>OKVED_79_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>OKVED_32_PlCredit</t>
+          <t>OKVED_79_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt</t>
+          <t>OKVED_79_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt1</t>
+          <t>OKVED_81_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt</t>
+          <t>OKVED_81_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt1</t>
+          <t>OKVED_81_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>OKVED_33_DrPost</t>
+          <t>OKVED_S_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_S_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_94_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>OKVED_38_PostDeyt1</t>
+          <t>OKVED_94_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>OKVED_38_DrPost</t>
+          <t>OKVED_01_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>OKVED_F_PostDeyt1</t>
+          <t>OKVED_01_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt</t>
+          <t>OKVED_B_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt1</t>
+          <t>OKVED_07_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt</t>
+          <t>OKVED_33_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt1</t>
+          <t>OKVED_33_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>OKVED_42_DrPost</t>
+          <t>OKVED_33_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>OKVED_43_PostDeyt1</t>
+          <t>OKVED_33_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>OKVED_43_DrPost</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt1</t>
+          <t>OKVED_E_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt</t>
+          <t>OKVED_E_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt1</t>
+          <t>OKVED_38_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt</t>
+          <t>OKVED_38_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt1</t>
+          <t>OKVED_F_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>OKVED_H_PostDeyt1</t>
+          <t>OKVED_41_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt</t>
+          <t>OKVED_43_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt1</t>
+          <t>OKVED_43_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>OKVED_50_DrPost</t>
+          <t>OKVED_G_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt</t>
+          <t>OKVED_46_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt1</t>
+          <t>OKVED_47_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>OKVED_51_DrPost</t>
+          <t>OKVED_H_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>OKVED_52_PostDeyt1</t>
+          <t>OKVED_49_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>OKVED_I_PostDeyt1</t>
+          <t>OKVED_49_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>OKVED_I_DrPost</t>
+          <t>OKVED_50_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>OKVED_55_PostDeyt1</t>
+          <t>OKVED_52_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>OKVED_55_DrPost</t>
+          <t>OKVED_I_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt</t>
+          <t>OKVED_I_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt1</t>
+          <t>OKVED_55_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>OKVED_K_DrPost</t>
+          <t>OKVED_55_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt</t>
+          <t>OKVED_K_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt1</t>
+          <t>OKVED_64_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>OKVED_64_DrPost</t>
+          <t>OKVED_68_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>OKVED_L_PostDeyt1</t>
+          <t>OKVED_M_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>OKVED_68_PostDeyt1</t>
+          <t>OKVED_70_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>OKVED_70_PlCredit</t>
+          <t>OKVED_70_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>OKVED_70_PostDeyt</t>
+          <t>OKVED_70_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>OKVED_71_PostDeyt</t>
+          <t>OKVED_70_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt</t>
+          <t>OKVED_71_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt1</t>
+          <t>OKVED_74_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>OKVED_74_DrPost</t>
+          <t>OKVED_74_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt</t>
+          <t>OKVED_74_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt1</t>
+          <t>OKVED_74_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt</t>
+          <t>OKVED_79_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt1</t>
+          <t>OKVED_79_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>OKVED_79_DrPost</t>
+          <t>OKVED_81_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>OKVED_81_PlCredit</t>
+          <t>OKVED_81_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt</t>
+          <t>OKVED_81_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt1</t>
+          <t>OKVED_81_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>OKVED_S_PlCredit</t>
+          <t>OKVED_S_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>OKVED_S_PostDeyt1</t>
+          <t>OKVED_S_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>OKVED_94_PlCredit</t>
+          <t>OKVED_S_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>OKVED_94_PostDeyt1</t>
+          <t>OKVED_94_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin1</t>
+          <t>OKVED_94_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin2</t>
+          <t>OKVED_94_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>OKVED_B_PlPoFin1</t>
+          <t>OKVED_01_Velch</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>OKVED_07_PlPoFin1</t>
+          <t>OKVED_11_Velch</t>
         </is>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin</t>
+          <t>OKVED_32_Velch</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin1</t>
+          <t>OKVED_33_Velch</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin2</t>
+          <t>OKVED_E_Velch</t>
         </is>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin3</t>
+          <t>OKVED_38_Velch</t>
         </is>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_F_Velch</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_41_Velch</t>
         </is>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin1</t>
+          <t>OKVED_42_Velch</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin2</t>
+          <t>OKVED_43_Velch</t>
         </is>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin1</t>
+          <t>OKVED_47_Velch</t>
         </is>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin2</t>
+          <t>OKVED_49_Velch</t>
         </is>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>OKVED_F_PlPoFin1</t>
+          <t>OKVED_I_Velch</t>
         </is>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>OKVED_41_PlPoFin1</t>
+          <t>OKVED_56_Velch</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin1</t>
+          <t>OKVED_J_Velch</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin2</t>
+          <t>OKVED_63_Velch</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>OKVED_G_PlPoFin1</t>
+          <t>OKVED_L_Velch</t>
         </is>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>OKVED_46_PlPoFin1</t>
+          <t>OKVED_68_Velch</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>OKVED_47_PlPoFin1</t>
+          <t>OKVED_M_Velch</t>
         </is>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
         <is>
-          <t>OKVED_H_PlPoFin1</t>
+          <t>OKVED_69_Velch</t>
         </is>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin1</t>
+          <t>OKVED_70_Velch</t>
         </is>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin2</t>
+          <t>OKVED_71_Velch</t>
         </is>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoFin1</t>
+          <t>OKVED_N_Velch</t>
         </is>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>OKVED_52_PlPoFin1</t>
+          <t>OKVED_77_Velch</t>
         </is>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin1</t>
+          <t>OKVED_79_Velch</t>
         </is>
       </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin2</t>
+          <t>OKVED_81_Velch</t>
         </is>
       </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin1</t>
+          <t>OKVED_82_Velch</t>
         </is>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin2</t>
+          <t>OKVED_O_Velch</t>
         </is>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoFin1</t>
+          <t>OKVED_84_Velch</t>
         </is>
       </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoFin1</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>OKVED_68_PlPoFin1</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>OKVED_M_PlPoFin1</t>
+          <t>OKVED_88_Velch</t>
         </is>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin</t>
+          <t>OKVED_R_Velch</t>
         </is>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin1</t>
+          <t>OKVED_93_Velch</t>
         </is>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin2</t>
+          <t>OKVED_S_Velch</t>
         </is>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin3</t>
+          <t>OKVED_94_Velch</t>
         </is>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>OKVED_71_PlPoFin1</t>
+          <t>OKVED_96_Velch</t>
         </is>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin1</t>
+          <t>OKVED_43_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin2</t>
+          <t>OKVED_43_ChiAkt</t>
         </is>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin3</t>
+          <t>OKVED_J_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>OKVED_74_SaldoDenPot</t>
+          <t>OKVED_J_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin1</t>
+          <t>OKVED_J_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin2</t>
+          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin1</t>
+          <t>OKVED_63_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin2</t>
+          <t>OKVED_63_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin3</t>
+          <t>OKVED_63_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>OKVED_81_SaldoDenPot</t>
+          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin1</t>
+          <t>OKVED_69_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin2</t>
+          <t>OKVED_69_ChiAkt</t>
         </is>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin3</t>
+          <t>OKVED_O_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin1</t>
+          <t>OKVED_84_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin2</t>
+          <t>OKVED_85_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin3</t>
+          <t>OKVED_Q_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
         <is>
-          <t>OKVED_01_Velch</t>
+          <t>OKVED_Q_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
         <is>
-          <t>OKVED_11_Velch</t>
+          <t>OKVED_Q_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
         <is>
-          <t>OKVED_32_Velch</t>
+          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
         <is>
-          <t>OKVED_33_Velch</t>
+          <t>OKVED_88_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
         <is>
-          <t>OKVED_E_Velch</t>
+          <t>OKVED_88_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
         <is>
-          <t>OKVED_38_Velch</t>
+          <t>OKVED_88_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
-        <is>
-          <t>OKVED_F_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1662">
-      <c r="A1662" t="inlineStr">
-        <is>
-          <t>OKVED_41_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1663">
-      <c r="A1663" t="inlineStr">
-        <is>
-          <t>OKVED_42_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1664">
-      <c r="A1664" t="inlineStr">
-        <is>
-          <t>OKVED_43_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1665">
-      <c r="A1665" t="inlineStr">
-        <is>
-          <t>OKVED_47_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1666">
-      <c r="A1666" t="inlineStr">
-        <is>
-          <t>OKVED_49_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1667">
-      <c r="A1667" t="inlineStr">
-        <is>
-          <t>OKVED_I_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1668">
-      <c r="A1668" t="inlineStr">
-        <is>
-          <t>OKVED_56_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1669">
-      <c r="A1669" t="inlineStr">
-        <is>
-          <t>OKVED_J_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1670">
-      <c r="A1670" t="inlineStr">
-        <is>
-          <t>OKVED_63_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1671">
-      <c r="A1671" t="inlineStr">
-        <is>
-          <t>OKVED_L_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1672">
-      <c r="A1672" t="inlineStr">
-        <is>
-          <t>OKVED_68_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1673">
-      <c r="A1673" t="inlineStr">
-        <is>
-          <t>OKVED_M_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1674">
-      <c r="A1674" t="inlineStr">
-        <is>
-          <t>OKVED_69_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1675">
-      <c r="A1675" t="inlineStr">
-        <is>
-          <t>OKVED_70_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1676">
-      <c r="A1676" t="inlineStr">
-        <is>
-          <t>OKVED_71_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1677">
-      <c r="A1677" t="inlineStr">
-        <is>
-          <t>OKVED_N_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1678">
-      <c r="A1678" t="inlineStr">
-        <is>
-          <t>OKVED_77_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1679">
-      <c r="A1679" t="inlineStr">
-        <is>
-          <t>OKVED_79_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1680">
-      <c r="A1680" t="inlineStr">
-        <is>
-          <t>OKVED_81_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1681">
-      <c r="A1681" t="inlineStr">
-        <is>
-          <t>OKVED_82_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1682">
-      <c r="A1682" t="inlineStr">
-        <is>
-          <t>OKVED_O_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1683">
-      <c r="A1683" t="inlineStr">
-        <is>
-          <t>OKVED_84_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1684">
-      <c r="A1684" t="inlineStr">
-        <is>
-          <t>OKVED_85_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1685">
-      <c r="A1685" t="inlineStr">
-        <is>
-          <t>OKVED_85_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1686">
-      <c r="A1686" t="inlineStr">
-        <is>
-          <t>OKVED_88_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1687">
-      <c r="A1687" t="inlineStr">
-        <is>
-          <t>OKVED_R_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1688">
-      <c r="A1688" t="inlineStr">
-        <is>
-          <t>OKVED_93_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1689">
-      <c r="A1689" t="inlineStr">
-        <is>
-          <t>OKVED_S_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1690">
-      <c r="A1690" t="inlineStr">
-        <is>
-          <t>OKVED_94_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1691">
-      <c r="A1691" t="inlineStr">
-        <is>
-          <t>OKVED_96_Velch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1692">
-      <c r="A1692" t="inlineStr">
-        <is>
-          <t>OKVED_43_UstKap</t>
-        </is>
-      </c>
-    </row>
-    <row r="1693">
-      <c r="A1693" t="inlineStr">
-        <is>
-          <t>OKVED_43_ChiAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="1694">
-      <c r="A1694" t="inlineStr">
-        <is>
-          <t>OKVED_J_UstKap</t>
-        </is>
-      </c>
-    </row>
-    <row r="1695">
-      <c r="A1695" t="inlineStr">
-        <is>
-          <t>OKVED_J_Pri(ubOtPro</t>
-        </is>
-      </c>
-    </row>
-    <row r="1696">
-      <c r="A1696" t="inlineStr">
-        <is>
-          <t>OKVED_J_ChiPri(ubOtcPer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1697">
-      <c r="A1697" t="inlineStr">
-        <is>
-          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
-        </is>
-      </c>
-    </row>
-    <row r="1698">
-      <c r="A1698" t="inlineStr">
-        <is>
-          <t>OKVED_63_UstKap</t>
-        </is>
-      </c>
-    </row>
-    <row r="1699">
-      <c r="A1699" t="inlineStr">
-        <is>
-          <t>OKVED_63_Pri(ubOtPro</t>
-        </is>
-      </c>
-    </row>
-    <row r="1700">
-      <c r="A1700" t="inlineStr">
-        <is>
-          <t>OKVED_63_ChiPri(ubOtcPer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1701">
-      <c r="A1701" t="inlineStr">
-        <is>
-          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
-        </is>
-      </c>
-    </row>
-    <row r="1702">
-      <c r="A1702" t="inlineStr">
-        <is>
-          <t>OKVED_69_UstKap</t>
-        </is>
-      </c>
-    </row>
-    <row r="1703">
-      <c r="A1703" t="inlineStr">
-        <is>
-          <t>OKVED_69_ChiAkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="1704">
-      <c r="A1704" t="inlineStr">
-        <is>
-          <t>OKVED_O_UstKap</t>
-        </is>
-      </c>
-    </row>
-    <row r="1705">
-      <c r="A1705" t="inlineStr">
-        <is>
-          <t>OKVED_84_UstKap</t>
-        </is>
-      </c>
-    </row>
-    <row r="1706">
-      <c r="A1706" t="inlineStr">
-        <is>
-          <t>OKVED_85_UstKap</t>
-        </is>
-      </c>
-    </row>
-    <row r="1707">
-      <c r="A1707" t="inlineStr">
-        <is>
-          <t>OKVED_Q_UstKap</t>
-        </is>
-      </c>
-    </row>
-    <row r="1708">
-      <c r="A1708" t="inlineStr">
-        <is>
-          <t>OKVED_Q_Pri(ubOtPro</t>
-        </is>
-      </c>
-    </row>
-    <row r="1709">
-      <c r="A1709" t="inlineStr">
-        <is>
-          <t>OKVED_Q_ChiPri(ubOtcPer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1710">
-      <c r="A1710" t="inlineStr">
-        <is>
-          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
-        </is>
-      </c>
-    </row>
-    <row r="1711">
-      <c r="A1711" t="inlineStr">
-        <is>
-          <t>OKVED_88_UstKap</t>
-        </is>
-      </c>
-    </row>
-    <row r="1712">
-      <c r="A1712" t="inlineStr">
-        <is>
-          <t>OKVED_88_Pri(ubOtPro</t>
-        </is>
-      </c>
-    </row>
-    <row r="1713">
-      <c r="A1713" t="inlineStr">
-        <is>
-          <t>OKVED_88_ChiPri(ubOtcPer</t>
-        </is>
-      </c>
-    </row>
-    <row r="1714">
-      <c r="A1714" t="inlineStr">
         <is>
           <t>OKVED_88_PriUby(-DoNalKChiAktV%</t>
         </is>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1693"/>
+  <dimension ref="A1:A1701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12130,140 +12130,196 @@
     <row r="1674">
       <c r="A1674" t="inlineStr">
         <is>
-          <t>OKVED_J_Pri(ubOtPro</t>
+          <t>OKVED_J_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
         <is>
-          <t>OKVED_J_ChiPri(ubOtcPer</t>
+          <t>OKVED_J_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_J_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap</t>
+          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
         <is>
-          <t>OKVED_63_Pri(ubOtPro</t>
+          <t>OKVED_63_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
         <is>
-          <t>OKVED_63_ChiPri(ubOtcPer</t>
+          <t>OKVED_63_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_63_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap</t>
+          <t>OKVED_63_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
         <is>
-          <t>OKVED_69_ChiAkt</t>
+          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap</t>
+          <t>OKVED_K_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap</t>
+          <t>OKVED_69_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap</t>
+          <t>OKVED_69_ChiAkt</t>
         </is>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap</t>
+          <t>OKVED_69_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>OKVED_Q_Pri(ubOtPro</t>
+          <t>OKVED_O_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>OKVED_Q_ChiPri(ubOtcPer</t>
+          <t>OKVED_84_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_85_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap</t>
+          <t>OKVED_Q_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>OKVED_88_Pri(ubOtPro</t>
+          <t>OKVED_Q_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>OKVED_88_ChiPri(ubOtcPer</t>
+          <t>OKVED_Q_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
+          <t>OKVED_Q_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>OKVED_88_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>OKVED_88_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>OKVED_88_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>OKVED_88_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
           <t>OKVED_88_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>OKVED_R_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>OKVED_93_SebPro</t>
         </is>
       </c>
     </row>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1703"/>
+  <dimension ref="A1:A1718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6880,5458 +6880,5563 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>OKVED_32_OtcGoOtlNalNaPri</t>
+          <t>OKVED_32_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>OKVED_33_OtcGoPro</t>
+          <t>OKVED_32_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoOtlNalNaPri</t>
+          <t>OKVED_33_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoPro</t>
+          <t>OKVED_38_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>OKVED_42_OtcGoPro</t>
+          <t>OKVED_38_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>OKVED_43_OtcGoPro</t>
+          <t>OKVED_38_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>OKVED_50_OtcGoPro</t>
+          <t>OKVED_42_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>OKVED_56_OtcGoOtlNalNaPri</t>
+          <t>OKVED_43_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoOtlNalNaPri</t>
+          <t>OKVED_50_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoPro</t>
+          <t>OKVED_50_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>OKVED_74_OtcGoPro</t>
+          <t>OKVED_56_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>OKVED_77_OtcGoPro</t>
+          <t>OKVED_56_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>OKVED_79_OtcGoPro</t>
+          <t>OKVED_69_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>OKVED_O_OtcGoOtlNalNaPri</t>
+          <t>OKVED_69_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>OKVED_O_OtcGoPro</t>
+          <t>OKVED_69_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>OKVED_84_OtcGoOtlNalNaPri</t>
+          <t>OKVED_71_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>OKVED_84_OtcGoPro</t>
+          <t>OKVED_74_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoPro</t>
+          <t>OKVED_74_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoPro</t>
+          <t>OKVED_77_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoSalProDohIRas</t>
+          <t>OKVED_79_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoOtlNalNaPri</t>
+          <t>OKVED_79_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoPro</t>
+          <t>OKVED_O_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoSalProDohIRas</t>
+          <t>OKVED_O_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoOtlNalNaPri</t>
+          <t>OKVED_84_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoPro</t>
+          <t>OKVED_84_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>OKVED_S_OtcGoPro</t>
+          <t>OKVED_85_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>OKVED_94_OtcGoPro</t>
+          <t>OKVED_85_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>OKVED_96_OtcGoPro</t>
+          <t>OKVED_85_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>OKVED_01_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_85_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>OKVED_B_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_R_OtcGoSalProDohIRas</t>
         </is>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>OKVED_B_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_R_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>OKVED_07_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_R_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>OKVED_07_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_R_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>OKVED_10_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_93_OtcGoSalProDohIRas</t>
         </is>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>OKVED_11_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_93_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>OKVED_11_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_93_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>OKVED_32_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_93_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>OKVED_33_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_S_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>OKVED_33_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_94_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>OKVED_35_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_96_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>OKVED_35_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_01_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>OKVED_35_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_B_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>OKVED_35_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_B_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>OKVED_36_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_07_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>OKVED_36_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_07_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_10_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_11_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>OKVED_F_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_11_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>OKVED_41_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_32_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>OKVED_41_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_33_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>OKVED_42_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_33_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>OKVED_43_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_35_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>OKVED_43_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_35_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>OKVED_G_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_35_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>OKVED_G_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_35_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>OKVED_46_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_36_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>OKVED_46_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_36_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>OKVED_47_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_38_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>OKVED_47_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_38_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>OKVED_50_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_F_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>OKVED_50_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_41_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>OKVED_52_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_41_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>OKVED_52_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_42_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>OKVED_I_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_43_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>OKVED_I_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_43_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>OKVED_55_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_G_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>OKVED_55_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_G_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>OKVED_56_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_46_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>OKVED_56_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_46_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>OKVED_K_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_47_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>OKVED_K_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_47_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>OKVED_64_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_50_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>OKVED_64_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_50_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>OKVED_L_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_52_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>OKVED_L_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_52_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>OKVED_68_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_I_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>OKVED_68_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_I_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>OKVED_M_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_55_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>OKVED_M_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_55_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_56_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_56_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>OKVED_71_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_K_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>OKVED_71_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_K_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>OKVED_74_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_64_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>OKVED_74_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_64_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>OKVED_N_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_L_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>OKVED_N_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_L_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>OKVED_77_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_68_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>OKVED_77_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_68_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>OKVED_79_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_M_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>OKVED_79_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_M_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>OKVED_81_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_69_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>OKVED_81_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_69_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>OKVED_82_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_71_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>OKVED_82_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_71_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>OKVED_84_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_74_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>OKVED_84_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_74_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_N_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_N_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_77_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_77_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_79_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_79_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_81_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_81_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>OKVED_S_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_82_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>OKVED_S_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_82_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>OKVED_94_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_84_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>OKVED_94_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_84_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>OKVED_96_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_85_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>OKVED_96_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_85_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerVyr_1</t>
+          <t>OKVED_85_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerKomIUprRas_1</t>
+          <t>OKVED_85_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>MO_30851_OtcGoPro_1</t>
+          <t>OKVED_R_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>MO_30501_OtcGoOtlNalNaPri_1</t>
+          <t>OKVED_R_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>MO_30501_OtcGoPro_1</t>
+          <t>OKVED_93_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>MO_30510_OtcGoSalProDohIRas_1</t>
+          <t>OKVED_93_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>MO_30510_OtcGoOtlNalNaPri_1</t>
+          <t>OKVED_S_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>MO_30510_OtcGoPro_1</t>
+          <t>OKVED_S_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>MO_30604_OtcGoPri(ubDoNal_1</t>
+          <t>OKVED_94_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>MO_30604_OtcGoOtlNalNaPri_1</t>
+          <t>OKVED_94_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>MO_30604_OtcGoPro_1</t>
+          <t>OKVED_96_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>MO_30832_OtcGoPro_1</t>
+          <t>OKVED_96_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>OKVED_11_OrgPolUbyKolOrgEdi</t>
+          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerVyr_1</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>OKVED_11_OrgPolUbyV%KObsKol</t>
+          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerKomIUprRas_1</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>OKVED_11_OrgPolUbyUby</t>
+          <t>MO_30851_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>OKVED_32_OrgPolUbyKolOrgEdi</t>
+          <t>MO_30501_OtcGoOtlNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>OKVED_32_OrgPolUbyV%KObsKol</t>
+          <t>MO_30501_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>OKVED_32_OrgPolUbyUby</t>
+          <t>MO_30510_OtcGoSalProDohIRas_1</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>OKVED_42_OrgPolPriKolOrgEdi</t>
+          <t>MO_30510_OtcGoTekNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>OKVED_42_OrgPolPriV%KObsKol</t>
+          <t>MO_30510_OtcGoOtlNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>OKVED_42_OrgPolPriPriDoNal</t>
+          <t>MO_30510_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>OKVED_43_OrgPolUbyKolOrgEdi</t>
+          <t>MO_30604_OtcGoPri(ubDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>OKVED_43_OrgPolUbyV%KObsKol</t>
+          <t>MO_30604_OtcGoTekNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>OKVED_43_OrgPolUbyUby</t>
+          <t>MO_30604_OtcGoOtlNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>OKVED_49_OrgPolUbyKolOrgEdi</t>
+          <t>MO_30604_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>OKVED_49_OrgPolUbyV%KObsKol</t>
+          <t>MO_30832_OtcGoTekNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>OKVED_49_OrgPolUbyUby</t>
+          <t>MO_30832_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>OKVED_51_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_11_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>OKVED_51_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_11_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>OKVED_51_OrgPolUbyUby</t>
+          <t>OKVED_11_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>OKVED_56_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_32_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>OKVED_56_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_32_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>OKVED_56_OrgPolUbyUby</t>
+          <t>OKVED_32_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-DoNal</t>
+          <t>OKVED_42_OrgPolPriKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>OKVED_J_OrgPolPriPriDoNal</t>
+          <t>OKVED_42_OrgPolPriV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>OKVED_J_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_42_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>OKVED_J_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_43_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>OKVED_J_OrgPolUbyUby</t>
+          <t>OKVED_43_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-DoNal</t>
+          <t>OKVED_43_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>OKVED_63_OrgPolPriPriDoNal</t>
+          <t>OKVED_49_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>OKVED_63_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_49_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>OKVED_63_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_49_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>OKVED_63_OrgPolUbyUby</t>
+          <t>OKVED_51_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>OKVED_69_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_51_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>OKVED_69_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_51_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>OKVED_69_OrgPolUbyUby</t>
+          <t>OKVED_56_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>OKVED_74_OrgPolPriKolOrgEdi</t>
+          <t>OKVED_56_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>OKVED_74_OrgPolPriV%KObsKol</t>
+          <t>OKVED_56_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>OKVED_74_OrgPolPriPriDoNal</t>
+          <t>OKVED_J_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>OKVED_79_OrgPolPriKolOrgEdi</t>
+          <t>OKVED_J_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>OKVED_79_OrgPolPriV%KObsKol</t>
+          <t>OKVED_J_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>OKVED_79_OrgPolPriPriDoNal</t>
+          <t>OKVED_J_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>OKVED_81_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_J_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>OKVED_81_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_63_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>OKVED_81_OrgPolUbyUby</t>
+          <t>OKVED_63_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>OKVED_O_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_63_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>OKVED_O_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_63_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>OKVED_O_OrgPolUbyUby</t>
+          <t>OKVED_63_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>OKVED_84_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_69_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>OKVED_84_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_69_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>OKVED_84_OrgPolUbyUby</t>
+          <t>OKVED_69_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_74_OrgPolPriKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_74_OrgPolPriV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyUby</t>
+          <t>OKVED_74_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_79_OrgPolPriKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_79_OrgPolPriV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyUby</t>
+          <t>OKVED_79_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-DoNal</t>
+          <t>OKVED_81_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>OKVED_Q_OrgPolPriPriDoNal</t>
+          <t>OKVED_81_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>OKVED_Q_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_81_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>OKVED_Q_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_O_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>OKVED_Q_OrgPolUbyUby</t>
+          <t>OKVED_O_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-DoNal</t>
+          <t>OKVED_O_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>OKVED_88_OrgPolPriPriDoNal</t>
+          <t>OKVED_84_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>OKVED_88_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_84_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>OKVED_88_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_84_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>OKVED_88_OrgPolUbyUby</t>
+          <t>OKVED_85_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>OKVED_93_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_85_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>OKVED_93_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_85_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>OKVED_93_OrgPolUbyUby</t>
+          <t>OKVED_85_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>OKVED_94_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_85_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>OKVED_94_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_85_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>OKVED_94_OrgPolUbyUby</t>
+          <t>OKVED_Q_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>OKVED_01_TeRosPriV%</t>
+          <t>OKVED_Q_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>OKVED_10_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_Q_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>OKVED_11_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_Q_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>OKVED_11_TeRosUbyV%</t>
+          <t>OKVED_Q_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>OKVED_32_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_88_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>OKVED_32_TeRosUbyV%</t>
+          <t>OKVED_88_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>OKVED_38_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_88_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>OKVED_F_TeRosPriV%</t>
+          <t>OKVED_88_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>OKVED_41_TeRosPriV%</t>
+          <t>OKVED_88_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>OKVED_41_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_93_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>OKVED_42_TeRosPriV%</t>
+          <t>OKVED_93_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>OKVED_42_TeRosSumPriV%</t>
+          <t>OKVED_93_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>OKVED_43_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_94_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>OKVED_43_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_94_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>OKVED_43_SumPriZaSooPerPreGo</t>
+          <t>OKVED_94_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>OKVED_43_TeRosUbyV%</t>
+          <t>OKVED_01_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>OKVED_49_TeRosUbyV%</t>
+          <t>OKVED_10_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>OKVED_50_TeRosPriV%</t>
+          <t>OKVED_11_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>OKVED_50_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_11_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>OKVED_50_TeRosSumPriV%</t>
+          <t>OKVED_32_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>OKVED_51_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_32_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>OKVED_51_TeRosUbyV%</t>
+          <t>OKVED_38_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>OKVED_I_TeRosPriV%</t>
+          <t>OKVED_F_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>OKVED_55_TeRosPriV%</t>
+          <t>OKVED_41_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>OKVED_55_SumPriZaSooPerPreGo</t>
+          <t>OKVED_41_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>OKVED_56_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_42_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>OKVED_56_TeRosUbyV%</t>
+          <t>OKVED_42_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>OKVED_L_TeRosPriV%</t>
+          <t>OKVED_43_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>OKVED_68_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_43_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>OKVED_68_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_43_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>OKVED_68_SumPriZaSooPerPreGo</t>
+          <t>OKVED_43_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>OKVED_68_TeRosUbyV%</t>
+          <t>OKVED_49_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>OKVED_M_TeRosPriV%</t>
+          <t>OKVED_50_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>OKVED_69_TeRosPriV%</t>
+          <t>OKVED_50_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>OKVED_70_TeRosPriV%</t>
+          <t>OKVED_50_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>OKVED_70_SumPriZaSooPerPreGo</t>
+          <t>OKVED_51_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>OKVED_70_TeRosSumPriV%</t>
+          <t>OKVED_51_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>OKVED_71_TeRosPriV%</t>
+          <t>OKVED_I_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>OKVED_74_TeRosPriV%</t>
+          <t>OKVED_55_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>OKVED_77_TeRosPriV%</t>
+          <t>OKVED_55_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>OKVED_77_SumPriZaSooPerPreGo</t>
+          <t>OKVED_56_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>OKVED_77_TeRosUbyV%</t>
+          <t>OKVED_56_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>OKVED_79_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_L_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>OKVED_79_TeRosUbyV%</t>
+          <t>OKVED_68_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>OKVED_81_TeRosPriV%</t>
+          <t>OKVED_68_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>OKVED_81_SumPriZaSooPerPreGo</t>
+          <t>OKVED_68_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>OKVED_81_TeRosUbyV%</t>
+          <t>OKVED_68_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>OKVED_82_TeRosPriV%</t>
+          <t>OKVED_M_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>OKVED_82_SumPriZaSooPerPreGo</t>
+          <t>OKVED_69_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>OKVED_82_TeRosUbyV%</t>
+          <t>OKVED_70_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>OKVED_O_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_70_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>OKVED_O_TeRosUbyV%</t>
+          <t>OKVED_70_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_71_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosPriV%</t>
+          <t>OKVED_74_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_77_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_77_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>OKVED_85_SumPriZaSooPerPreGo</t>
+          <t>OKVED_77_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosUbyV%</t>
+          <t>OKVED_79_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosSumPriV%</t>
+          <t>OKVED_79_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_81_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosPriV%</t>
+          <t>OKVED_81_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_81_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_82_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>OKVED_85_SumPriZaSooPerPreGo</t>
+          <t>OKVED_82_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosUbyV%</t>
+          <t>OKVED_82_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosSumPriV%</t>
+          <t>OKVED_O_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>OKVED_93_TeRosUbyV%</t>
+          <t>OKVED_O_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>OKVED_S_TeRosPriV%</t>
+          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>OKVED_94_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_85_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosPriV%</t>
+          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>OKVED_94_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>OKVED_94_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_85_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>OKVED_94_SumPriZaSooPerPreGo</t>
+          <t>OKVED_85_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosUbyV%</t>
+          <t>OKVED_85_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosSumPriV%</t>
+          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>OKVED_96_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_85_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosPriV%</t>
+          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>OKVED_96_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>OKVED_96_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_85_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>OKVED_96_SumPriZaSooPerPreGo</t>
+          <t>OKVED_85_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosUbyV%</t>
+          <t>OKVED_85_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosSumPriV%</t>
+          <t>OKVED_93_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>MO_30851_OrgPolUbyKolOrgEdi_1</t>
+          <t>OKVED_S_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t>MO_30851_OrgPolUbyV%KObsKol_1</t>
+          <t>OKVED_94_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t>MO_30851_OrgPolUbyUby_1</t>
+          <t>OKVED_94_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t>MO_30501_OrgPolPriKolOrgEdi_1</t>
+          <t>OKVED_94_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>MO_30501_OrgPolPriV%KObsKol_1</t>
+          <t>OKVED_94_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t>MO_30501_OrgPolPriPriDoNal_1</t>
+          <t>OKVED_94_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>MO_30510_OrgPolPriPriDoNal_1</t>
+          <t>OKVED_94_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>MO_30604_PriUby(-DoNal_1</t>
+          <t>OKVED_94_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolPriPriDoNal_1</t>
+          <t>OKVED_96_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolUbyKolOrgEdi_1</t>
+          <t>OKVED_96_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolUbyV%KObsKol_1</t>
+          <t>OKVED_96_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolUbyUby_1</t>
+          <t>OKVED_96_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>MO_30851_SumUbyZaSooPerPreGo_1</t>
+          <t>OKVED_96_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
-          <t>MO_30851_TeRosUbyV%_1</t>
+          <t>OKVED_96_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>MO_30501_TeRosPriV%_1</t>
+          <t>OKVED_96_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>MO_30501_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30851_OrgPolUbyKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t>MO_30501_TeRosSumPriV%_1</t>
+          <t>MO_30851_OrgPolUbyV%KObsKol_1</t>
         </is>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>MO_30510_TeRosPriV%_1</t>
+          <t>MO_30851_OrgPolUbyUby_1</t>
         </is>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>MO_30510_SumPriZaSooPerPreGo_1</t>
+          <t>MO_30501_OrgPolPriKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>MO_30510_TeRosSumPriV%_1</t>
+          <t>MO_30501_OrgPolPriV%KObsKol_1</t>
         </is>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>MO_30604_PriUby(-DoNalZaAnaPerPreGo_1</t>
+          <t>MO_30501_OrgPolPriPriDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosPriV%_1</t>
+          <t>MO_30510_OrgPolPriPriDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>MO_30604_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30604_PriUby(-DoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>MO_30604_SumPriZaSooPerPreGo_1</t>
+          <t>MO_30604_OrgPolPriPriDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosUbyV%_1</t>
+          <t>MO_30604_OrgPolUbyKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosSumPriV%_1</t>
+          <t>MO_30604_OrgPolUbyV%KObsKol_1</t>
         </is>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>MO_30616_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30604_OrgPolUbyUby_1</t>
         </is>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="inlineStr">
         <is>
-          <t>MO_30619_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30851_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>MO_30832_TeRosPriV%_1</t>
+          <t>MO_30851_TeRosUbyV%_1</t>
         </is>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>OKVED_56_VToChiKomIUprRas</t>
+          <t>MO_30501_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-OtPro</t>
+          <t>MO_30501_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>OKVED_J_SebProSUchKomIUprRas</t>
+          <t>MO_30501_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>OKVED_J_VToChiKomIUprRas</t>
+          <t>MO_30510_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>MO_30510_SumPriZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%KKomIUprRas</t>
+          <t>MO_30510_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%KVyr</t>
+          <t>MO_30604_PriUby(-DoNalZaAnaPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>MO_30604_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-OtPro</t>
+          <t>MO_30604_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>OKVED_63_SebProSUchKomIUprRas</t>
+          <t>MO_30604_SumPriZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>OKVED_63_VToChiKomIUprRas</t>
+          <t>MO_30604_TeRosUbyV%_1</t>
         </is>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>MO_30604_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%KKomIUprRas</t>
+          <t>MO_30616_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%KVyr</t>
+          <t>MO_30619_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>MO_30832_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>OKVED_74_VToChiKomIUprRas</t>
+          <t>OKVED_56_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>OKVED_81_VToChiKomIUprRas</t>
+          <t>OKVED_J_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>OKVED_82_VToChiKomIUprRas</t>
+          <t>OKVED_J_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>OKVED_O_VToChiKomIUprRas</t>
+          <t>OKVED_J_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>OKVED_84_VToChiKomIUprRas</t>
+          <t>OKVED_J_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>OKVED_85_VToChiKomIUprRas</t>
+          <t>OKVED_J_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-OtPro</t>
+          <t>OKVED_J_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>OKVED_Q_SebProSUchKomIUprRas</t>
+          <t>OKVED_J_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>OKVED_Q_VToChiKomIUprRas</t>
+          <t>OKVED_63_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>OKVED_63_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%KKomIUprRas</t>
+          <t>OKVED_63_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%KVyr</t>
+          <t>OKVED_63_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>OKVED_63_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-OtPro</t>
+          <t>OKVED_63_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>OKVED_88_SebProSUchKomIUprRas</t>
+          <t>OKVED_63_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>OKVED_88_VToChiKomIUprRas</t>
+          <t>OKVED_74_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>OKVED_81_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%KKomIUprRas</t>
+          <t>OKVED_82_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%KVyr</t>
+          <t>OKVED_O_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>OKVED_84_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>OKVED_R_SebProSUchKomIUprRas</t>
+          <t>OKVED_85_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>OKVED_R_VToChiKomIUprRas</t>
+          <t>OKVED_Q_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>OKVED_93_SebProSUchKomIUprRas</t>
+          <t>OKVED_Q_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>OKVED_93_VToChiKomIUprRas</t>
+          <t>OKVED_Q_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>OKVED_56_OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OKVED_Q_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>OKVED_O_OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OKVED_Q_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>OKVED_84_OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OKVED_Q_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>OKVED_11_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_Q_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>OKVED_43_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_88_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>OKVED_49_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_88_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>OKVED_56_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_88_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>OKVED_56_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_88_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>OKVED_69_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_88_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>OKVED_69_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_88_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>OKVED_74_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_88_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>OKVED_81_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_R_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>OKVED_81_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_R_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>OKVED_82_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_93_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>OKVED_82_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_93_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>OKVED_O_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_56_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>OKVED_O_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_O_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_84_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_11_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_43_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_49_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>OKVED_R_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_56_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>OKVED_R_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_56_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>OKVED_93_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_69_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>OKVED_93_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_69_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>OKVED_94_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_74_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>OKVED_96_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_81_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_81_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>OKVED_82_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>OKVED_82_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10DebZad</t>
+          <t>OKVED_O_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10V%KObsZad</t>
+          <t>OKVED_O_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>OKVED_70_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>OKVED_R_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>OKVED_93_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>OKVED_94_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_R_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>OKVED_96_KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>OKVED_R_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>OKVED_96_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>OKVED_93_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
+          <t>OKVED_93_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsKol</t>
+          <t>OKVED_94_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20DebZad</t>
+          <t>OKVED_96_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZad</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KreZad</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20DenSreIDenEkv</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10DebZad</t>
         </is>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeTekLikOt&gt;=20DebZad</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeTekLikOt&gt;=20V%KObsZad</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>OKVED_01_ArendPlDeVsego</t>
+          <t>OKVED_70_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>OKVED_32_ArendPlDeVsego</t>
+          <t>OKVED_R_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>OKVED_E_ArendPlDeVsego</t>
+          <t>OKVED_93_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>OKVED_36_ArendPlDeVsego</t>
+          <t>OKVED_94_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>OKVED_38_ArendPlDeVsego</t>
+          <t>OKVED_96_KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>OKVED_41_ArendPlDeVsego</t>
+          <t>OKVED_96_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>OKVED_43_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>OKVED_49_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>OKVED_50_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>OKVED_I_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>OKVED_55_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KreZad</t>
         </is>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>OKVED_56_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>OKVED_J_OtProdDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>OKVED_J_ArendPlDeVsego</t>
+          <t>OKVED_69_KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>OKVED_63_OtProdDeVsego</t>
+          <t>OKVED_69_KoeTekLikOt&gt;=20V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>OKVED_63_ArendPlDeVsego</t>
+          <t>OKVED_01_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>OKVED_64_ArendPlDeVsego</t>
+          <t>OKVED_32_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>OKVED_69_ArendPlDeVsego</t>
+          <t>OKVED_E_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>OKVED_79_ArendPlDeVsego</t>
+          <t>OKVED_36_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>OKVED_81_ArendPlDeVsego</t>
+          <t>OKVED_38_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>OKVED_82_ArendPlDeVsego</t>
+          <t>OKVED_41_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>OKVED_O_ArendPlDeVsego</t>
+          <t>OKVED_43_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>OKVED_84_ArendPlDeVsego</t>
+          <t>OKVED_49_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_50_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_I_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>OKVED_88_OtProdDeVsego</t>
+          <t>OKVED_55_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>OKVED_88_ArendPlDeVsego</t>
+          <t>OKVED_56_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>OKVED_R_OtProdDeVsego</t>
+          <t>OKVED_J_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>OKVED_R_ArendPlDeVsego</t>
+          <t>OKVED_J_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>OKVED_93_OtProdDeVsego</t>
+          <t>OKVED_63_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>OKVED_93_ArendPlDeVsego</t>
+          <t>OKVED_63_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>OKVED_S_ArendPlDeVsego</t>
+          <t>OKVED_64_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>OKVED_94_ArendPlDeVsego</t>
+          <t>OKVED_69_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>OKVED_96_ArendPlDeVsego</t>
+          <t>OKVED_79_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcPoDolgObyaz</t>
+          <t>OKVED_81_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>OKVED_32_ProcPoDolgObyaz</t>
+          <t>OKVED_82_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>OKVED_32_NalogNaPri</t>
+          <t>OKVED_O_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>OKVED_33_NalogNaPri</t>
+          <t>OKVED_84_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcPoDolgObyaz</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>OKVED_38_NalogNaPri</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcPoDolgObyaz</t>
+          <t>OKVED_88_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>OKVED_56_ProcPoDolgObyaz</t>
+          <t>OKVED_88_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>OKVED_56_NalogNaPri</t>
+          <t>OKVED_R_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>OKVED_J_ProcPoDolgObyaz</t>
+          <t>OKVED_R_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>OKVED_J_NalogNaPri</t>
+          <t>OKVED_93_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>OKVED_63_ProcPoDolgObyaz</t>
+          <t>OKVED_93_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>OKVED_63_NalogNaPri</t>
+          <t>OKVED_S_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>OKVED_M_ProcPoDolgObyaz</t>
+          <t>OKVED_94_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>OKVED_69_ProcPoDolgObyaz</t>
+          <t>OKVED_96_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>OKVED_69_NalogNaPri</t>
+          <t>OKVED_11_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>OKVED_71_ProcPoDolgObyaz</t>
+          <t>OKVED_32_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>OKVED_71_NalogNaPri</t>
+          <t>OKVED_32_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>OKVED_74_ProcPoDolgObyaz</t>
+          <t>OKVED_33_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcPoDolgObyaz</t>
+          <t>OKVED_36_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>OKVED_79_NalogNaPri</t>
+          <t>OKVED_38_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>OKVED_81_NalogNaPri</t>
+          <t>OKVED_49_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_56_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>OKVED_O_VSvyaziSOplTrudRab</t>
+          <t>OKVED_56_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>OKVED_O_ProcPoDolgObyaz</t>
+          <t>OKVED_J_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_J_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>OKVED_84_VSvyaziSOplTrudRab</t>
+          <t>OKVED_63_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>OKVED_84_ProcPoDolgObyaz</t>
+          <t>OKVED_63_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_M_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_69_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_69_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_71_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>OKVED_Q_ProcPoDolgObyaz</t>
+          <t>OKVED_71_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>OKVED_Q_NalogNaPri</t>
+          <t>OKVED_74_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_77_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>OKVED_R_VSvyaziSOplTrudRab</t>
+          <t>OKVED_79_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>OKVED_R_ProcPoDolgObyaz</t>
+          <t>OKVED_81_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>OKVED_R_NalogNaPri</t>
+          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_O_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>OKVED_93_VSvyaziSOplTrudRab</t>
+          <t>OKVED_O_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>OKVED_93_ProcPoDolgObyaz</t>
+          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>OKVED_93_NalogNaPri</t>
+          <t>OKVED_84_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>OKVED_96_ProcPoDolgObyaz</t>
+          <t>OKVED_84_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>OKVED_96_NalogNaPri</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdAkcOrgDolUch</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>OKVED_01_DivProcDolgFinVlozh</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>OKVED_B_OtProdAkcOrgDolUch</t>
+          <t>OKVED_Q_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>OKVED_07_OtProdAkcOrgDolUch</t>
+          <t>OKVED_Q_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>OKVED_C_OtProdAkcOrgDolUch</t>
+          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>OKVED_10_OtProdAkcOrgDolUch</t>
+          <t>OKVED_R_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_R_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdAkcOrgDolUch</t>
+          <t>OKVED_R_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdFinVlozh</t>
+          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdFinVlozh</t>
+          <t>OKVED_96_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>OKVED_E_DivProcDolgFinVlozh</t>
+          <t>OKVED_96_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdFinVlozh</t>
+          <t>OKVED_01_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>OKVED_36_DivProcDolgFinVlozh</t>
+          <t>OKVED_01_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_B_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdAkcOrgDolUch</t>
+          <t>OKVED_07_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdFinVlozh</t>
+          <t>OKVED_C_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>OKVED_38_DivProcDolgFinVlozh</t>
+          <t>OKVED_10_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdAkcOrgDolUch</t>
+          <t>OKVED_11_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_11_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdAkcOrgDolUch</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdAkcOrgDolUch</t>
+          <t>OKVED_E_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdFinVlozh</t>
+          <t>OKVED_E_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>OKVED_G_OtProdAkcOrgDolUch</t>
+          <t>OKVED_E_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>OKVED_46_OtProdAkcOrgDolUch</t>
+          <t>OKVED_36_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>OKVED_47_OtProdAkcOrgDolUch</t>
+          <t>OKVED_36_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>OKVED_H_OtProdAkcOrgDolUch</t>
+          <t>OKVED_36_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>OKVED_49_DivProcDolgFinVlozh</t>
+          <t>OKVED_38_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>OKVED_52_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdAkcOrgDolUch</t>
+          <t>OKVED_F_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdAkcOrgDolUch</t>
+          <t>OKVED_41_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_43_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdAkcOrgDolUch</t>
+          <t>OKVED_G_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>OKVED_L_OtProdAkcOrgDolUch</t>
+          <t>OKVED_46_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_47_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdAkcOrgDolUch</t>
+          <t>OKVED_H_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdAkcOrgDolUch</t>
+          <t>OKVED_49_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_49_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdAkcOrgDolUch</t>
+          <t>OKVED_52_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>OKVED_71_DivProcDolgFinVlozh</t>
+          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdAkcOrgDolUch</t>
+          <t>OKVED_I_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdFinVlozh</t>
+          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdAkcOrgDolUch</t>
+          <t>OKVED_55_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdFinVlozh</t>
+          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_K_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdAkcOrgDolUch</t>
+          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>OKVED_S_DivProcDolgFinVlozh</t>
+          <t>OKVED_64_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_L_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdAkcOrgDolUch</t>
+          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>OKVED_94_DivProcDolgFinVlozh</t>
+          <t>OKVED_M_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>OKVED_01_DolUch</t>
+          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_70_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>OKVED_B_DolUch</t>
+          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_71_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>OKVED_C_DolUch</t>
+          <t>OKVED_71_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_N_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>OKVED_10_DolUch</t>
+          <t>OKVED_N_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_77_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>OKVED_11_DolUch</t>
+          <t>OKVED_77_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>OKVED_11_PrCenBum</t>
+          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_S_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>OKVED_33_DolUch</t>
+          <t>OKVED_S_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>OKVED_E_DolUch</t>
+          <t>OKVED_94_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>OKVED_E_PrCenBum</t>
+          <t>OKVED_94_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_01_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>OKVED_36_DolUch</t>
+          <t>OKVED_01_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>OKVED_36_PrCenBum</t>
+          <t>OKVED_B_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>OKVED_F_DolUch</t>
+          <t>OKVED_C_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>OKVED_41_DolUch</t>
+          <t>OKVED_10_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>OKVED_42_DolUch</t>
+          <t>OKVED_11_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_11_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>OKVED_43_DolUch</t>
+          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>OKVED_43_PrCenBum</t>
+          <t>OKVED_33_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>OKVED_47_DolUch</t>
+          <t>OKVED_E_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>OKVED_H_DolUch</t>
+          <t>OKVED_E_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>OKVED_49_DolUch</t>
+          <t>OKVED_36_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_36_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>OKVED_50_DolUch</t>
+          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>OKVED_50_PrCenBum</t>
+          <t>OKVED_F_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>OKVED_52_DolUch</t>
+          <t>OKVED_41_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_42_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>OKVED_K_DolUch</t>
+          <t>OKVED_43_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_43_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>OKVED_M_DolUch</t>
+          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>OKVED_71_DolUch</t>
+          <t>OKVED_47_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>OKVED_N_DolUch</t>
+          <t>OKVED_H_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>OKVED_N_PrCenBum</t>
+          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>OKVED_79_DolUch</t>
+          <t>OKVED_49_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>OKVED_79_PrCenBum</t>
+          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>OKVED_S_Modern</t>
+          <t>OKVED_50_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>OKVED_S_DolUch</t>
+          <t>OKVED_50_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>OKVED_94_Modern</t>
+          <t>OKVED_52_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>OKVED_94_DolUch</t>
+          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>OKVED_01_PostDeyt1</t>
+          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>OKVED_01_DrPost</t>
+          <t>OKVED_K_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt</t>
+          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt1</t>
+          <t>OKVED_M_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt</t>
+          <t>OKVED_71_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt1</t>
+          <t>OKVED_N_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>OKVED_C_PostDeyt1</t>
+          <t>OKVED_N_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>OKVED_10_PostDeyt1</t>
+          <t>OKVED_79_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>OKVED_32_PlCredit</t>
+          <t>OKVED_79_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt</t>
+          <t>OKVED_S_Modern</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt1</t>
+          <t>OKVED_S_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt</t>
+          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt1</t>
+          <t>OKVED_94_Modern</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>OKVED_33_DrPost</t>
+          <t>OKVED_94_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_01_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>OKVED_38_PostDeyt1</t>
+          <t>OKVED_01_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>OKVED_38_DrPost</t>
+          <t>OKVED_B_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>OKVED_F_PostDeyt1</t>
+          <t>OKVED_B_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt</t>
+          <t>OKVED_07_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt1</t>
+          <t>OKVED_07_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt</t>
+          <t>OKVED_C_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt1</t>
+          <t>OKVED_10_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>OKVED_42_DrPost</t>
+          <t>OKVED_32_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>OKVED_43_PostDeyt1</t>
+          <t>OKVED_32_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>OKVED_43_DrPost</t>
+          <t>OKVED_32_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt</t>
+          <t>OKVED_33_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt1</t>
+          <t>OKVED_33_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt</t>
+          <t>OKVED_33_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt1</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt1</t>
+          <t>OKVED_38_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>OKVED_H_PostDeyt1</t>
+          <t>OKVED_38_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt</t>
+          <t>OKVED_F_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt1</t>
+          <t>OKVED_41_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>OKVED_50_DrPost</t>
+          <t>OKVED_41_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt</t>
+          <t>OKVED_42_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt1</t>
+          <t>OKVED_42_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>OKVED_51_DrPost</t>
+          <t>OKVED_42_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>OKVED_52_PostDeyt1</t>
+          <t>OKVED_43_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>OKVED_I_PostDeyt1</t>
+          <t>OKVED_43_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>OKVED_I_DrPost</t>
+          <t>OKVED_G_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>OKVED_55_PostDeyt1</t>
+          <t>OKVED_G_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>OKVED_55_DrPost</t>
+          <t>OKVED_46_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt</t>
+          <t>OKVED_46_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt1</t>
+          <t>OKVED_47_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>OKVED_K_DrPost</t>
+          <t>OKVED_47_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt</t>
+          <t>OKVED_H_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt1</t>
+          <t>OKVED_50_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>OKVED_64_DrPost</t>
+          <t>OKVED_50_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>OKVED_L_PostDeyt1</t>
+          <t>OKVED_50_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>OKVED_68_PostDeyt1</t>
+          <t>OKVED_51_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>OKVED_70_PlCredit</t>
+          <t>OKVED_51_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>OKVED_70_PostDeyt</t>
+          <t>OKVED_51_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>OKVED_71_PostDeyt</t>
+          <t>OKVED_52_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt</t>
+          <t>OKVED_I_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt1</t>
+          <t>OKVED_I_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>OKVED_74_DrPost</t>
+          <t>OKVED_55_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt</t>
+          <t>OKVED_55_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt1</t>
+          <t>OKVED_K_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt</t>
+          <t>OKVED_K_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt1</t>
+          <t>OKVED_K_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>OKVED_79_DrPost</t>
+          <t>OKVED_64_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>OKVED_81_PlCredit</t>
+          <t>OKVED_64_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt</t>
+          <t>OKVED_64_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt1</t>
+          <t>OKVED_L_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>OKVED_S_PlCredit</t>
+          <t>OKVED_68_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>OKVED_S_PostDeyt1</t>
+          <t>OKVED_70_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>OKVED_94_PlCredit</t>
+          <t>OKVED_70_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>OKVED_94_PostDeyt1</t>
+          <t>OKVED_71_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin1</t>
+          <t>OKVED_74_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin2</t>
+          <t>OKVED_74_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>OKVED_B_PlPoFin1</t>
+          <t>OKVED_74_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>OKVED_07_PlPoFin1</t>
+          <t>OKVED_N_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin</t>
+          <t>OKVED_N_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin1</t>
+          <t>OKVED_79_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin2</t>
+          <t>OKVED_79_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin3</t>
+          <t>OKVED_79_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_81_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_81_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin1</t>
+          <t>OKVED_81_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin2</t>
+          <t>OKVED_S_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin1</t>
+          <t>OKVED_S_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin2</t>
+          <t>OKVED_94_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>OKVED_F_PlPoFin1</t>
+          <t>OKVED_94_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>OKVED_41_PlPoFin1</t>
+          <t>OKVED_01_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin1</t>
+          <t>OKVED_01_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin2</t>
+          <t>OKVED_B_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>OKVED_G_PlPoFin1</t>
+          <t>OKVED_07_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>OKVED_46_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>OKVED_47_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>OKVED_H_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin2</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoFin1</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>OKVED_52_PlPoFin1</t>
+          <t>OKVED_E_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin1</t>
+          <t>OKVED_E_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin2</t>
+          <t>OKVED_38_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin1</t>
+          <t>OKVED_38_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin2</t>
+          <t>OKVED_F_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoFin1</t>
+          <t>OKVED_41_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoFin1</t>
+          <t>OKVED_43_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>OKVED_68_PlPoFin1</t>
+          <t>OKVED_43_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>OKVED_M_PlPoFin1</t>
+          <t>OKVED_G_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin</t>
+          <t>OKVED_46_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin1</t>
+          <t>OKVED_47_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin2</t>
+          <t>OKVED_H_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin3</t>
+          <t>OKVED_49_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>OKVED_71_PlPoFin1</t>
+          <t>OKVED_49_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin1</t>
+          <t>OKVED_50_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin2</t>
+          <t>OKVED_52_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin3</t>
+          <t>OKVED_I_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>OKVED_74_SaldoDenPot</t>
+          <t>OKVED_I_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin1</t>
+          <t>OKVED_55_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin2</t>
+          <t>OKVED_55_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin1</t>
+          <t>OKVED_K_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin2</t>
+          <t>OKVED_64_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin3</t>
+          <t>OKVED_68_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>OKVED_81_SaldoDenPot</t>
+          <t>OKVED_M_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin1</t>
+          <t>OKVED_70_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin2</t>
+          <t>OKVED_70_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin3</t>
+          <t>OKVED_70_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin1</t>
+          <t>OKVED_70_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin2</t>
+          <t>OKVED_71_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin3</t>
+          <t>OKVED_74_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>OKVED_01_Velch</t>
+          <t>OKVED_74_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>OKVED_11_Velch</t>
+          <t>OKVED_74_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>OKVED_32_Velch</t>
+          <t>OKVED_74_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>OKVED_33_Velch</t>
+          <t>OKVED_79_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>OKVED_E_Velch</t>
+          <t>OKVED_79_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>OKVED_38_Velch</t>
+          <t>OKVED_81_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>OKVED_F_Velch</t>
+          <t>OKVED_81_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>OKVED_41_Velch</t>
+          <t>OKVED_81_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>OKVED_42_Velch</t>
+          <t>OKVED_81_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>OKVED_43_Velch</t>
+          <t>OKVED_S_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
         <is>
-          <t>OKVED_47_Velch</t>
+          <t>OKVED_S_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>OKVED_49_Velch</t>
+          <t>OKVED_S_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>OKVED_I_Velch</t>
+          <t>OKVED_94_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>OKVED_56_Velch</t>
+          <t>OKVED_94_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
         <is>
-          <t>OKVED_J_Velch</t>
+          <t>OKVED_94_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
         <is>
-          <t>OKVED_63_Velch</t>
+          <t>OKVED_01_Velch</t>
         </is>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>OKVED_L_Velch</t>
+          <t>OKVED_11_Velch</t>
         </is>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
         <is>
-          <t>OKVED_68_Velch</t>
+          <t>OKVED_32_Velch</t>
         </is>
       </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
         <is>
-          <t>OKVED_M_Velch</t>
+          <t>OKVED_33_Velch</t>
         </is>
       </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
         <is>
-          <t>OKVED_69_Velch</t>
+          <t>OKVED_E_Velch</t>
         </is>
       </c>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
         <is>
-          <t>OKVED_70_Velch</t>
+          <t>OKVED_38_Velch</t>
         </is>
       </c>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
         <is>
-          <t>OKVED_71_Velch</t>
+          <t>OKVED_F_Velch</t>
         </is>
       </c>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
         <is>
-          <t>OKVED_N_Velch</t>
+          <t>OKVED_41_Velch</t>
         </is>
       </c>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
         <is>
-          <t>OKVED_77_Velch</t>
+          <t>OKVED_42_Velch</t>
         </is>
       </c>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
         <is>
-          <t>OKVED_79_Velch</t>
+          <t>OKVED_43_Velch</t>
         </is>
       </c>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
         <is>
-          <t>OKVED_81_Velch</t>
+          <t>OKVED_47_Velch</t>
         </is>
       </c>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
         <is>
-          <t>OKVED_82_Velch</t>
+          <t>OKVED_49_Velch</t>
         </is>
       </c>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
         <is>
-          <t>OKVED_O_Velch</t>
+          <t>OKVED_I_Velch</t>
         </is>
       </c>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
         <is>
-          <t>OKVED_84_Velch</t>
+          <t>OKVED_56_Velch</t>
         </is>
       </c>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_J_Velch</t>
         </is>
       </c>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_63_Velch</t>
         </is>
       </c>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>OKVED_88_Velch</t>
+          <t>OKVED_L_Velch</t>
         </is>
       </c>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
         <is>
-          <t>OKVED_R_Velch</t>
+          <t>OKVED_68_Velch</t>
         </is>
       </c>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
         <is>
-          <t>OKVED_93_Velch</t>
+          <t>OKVED_M_Velch</t>
         </is>
       </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>OKVED_S_Velch</t>
+          <t>OKVED_69_Velch</t>
         </is>
       </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>OKVED_94_Velch</t>
+          <t>OKVED_70_Velch</t>
         </is>
       </c>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>OKVED_96_Velch</t>
+          <t>OKVED_71_Velch</t>
         </is>
       </c>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>OKVED_43_UstKap</t>
+          <t>OKVED_N_Velch</t>
         </is>
       </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
         <is>
-          <t>OKVED_43_ChiAkt</t>
+          <t>OKVED_77_Velch</t>
         </is>
       </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap</t>
+          <t>OKVED_79_Velch</t>
         </is>
       </c>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>OKVED_J_SebPro</t>
+          <t>OKVED_81_Velch</t>
         </is>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
         <is>
-          <t>OKVED_J_Pri(ubOtPro</t>
+          <t>OKVED_82_Velch</t>
         </is>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
         <is>
-          <t>OKVED_J_ChiPri(ubOtcPer</t>
+          <t>OKVED_O_Velch</t>
         </is>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_84_Velch</t>
         </is>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>OKVED_63_SebPro</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
         <is>
-          <t>OKVED_63_Pri(ubOtPro</t>
+          <t>OKVED_88_Velch</t>
         </is>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>OKVED_63_ChiPri(ubOtcPer</t>
+          <t>OKVED_R_Velch</t>
         </is>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_93_Velch</t>
         </is>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>OKVED_K_SebPro</t>
+          <t>OKVED_S_Velch</t>
         </is>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap</t>
+          <t>OKVED_94_Velch</t>
         </is>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>OKVED_69_ChiAkt</t>
+          <t>OKVED_96_Velch</t>
         </is>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>OKVED_69_SebPro</t>
+          <t>OKVED_43_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap</t>
+          <t>OKVED_43_ChiAkt</t>
         </is>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap</t>
+          <t>OKVED_J_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap</t>
+          <t>OKVED_J_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap</t>
+          <t>OKVED_J_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
-          <t>OKVED_Q_SebPro</t>
+          <t>OKVED_J_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>OKVED_Q_Pri(ubOtPro</t>
+          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>OKVED_Q_ChiPri(ubOtcPer</t>
+          <t>OKVED_63_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1696">
       <c r="A1696" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_63_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1697">
       <c r="A1697" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap</t>
+          <t>OKVED_63_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1698">
       <c r="A1698" t="inlineStr">
         <is>
-          <t>OKVED_88_SebPro</t>
+          <t>OKVED_63_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1699">
       <c r="A1699" t="inlineStr">
         <is>
-          <t>OKVED_88_Pri(ubOtPro</t>
+          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1700">
       <c r="A1700" t="inlineStr">
         <is>
-          <t>OKVED_88_ChiPri(ubOtcPer</t>
+          <t>OKVED_K_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1701">
       <c r="A1701" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_69_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1702">
       <c r="A1702" t="inlineStr">
         <is>
-          <t>OKVED_R_SebPro</t>
+          <t>OKVED_69_ChiAkt</t>
         </is>
       </c>
     </row>
     <row r="1703">
       <c r="A1703" t="inlineStr">
+        <is>
+          <t>OKVED_69_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>OKVED_O_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>OKVED_84_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>OKVED_Q_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>OKVED_Q_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>OKVED_Q_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>OKVED_Q_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>OKVED_88_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>OKVED_88_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>OKVED_88_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>OKVED_88_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>OKVED_88_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>OKVED_R_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
         <is>
           <t>OKVED_93_SebPro</t>
         </is>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1718"/>
+  <dimension ref="A1:A1731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8357,4086 +8357,4177 @@
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>OKVED_11_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_10_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>OKVED_11_TeRosUbyV%</t>
+          <t>OKVED_11_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>OKVED_32_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_11_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>OKVED_32_TeRosUbyV%</t>
+          <t>OKVED_11_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>OKVED_38_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_32_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>OKVED_F_TeRosPriV%</t>
+          <t>OKVED_32_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>OKVED_41_TeRosPriV%</t>
+          <t>OKVED_32_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>OKVED_41_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_38_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>OKVED_42_TeRosPriV%</t>
+          <t>OKVED_38_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>OKVED_42_TeRosSumPriV%</t>
+          <t>OKVED_F_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>OKVED_43_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_41_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>OKVED_43_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_41_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>OKVED_43_SumPriZaSooPerPreGo</t>
+          <t>OKVED_41_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>OKVED_43_TeRosUbyV%</t>
+          <t>OKVED_42_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>OKVED_49_TeRosUbyV%</t>
+          <t>OKVED_42_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>OKVED_50_TeRosPriV%</t>
+          <t>OKVED_43_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>OKVED_50_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_43_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>OKVED_50_TeRosSumPriV%</t>
+          <t>OKVED_43_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>OKVED_51_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_43_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>OKVED_51_TeRosUbyV%</t>
+          <t>OKVED_43_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>OKVED_I_TeRosPriV%</t>
+          <t>OKVED_49_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>OKVED_55_TeRosPriV%</t>
+          <t>OKVED_50_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>OKVED_55_SumPriZaSooPerPreGo</t>
+          <t>OKVED_50_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>OKVED_56_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_50_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>OKVED_56_TeRosUbyV%</t>
+          <t>OKVED_50_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>OKVED_L_TeRosPriV%</t>
+          <t>OKVED_51_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>OKVED_68_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_51_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>OKVED_68_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_51_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>OKVED_68_SumPriZaSooPerPreGo</t>
+          <t>OKVED_I_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>OKVED_68_TeRosUbyV%</t>
+          <t>OKVED_55_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>OKVED_M_TeRosPriV%</t>
+          <t>OKVED_55_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>OKVED_69_TeRosPriV%</t>
+          <t>OKVED_56_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>OKVED_70_TeRosPriV%</t>
+          <t>OKVED_56_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>OKVED_70_SumPriZaSooPerPreGo</t>
+          <t>OKVED_56_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>OKVED_70_TeRosSumPriV%</t>
+          <t>OKVED_L_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>OKVED_71_TeRosPriV%</t>
+          <t>OKVED_68_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>OKVED_74_TeRosPriV%</t>
+          <t>OKVED_68_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>OKVED_77_TeRosPriV%</t>
+          <t>OKVED_68_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>OKVED_77_SumPriZaSooPerPreGo</t>
+          <t>OKVED_68_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>OKVED_77_TeRosUbyV%</t>
+          <t>OKVED_68_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>OKVED_79_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_M_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>OKVED_79_TeRosUbyV%</t>
+          <t>OKVED_69_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>OKVED_81_TeRosPriV%</t>
+          <t>OKVED_70_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>OKVED_81_SumPriZaSooPerPreGo</t>
+          <t>OKVED_70_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>OKVED_81_TeRosUbyV%</t>
+          <t>OKVED_70_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>OKVED_82_TeRosPriV%</t>
+          <t>OKVED_71_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>OKVED_82_SumPriZaSooPerPreGo</t>
+          <t>OKVED_74_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>OKVED_82_TeRosUbyV%</t>
+          <t>OKVED_77_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>OKVED_O_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_77_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>OKVED_O_TeRosUbyV%</t>
+          <t>OKVED_77_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_79_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosPriV%</t>
+          <t>OKVED_79_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_79_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_81_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>OKVED_85_SumPriZaSooPerPreGo</t>
+          <t>OKVED_81_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosUbyV%</t>
+          <t>OKVED_81_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosSumPriV%</t>
+          <t>OKVED_82_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_82_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosPriV%</t>
+          <t>OKVED_82_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_O_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_O_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>OKVED_85_SumPriZaSooPerPreGo</t>
+          <t>OKVED_O_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosUbyV%</t>
+          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosSumPriV%</t>
+          <t>OKVED_85_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>OKVED_93_TeRosUbyV%</t>
+          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>OKVED_S_TeRosPriV%</t>
+          <t>OKVED_85_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t>OKVED_94_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_85_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosPriV%</t>
+          <t>OKVED_85_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t>OKVED_94_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>OKVED_94_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_85_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t>OKVED_94_SumPriZaSooPerPreGo</t>
+          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosUbyV%</t>
+          <t>OKVED_85_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosSumPriV%</t>
+          <t>OKVED_85_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>OKVED_96_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_85_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosPriV%</t>
+          <t>OKVED_93_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>OKVED_96_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_S_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>OKVED_96_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_94_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>OKVED_96_SumPriZaSooPerPreGo</t>
+          <t>OKVED_94_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosUbyV%</t>
+          <t>OKVED_94_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosSumPriV%</t>
+          <t>OKVED_94_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>MO_30851_OrgPolUbyKolOrgEdi_1</t>
+          <t>OKVED_94_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t>MO_30851_OrgPolUbyV%KObsKol_1</t>
+          <t>OKVED_94_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>MO_30851_OrgPolUbyUby_1</t>
+          <t>OKVED_96_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>MO_30501_OrgPolPriKolOrgEdi_1</t>
+          <t>OKVED_96_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>MO_30501_OrgPolPriV%KObsKol_1</t>
+          <t>OKVED_96_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>MO_30501_OrgPolPriPriDoNal_1</t>
+          <t>OKVED_96_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>MO_30510_OrgPolPriPriDoNal_1</t>
+          <t>OKVED_96_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>MO_30604_PriUby(-DoNal_1</t>
+          <t>OKVED_96_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolPriPriDoNal_1</t>
+          <t>MO_30851_OrgPolUbyKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolUbyKolOrgEdi_1</t>
+          <t>MO_30851_OrgPolUbyV%KObsKol_1</t>
         </is>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolUbyV%KObsKol_1</t>
+          <t>MO_30851_OrgPolUbyUby_1</t>
         </is>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolUbyUby_1</t>
+          <t>MO_30501_OrgPolPriKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="inlineStr">
         <is>
-          <t>MO_30851_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30501_OrgPolPriV%KObsKol_1</t>
         </is>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>MO_30851_TeRosUbyV%_1</t>
+          <t>MO_30501_OrgPolPriPriDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>MO_30501_TeRosPriV%_1</t>
+          <t>MO_30510_OrgPolPriPriDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>MO_30501_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30604_PriUby(-DoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>MO_30501_TeRosSumPriV%_1</t>
+          <t>MO_30604_OrgPolPriPriDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>MO_30510_TeRosPriV%_1</t>
+          <t>MO_30604_OrgPolUbyKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>MO_30510_SumPriZaSooPerPreGo_1</t>
+          <t>MO_30604_OrgPolUbyV%KObsKol_1</t>
         </is>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>MO_30510_TeRosSumPriV%_1</t>
+          <t>MO_30604_OrgPolUbyUby_1</t>
         </is>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>MO_30604_PriUby(-DoNalZaAnaPerPreGo_1</t>
+          <t>MO_30851_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosPriV%_1</t>
+          <t>MO_30851_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>MO_30604_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30851_TeRosUbyV%_1</t>
         </is>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>MO_30604_SumPriZaSooPerPreGo_1</t>
+          <t>MO_30501_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosUbyV%_1</t>
+          <t>MO_30501_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosSumPriV%_1</t>
+          <t>MO_30501_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>MO_30616_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30501_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>MO_30619_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30510_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>MO_30832_TeRosPriV%_1</t>
+          <t>MO_30510_SumPriZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>OKVED_56_VToChiKomIUprRas</t>
+          <t>MO_30510_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-OtPro</t>
+          <t>MO_30604_PriUby(-DoNalZaAnaPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>OKVED_J_SebProSUchKomIUprRas</t>
+          <t>MO_30604_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>OKVED_J_VToChiKomIUprRas</t>
+          <t>MO_30604_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>MO_30604_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%KKomIUprRas</t>
+          <t>MO_30604_SumPriZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%KVyr</t>
+          <t>MO_30604_TeRosUbyV%_1</t>
         </is>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>MO_30604_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-OtPro</t>
+          <t>MO_30616_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>OKVED_63_SebProSUchKomIUprRas</t>
+          <t>MO_30616_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="inlineStr">
         <is>
-          <t>OKVED_63_VToChiKomIUprRas</t>
+          <t>MO_30619_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>MO_30619_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%KKomIUprRas</t>
+          <t>MO_30832_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%KVyr</t>
+          <t>OKVED_56_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>OKVED_J_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>OKVED_74_VToChiKomIUprRas</t>
+          <t>OKVED_J_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
         <is>
-          <t>OKVED_81_VToChiKomIUprRas</t>
+          <t>OKVED_J_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>OKVED_82_VToChiKomIUprRas</t>
+          <t>OKVED_J_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>OKVED_O_VToChiKomIUprRas</t>
+          <t>OKVED_J_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>OKVED_84_VToChiKomIUprRas</t>
+          <t>OKVED_J_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>OKVED_85_VToChiKomIUprRas</t>
+          <t>OKVED_J_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-OtPro</t>
+          <t>OKVED_63_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>OKVED_Q_SebProSUchKomIUprRas</t>
+          <t>OKVED_63_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>OKVED_Q_VToChiKomIUprRas</t>
+          <t>OKVED_63_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>OKVED_63_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%KKomIUprRas</t>
+          <t>OKVED_63_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%KVyr</t>
+          <t>OKVED_63_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>OKVED_63_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-OtPro</t>
+          <t>OKVED_74_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>OKVED_88_SebProSUchKomIUprRas</t>
+          <t>OKVED_81_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>OKVED_88_VToChiKomIUprRas</t>
+          <t>OKVED_82_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>OKVED_O_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%KKomIUprRas</t>
+          <t>OKVED_84_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%KVyr</t>
+          <t>OKVED_85_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>OKVED_Q_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>OKVED_R_SebProSUchKomIUprRas</t>
+          <t>OKVED_Q_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>OKVED_R_VToChiKomIUprRas</t>
+          <t>OKVED_Q_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>OKVED_93_SebProSUchKomIUprRas</t>
+          <t>OKVED_Q_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>OKVED_93_VToChiKomIUprRas</t>
+          <t>OKVED_Q_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>OKVED_56_OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OKVED_Q_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>OKVED_O_OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OKVED_Q_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>OKVED_84_OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OKVED_88_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>OKVED_11_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_88_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>OKVED_43_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_88_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>OKVED_49_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_88_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>OKVED_56_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_88_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>OKVED_56_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_88_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>OKVED_69_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_88_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>OKVED_69_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_R_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>OKVED_74_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_R_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>OKVED_81_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_93_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>OKVED_81_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_93_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>OKVED_82_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_56_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>OKVED_82_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_O_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>OKVED_O_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_84_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>OKVED_O_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_11_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_43_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_49_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_56_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_56_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>OKVED_R_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_69_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>OKVED_R_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_69_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>OKVED_93_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_74_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>OKVED_93_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_81_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>OKVED_94_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_81_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>OKVED_96_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_82_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_82_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>OKVED_O_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>OKVED_O_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10DebZad</t>
+          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10V%KObsZad</t>
+          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>OKVED_70_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>OKVED_R_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_R_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>OKVED_93_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_R_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>OKVED_94_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_93_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>OKVED_96_KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>OKVED_93_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>OKVED_96_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>OKVED_94_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
+          <t>OKVED_96_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsKol</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20DebZad</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZad</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KreZad</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10DebZad</t>
         </is>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20DenSreIDenEkv</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeTekLikOt&gt;=20DebZad</t>
+          <t>OKVED_70_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeTekLikOt&gt;=20V%KObsZad</t>
+          <t>OKVED_R_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>OKVED_01_ArendPlDeVsego</t>
+          <t>OKVED_93_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>OKVED_32_ArendPlDeVsego</t>
+          <t>OKVED_94_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>OKVED_E_ArendPlDeVsego</t>
+          <t>OKVED_96_KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>OKVED_36_ArendPlDeVsego</t>
+          <t>OKVED_96_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>OKVED_38_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>OKVED_41_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>OKVED_43_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>OKVED_49_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>OKVED_50_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KreZad</t>
         </is>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>OKVED_I_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>OKVED_55_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>OKVED_56_ArendPlDeVsego</t>
+          <t>OKVED_69_KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>OKVED_J_OtProdDeVsego</t>
+          <t>OKVED_69_KoeTekLikOt&gt;=20V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>OKVED_J_ArendPlDeVsego</t>
+          <t>OKVED_01_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>OKVED_63_OtProdDeVsego</t>
+          <t>OKVED_32_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>OKVED_63_ArendPlDeVsego</t>
+          <t>OKVED_E_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>OKVED_64_ArendPlDeVsego</t>
+          <t>OKVED_36_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>OKVED_69_ArendPlDeVsego</t>
+          <t>OKVED_38_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>OKVED_79_ArendPlDeVsego</t>
+          <t>OKVED_41_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>OKVED_81_ArendPlDeVsego</t>
+          <t>OKVED_43_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>OKVED_82_ArendPlDeVsego</t>
+          <t>OKVED_49_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>OKVED_O_ArendPlDeVsego</t>
+          <t>OKVED_50_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>OKVED_84_ArendPlDeVsego</t>
+          <t>OKVED_I_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_55_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_56_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>OKVED_88_OtProdDeVsego</t>
+          <t>OKVED_J_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>OKVED_88_ArendPlDeVsego</t>
+          <t>OKVED_J_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>OKVED_R_OtProdDeVsego</t>
+          <t>OKVED_63_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>OKVED_R_ArendPlDeVsego</t>
+          <t>OKVED_63_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>OKVED_93_OtProdDeVsego</t>
+          <t>OKVED_64_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>OKVED_93_ArendPlDeVsego</t>
+          <t>OKVED_69_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>OKVED_S_ArendPlDeVsego</t>
+          <t>OKVED_79_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>OKVED_94_ArendPlDeVsego</t>
+          <t>OKVED_81_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>OKVED_96_ArendPlDeVsego</t>
+          <t>OKVED_82_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcPoDolgObyaz</t>
+          <t>OKVED_O_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>OKVED_32_ProcPoDolgObyaz</t>
+          <t>OKVED_84_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>OKVED_32_NalogNaPri</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>OKVED_33_NalogNaPri</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcPoDolgObyaz</t>
+          <t>OKVED_88_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>OKVED_38_NalogNaPri</t>
+          <t>OKVED_88_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcPoDolgObyaz</t>
+          <t>OKVED_R_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>OKVED_56_ProcPoDolgObyaz</t>
+          <t>OKVED_R_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>OKVED_56_NalogNaPri</t>
+          <t>OKVED_93_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>OKVED_J_ProcPoDolgObyaz</t>
+          <t>OKVED_93_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>OKVED_J_NalogNaPri</t>
+          <t>OKVED_S_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>OKVED_63_ProcPoDolgObyaz</t>
+          <t>OKVED_94_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>OKVED_63_NalogNaPri</t>
+          <t>OKVED_96_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>OKVED_M_ProcPoDolgObyaz</t>
+          <t>OKVED_11_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>OKVED_69_ProcPoDolgObyaz</t>
+          <t>OKVED_32_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>OKVED_69_NalogNaPri</t>
+          <t>OKVED_32_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>OKVED_71_ProcPoDolgObyaz</t>
+          <t>OKVED_33_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>OKVED_71_NalogNaPri</t>
+          <t>OKVED_36_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>OKVED_74_ProcPoDolgObyaz</t>
+          <t>OKVED_38_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcPoDolgObyaz</t>
+          <t>OKVED_49_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>OKVED_79_NalogNaPri</t>
+          <t>OKVED_56_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>OKVED_81_NalogNaPri</t>
+          <t>OKVED_56_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_J_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>OKVED_O_VSvyaziSOplTrudRab</t>
+          <t>OKVED_J_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>OKVED_O_ProcPoDolgObyaz</t>
+          <t>OKVED_63_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_63_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>OKVED_84_VSvyaziSOplTrudRab</t>
+          <t>OKVED_M_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>OKVED_84_ProcPoDolgObyaz</t>
+          <t>OKVED_69_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_69_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_71_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_71_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_74_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>OKVED_Q_ProcPoDolgObyaz</t>
+          <t>OKVED_77_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>OKVED_Q_NalogNaPri</t>
+          <t>OKVED_79_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_81_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>OKVED_R_VSvyaziSOplTrudRab</t>
+          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>OKVED_R_ProcPoDolgObyaz</t>
+          <t>OKVED_O_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>OKVED_R_NalogNaPri</t>
+          <t>OKVED_O_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>OKVED_93_VSvyaziSOplTrudRab</t>
+          <t>OKVED_84_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>OKVED_93_ProcPoDolgObyaz</t>
+          <t>OKVED_84_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>OKVED_93_NalogNaPri</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>OKVED_96_ProcPoDolgObyaz</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>OKVED_96_NalogNaPri</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdAkcOrgDolUch</t>
+          <t>OKVED_Q_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>OKVED_01_DivProcDolgFinVlozh</t>
+          <t>OKVED_Q_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>OKVED_B_OtProdAkcOrgDolUch</t>
+          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>OKVED_07_OtProdAkcOrgDolUch</t>
+          <t>OKVED_R_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>OKVED_C_OtProdAkcOrgDolUch</t>
+          <t>OKVED_R_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>OKVED_10_OtProdAkcOrgDolUch</t>
+          <t>OKVED_R_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdFinVlozh</t>
+          <t>OKVED_93_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_96_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdAkcOrgDolUch</t>
+          <t>OKVED_96_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdFinVlozh</t>
+          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>OKVED_E_DivProcDolgFinVlozh</t>
+          <t>OKVED_01_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdFinVlozh</t>
+          <t>OKVED_B_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>OKVED_36_DivProcDolgFinVlozh</t>
+          <t>OKVED_07_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_C_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdAkcOrgDolUch</t>
+          <t>OKVED_10_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdFinVlozh</t>
+          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>OKVED_38_DivProcDolgFinVlozh</t>
+          <t>OKVED_11_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_11_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdAkcOrgDolUch</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdAkcOrgDolUch</t>
+          <t>OKVED_E_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_E_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdAkcOrgDolUch</t>
+          <t>OKVED_E_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdFinVlozh</t>
+          <t>OKVED_36_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>OKVED_G_OtProdAkcOrgDolUch</t>
+          <t>OKVED_36_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>OKVED_46_OtProdAkcOrgDolUch</t>
+          <t>OKVED_36_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>OKVED_47_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>OKVED_H_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_38_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>OKVED_49_DivProcDolgFinVlozh</t>
+          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>OKVED_52_OtProdAkcOrgDolUch</t>
+          <t>OKVED_F_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdAkcOrgDolUch</t>
+          <t>OKVED_41_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_43_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdAkcOrgDolUch</t>
+          <t>OKVED_G_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_46_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdAkcOrgDolUch</t>
+          <t>OKVED_47_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>OKVED_L_OtProdAkcOrgDolUch</t>
+          <t>OKVED_H_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdAkcOrgDolUch</t>
+          <t>OKVED_49_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_49_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdAkcOrgDolUch</t>
+          <t>OKVED_52_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdAkcOrgDolUch</t>
+          <t>OKVED_I_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>OKVED_71_DivProcDolgFinVlozh</t>
+          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdAkcOrgDolUch</t>
+          <t>OKVED_55_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdFinVlozh</t>
+          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdAkcOrgDolUch</t>
+          <t>OKVED_K_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdFinVlozh</t>
+          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_64_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdAkcOrgDolUch</t>
+          <t>OKVED_L_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>OKVED_S_DivProcDolgFinVlozh</t>
+          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_M_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdAkcOrgDolUch</t>
+          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>OKVED_94_DivProcDolgFinVlozh</t>
+          <t>OKVED_70_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>OKVED_01_DolUch</t>
+          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_71_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>OKVED_B_DolUch</t>
+          <t>OKVED_71_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_N_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>OKVED_C_DolUch</t>
+          <t>OKVED_N_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_77_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>OKVED_10_DolUch</t>
+          <t>OKVED_77_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>OKVED_11_DolUch</t>
+          <t>OKVED_S_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>OKVED_11_PrCenBum</t>
+          <t>OKVED_S_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>OKVED_33_DolUch</t>
+          <t>OKVED_94_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_94_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>OKVED_E_DolUch</t>
+          <t>OKVED_01_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>OKVED_E_PrCenBum</t>
+          <t>OKVED_01_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_B_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>OKVED_36_DolUch</t>
+          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>OKVED_36_PrCenBum</t>
+          <t>OKVED_C_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>OKVED_F_DolUch</t>
+          <t>OKVED_10_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>OKVED_41_DolUch</t>
+          <t>OKVED_11_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_11_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>OKVED_42_DolUch</t>
+          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_33_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>OKVED_43_DolUch</t>
+          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>OKVED_43_PrCenBum</t>
+          <t>OKVED_E_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_E_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>OKVED_47_DolUch</t>
+          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>OKVED_H_DolUch</t>
+          <t>OKVED_36_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_36_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>OKVED_49_DolUch</t>
+          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_F_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>OKVED_50_DolUch</t>
+          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>OKVED_50_PrCenBum</t>
+          <t>OKVED_41_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>OKVED_52_DolUch</t>
+          <t>OKVED_42_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_43_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_43_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>OKVED_K_DolUch</t>
+          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_47_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>OKVED_M_DolUch</t>
+          <t>OKVED_H_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>OKVED_71_DolUch</t>
+          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>OKVED_N_DolUch</t>
+          <t>OKVED_49_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>OKVED_N_PrCenBum</t>
+          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>OKVED_79_DolUch</t>
+          <t>OKVED_50_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>OKVED_79_PrCenBum</t>
+          <t>OKVED_50_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>OKVED_S_Modern</t>
+          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>OKVED_S_DolUch</t>
+          <t>OKVED_52_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>OKVED_94_Modern</t>
+          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>OKVED_94_DolUch</t>
+          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_K_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>OKVED_01_PostDeyt1</t>
+          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>OKVED_01_DrPost</t>
+          <t>OKVED_M_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt</t>
+          <t>OKVED_71_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt1</t>
+          <t>OKVED_N_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt</t>
+          <t>OKVED_N_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt1</t>
+          <t>OKVED_79_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>OKVED_C_PostDeyt1</t>
+          <t>OKVED_79_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>OKVED_10_PostDeyt1</t>
+          <t>OKVED_S_Modern</t>
         </is>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>OKVED_32_PlCredit</t>
+          <t>OKVED_S_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt</t>
+          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt1</t>
+          <t>OKVED_94_Modern</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt</t>
+          <t>OKVED_94_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt1</t>
+          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>OKVED_33_DrPost</t>
+          <t>OKVED_01_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_01_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_B_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>OKVED_38_PostDeyt1</t>
+          <t>OKVED_B_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>OKVED_38_DrPost</t>
+          <t>OKVED_07_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>OKVED_F_PostDeyt1</t>
+          <t>OKVED_07_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt</t>
+          <t>OKVED_C_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt1</t>
+          <t>OKVED_10_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt</t>
+          <t>OKVED_32_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt1</t>
+          <t>OKVED_32_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>OKVED_42_DrPost</t>
+          <t>OKVED_32_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>OKVED_43_PostDeyt1</t>
+          <t>OKVED_33_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>OKVED_43_DrPost</t>
+          <t>OKVED_33_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt</t>
+          <t>OKVED_33_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt1</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt1</t>
+          <t>OKVED_38_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt</t>
+          <t>OKVED_38_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt1</t>
+          <t>OKVED_F_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>OKVED_H_PostDeyt1</t>
+          <t>OKVED_41_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt</t>
+          <t>OKVED_41_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt1</t>
+          <t>OKVED_42_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>OKVED_50_DrPost</t>
+          <t>OKVED_42_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt</t>
+          <t>OKVED_42_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt1</t>
+          <t>OKVED_43_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>OKVED_51_DrPost</t>
+          <t>OKVED_43_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>OKVED_52_PostDeyt1</t>
+          <t>OKVED_G_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>OKVED_I_PostDeyt1</t>
+          <t>OKVED_G_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>OKVED_I_DrPost</t>
+          <t>OKVED_46_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>OKVED_55_PostDeyt1</t>
+          <t>OKVED_46_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>OKVED_55_DrPost</t>
+          <t>OKVED_47_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt</t>
+          <t>OKVED_47_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt1</t>
+          <t>OKVED_H_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>OKVED_K_DrPost</t>
+          <t>OKVED_50_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt</t>
+          <t>OKVED_50_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt1</t>
+          <t>OKVED_50_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>OKVED_64_DrPost</t>
+          <t>OKVED_51_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>OKVED_L_PostDeyt1</t>
+          <t>OKVED_51_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>OKVED_68_PostDeyt1</t>
+          <t>OKVED_51_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>OKVED_70_PlCredit</t>
+          <t>OKVED_52_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>OKVED_70_PostDeyt</t>
+          <t>OKVED_I_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>OKVED_71_PostDeyt</t>
+          <t>OKVED_I_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt</t>
+          <t>OKVED_55_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt1</t>
+          <t>OKVED_55_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>OKVED_74_DrPost</t>
+          <t>OKVED_K_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt</t>
+          <t>OKVED_K_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt1</t>
+          <t>OKVED_K_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt</t>
+          <t>OKVED_64_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt1</t>
+          <t>OKVED_64_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>OKVED_79_DrPost</t>
+          <t>OKVED_64_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>OKVED_81_PlCredit</t>
+          <t>OKVED_L_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt</t>
+          <t>OKVED_68_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt1</t>
+          <t>OKVED_70_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>OKVED_S_PlCredit</t>
+          <t>OKVED_70_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>OKVED_S_PostDeyt1</t>
+          <t>OKVED_71_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>OKVED_94_PlCredit</t>
+          <t>OKVED_74_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>OKVED_94_PostDeyt1</t>
+          <t>OKVED_74_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin1</t>
+          <t>OKVED_74_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin2</t>
+          <t>OKVED_N_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>OKVED_B_PlPoFin1</t>
+          <t>OKVED_N_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>OKVED_07_PlPoFin1</t>
+          <t>OKVED_79_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin</t>
+          <t>OKVED_79_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin1</t>
+          <t>OKVED_79_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin2</t>
+          <t>OKVED_81_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin3</t>
+          <t>OKVED_81_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_81_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_S_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin1</t>
+          <t>OKVED_S_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin2</t>
+          <t>OKVED_94_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin1</t>
+          <t>OKVED_94_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin2</t>
+          <t>OKVED_01_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>OKVED_F_PlPoFin1</t>
+          <t>OKVED_01_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>OKVED_41_PlPoFin1</t>
+          <t>OKVED_B_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin1</t>
+          <t>OKVED_07_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>OKVED_G_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>OKVED_46_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>OKVED_47_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>OKVED_H_PlPoFin1</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin1</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin2</t>
+          <t>OKVED_E_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoFin1</t>
+          <t>OKVED_E_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
         <is>
-          <t>OKVED_52_PlPoFin1</t>
+          <t>OKVED_38_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin1</t>
+          <t>OKVED_38_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin2</t>
+          <t>OKVED_F_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin1</t>
+          <t>OKVED_41_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin2</t>
+          <t>OKVED_43_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoFin1</t>
+          <t>OKVED_43_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoFin1</t>
+          <t>OKVED_G_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>OKVED_68_PlPoFin1</t>
+          <t>OKVED_46_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>OKVED_M_PlPoFin1</t>
+          <t>OKVED_47_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin</t>
+          <t>OKVED_H_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin1</t>
+          <t>OKVED_49_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin2</t>
+          <t>OKVED_49_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin3</t>
+          <t>OKVED_50_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>OKVED_71_PlPoFin1</t>
+          <t>OKVED_52_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin1</t>
+          <t>OKVED_I_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin2</t>
+          <t>OKVED_I_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin3</t>
+          <t>OKVED_55_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>OKVED_74_SaldoDenPot</t>
+          <t>OKVED_55_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin1</t>
+          <t>OKVED_K_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin2</t>
+          <t>OKVED_64_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin1</t>
+          <t>OKVED_68_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin2</t>
+          <t>OKVED_M_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin3</t>
+          <t>OKVED_70_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>OKVED_81_SaldoDenPot</t>
+          <t>OKVED_70_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin1</t>
+          <t>OKVED_70_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin2</t>
+          <t>OKVED_70_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin3</t>
+          <t>OKVED_71_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin1</t>
+          <t>OKVED_74_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin2</t>
+          <t>OKVED_74_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin3</t>
+          <t>OKVED_74_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
         <is>
-          <t>OKVED_01_Velch</t>
+          <t>OKVED_74_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>OKVED_11_Velch</t>
+          <t>OKVED_79_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
         <is>
-          <t>OKVED_32_Velch</t>
+          <t>OKVED_79_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
         <is>
-          <t>OKVED_33_Velch</t>
+          <t>OKVED_81_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
         <is>
-          <t>OKVED_E_Velch</t>
+          <t>OKVED_81_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
         <is>
-          <t>OKVED_38_Velch</t>
+          <t>OKVED_81_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
         <is>
-          <t>OKVED_F_Velch</t>
+          <t>OKVED_81_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
         <is>
-          <t>OKVED_41_Velch</t>
+          <t>OKVED_S_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
         <is>
-          <t>OKVED_42_Velch</t>
+          <t>OKVED_S_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
         <is>
-          <t>OKVED_43_Velch</t>
+          <t>OKVED_S_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
         <is>
-          <t>OKVED_47_Velch</t>
+          <t>OKVED_94_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
         <is>
-          <t>OKVED_49_Velch</t>
+          <t>OKVED_94_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
         <is>
-          <t>OKVED_I_Velch</t>
+          <t>OKVED_94_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
         <is>
-          <t>OKVED_56_Velch</t>
+          <t>OKVED_01_Velch</t>
         </is>
       </c>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
         <is>
-          <t>OKVED_J_Velch</t>
+          <t>OKVED_11_Velch</t>
         </is>
       </c>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>OKVED_63_Velch</t>
+          <t>OKVED_32_Velch</t>
         </is>
       </c>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>OKVED_L_Velch</t>
+          <t>OKVED_33_Velch</t>
         </is>
       </c>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
         <is>
-          <t>OKVED_68_Velch</t>
+          <t>OKVED_E_Velch</t>
         </is>
       </c>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
         <is>
-          <t>OKVED_M_Velch</t>
+          <t>OKVED_38_Velch</t>
         </is>
       </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>OKVED_69_Velch</t>
+          <t>OKVED_F_Velch</t>
         </is>
       </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>OKVED_70_Velch</t>
+          <t>OKVED_41_Velch</t>
         </is>
       </c>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>OKVED_71_Velch</t>
+          <t>OKVED_42_Velch</t>
         </is>
       </c>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>OKVED_N_Velch</t>
+          <t>OKVED_43_Velch</t>
         </is>
       </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
         <is>
-          <t>OKVED_77_Velch</t>
+          <t>OKVED_47_Velch</t>
         </is>
       </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
         <is>
-          <t>OKVED_79_Velch</t>
+          <t>OKVED_49_Velch</t>
         </is>
       </c>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>OKVED_81_Velch</t>
+          <t>OKVED_I_Velch</t>
         </is>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
         <is>
-          <t>OKVED_82_Velch</t>
+          <t>OKVED_56_Velch</t>
         </is>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
         <is>
-          <t>OKVED_O_Velch</t>
+          <t>OKVED_J_Velch</t>
         </is>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
         <is>
-          <t>OKVED_84_Velch</t>
+          <t>OKVED_63_Velch</t>
         </is>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_L_Velch</t>
         </is>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_68_Velch</t>
         </is>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
         <is>
-          <t>OKVED_88_Velch</t>
+          <t>OKVED_M_Velch</t>
         </is>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>OKVED_R_Velch</t>
+          <t>OKVED_69_Velch</t>
         </is>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>OKVED_93_Velch</t>
+          <t>OKVED_70_Velch</t>
         </is>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>OKVED_S_Velch</t>
+          <t>OKVED_71_Velch</t>
         </is>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>OKVED_94_Velch</t>
+          <t>OKVED_N_Velch</t>
         </is>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>OKVED_96_Velch</t>
+          <t>OKVED_77_Velch</t>
         </is>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>OKVED_43_UstKap</t>
+          <t>OKVED_79_Velch</t>
         </is>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>OKVED_43_ChiAkt</t>
+          <t>OKVED_81_Velch</t>
         </is>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap</t>
+          <t>OKVED_82_Velch</t>
         </is>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>OKVED_J_SebPro</t>
+          <t>OKVED_O_Velch</t>
         </is>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>OKVED_J_Pri(ubOtPro</t>
+          <t>OKVED_84_Velch</t>
         </is>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
-          <t>OKVED_J_ChiPri(ubOtcPer</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap</t>
+          <t>OKVED_88_Velch</t>
         </is>
       </c>
     </row>
     <row r="1696">
       <c r="A1696" t="inlineStr">
         <is>
-          <t>OKVED_63_SebPro</t>
+          <t>OKVED_R_Velch</t>
         </is>
       </c>
     </row>
     <row r="1697">
       <c r="A1697" t="inlineStr">
         <is>
-          <t>OKVED_63_Pri(ubOtPro</t>
+          <t>OKVED_93_Velch</t>
         </is>
       </c>
     </row>
     <row r="1698">
       <c r="A1698" t="inlineStr">
         <is>
-          <t>OKVED_63_ChiPri(ubOtcPer</t>
+          <t>OKVED_S_Velch</t>
         </is>
       </c>
     </row>
     <row r="1699">
       <c r="A1699" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_94_Velch</t>
         </is>
       </c>
     </row>
     <row r="1700">
       <c r="A1700" t="inlineStr">
         <is>
-          <t>OKVED_K_SebPro</t>
+          <t>OKVED_96_Velch</t>
         </is>
       </c>
     </row>
     <row r="1701">
       <c r="A1701" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap</t>
+          <t>OKVED_43_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1702">
       <c r="A1702" t="inlineStr">
         <is>
-          <t>OKVED_69_ChiAkt</t>
+          <t>OKVED_43_ChiAkt</t>
         </is>
       </c>
     </row>
     <row r="1703">
       <c r="A1703" t="inlineStr">
         <is>
-          <t>OKVED_69_SebPro</t>
+          <t>OKVED_J_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1704">
       <c r="A1704" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap</t>
+          <t>OKVED_J_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1705">
       <c r="A1705" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap</t>
+          <t>OKVED_J_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1706">
       <c r="A1706" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap</t>
+          <t>OKVED_J_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1707">
       <c r="A1707" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap</t>
+          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1708">
       <c r="A1708" t="inlineStr">
         <is>
-          <t>OKVED_Q_SebPro</t>
+          <t>OKVED_63_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1709">
       <c r="A1709" t="inlineStr">
         <is>
-          <t>OKVED_Q_Pri(ubOtPro</t>
+          <t>OKVED_63_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1710">
       <c r="A1710" t="inlineStr">
         <is>
-          <t>OKVED_Q_ChiPri(ubOtcPer</t>
+          <t>OKVED_63_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1711">
       <c r="A1711" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_63_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1712">
       <c r="A1712" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap</t>
+          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1713">
       <c r="A1713" t="inlineStr">
         <is>
-          <t>OKVED_88_SebPro</t>
+          <t>OKVED_K_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1714">
       <c r="A1714" t="inlineStr">
         <is>
-          <t>OKVED_88_Pri(ubOtPro</t>
+          <t>OKVED_69_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1715">
       <c r="A1715" t="inlineStr">
         <is>
-          <t>OKVED_88_ChiPri(ubOtcPer</t>
+          <t>OKVED_69_ChiAkt</t>
         </is>
       </c>
     </row>
     <row r="1716">
       <c r="A1716" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_69_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1717">
       <c r="A1717" t="inlineStr">
         <is>
-          <t>OKVED_R_SebPro</t>
+          <t>OKVED_O_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1718">
       <c r="A1718" t="inlineStr">
+        <is>
+          <t>OKVED_84_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>OKVED_Q_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>OKVED_Q_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>OKVED_Q_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>OKVED_Q_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>OKVED_88_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>OKVED_88_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>OKVED_88_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>OKVED_88_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>OKVED_88_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>OKVED_R_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
         <is>
           <t>OKVED_93_SebPro</t>
         </is>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1731"/>
+  <dimension ref="A1:A1735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8812,3722 +8812,3750 @@
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>OKVED_85_SumPriZaSooPerPreGo</t>
+          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosUbyV%</t>
+          <t>OKVED_85_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosSumPriV%</t>
+          <t>OKVED_85_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_85_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosPriV%</t>
+          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_85_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>OKVED_85_SumPriZaSooPerPreGo</t>
+          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosUbyV%</t>
+          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosSumPriV%</t>
+          <t>OKVED_85_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t>OKVED_93_TeRosUbyV%</t>
+          <t>OKVED_85_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>OKVED_S_TeRosPriV%</t>
+          <t>OKVED_85_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>OKVED_94_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_93_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosPriV%</t>
+          <t>OKVED_S_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
-          <t>OKVED_94_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_94_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>OKVED_94_SumPriZaSooPerPreGo</t>
+          <t>OKVED_94_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosUbyV%</t>
+          <t>OKVED_94_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosSumPriV%</t>
+          <t>OKVED_94_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>OKVED_96_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_94_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosPriV%</t>
+          <t>OKVED_94_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>OKVED_96_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_94_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>OKVED_96_SumPriZaSooPerPreGo</t>
+          <t>OKVED_96_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosUbyV%</t>
+          <t>OKVED_96_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosSumPriV%</t>
+          <t>OKVED_96_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>MO_30851_OrgPolUbyKolOrgEdi_1</t>
+          <t>OKVED_96_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="inlineStr">
         <is>
-          <t>MO_30851_OrgPolUbyV%KObsKol_1</t>
+          <t>OKVED_96_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
         <is>
-          <t>MO_30851_OrgPolUbyUby_1</t>
+          <t>OKVED_96_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>MO_30501_OrgPolPriKolOrgEdi_1</t>
+          <t>OKVED_96_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="inlineStr">
         <is>
-          <t>MO_30501_OrgPolPriV%KObsKol_1</t>
+          <t>MO_30851_OrgPolUbyKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>MO_30501_OrgPolPriPriDoNal_1</t>
+          <t>MO_30851_OrgPolUbyV%KObsKol_1</t>
         </is>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>MO_30510_OrgPolPriPriDoNal_1</t>
+          <t>MO_30851_OrgPolUbyUby_1</t>
         </is>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>MO_30604_PriUby(-DoNal_1</t>
+          <t>MO_30501_OrgPolPriKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolPriPriDoNal_1</t>
+          <t>MO_30501_OrgPolPriV%KObsKol_1</t>
         </is>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolUbyKolOrgEdi_1</t>
+          <t>MO_30501_OrgPolPriPriDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolUbyV%KObsKol_1</t>
+          <t>MO_30510_OrgPolPriPriDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolUbyUby_1</t>
+          <t>MO_30604_PriUby(-DoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>MO_30851_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30604_OrgPolPriPriDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>MO_30851_KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>MO_30604_OrgPolUbyKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>MO_30851_TeRosUbyV%_1</t>
+          <t>MO_30604_OrgPolUbyV%KObsKol_1</t>
         </is>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>MO_30501_TeRosPriV%_1</t>
+          <t>MO_30604_OrgPolUbyUby_1</t>
         </is>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>MO_30501_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30851_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>MO_30501_KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>MO_30851_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>MO_30501_TeRosSumPriV%_1</t>
+          <t>MO_30851_TeRosUbyV%_1</t>
         </is>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>MO_30510_TeRosPriV%_1</t>
+          <t>MO_30501_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>MO_30510_SumPriZaSooPerPreGo_1</t>
+          <t>MO_30501_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>MO_30510_TeRosSumPriV%_1</t>
+          <t>MO_30501_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>MO_30604_PriUby(-DoNalZaAnaPerPreGo_1</t>
+          <t>MO_30501_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosPriV%_1</t>
+          <t>MO_30510_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>MO_30604_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30510_SumPriZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>MO_30604_KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>MO_30510_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>MO_30604_SumPriZaSooPerPreGo_1</t>
+          <t>MO_30604_PriUby(-DoNalZaAnaPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosUbyV%_1</t>
+          <t>MO_30604_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosSumPriV%_1</t>
+          <t>MO_30604_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>MO_30616_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30604_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>MO_30616_KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>MO_30604_SumPriZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="inlineStr">
         <is>
-          <t>MO_30619_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30604_TeRosUbyV%_1</t>
         </is>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="inlineStr">
         <is>
-          <t>MO_30619_KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>MO_30604_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>MO_30832_TeRosPriV%_1</t>
+          <t>MO_30616_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>OKVED_56_VToChiKomIUprRas</t>
+          <t>MO_30616_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-OtPro</t>
+          <t>MO_30619_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>OKVED_J_SebProSUchKomIUprRas</t>
+          <t>MO_30619_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
         <is>
-          <t>OKVED_J_VToChiKomIUprRas</t>
+          <t>MO_30832_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>OKVED_56_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%KKomIUprRas</t>
+          <t>OKVED_J_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%KVyr</t>
+          <t>OKVED_J_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>OKVED_J_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-OtPro</t>
+          <t>OKVED_J_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>OKVED_63_SebProSUchKomIUprRas</t>
+          <t>OKVED_J_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>OKVED_63_VToChiKomIUprRas</t>
+          <t>OKVED_J_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>OKVED_J_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%KKomIUprRas</t>
+          <t>OKVED_63_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%KVyr</t>
+          <t>OKVED_63_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>OKVED_63_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>OKVED_74_VToChiKomIUprRas</t>
+          <t>OKVED_63_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>OKVED_81_VToChiKomIUprRas</t>
+          <t>OKVED_63_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>OKVED_82_VToChiKomIUprRas</t>
+          <t>OKVED_63_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>OKVED_O_VToChiKomIUprRas</t>
+          <t>OKVED_63_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>OKVED_84_VToChiKomIUprRas</t>
+          <t>OKVED_74_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>OKVED_85_VToChiKomIUprRas</t>
+          <t>OKVED_81_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-OtPro</t>
+          <t>OKVED_82_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>OKVED_Q_SebProSUchKomIUprRas</t>
+          <t>OKVED_O_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>OKVED_Q_VToChiKomIUprRas</t>
+          <t>OKVED_84_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>OKVED_85_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%KKomIUprRas</t>
+          <t>OKVED_Q_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%KVyr</t>
+          <t>OKVED_Q_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>OKVED_Q_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-OtPro</t>
+          <t>OKVED_Q_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>OKVED_88_SebProSUchKomIUprRas</t>
+          <t>OKVED_Q_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>OKVED_88_VToChiKomIUprRas</t>
+          <t>OKVED_Q_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>OKVED_Q_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%KKomIUprRas</t>
+          <t>OKVED_88_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%KVyr</t>
+          <t>OKVED_88_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>OKVED_88_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>OKVED_R_SebProSUchKomIUprRas</t>
+          <t>OKVED_88_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>OKVED_R_VToChiKomIUprRas</t>
+          <t>OKVED_88_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>OKVED_93_SebProSUchKomIUprRas</t>
+          <t>OKVED_88_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>OKVED_93_VToChiKomIUprRas</t>
+          <t>OKVED_88_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>OKVED_56_OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OKVED_R_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>OKVED_O_OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OKVED_R_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>OKVED_84_OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OKVED_93_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>OKVED_11_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_93_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>OKVED_43_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_56_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>OKVED_49_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_O_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>OKVED_56_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_84_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>OKVED_56_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_11_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>OKVED_69_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_43_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>OKVED_69_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_49_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>OKVED_74_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_56_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>OKVED_81_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_56_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>OKVED_81_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_69_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>OKVED_82_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_69_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>OKVED_82_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_74_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>OKVED_O_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_81_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>OKVED_O_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_81_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_82_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_82_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_O_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_O_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>OKVED_R_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>OKVED_R_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>OKVED_93_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>OKVED_93_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>OKVED_94_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_R_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>OKVED_96_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_R_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_93_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>OKVED_93_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>OKVED_94_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10DebZad</t>
+          <t>OKVED_96_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10V%KObsZad</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>OKVED_70_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>OKVED_R_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10DebZad</t>
         </is>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>OKVED_93_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>OKVED_94_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>OKVED_96_KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>OKVED_70_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>OKVED_96_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>OKVED_R_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
+          <t>OKVED_93_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsKol</t>
+          <t>OKVED_94_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20DebZad</t>
+          <t>OKVED_96_KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZad</t>
+          <t>OKVED_96_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KreZad</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20DenSreIDenEkv</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeTekLikOt&gt;=20DebZad</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeTekLikOt&gt;=20V%KObsZad</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KreZad</t>
         </is>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>OKVED_01_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>OKVED_32_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>OKVED_E_ArendPlDeVsego</t>
+          <t>OKVED_69_KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>OKVED_36_ArendPlDeVsego</t>
+          <t>OKVED_69_KoeTekLikOt&gt;=20V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>OKVED_38_ArendPlDeVsego</t>
+          <t>OKVED_01_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>OKVED_41_ArendPlDeVsego</t>
+          <t>OKVED_32_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>OKVED_43_ArendPlDeVsego</t>
+          <t>OKVED_E_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>OKVED_49_ArendPlDeVsego</t>
+          <t>OKVED_36_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>OKVED_50_ArendPlDeVsego</t>
+          <t>OKVED_38_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>OKVED_I_ArendPlDeVsego</t>
+          <t>OKVED_41_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>OKVED_55_ArendPlDeVsego</t>
+          <t>OKVED_43_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>OKVED_56_ArendPlDeVsego</t>
+          <t>OKVED_49_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>OKVED_J_OtProdDeVsego</t>
+          <t>OKVED_50_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>OKVED_J_ArendPlDeVsego</t>
+          <t>OKVED_I_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>OKVED_63_OtProdDeVsego</t>
+          <t>OKVED_55_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>OKVED_63_ArendPlDeVsego</t>
+          <t>OKVED_56_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>OKVED_64_ArendPlDeVsego</t>
+          <t>OKVED_J_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>OKVED_69_ArendPlDeVsego</t>
+          <t>OKVED_J_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>OKVED_79_ArendPlDeVsego</t>
+          <t>OKVED_63_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>OKVED_81_ArendPlDeVsego</t>
+          <t>OKVED_63_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>OKVED_82_ArendPlDeVsego</t>
+          <t>OKVED_64_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>OKVED_O_ArendPlDeVsego</t>
+          <t>OKVED_69_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>OKVED_84_ArendPlDeVsego</t>
+          <t>OKVED_79_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_81_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_82_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>OKVED_88_OtProdDeVsego</t>
+          <t>OKVED_O_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>OKVED_88_ArendPlDeVsego</t>
+          <t>OKVED_84_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>OKVED_R_OtProdDeVsego</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>OKVED_R_ArendPlDeVsego</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>OKVED_93_OtProdDeVsego</t>
+          <t>OKVED_88_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>OKVED_93_ArendPlDeVsego</t>
+          <t>OKVED_88_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>OKVED_S_ArendPlDeVsego</t>
+          <t>OKVED_R_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>OKVED_94_ArendPlDeVsego</t>
+          <t>OKVED_R_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>OKVED_96_ArendPlDeVsego</t>
+          <t>OKVED_93_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcPoDolgObyaz</t>
+          <t>OKVED_93_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>OKVED_32_ProcPoDolgObyaz</t>
+          <t>OKVED_S_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>OKVED_32_NalogNaPri</t>
+          <t>OKVED_94_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>OKVED_33_NalogNaPri</t>
+          <t>OKVED_96_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcPoDolgObyaz</t>
+          <t>OKVED_11_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>OKVED_38_NalogNaPri</t>
+          <t>OKVED_32_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcPoDolgObyaz</t>
+          <t>OKVED_32_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>OKVED_56_ProcPoDolgObyaz</t>
+          <t>OKVED_33_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>OKVED_56_NalogNaPri</t>
+          <t>OKVED_36_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>OKVED_J_ProcPoDolgObyaz</t>
+          <t>OKVED_38_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>OKVED_J_NalogNaPri</t>
+          <t>OKVED_49_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>OKVED_63_ProcPoDolgObyaz</t>
+          <t>OKVED_56_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>OKVED_63_NalogNaPri</t>
+          <t>OKVED_56_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>OKVED_M_ProcPoDolgObyaz</t>
+          <t>OKVED_J_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>OKVED_69_ProcPoDolgObyaz</t>
+          <t>OKVED_J_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>OKVED_69_NalogNaPri</t>
+          <t>OKVED_63_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>OKVED_71_ProcPoDolgObyaz</t>
+          <t>OKVED_63_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>OKVED_71_NalogNaPri</t>
+          <t>OKVED_M_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>OKVED_74_ProcPoDolgObyaz</t>
+          <t>OKVED_69_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcPoDolgObyaz</t>
+          <t>OKVED_69_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>OKVED_79_NalogNaPri</t>
+          <t>OKVED_71_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>OKVED_81_NalogNaPri</t>
+          <t>OKVED_71_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_74_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>OKVED_O_VSvyaziSOplTrudRab</t>
+          <t>OKVED_77_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>OKVED_O_ProcPoDolgObyaz</t>
+          <t>OKVED_79_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_81_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>OKVED_84_VSvyaziSOplTrudRab</t>
+          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>OKVED_84_ProcPoDolgObyaz</t>
+          <t>OKVED_O_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_O_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_84_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_84_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>OKVED_Q_ProcPoDolgObyaz</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>OKVED_Q_NalogNaPri</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>OKVED_R_VSvyaziSOplTrudRab</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>OKVED_R_ProcPoDolgObyaz</t>
+          <t>OKVED_Q_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>OKVED_R_NalogNaPri</t>
+          <t>OKVED_Q_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>OKVED_93_VSvyaziSOplTrudRab</t>
+          <t>OKVED_R_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>OKVED_93_ProcPoDolgObyaz</t>
+          <t>OKVED_R_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>OKVED_93_NalogNaPri</t>
+          <t>OKVED_R_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>OKVED_96_ProcPoDolgObyaz</t>
+          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>OKVED_96_NalogNaPri</t>
+          <t>OKVED_93_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_93_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>OKVED_01_DivProcDolgFinVlozh</t>
+          <t>OKVED_96_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>OKVED_B_OtProdAkcOrgDolUch</t>
+          <t>OKVED_96_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>OKVED_07_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>OKVED_C_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>OKVED_10_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_B_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdAkcOrgDolUch</t>
+          <t>OKVED_07_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdFinVlozh</t>
+          <t>OKVED_C_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_10_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdAkcOrgDolUch</t>
+          <t>OKVED_11_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdFinVlozh</t>
+          <t>OKVED_11_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>OKVED_E_DivProcDolgFinVlozh</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdAkcOrgDolUch</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdFinVlozh</t>
+          <t>OKVED_E_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>OKVED_36_DivProcDolgFinVlozh</t>
+          <t>OKVED_E_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_E_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdAkcOrgDolUch</t>
+          <t>OKVED_36_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdFinVlozh</t>
+          <t>OKVED_36_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>OKVED_38_DivProcDolgFinVlozh</t>
+          <t>OKVED_36_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_38_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdAkcOrgDolUch</t>
+          <t>OKVED_F_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdFinVlozh</t>
+          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>OKVED_G_OtProdAkcOrgDolUch</t>
+          <t>OKVED_41_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>OKVED_46_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>OKVED_47_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>OKVED_H_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_G_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdAkcOrgDolUch</t>
+          <t>OKVED_46_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>OKVED_49_DivProcDolgFinVlozh</t>
+          <t>OKVED_47_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>OKVED_52_OtProdAkcOrgDolUch</t>
+          <t>OKVED_H_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdAkcOrgDolUch</t>
+          <t>OKVED_49_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_49_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdAkcOrgDolUch</t>
+          <t>OKVED_52_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdAkcOrgDolUch</t>
+          <t>OKVED_I_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdAkcOrgDolUch</t>
+          <t>OKVED_55_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>OKVED_L_OtProdAkcOrgDolUch</t>
+          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_K_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdAkcOrgDolUch</t>
+          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_64_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdAkcOrgDolUch</t>
+          <t>OKVED_L_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdAkcOrgDolUch</t>
+          <t>OKVED_M_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>OKVED_71_DivProcDolgFinVlozh</t>
+          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdAkcOrgDolUch</t>
+          <t>OKVED_70_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdFinVlozh</t>
+          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdAkcOrgDolUch</t>
+          <t>OKVED_71_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdFinVlozh</t>
+          <t>OKVED_71_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_N_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdAkcOrgDolUch</t>
+          <t>OKVED_N_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>OKVED_S_DivProcDolgFinVlozh</t>
+          <t>OKVED_77_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_77_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdAkcOrgDolUch</t>
+          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>OKVED_94_DivProcDolgFinVlozh</t>
+          <t>OKVED_S_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>OKVED_01_DolUch</t>
+          <t>OKVED_S_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>OKVED_B_DolUch</t>
+          <t>OKVED_94_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_94_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>OKVED_C_DolUch</t>
+          <t>OKVED_01_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_01_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>OKVED_10_DolUch</t>
+          <t>OKVED_B_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>OKVED_11_DolUch</t>
+          <t>OKVED_C_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>OKVED_11_PrCenBum</t>
+          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_10_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>OKVED_33_DolUch</t>
+          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_11_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>OKVED_E_DolUch</t>
+          <t>OKVED_11_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>OKVED_E_PrCenBum</t>
+          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_33_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>OKVED_36_DolUch</t>
+          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>OKVED_36_PrCenBum</t>
+          <t>OKVED_E_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_E_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>OKVED_F_DolUch</t>
+          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_36_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>OKVED_41_DolUch</t>
+          <t>OKVED_36_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>OKVED_42_DolUch</t>
+          <t>OKVED_F_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>OKVED_43_DolUch</t>
+          <t>OKVED_41_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>OKVED_43_PrCenBum</t>
+          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_42_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>OKVED_47_DolUch</t>
+          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>OKVED_H_DolUch</t>
+          <t>OKVED_43_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_43_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>OKVED_49_DolUch</t>
+          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_47_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>OKVED_50_DolUch</t>
+          <t>OKVED_H_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>OKVED_50_PrCenBum</t>
+          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_49_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>OKVED_52_DolUch</t>
+          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_50_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_50_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>OKVED_K_DolUch</t>
+          <t>OKVED_52_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>OKVED_M_DolUch</t>
+          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>OKVED_71_DolUch</t>
+          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>OKVED_N_DolUch</t>
+          <t>OKVED_K_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>OKVED_N_PrCenBum</t>
+          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>OKVED_79_DolUch</t>
+          <t>OKVED_M_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>OKVED_79_PrCenBum</t>
+          <t>OKVED_71_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>OKVED_S_Modern</t>
+          <t>OKVED_N_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>OKVED_S_DolUch</t>
+          <t>OKVED_N_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_79_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>OKVED_94_Modern</t>
+          <t>OKVED_79_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>OKVED_94_DolUch</t>
+          <t>OKVED_S_Modern</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_S_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>OKVED_01_PostDeyt1</t>
+          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>OKVED_01_DrPost</t>
+          <t>OKVED_94_Modern</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt</t>
+          <t>OKVED_94_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt1</t>
+          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt</t>
+          <t>OKVED_01_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt1</t>
+          <t>OKVED_01_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>OKVED_C_PostDeyt1</t>
+          <t>OKVED_B_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>OKVED_10_PostDeyt1</t>
+          <t>OKVED_B_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>OKVED_32_PlCredit</t>
+          <t>OKVED_07_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt</t>
+          <t>OKVED_07_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt1</t>
+          <t>OKVED_C_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt</t>
+          <t>OKVED_10_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt1</t>
+          <t>OKVED_32_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>OKVED_33_DrPost</t>
+          <t>OKVED_32_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_32_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_33_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>OKVED_38_PostDeyt1</t>
+          <t>OKVED_33_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>OKVED_38_DrPost</t>
+          <t>OKVED_33_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>OKVED_F_PostDeyt1</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt1</t>
+          <t>OKVED_38_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt</t>
+          <t>OKVED_38_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt1</t>
+          <t>OKVED_F_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>OKVED_42_DrPost</t>
+          <t>OKVED_41_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>OKVED_43_PostDeyt1</t>
+          <t>OKVED_41_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>OKVED_43_DrPost</t>
+          <t>OKVED_42_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt</t>
+          <t>OKVED_42_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt1</t>
+          <t>OKVED_42_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt</t>
+          <t>OKVED_43_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt1</t>
+          <t>OKVED_43_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt</t>
+          <t>OKVED_G_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt1</t>
+          <t>OKVED_G_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>OKVED_H_PostDeyt1</t>
+          <t>OKVED_46_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt</t>
+          <t>OKVED_46_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt1</t>
+          <t>OKVED_47_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>OKVED_50_DrPost</t>
+          <t>OKVED_47_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt</t>
+          <t>OKVED_H_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt1</t>
+          <t>OKVED_50_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>OKVED_51_DrPost</t>
+          <t>OKVED_50_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>OKVED_52_PostDeyt1</t>
+          <t>OKVED_50_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>OKVED_I_PostDeyt1</t>
+          <t>OKVED_51_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>OKVED_I_DrPost</t>
+          <t>OKVED_51_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>OKVED_55_PostDeyt1</t>
+          <t>OKVED_51_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>OKVED_55_DrPost</t>
+          <t>OKVED_52_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt</t>
+          <t>OKVED_I_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt1</t>
+          <t>OKVED_I_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>OKVED_K_DrPost</t>
+          <t>OKVED_55_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt</t>
+          <t>OKVED_55_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt1</t>
+          <t>OKVED_K_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>OKVED_64_DrPost</t>
+          <t>OKVED_K_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>OKVED_L_PostDeyt1</t>
+          <t>OKVED_K_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>OKVED_68_PostDeyt1</t>
+          <t>OKVED_64_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>OKVED_70_PlCredit</t>
+          <t>OKVED_64_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>OKVED_70_PostDeyt</t>
+          <t>OKVED_64_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>OKVED_71_PostDeyt</t>
+          <t>OKVED_L_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt</t>
+          <t>OKVED_68_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt1</t>
+          <t>OKVED_70_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>OKVED_74_DrPost</t>
+          <t>OKVED_70_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt</t>
+          <t>OKVED_71_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt1</t>
+          <t>OKVED_74_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt</t>
+          <t>OKVED_74_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt1</t>
+          <t>OKVED_74_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>OKVED_79_DrPost</t>
+          <t>OKVED_N_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>OKVED_81_PlCredit</t>
+          <t>OKVED_N_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt</t>
+          <t>OKVED_79_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt1</t>
+          <t>OKVED_79_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>OKVED_S_PlCredit</t>
+          <t>OKVED_79_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>OKVED_S_PostDeyt1</t>
+          <t>OKVED_81_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>OKVED_94_PlCredit</t>
+          <t>OKVED_81_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>OKVED_94_PostDeyt1</t>
+          <t>OKVED_81_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin1</t>
+          <t>OKVED_S_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin2</t>
+          <t>OKVED_S_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>OKVED_B_PlPoFin1</t>
+          <t>OKVED_94_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>OKVED_07_PlPoFin1</t>
+          <t>OKVED_94_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin</t>
+          <t>OKVED_01_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin1</t>
+          <t>OKVED_01_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin2</t>
+          <t>OKVED_B_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin3</t>
+          <t>OKVED_07_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin1</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin2</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>OKVED_F_PlPoFin1</t>
+          <t>OKVED_E_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>OKVED_41_PlPoFin1</t>
+          <t>OKVED_E_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin1</t>
+          <t>OKVED_38_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin2</t>
+          <t>OKVED_38_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>OKVED_G_PlPoFin1</t>
+          <t>OKVED_F_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>OKVED_46_PlPoFin1</t>
+          <t>OKVED_41_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>OKVED_47_PlPoFin1</t>
+          <t>OKVED_43_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>OKVED_H_PlPoFin1</t>
+          <t>OKVED_43_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin1</t>
+          <t>OKVED_G_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin2</t>
+          <t>OKVED_46_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoFin1</t>
+          <t>OKVED_47_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>OKVED_52_PlPoFin1</t>
+          <t>OKVED_H_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin1</t>
+          <t>OKVED_49_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin2</t>
+          <t>OKVED_49_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin1</t>
+          <t>OKVED_50_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin2</t>
+          <t>OKVED_52_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoFin1</t>
+          <t>OKVED_I_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoFin1</t>
+          <t>OKVED_I_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>OKVED_68_PlPoFin1</t>
+          <t>OKVED_55_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>OKVED_M_PlPoFin1</t>
+          <t>OKVED_55_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin</t>
+          <t>OKVED_K_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin1</t>
+          <t>OKVED_64_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin2</t>
+          <t>OKVED_68_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin3</t>
+          <t>OKVED_M_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>OKVED_71_PlPoFin1</t>
+          <t>OKVED_70_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin1</t>
+          <t>OKVED_70_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin2</t>
+          <t>OKVED_70_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin3</t>
+          <t>OKVED_70_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
         <is>
-          <t>OKVED_74_SaldoDenPot</t>
+          <t>OKVED_71_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin1</t>
+          <t>OKVED_74_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin2</t>
+          <t>OKVED_74_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin1</t>
+          <t>OKVED_74_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin2</t>
+          <t>OKVED_74_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin3</t>
+          <t>OKVED_79_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
         <is>
-          <t>OKVED_81_SaldoDenPot</t>
+          <t>OKVED_79_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin1</t>
+          <t>OKVED_81_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin2</t>
+          <t>OKVED_81_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin3</t>
+          <t>OKVED_81_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin1</t>
+          <t>OKVED_81_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin2</t>
+          <t>OKVED_S_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin3</t>
+          <t>OKVED_S_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
         <is>
-          <t>OKVED_01_Velch</t>
+          <t>OKVED_S_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
         <is>
-          <t>OKVED_11_Velch</t>
+          <t>OKVED_94_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>OKVED_32_Velch</t>
+          <t>OKVED_94_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>OKVED_33_Velch</t>
+          <t>OKVED_94_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
         <is>
-          <t>OKVED_E_Velch</t>
+          <t>OKVED_01_Velch</t>
         </is>
       </c>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
         <is>
-          <t>OKVED_38_Velch</t>
+          <t>OKVED_11_Velch</t>
         </is>
       </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>OKVED_F_Velch</t>
+          <t>OKVED_32_Velch</t>
         </is>
       </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>OKVED_41_Velch</t>
+          <t>OKVED_33_Velch</t>
         </is>
       </c>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>OKVED_42_Velch</t>
+          <t>OKVED_E_Velch</t>
         </is>
       </c>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>OKVED_43_Velch</t>
+          <t>OKVED_38_Velch</t>
         </is>
       </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
         <is>
-          <t>OKVED_47_Velch</t>
+          <t>OKVED_F_Velch</t>
         </is>
       </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
         <is>
-          <t>OKVED_49_Velch</t>
+          <t>OKVED_41_Velch</t>
         </is>
       </c>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>OKVED_I_Velch</t>
+          <t>OKVED_42_Velch</t>
         </is>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
         <is>
-          <t>OKVED_56_Velch</t>
+          <t>OKVED_43_Velch</t>
         </is>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
         <is>
-          <t>OKVED_J_Velch</t>
+          <t>OKVED_47_Velch</t>
         </is>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
         <is>
-          <t>OKVED_63_Velch</t>
+          <t>OKVED_49_Velch</t>
         </is>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
         <is>
-          <t>OKVED_L_Velch</t>
+          <t>OKVED_I_Velch</t>
         </is>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>OKVED_68_Velch</t>
+          <t>OKVED_56_Velch</t>
         </is>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
         <is>
-          <t>OKVED_M_Velch</t>
+          <t>OKVED_J_Velch</t>
         </is>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>OKVED_69_Velch</t>
+          <t>OKVED_63_Velch</t>
         </is>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>OKVED_70_Velch</t>
+          <t>OKVED_L_Velch</t>
         </is>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>OKVED_71_Velch</t>
+          <t>OKVED_68_Velch</t>
         </is>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>OKVED_N_Velch</t>
+          <t>OKVED_M_Velch</t>
         </is>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>OKVED_77_Velch</t>
+          <t>OKVED_69_Velch</t>
         </is>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>OKVED_79_Velch</t>
+          <t>OKVED_70_Velch</t>
         </is>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>OKVED_81_Velch</t>
+          <t>OKVED_71_Velch</t>
         </is>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>OKVED_82_Velch</t>
+          <t>OKVED_N_Velch</t>
         </is>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>OKVED_O_Velch</t>
+          <t>OKVED_77_Velch</t>
         </is>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>OKVED_84_Velch</t>
+          <t>OKVED_79_Velch</t>
         </is>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_81_Velch</t>
         </is>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_82_Velch</t>
         </is>
       </c>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>OKVED_88_Velch</t>
+          <t>OKVED_O_Velch</t>
         </is>
       </c>
     </row>
     <row r="1696">
       <c r="A1696" t="inlineStr">
         <is>
-          <t>OKVED_R_Velch</t>
+          <t>OKVED_84_Velch</t>
         </is>
       </c>
     </row>
     <row r="1697">
       <c r="A1697" t="inlineStr">
         <is>
-          <t>OKVED_93_Velch</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1698">
       <c r="A1698" t="inlineStr">
         <is>
-          <t>OKVED_S_Velch</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1699">
       <c r="A1699" t="inlineStr">
         <is>
-          <t>OKVED_94_Velch</t>
+          <t>OKVED_88_Velch</t>
         </is>
       </c>
     </row>
     <row r="1700">
       <c r="A1700" t="inlineStr">
         <is>
-          <t>OKVED_96_Velch</t>
+          <t>OKVED_R_Velch</t>
         </is>
       </c>
     </row>
     <row r="1701">
       <c r="A1701" t="inlineStr">
         <is>
-          <t>OKVED_43_UstKap</t>
+          <t>OKVED_93_Velch</t>
         </is>
       </c>
     </row>
     <row r="1702">
       <c r="A1702" t="inlineStr">
         <is>
-          <t>OKVED_43_ChiAkt</t>
+          <t>OKVED_S_Velch</t>
         </is>
       </c>
     </row>
     <row r="1703">
       <c r="A1703" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap</t>
+          <t>OKVED_94_Velch</t>
         </is>
       </c>
     </row>
     <row r="1704">
       <c r="A1704" t="inlineStr">
         <is>
-          <t>OKVED_J_SebPro</t>
+          <t>OKVED_96_Velch</t>
         </is>
       </c>
     </row>
     <row r="1705">
       <c r="A1705" t="inlineStr">
         <is>
-          <t>OKVED_J_Pri(ubOtPro</t>
+          <t>OKVED_43_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1706">
       <c r="A1706" t="inlineStr">
         <is>
-          <t>OKVED_J_ChiPri(ubOtcPer</t>
+          <t>OKVED_43_ChiAkt</t>
         </is>
       </c>
     </row>
     <row r="1707">
       <c r="A1707" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_J_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1708">
       <c r="A1708" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap</t>
+          <t>OKVED_J_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1709">
       <c r="A1709" t="inlineStr">
         <is>
-          <t>OKVED_63_SebPro</t>
+          <t>OKVED_J_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1710">
       <c r="A1710" t="inlineStr">
         <is>
-          <t>OKVED_63_Pri(ubOtPro</t>
+          <t>OKVED_J_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1711">
       <c r="A1711" t="inlineStr">
         <is>
-          <t>OKVED_63_ChiPri(ubOtcPer</t>
+          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1712">
       <c r="A1712" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_63_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1713">
       <c r="A1713" t="inlineStr">
         <is>
-          <t>OKVED_K_SebPro</t>
+          <t>OKVED_63_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1714">
       <c r="A1714" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap</t>
+          <t>OKVED_63_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1715">
       <c r="A1715" t="inlineStr">
         <is>
-          <t>OKVED_69_ChiAkt</t>
+          <t>OKVED_63_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1716">
       <c r="A1716" t="inlineStr">
         <is>
-          <t>OKVED_69_SebPro</t>
+          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1717">
       <c r="A1717" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap</t>
+          <t>OKVED_K_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1718">
       <c r="A1718" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap</t>
+          <t>OKVED_69_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1719">
       <c r="A1719" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap</t>
+          <t>OKVED_69_ChiAkt</t>
         </is>
       </c>
     </row>
     <row r="1720">
       <c r="A1720" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap</t>
+          <t>OKVED_69_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1721">
       <c r="A1721" t="inlineStr">
         <is>
-          <t>OKVED_Q_SebPro</t>
+          <t>OKVED_O_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1722">
       <c r="A1722" t="inlineStr">
         <is>
-          <t>OKVED_Q_Pri(ubOtPro</t>
+          <t>OKVED_84_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1723">
       <c r="A1723" t="inlineStr">
         <is>
-          <t>OKVED_Q_ChiPri(ubOtcPer</t>
+          <t>OKVED_85_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1724">
       <c r="A1724" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_Q_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1725">
       <c r="A1725" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap</t>
+          <t>OKVED_Q_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1726">
       <c r="A1726" t="inlineStr">
         <is>
-          <t>OKVED_88_SebPro</t>
+          <t>OKVED_Q_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1727">
       <c r="A1727" t="inlineStr">
         <is>
-          <t>OKVED_88_Pri(ubOtPro</t>
+          <t>OKVED_Q_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1728">
       <c r="A1728" t="inlineStr">
         <is>
-          <t>OKVED_88_ChiPri(ubOtcPer</t>
+          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1729">
       <c r="A1729" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_88_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1730">
       <c r="A1730" t="inlineStr">
         <is>
-          <t>OKVED_R_SebPro</t>
+          <t>OKVED_88_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1731">
       <c r="A1731" t="inlineStr">
+        <is>
+          <t>OKVED_88_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>OKVED_88_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>OKVED_88_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>OKVED_R_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
         <is>
           <t>OKVED_93_SebPro</t>
         </is>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1735"/>
+  <dimension ref="A1:A1741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9701,2861 +9701,2903 @@
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10DebZad</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10V%KObsZad</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10DebZad</t>
         </is>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>OKVED_70_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>OKVED_R_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_70_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>OKVED_93_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_70_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>OKVED_94_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_R_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>OKVED_96_KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>OKVED_R_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>OKVED_96_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>OKVED_93_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
+          <t>OKVED_93_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsKol</t>
+          <t>OKVED_94_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20DebZad</t>
+          <t>OKVED_94_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZad</t>
+          <t>OKVED_96_KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KreZad</t>
+          <t>OKVED_96_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20DenSreIDenEkv</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeTekLikOt&gt;=20DebZad</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeTekLikOt&gt;=20V%KObsZad</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>OKVED_01_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KreZad</t>
         </is>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>OKVED_32_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>OKVED_E_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>OKVED_36_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>OKVED_38_ArendPlDeVsego</t>
+          <t>OKVED_69_KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>OKVED_41_ArendPlDeVsego</t>
+          <t>OKVED_69_KoeTekLikOt&gt;=20V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>OKVED_43_ArendPlDeVsego</t>
+          <t>OKVED_01_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>OKVED_49_ArendPlDeVsego</t>
+          <t>OKVED_32_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>OKVED_50_ArendPlDeVsego</t>
+          <t>OKVED_E_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>OKVED_I_ArendPlDeVsego</t>
+          <t>OKVED_36_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>OKVED_55_ArendPlDeVsego</t>
+          <t>OKVED_38_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>OKVED_56_ArendPlDeVsego</t>
+          <t>OKVED_41_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>OKVED_J_OtProdDeVsego</t>
+          <t>OKVED_43_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>OKVED_J_ArendPlDeVsego</t>
+          <t>OKVED_49_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>OKVED_63_OtProdDeVsego</t>
+          <t>OKVED_50_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>OKVED_63_ArendPlDeVsego</t>
+          <t>OKVED_I_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>OKVED_64_ArendPlDeVsego</t>
+          <t>OKVED_55_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>OKVED_69_ArendPlDeVsego</t>
+          <t>OKVED_56_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>OKVED_79_ArendPlDeVsego</t>
+          <t>OKVED_J_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>OKVED_81_ArendPlDeVsego</t>
+          <t>OKVED_J_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>OKVED_82_ArendPlDeVsego</t>
+          <t>OKVED_63_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>OKVED_O_ArendPlDeVsego</t>
+          <t>OKVED_63_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>OKVED_84_ArendPlDeVsego</t>
+          <t>OKVED_64_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_69_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_79_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>OKVED_88_OtProdDeVsego</t>
+          <t>OKVED_81_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>OKVED_88_ArendPlDeVsego</t>
+          <t>OKVED_82_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>OKVED_R_OtProdDeVsego</t>
+          <t>OKVED_O_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>OKVED_R_ArendPlDeVsego</t>
+          <t>OKVED_84_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>OKVED_93_OtProdDeVsego</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>OKVED_93_ArendPlDeVsego</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>OKVED_S_ArendPlDeVsego</t>
+          <t>OKVED_88_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>OKVED_94_ArendPlDeVsego</t>
+          <t>OKVED_88_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>OKVED_96_ArendPlDeVsego</t>
+          <t>OKVED_R_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcPoDolgObyaz</t>
+          <t>OKVED_R_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>OKVED_32_ProcPoDolgObyaz</t>
+          <t>OKVED_93_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>OKVED_32_NalogNaPri</t>
+          <t>OKVED_93_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>OKVED_33_NalogNaPri</t>
+          <t>OKVED_S_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcPoDolgObyaz</t>
+          <t>OKVED_94_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>OKVED_38_NalogNaPri</t>
+          <t>OKVED_96_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcPoDolgObyaz</t>
+          <t>OKVED_11_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>OKVED_56_ProcPoDolgObyaz</t>
+          <t>OKVED_32_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>OKVED_56_NalogNaPri</t>
+          <t>OKVED_32_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>OKVED_J_ProcPoDolgObyaz</t>
+          <t>OKVED_33_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>OKVED_J_NalogNaPri</t>
+          <t>OKVED_36_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>OKVED_63_ProcPoDolgObyaz</t>
+          <t>OKVED_38_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>OKVED_63_NalogNaPri</t>
+          <t>OKVED_49_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>OKVED_M_ProcPoDolgObyaz</t>
+          <t>OKVED_56_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>OKVED_69_ProcPoDolgObyaz</t>
+          <t>OKVED_56_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>OKVED_69_NalogNaPri</t>
+          <t>OKVED_J_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>OKVED_71_ProcPoDolgObyaz</t>
+          <t>OKVED_J_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>OKVED_71_NalogNaPri</t>
+          <t>OKVED_63_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>OKVED_74_ProcPoDolgObyaz</t>
+          <t>OKVED_63_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcPoDolgObyaz</t>
+          <t>OKVED_M_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>OKVED_79_NalogNaPri</t>
+          <t>OKVED_69_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>OKVED_81_NalogNaPri</t>
+          <t>OKVED_69_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_71_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>OKVED_O_VSvyaziSOplTrudRab</t>
+          <t>OKVED_71_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>OKVED_O_ProcPoDolgObyaz</t>
+          <t>OKVED_74_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_77_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>OKVED_84_VSvyaziSOplTrudRab</t>
+          <t>OKVED_79_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>OKVED_84_ProcPoDolgObyaz</t>
+          <t>OKVED_81_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_O_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_O_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>OKVED_Q_ProcPoDolgObyaz</t>
+          <t>OKVED_84_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>OKVED_Q_NalogNaPri</t>
+          <t>OKVED_84_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>OKVED_R_VSvyaziSOplTrudRab</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>OKVED_R_ProcPoDolgObyaz</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>OKVED_R_NalogNaPri</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_Q_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>OKVED_93_VSvyaziSOplTrudRab</t>
+          <t>OKVED_Q_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>OKVED_93_ProcPoDolgObyaz</t>
+          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>OKVED_93_NalogNaPri</t>
+          <t>OKVED_R_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>OKVED_96_ProcPoDolgObyaz</t>
+          <t>OKVED_R_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>OKVED_96_NalogNaPri</t>
+          <t>OKVED_R_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>OKVED_01_DivProcDolgFinVlozh</t>
+          <t>OKVED_93_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>OKVED_B_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>OKVED_07_OtProdAkcOrgDolUch</t>
+          <t>OKVED_96_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>OKVED_C_OtProdAkcOrgDolUch</t>
+          <t>OKVED_96_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>OKVED_10_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_01_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdFinVlozh</t>
+          <t>OKVED_B_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_07_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_C_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdAkcOrgDolUch</t>
+          <t>OKVED_10_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdFinVlozh</t>
+          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>OKVED_E_DivProcDolgFinVlozh</t>
+          <t>OKVED_11_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdAkcOrgDolUch</t>
+          <t>OKVED_11_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdFinVlozh</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>OKVED_36_DivProcDolgFinVlozh</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_E_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdAkcOrgDolUch</t>
+          <t>OKVED_E_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdFinVlozh</t>
+          <t>OKVED_E_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>OKVED_38_DivProcDolgFinVlozh</t>
+          <t>OKVED_36_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_36_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdAkcOrgDolUch</t>
+          <t>OKVED_36_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_38_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdFinVlozh</t>
+          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>OKVED_G_OtProdAkcOrgDolUch</t>
+          <t>OKVED_F_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>OKVED_46_OtProdAkcOrgDolUch</t>
+          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>OKVED_47_OtProdAkcOrgDolUch</t>
+          <t>OKVED_41_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>OKVED_H_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_43_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>OKVED_49_DivProcDolgFinVlozh</t>
+          <t>OKVED_G_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>OKVED_52_OtProdAkcOrgDolUch</t>
+          <t>OKVED_46_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_47_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdAkcOrgDolUch</t>
+          <t>OKVED_H_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdAkcOrgDolUch</t>
+          <t>OKVED_49_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_49_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdAkcOrgDolUch</t>
+          <t>OKVED_52_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdAkcOrgDolUch</t>
+          <t>OKVED_I_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>OKVED_L_OtProdAkcOrgDolUch</t>
+          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_55_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdAkcOrgDolUch</t>
+          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_K_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdAkcOrgDolUch</t>
+          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_64_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdAkcOrgDolUch</t>
+          <t>OKVED_L_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>OKVED_71_DivProcDolgFinVlozh</t>
+          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdAkcOrgDolUch</t>
+          <t>OKVED_M_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdFinVlozh</t>
+          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdAkcOrgDolUch</t>
+          <t>OKVED_70_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdFinVlozh</t>
+          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_71_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdAkcOrgDolUch</t>
+          <t>OKVED_71_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>OKVED_S_DivProcDolgFinVlozh</t>
+          <t>OKVED_N_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_N_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdAkcOrgDolUch</t>
+          <t>OKVED_77_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>OKVED_94_DivProcDolgFinVlozh</t>
+          <t>OKVED_77_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>OKVED_01_DolUch</t>
+          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_S_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>OKVED_B_DolUch</t>
+          <t>OKVED_S_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>OKVED_C_DolUch</t>
+          <t>OKVED_94_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_94_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>OKVED_10_DolUch</t>
+          <t>OKVED_01_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_01_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>OKVED_11_DolUch</t>
+          <t>OKVED_B_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>OKVED_11_PrCenBum</t>
+          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_C_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>OKVED_33_DolUch</t>
+          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_10_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>OKVED_E_DolUch</t>
+          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>OKVED_E_PrCenBum</t>
+          <t>OKVED_11_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_11_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>OKVED_36_DolUch</t>
+          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>OKVED_36_PrCenBum</t>
+          <t>OKVED_33_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>OKVED_F_DolUch</t>
+          <t>OKVED_E_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_E_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>OKVED_41_DolUch</t>
+          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_36_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>OKVED_42_DolUch</t>
+          <t>OKVED_36_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>OKVED_43_DolUch</t>
+          <t>OKVED_F_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>OKVED_43_PrCenBum</t>
+          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_41_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>OKVED_47_DolUch</t>
+          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>OKVED_H_DolUch</t>
+          <t>OKVED_42_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>OKVED_49_DolUch</t>
+          <t>OKVED_43_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_43_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>OKVED_50_DolUch</t>
+          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>OKVED_50_PrCenBum</t>
+          <t>OKVED_47_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_H_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>OKVED_52_DolUch</t>
+          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_49_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_50_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>OKVED_K_DolUch</t>
+          <t>OKVED_50_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>OKVED_M_DolUch</t>
+          <t>OKVED_52_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>OKVED_71_DolUch</t>
+          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>OKVED_N_DolUch</t>
+          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>OKVED_N_PrCenBum</t>
+          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>OKVED_79_DolUch</t>
+          <t>OKVED_K_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>OKVED_79_PrCenBum</t>
+          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>OKVED_S_Modern</t>
+          <t>OKVED_M_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>OKVED_S_DolUch</t>
+          <t>OKVED_71_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_N_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>OKVED_94_Modern</t>
+          <t>OKVED_N_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>OKVED_94_DolUch</t>
+          <t>OKVED_79_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_79_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>OKVED_01_PostDeyt1</t>
+          <t>OKVED_S_Modern</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>OKVED_01_DrPost</t>
+          <t>OKVED_S_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt</t>
+          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt1</t>
+          <t>OKVED_94_Modern</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt</t>
+          <t>OKVED_94_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt1</t>
+          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>OKVED_C_PostDeyt1</t>
+          <t>OKVED_01_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>OKVED_10_PostDeyt1</t>
+          <t>OKVED_01_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>OKVED_32_PlCredit</t>
+          <t>OKVED_B_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt</t>
+          <t>OKVED_B_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt1</t>
+          <t>OKVED_07_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt</t>
+          <t>OKVED_07_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt1</t>
+          <t>OKVED_C_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>OKVED_33_DrPost</t>
+          <t>OKVED_10_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_32_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_32_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>OKVED_38_PostDeyt1</t>
+          <t>OKVED_32_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>OKVED_38_DrPost</t>
+          <t>OKVED_33_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>OKVED_F_PostDeyt1</t>
+          <t>OKVED_33_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt</t>
+          <t>OKVED_33_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt1</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt1</t>
+          <t>OKVED_38_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>OKVED_42_DrPost</t>
+          <t>OKVED_38_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>OKVED_43_PostDeyt1</t>
+          <t>OKVED_F_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>OKVED_43_DrPost</t>
+          <t>OKVED_41_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt</t>
+          <t>OKVED_41_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt1</t>
+          <t>OKVED_42_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt</t>
+          <t>OKVED_42_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt1</t>
+          <t>OKVED_42_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt</t>
+          <t>OKVED_43_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt1</t>
+          <t>OKVED_43_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>OKVED_H_PostDeyt1</t>
+          <t>OKVED_G_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt</t>
+          <t>OKVED_G_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt1</t>
+          <t>OKVED_46_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>OKVED_50_DrPost</t>
+          <t>OKVED_46_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt</t>
+          <t>OKVED_47_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt1</t>
+          <t>OKVED_47_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>OKVED_51_DrPost</t>
+          <t>OKVED_H_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>OKVED_52_PostDeyt1</t>
+          <t>OKVED_50_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>OKVED_I_PostDeyt1</t>
+          <t>OKVED_50_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>OKVED_I_DrPost</t>
+          <t>OKVED_50_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>OKVED_55_PostDeyt1</t>
+          <t>OKVED_51_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>OKVED_55_DrPost</t>
+          <t>OKVED_51_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt</t>
+          <t>OKVED_51_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt1</t>
+          <t>OKVED_52_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>OKVED_K_DrPost</t>
+          <t>OKVED_I_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt</t>
+          <t>OKVED_I_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt1</t>
+          <t>OKVED_55_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>OKVED_64_DrPost</t>
+          <t>OKVED_55_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>OKVED_L_PostDeyt1</t>
+          <t>OKVED_K_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>OKVED_68_PostDeyt1</t>
+          <t>OKVED_K_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>OKVED_70_PlCredit</t>
+          <t>OKVED_K_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>OKVED_70_PostDeyt</t>
+          <t>OKVED_64_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>OKVED_71_PostDeyt</t>
+          <t>OKVED_64_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt</t>
+          <t>OKVED_64_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt1</t>
+          <t>OKVED_L_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>OKVED_74_DrPost</t>
+          <t>OKVED_68_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt</t>
+          <t>OKVED_70_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt1</t>
+          <t>OKVED_70_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt</t>
+          <t>OKVED_71_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt1</t>
+          <t>OKVED_74_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>OKVED_79_DrPost</t>
+          <t>OKVED_74_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>OKVED_81_PlCredit</t>
+          <t>OKVED_74_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt</t>
+          <t>OKVED_N_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt1</t>
+          <t>OKVED_N_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>OKVED_S_PlCredit</t>
+          <t>OKVED_79_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>OKVED_S_PostDeyt1</t>
+          <t>OKVED_79_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>OKVED_94_PlCredit</t>
+          <t>OKVED_79_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>OKVED_94_PostDeyt1</t>
+          <t>OKVED_81_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin1</t>
+          <t>OKVED_81_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin2</t>
+          <t>OKVED_81_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>OKVED_B_PlPoFin1</t>
+          <t>OKVED_S_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>OKVED_07_PlPoFin1</t>
+          <t>OKVED_S_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin</t>
+          <t>OKVED_94_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin1</t>
+          <t>OKVED_94_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin2</t>
+          <t>OKVED_01_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin3</t>
+          <t>OKVED_01_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_B_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_07_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>OKVED_F_PlPoFin1</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>OKVED_41_PlPoFin1</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin1</t>
+          <t>OKVED_E_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin2</t>
+          <t>OKVED_E_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>OKVED_G_PlPoFin1</t>
+          <t>OKVED_38_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>OKVED_46_PlPoFin1</t>
+          <t>OKVED_38_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>OKVED_47_PlPoFin1</t>
+          <t>OKVED_F_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>OKVED_H_PlPoFin1</t>
+          <t>OKVED_41_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin1</t>
+          <t>OKVED_43_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin2</t>
+          <t>OKVED_43_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoFin1</t>
+          <t>OKVED_G_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>OKVED_52_PlPoFin1</t>
+          <t>OKVED_46_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin1</t>
+          <t>OKVED_47_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin2</t>
+          <t>OKVED_H_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin1</t>
+          <t>OKVED_49_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin2</t>
+          <t>OKVED_49_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoFin1</t>
+          <t>OKVED_50_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoFin1</t>
+          <t>OKVED_52_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>OKVED_68_PlPoFin1</t>
+          <t>OKVED_I_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
         <is>
-          <t>OKVED_M_PlPoFin1</t>
+          <t>OKVED_I_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin</t>
+          <t>OKVED_55_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin1</t>
+          <t>OKVED_55_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin2</t>
+          <t>OKVED_K_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin3</t>
+          <t>OKVED_64_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
         <is>
-          <t>OKVED_71_PlPoFin1</t>
+          <t>OKVED_68_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin1</t>
+          <t>OKVED_M_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin2</t>
+          <t>OKVED_70_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin3</t>
+          <t>OKVED_70_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
         <is>
-          <t>OKVED_74_SaldoDenPot</t>
+          <t>OKVED_70_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin1</t>
+          <t>OKVED_70_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin2</t>
+          <t>OKVED_71_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin1</t>
+          <t>OKVED_74_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin2</t>
+          <t>OKVED_74_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin3</t>
+          <t>OKVED_74_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
         <is>
-          <t>OKVED_81_SaldoDenPot</t>
+          <t>OKVED_74_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin1</t>
+          <t>OKVED_79_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin2</t>
+          <t>OKVED_79_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin3</t>
+          <t>OKVED_81_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin1</t>
+          <t>OKVED_81_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin2</t>
+          <t>OKVED_81_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin3</t>
+          <t>OKVED_81_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
         <is>
-          <t>OKVED_01_Velch</t>
+          <t>OKVED_S_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
         <is>
-          <t>OKVED_11_Velch</t>
+          <t>OKVED_S_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>OKVED_32_Velch</t>
+          <t>OKVED_S_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>OKVED_33_Velch</t>
+          <t>OKVED_94_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>OKVED_E_Velch</t>
+          <t>OKVED_94_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>OKVED_38_Velch</t>
+          <t>OKVED_94_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
         <is>
-          <t>OKVED_F_Velch</t>
+          <t>OKVED_01_Velch</t>
         </is>
       </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
         <is>
-          <t>OKVED_41_Velch</t>
+          <t>OKVED_11_Velch</t>
         </is>
       </c>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>OKVED_42_Velch</t>
+          <t>OKVED_32_Velch</t>
         </is>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
         <is>
-          <t>OKVED_43_Velch</t>
+          <t>OKVED_33_Velch</t>
         </is>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
         <is>
-          <t>OKVED_47_Velch</t>
+          <t>OKVED_E_Velch</t>
         </is>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
         <is>
-          <t>OKVED_49_Velch</t>
+          <t>OKVED_38_Velch</t>
         </is>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
         <is>
-          <t>OKVED_I_Velch</t>
+          <t>OKVED_F_Velch</t>
         </is>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>OKVED_56_Velch</t>
+          <t>OKVED_41_Velch</t>
         </is>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
         <is>
-          <t>OKVED_J_Velch</t>
+          <t>OKVED_42_Velch</t>
         </is>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>OKVED_63_Velch</t>
+          <t>OKVED_43_Velch</t>
         </is>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>OKVED_L_Velch</t>
+          <t>OKVED_47_Velch</t>
         </is>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>OKVED_68_Velch</t>
+          <t>OKVED_49_Velch</t>
         </is>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>OKVED_M_Velch</t>
+          <t>OKVED_I_Velch</t>
         </is>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>OKVED_69_Velch</t>
+          <t>OKVED_56_Velch</t>
         </is>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>OKVED_70_Velch</t>
+          <t>OKVED_J_Velch</t>
         </is>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>OKVED_71_Velch</t>
+          <t>OKVED_63_Velch</t>
         </is>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>OKVED_N_Velch</t>
+          <t>OKVED_L_Velch</t>
         </is>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>OKVED_77_Velch</t>
+          <t>OKVED_68_Velch</t>
         </is>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>OKVED_79_Velch</t>
+          <t>OKVED_M_Velch</t>
         </is>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
-          <t>OKVED_81_Velch</t>
+          <t>OKVED_69_Velch</t>
         </is>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>OKVED_82_Velch</t>
+          <t>OKVED_70_Velch</t>
         </is>
       </c>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>OKVED_O_Velch</t>
+          <t>OKVED_71_Velch</t>
         </is>
       </c>
     </row>
     <row r="1696">
       <c r="A1696" t="inlineStr">
         <is>
-          <t>OKVED_84_Velch</t>
+          <t>OKVED_N_Velch</t>
         </is>
       </c>
     </row>
     <row r="1697">
       <c r="A1697" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_77_Velch</t>
         </is>
       </c>
     </row>
     <row r="1698">
       <c r="A1698" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_79_Velch</t>
         </is>
       </c>
     </row>
     <row r="1699">
       <c r="A1699" t="inlineStr">
         <is>
-          <t>OKVED_88_Velch</t>
+          <t>OKVED_81_Velch</t>
         </is>
       </c>
     </row>
     <row r="1700">
       <c r="A1700" t="inlineStr">
         <is>
-          <t>OKVED_R_Velch</t>
+          <t>OKVED_82_Velch</t>
         </is>
       </c>
     </row>
     <row r="1701">
       <c r="A1701" t="inlineStr">
         <is>
-          <t>OKVED_93_Velch</t>
+          <t>OKVED_O_Velch</t>
         </is>
       </c>
     </row>
     <row r="1702">
       <c r="A1702" t="inlineStr">
         <is>
-          <t>OKVED_S_Velch</t>
+          <t>OKVED_84_Velch</t>
         </is>
       </c>
     </row>
     <row r="1703">
       <c r="A1703" t="inlineStr">
         <is>
-          <t>OKVED_94_Velch</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1704">
       <c r="A1704" t="inlineStr">
         <is>
-          <t>OKVED_96_Velch</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1705">
       <c r="A1705" t="inlineStr">
         <is>
-          <t>OKVED_43_UstKap</t>
+          <t>OKVED_88_Velch</t>
         </is>
       </c>
     </row>
     <row r="1706">
       <c r="A1706" t="inlineStr">
         <is>
-          <t>OKVED_43_ChiAkt</t>
+          <t>OKVED_R_Velch</t>
         </is>
       </c>
     </row>
     <row r="1707">
       <c r="A1707" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap</t>
+          <t>OKVED_93_Velch</t>
         </is>
       </c>
     </row>
     <row r="1708">
       <c r="A1708" t="inlineStr">
         <is>
-          <t>OKVED_J_SebPro</t>
+          <t>OKVED_S_Velch</t>
         </is>
       </c>
     </row>
     <row r="1709">
       <c r="A1709" t="inlineStr">
         <is>
-          <t>OKVED_J_Pri(ubOtPro</t>
+          <t>OKVED_94_Velch</t>
         </is>
       </c>
     </row>
     <row r="1710">
       <c r="A1710" t="inlineStr">
         <is>
-          <t>OKVED_J_ChiPri(ubOtcPer</t>
+          <t>OKVED_96_Velch</t>
         </is>
       </c>
     </row>
     <row r="1711">
       <c r="A1711" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_43_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1712">
       <c r="A1712" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap</t>
+          <t>OKVED_43_ChiAkt</t>
         </is>
       </c>
     </row>
     <row r="1713">
       <c r="A1713" t="inlineStr">
         <is>
-          <t>OKVED_63_SebPro</t>
+          <t>OKVED_J_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1714">
       <c r="A1714" t="inlineStr">
         <is>
-          <t>OKVED_63_Pri(ubOtPro</t>
+          <t>OKVED_J_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1715">
       <c r="A1715" t="inlineStr">
         <is>
-          <t>OKVED_63_ChiPri(ubOtcPer</t>
+          <t>OKVED_J_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1716">
       <c r="A1716" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_J_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1717">
       <c r="A1717" t="inlineStr">
         <is>
-          <t>OKVED_K_SebPro</t>
+          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1718">
       <c r="A1718" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap</t>
+          <t>OKVED_63_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1719">
       <c r="A1719" t="inlineStr">
         <is>
-          <t>OKVED_69_ChiAkt</t>
+          <t>OKVED_63_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1720">
       <c r="A1720" t="inlineStr">
         <is>
-          <t>OKVED_69_SebPro</t>
+          <t>OKVED_63_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1721">
       <c r="A1721" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap</t>
+          <t>OKVED_63_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1722">
       <c r="A1722" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap</t>
+          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1723">
       <c r="A1723" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap</t>
+          <t>OKVED_K_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1724">
       <c r="A1724" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap</t>
+          <t>OKVED_69_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1725">
       <c r="A1725" t="inlineStr">
         <is>
-          <t>OKVED_Q_SebPro</t>
+          <t>OKVED_69_ChiAkt</t>
         </is>
       </c>
     </row>
     <row r="1726">
       <c r="A1726" t="inlineStr">
         <is>
-          <t>OKVED_Q_Pri(ubOtPro</t>
+          <t>OKVED_69_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1727">
       <c r="A1727" t="inlineStr">
         <is>
-          <t>OKVED_Q_ChiPri(ubOtcPer</t>
+          <t>OKVED_O_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1728">
       <c r="A1728" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_84_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1729">
       <c r="A1729" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap</t>
+          <t>OKVED_85_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1730">
       <c r="A1730" t="inlineStr">
         <is>
-          <t>OKVED_88_SebPro</t>
+          <t>OKVED_Q_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1731">
       <c r="A1731" t="inlineStr">
         <is>
-          <t>OKVED_88_Pri(ubOtPro</t>
+          <t>OKVED_Q_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1732">
       <c r="A1732" t="inlineStr">
         <is>
-          <t>OKVED_88_ChiPri(ubOtcPer</t>
+          <t>OKVED_Q_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1733">
       <c r="A1733" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_Q_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1734">
       <c r="A1734" t="inlineStr">
         <is>
-          <t>OKVED_R_SebPro</t>
+          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1735">
       <c r="A1735" t="inlineStr">
+        <is>
+          <t>OKVED_88_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>OKVED_88_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>OKVED_88_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>OKVED_88_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>OKVED_88_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>OKVED_R_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
         <is>
           <t>OKVED_93_SebPro</t>
         </is>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1741"/>
+  <dimension ref="A1:A1779"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9239,3365 +9239,3631 @@
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>OKVED_56_VToChiKomIUprRas</t>
+          <t>OPF_20200_OrgPolUbyKolOrgEdi_2</t>
         </is>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-OtPro</t>
+          <t>OPF_20200_OrgPolUbyV%KObsKol_2</t>
         </is>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>OKVED_J_SebProSUchKomIUprRas</t>
+          <t>OPF_20200_OrgPolUbyUby_2</t>
         </is>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>OKVED_J_VToChiKomIUprRas</t>
+          <t>OPF_20600_OrgPolUbyKolOrgEdi_2</t>
         </is>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>OPF_20600_OrgPolUbyV%KObsKol_2</t>
         </is>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%KKomIUprRas</t>
+          <t>OPF_20600_OrgPolUbyUby_2</t>
         </is>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%KVyr</t>
+          <t>OPF_71400_OrgPolUbyKolOrgEdi_2</t>
         </is>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>OPF_71400_OrgPolUbyV%KObsKol_2</t>
         </is>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-OtPro</t>
+          <t>OPF_71400_OrgPolUbyUby_2</t>
         </is>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>OKVED_63_SebProSUchKomIUprRas</t>
+          <t>OPF_75500_OrgPolUbyKolOrgEdi_2</t>
         </is>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>OKVED_63_VToChiKomIUprRas</t>
+          <t>OPF_75500_OrgPolUbyV%KObsKol_2</t>
         </is>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>OPF_75500_OrgPolUbyUby_2</t>
         </is>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%KKomIUprRas</t>
+          <t>OPF_14000_TeRosPriV%_2</t>
         </is>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%KVyr</t>
+          <t>OPF_14100_TeRosPriV%_2</t>
         </is>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>OPF_20200_TeRosUbyV%_2</t>
         </is>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>OKVED_74_VToChiKomIUprRas</t>
+          <t>OPF_21200_TeRosPriV%_2</t>
         </is>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>OKVED_81_VToChiKomIUprRas</t>
+          <t>OPF_70000_SumUbyZaSooPerPreGo_2</t>
         </is>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>OKVED_82_VToChiKomIUprRas</t>
+          <t>OPF_70000_KolOrgPolUbyZaPreGo(ed_2</t>
         </is>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>OKVED_O_VToChiKomIUprRas</t>
+          <t>OPF_70400_SumUbyZaSooPerPreGo_2</t>
         </is>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>OKVED_84_VToChiKomIUprRas</t>
+          <t>OPF_70400_KolOrgPolUbyZaPreGo(ed_2</t>
         </is>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>OKVED_85_VToChiKomIUprRas</t>
+          <t>OPF_71400_SumUbyZaSooPerPreGo_2</t>
         </is>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-OtPro</t>
+          <t>OPF_71400_KolOrgPolUbyZaPreGo(ed_2</t>
         </is>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>OKVED_Q_SebProSUchKomIUprRas</t>
+          <t>OPF_71400_TeRosUbyV%_2</t>
         </is>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>OKVED_Q_VToChiKomIUprRas</t>
+          <t>OPF_75500_SumUbyZaSooPerPreGo_2</t>
         </is>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>OPF_75500_KolOrgPolUbyZaPreGo(ed_2</t>
         </is>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%KKomIUprRas</t>
+          <t>OPF_75500_TeRosUbyV%_2</t>
         </is>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%KVyr</t>
+          <t>FS_12_OrgPolPriKolOrgEdi_3</t>
         </is>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>FS_12_OrgPolPriV%KObsKol_3</t>
         </is>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-OtPro</t>
+          <t>FS_12_OrgPolPriPriDoNal_3</t>
         </is>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>OKVED_88_SebProSUchKomIUprRas</t>
+          <t>FS_15_OrgPolUbyKolOrgEdi_3</t>
         </is>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>OKVED_88_VToChiKomIUprRas</t>
+          <t>FS_15_OrgPolUbyV%KObsKol_3</t>
         </is>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>FS_15_OrgPolUbyUby_3</t>
         </is>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%KKomIUprRas</t>
+          <t>FS_12_TeRosPriV%_3</t>
         </is>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%KVyr</t>
+          <t>FS_12_SumPriZaSooPerPreGo_3</t>
         </is>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>FS_12_TeRosSumPriV%_3</t>
         </is>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>OKVED_R_SebProSUchKomIUprRas</t>
+          <t>FS_15_TeRosUbyV%_3</t>
         </is>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>OKVED_R_VToChiKomIUprRas</t>
+          <t>FS_17_SumUbyZaSooPerPreGo_3</t>
         </is>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>OKVED_93_SebProSUchKomIUprRas</t>
+          <t>FS_17_KolOrgPolUbyZaPreGo(ed_3</t>
         </is>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>OKVED_93_VToChiKomIUprRas</t>
+          <t>OKVED_56_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>OKVED_56_OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OKVED_J_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>OKVED_O_OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OKVED_J_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>OKVED_84_OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OKVED_J_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>OKVED_11_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_J_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>OKVED_43_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_J_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>OKVED_49_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_J_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>OKVED_56_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_J_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>OKVED_56_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_63_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>OKVED_69_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_63_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>OKVED_69_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_63_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>OKVED_74_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_63_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>OKVED_81_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_63_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>OKVED_81_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_63_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>OKVED_82_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_63_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>OKVED_82_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_74_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>OKVED_O_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_81_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>OKVED_O_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_82_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_O_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_84_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_85_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_Q_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>OKVED_R_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_Q_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>OKVED_R_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_Q_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>OKVED_93_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_Q_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>OKVED_93_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_Q_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>OKVED_94_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_Q_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>OKVED_96_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_Q_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_88_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_88_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>OKVED_88_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>OKVED_88_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10DebZad</t>
+          <t>OKVED_88_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_88_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_88_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>OKVED_70_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_R_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>OKVED_70_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_R_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>OKVED_R_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_93_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>OKVED_R_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_93_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>OKVED_93_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_56_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>OKVED_93_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_O_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>OKVED_94_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_84_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>OKVED_94_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_11_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>OKVED_96_KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>OKVED_43_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>OKVED_96_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>OKVED_49_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
+          <t>OKVED_56_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsKol</t>
+          <t>OKVED_56_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20DebZad</t>
+          <t>OKVED_69_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZad</t>
+          <t>OKVED_69_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KreZad</t>
+          <t>OKVED_74_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZadKre</t>
+          <t>OKVED_81_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20DenSreIDenEkv</t>
+          <t>OKVED_81_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
+          <t>OKVED_82_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeTekLikOt&gt;=20DebZad</t>
+          <t>OKVED_82_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeTekLikOt&gt;=20V%KObsZad</t>
+          <t>OKVED_O_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>OKVED_01_ArendPlDeVsego</t>
+          <t>OKVED_O_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>OKVED_32_ArendPlDeVsego</t>
+          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>OKVED_E_ArendPlDeVsego</t>
+          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>OKVED_36_ArendPlDeVsego</t>
+          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>OKVED_38_ArendPlDeVsego</t>
+          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>OKVED_41_ArendPlDeVsego</t>
+          <t>OKVED_R_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>OKVED_43_ArendPlDeVsego</t>
+          <t>OKVED_R_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>OKVED_49_ArendPlDeVsego</t>
+          <t>OKVED_93_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>OKVED_50_ArendPlDeVsego</t>
+          <t>OKVED_93_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>OKVED_I_ArendPlDeVsego</t>
+          <t>OKVED_94_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>OKVED_55_ArendPlDeVsego</t>
+          <t>OKVED_96_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>OKVED_56_ArendPlDeVsego</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>OKVED_J_OtProdDeVsego</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>OKVED_J_ArendPlDeVsego</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>OKVED_63_OtProdDeVsego</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>OKVED_63_ArendPlDeVsego</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10DebZad</t>
         </is>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>OKVED_64_ArendPlDeVsego</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>OKVED_69_ArendPlDeVsego</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>OKVED_79_ArendPlDeVsego</t>
+          <t>OKVED_70_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>OKVED_81_ArendPlDeVsego</t>
+          <t>OKVED_70_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>OKVED_82_ArendPlDeVsego</t>
+          <t>OKVED_R_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>OKVED_O_ArendPlDeVsego</t>
+          <t>OKVED_R_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>OKVED_84_ArendPlDeVsego</t>
+          <t>OKVED_93_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_93_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_94_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>OKVED_88_OtProdDeVsego</t>
+          <t>OKVED_94_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>OKVED_88_ArendPlDeVsego</t>
+          <t>OKVED_96_KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>OKVED_R_OtProdDeVsego</t>
+          <t>OKVED_96_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>OKVED_R_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>OKVED_93_OtProdDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>OKVED_93_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>OKVED_S_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>OKVED_94_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KreZad</t>
         </is>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>OKVED_96_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcPoDolgObyaz</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>OKVED_32_ProcPoDolgObyaz</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>OKVED_32_NalogNaPri</t>
+          <t>OKVED_69_KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>OKVED_33_NalogNaPri</t>
+          <t>OKVED_69_KoeTekLikOt&gt;=20V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcPoDolgObyaz</t>
+          <t>OKVED_01_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>OKVED_38_NalogNaPri</t>
+          <t>OKVED_32_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcPoDolgObyaz</t>
+          <t>OKVED_E_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>OKVED_56_ProcPoDolgObyaz</t>
+          <t>OKVED_36_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>OKVED_56_NalogNaPri</t>
+          <t>OKVED_38_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>OKVED_J_ProcPoDolgObyaz</t>
+          <t>OKVED_41_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>OKVED_J_NalogNaPri</t>
+          <t>OKVED_43_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>OKVED_63_ProcPoDolgObyaz</t>
+          <t>OKVED_49_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>OKVED_63_NalogNaPri</t>
+          <t>OKVED_50_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>OKVED_M_ProcPoDolgObyaz</t>
+          <t>OKVED_I_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>OKVED_69_ProcPoDolgObyaz</t>
+          <t>OKVED_55_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>OKVED_69_NalogNaPri</t>
+          <t>OKVED_56_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>OKVED_71_ProcPoDolgObyaz</t>
+          <t>OKVED_J_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>OKVED_71_NalogNaPri</t>
+          <t>OKVED_J_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>OKVED_74_ProcPoDolgObyaz</t>
+          <t>OKVED_63_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcPoDolgObyaz</t>
+          <t>OKVED_63_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>OKVED_79_NalogNaPri</t>
+          <t>OKVED_64_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>OKVED_81_NalogNaPri</t>
+          <t>OKVED_69_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_79_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>OKVED_O_VSvyaziSOplTrudRab</t>
+          <t>OKVED_81_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>OKVED_O_ProcPoDolgObyaz</t>
+          <t>OKVED_82_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_O_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>OKVED_84_VSvyaziSOplTrudRab</t>
+          <t>OKVED_84_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>OKVED_84_ProcPoDolgObyaz</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_88_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_88_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_R_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>OKVED_Q_ProcPoDolgObyaz</t>
+          <t>OKVED_R_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>OKVED_Q_NalogNaPri</t>
+          <t>OKVED_93_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_93_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>OKVED_R_VSvyaziSOplTrudRab</t>
+          <t>OKVED_S_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>OKVED_R_ProcPoDolgObyaz</t>
+          <t>OKVED_94_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>OKVED_R_NalogNaPri</t>
+          <t>OKVED_96_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_11_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>OKVED_93_VSvyaziSOplTrudRab</t>
+          <t>OKVED_32_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>OKVED_93_ProcPoDolgObyaz</t>
+          <t>OKVED_32_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>OKVED_93_NalogNaPri</t>
+          <t>OKVED_33_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>OKVED_96_ProcPoDolgObyaz</t>
+          <t>OKVED_36_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>OKVED_96_NalogNaPri</t>
+          <t>OKVED_38_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_49_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdAkcOrgDolUch</t>
+          <t>OKVED_56_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>OKVED_01_DivProcDolgFinVlozh</t>
+          <t>OKVED_56_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>OKVED_B_OtProdAkcOrgDolUch</t>
+          <t>OKVED_J_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>OKVED_07_OtProdAkcOrgDolUch</t>
+          <t>OKVED_J_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>OKVED_C_OtProdAkcOrgDolUch</t>
+          <t>OKVED_63_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>OKVED_10_OtProdAkcOrgDolUch</t>
+          <t>OKVED_63_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_M_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdAkcOrgDolUch</t>
+          <t>OKVED_69_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdFinVlozh</t>
+          <t>OKVED_69_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_71_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_71_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdAkcOrgDolUch</t>
+          <t>OKVED_74_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdFinVlozh</t>
+          <t>OKVED_77_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>OKVED_E_DivProcDolgFinVlozh</t>
+          <t>OKVED_79_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdAkcOrgDolUch</t>
+          <t>OKVED_81_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdFinVlozh</t>
+          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>OKVED_36_DivProcDolgFinVlozh</t>
+          <t>OKVED_O_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_O_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdAkcOrgDolUch</t>
+          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdFinVlozh</t>
+          <t>OKVED_84_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>OKVED_38_DivProcDolgFinVlozh</t>
+          <t>OKVED_84_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdAkcOrgDolUch</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdAkcOrgDolUch</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_Q_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdAkcOrgDolUch</t>
+          <t>OKVED_Q_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdFinVlozh</t>
+          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>OKVED_G_OtProdAkcOrgDolUch</t>
+          <t>OKVED_R_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>OKVED_46_OtProdAkcOrgDolUch</t>
+          <t>OKVED_R_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>OKVED_47_OtProdAkcOrgDolUch</t>
+          <t>OKVED_R_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>OKVED_H_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_93_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>OKVED_49_DivProcDolgFinVlozh</t>
+          <t>OKVED_93_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>OKVED_52_OtProdAkcOrgDolUch</t>
+          <t>OKVED_96_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_96_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_01_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_B_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdAkcOrgDolUch</t>
+          <t>OKVED_07_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_C_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdAkcOrgDolUch</t>
+          <t>OKVED_10_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>OKVED_L_OtProdAkcOrgDolUch</t>
+          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_11_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdAkcOrgDolUch</t>
+          <t>OKVED_11_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdAkcOrgDolUch</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_E_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdAkcOrgDolUch</t>
+          <t>OKVED_E_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>OKVED_71_DivProcDolgFinVlozh</t>
+          <t>OKVED_E_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdAkcOrgDolUch</t>
+          <t>OKVED_36_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdFinVlozh</t>
+          <t>OKVED_36_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdAkcOrgDolUch</t>
+          <t>OKVED_36_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdFinVlozh</t>
+          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_38_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>OKVED_S_DivProcDolgFinVlozh</t>
+          <t>OKVED_38_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdAkcOrgDolUch</t>
+          <t>OKVED_F_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>OKVED_94_DivProcDolgFinVlozh</t>
+          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>OKVED_01_DolUch</t>
+          <t>OKVED_41_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>OKVED_B_DolUch</t>
+          <t>OKVED_43_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_43_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>OKVED_C_DolUch</t>
+          <t>OKVED_G_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_46_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>OKVED_10_DolUch</t>
+          <t>OKVED_47_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_H_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>OKVED_11_DolUch</t>
+          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>OKVED_11_PrCenBum</t>
+          <t>OKVED_49_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_49_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>OKVED_33_DolUch</t>
+          <t>OKVED_52_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>OKVED_E_DolUch</t>
+          <t>OKVED_I_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>OKVED_E_PrCenBum</t>
+          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_55_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>OKVED_36_DolUch</t>
+          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>OKVED_36_PrCenBum</t>
+          <t>OKVED_K_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>OKVED_F_DolUch</t>
+          <t>OKVED_64_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_L_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>OKVED_41_DolUch</t>
+          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_M_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>OKVED_42_DolUch</t>
+          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_70_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>OKVED_43_DolUch</t>
+          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>OKVED_43_PrCenBum</t>
+          <t>OKVED_71_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_71_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>OKVED_47_DolUch</t>
+          <t>OKVED_N_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>OKVED_H_DolUch</t>
+          <t>OKVED_N_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_77_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>OKVED_49_DolUch</t>
+          <t>OKVED_77_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>OKVED_50_DolUch</t>
+          <t>OKVED_S_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>OKVED_50_PrCenBum</t>
+          <t>OKVED_S_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>OKVED_52_DolUch</t>
+          <t>OKVED_94_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_94_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_01_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_01_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>OKVED_K_DolUch</t>
+          <t>OKVED_B_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>OKVED_M_DolUch</t>
+          <t>OKVED_C_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>OKVED_71_DolUch</t>
+          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>OKVED_N_DolUch</t>
+          <t>OKVED_10_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>OKVED_N_PrCenBum</t>
+          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>OKVED_79_DolUch</t>
+          <t>OKVED_11_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>OKVED_79_PrCenBum</t>
+          <t>OKVED_11_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>OKVED_S_Modern</t>
+          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>OKVED_S_DolUch</t>
+          <t>OKVED_33_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>OKVED_94_Modern</t>
+          <t>OKVED_E_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>OKVED_94_DolUch</t>
+          <t>OKVED_E_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>OKVED_01_PostDeyt1</t>
+          <t>OKVED_36_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>OKVED_01_DrPost</t>
+          <t>OKVED_36_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt</t>
+          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt1</t>
+          <t>OKVED_F_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt</t>
+          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt1</t>
+          <t>OKVED_41_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>OKVED_C_PostDeyt1</t>
+          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>OKVED_10_PostDeyt1</t>
+          <t>OKVED_42_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>OKVED_32_PlCredit</t>
+          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt</t>
+          <t>OKVED_43_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt1</t>
+          <t>OKVED_43_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt</t>
+          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt1</t>
+          <t>OKVED_47_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>OKVED_33_DrPost</t>
+          <t>OKVED_H_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_49_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>OKVED_38_PostDeyt1</t>
+          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>OKVED_38_DrPost</t>
+          <t>OKVED_50_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>OKVED_F_PostDeyt1</t>
+          <t>OKVED_50_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt</t>
+          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt1</t>
+          <t>OKVED_52_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt</t>
+          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt1</t>
+          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>OKVED_42_DrPost</t>
+          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>OKVED_43_PostDeyt1</t>
+          <t>OKVED_K_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>OKVED_43_DrPost</t>
+          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt</t>
+          <t>OKVED_M_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt1</t>
+          <t>OKVED_71_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt</t>
+          <t>OKVED_N_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt1</t>
+          <t>OKVED_N_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt</t>
+          <t>OKVED_79_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt1</t>
+          <t>OKVED_79_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>OKVED_H_PostDeyt1</t>
+          <t>OKVED_S_Modern</t>
         </is>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt</t>
+          <t>OKVED_S_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt1</t>
+          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>OKVED_50_DrPost</t>
+          <t>OKVED_94_Modern</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt</t>
+          <t>OKVED_94_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt1</t>
+          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>OKVED_51_DrPost</t>
+          <t>OKVED_01_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>OKVED_52_PostDeyt1</t>
+          <t>OKVED_01_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>OKVED_I_PostDeyt1</t>
+          <t>OKVED_B_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>OKVED_I_DrPost</t>
+          <t>OKVED_B_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>OKVED_55_PostDeyt1</t>
+          <t>OKVED_07_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>OKVED_55_DrPost</t>
+          <t>OKVED_07_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt</t>
+          <t>OKVED_C_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt1</t>
+          <t>OKVED_10_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>OKVED_K_DrPost</t>
+          <t>OKVED_32_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt</t>
+          <t>OKVED_32_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt1</t>
+          <t>OKVED_32_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>OKVED_64_DrPost</t>
+          <t>OKVED_33_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>OKVED_L_PostDeyt1</t>
+          <t>OKVED_33_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>OKVED_68_PostDeyt1</t>
+          <t>OKVED_33_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>OKVED_70_PlCredit</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>OKVED_70_PostDeyt</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>OKVED_71_PostDeyt</t>
+          <t>OKVED_38_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt</t>
+          <t>OKVED_38_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt1</t>
+          <t>OKVED_F_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>OKVED_74_DrPost</t>
+          <t>OKVED_41_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt</t>
+          <t>OKVED_41_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt1</t>
+          <t>OKVED_42_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt</t>
+          <t>OKVED_42_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt1</t>
+          <t>OKVED_42_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>OKVED_79_DrPost</t>
+          <t>OKVED_43_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>OKVED_81_PlCredit</t>
+          <t>OKVED_43_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt</t>
+          <t>OKVED_G_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt1</t>
+          <t>OKVED_G_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>OKVED_S_PlCredit</t>
+          <t>OKVED_46_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>OKVED_S_PostDeyt1</t>
+          <t>OKVED_46_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>OKVED_94_PlCredit</t>
+          <t>OKVED_47_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>OKVED_94_PostDeyt1</t>
+          <t>OKVED_47_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin1</t>
+          <t>OKVED_H_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin2</t>
+          <t>OKVED_50_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
         <is>
-          <t>OKVED_B_PlPoFin1</t>
+          <t>OKVED_50_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>OKVED_07_PlPoFin1</t>
+          <t>OKVED_50_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin</t>
+          <t>OKVED_51_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin1</t>
+          <t>OKVED_51_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin2</t>
+          <t>OKVED_51_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin3</t>
+          <t>OKVED_52_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_I_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_I_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin1</t>
+          <t>OKVED_55_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin2</t>
+          <t>OKVED_55_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin1</t>
+          <t>OKVED_K_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin2</t>
+          <t>OKVED_K_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>OKVED_F_PlPoFin1</t>
+          <t>OKVED_K_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>OKVED_41_PlPoFin1</t>
+          <t>OKVED_64_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin1</t>
+          <t>OKVED_64_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin2</t>
+          <t>OKVED_64_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>OKVED_G_PlPoFin1</t>
+          <t>OKVED_L_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>OKVED_46_PlPoFin1</t>
+          <t>OKVED_68_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>OKVED_47_PlPoFin1</t>
+          <t>OKVED_70_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>OKVED_H_PlPoFin1</t>
+          <t>OKVED_70_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin1</t>
+          <t>OKVED_71_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin2</t>
+          <t>OKVED_74_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoFin1</t>
+          <t>OKVED_74_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>OKVED_52_PlPoFin1</t>
+          <t>OKVED_74_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin1</t>
+          <t>OKVED_N_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin2</t>
+          <t>OKVED_N_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin1</t>
+          <t>OKVED_79_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin2</t>
+          <t>OKVED_79_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoFin1</t>
+          <t>OKVED_79_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoFin1</t>
+          <t>OKVED_81_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
         <is>
-          <t>OKVED_68_PlPoFin1</t>
+          <t>OKVED_81_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>OKVED_M_PlPoFin1</t>
+          <t>OKVED_81_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin</t>
+          <t>OKVED_S_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin1</t>
+          <t>OKVED_S_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin2</t>
+          <t>OKVED_94_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin3</t>
+          <t>OKVED_94_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
         <is>
-          <t>OKVED_71_PlPoFin1</t>
+          <t>OKVED_01_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin1</t>
+          <t>OKVED_01_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin2</t>
+          <t>OKVED_B_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin3</t>
+          <t>OKVED_07_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
         <is>
-          <t>OKVED_74_SaldoDenPot</t>
+          <t>OKVED_33_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin2</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin3</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>OKVED_81_SaldoDenPot</t>
+          <t>OKVED_E_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin1</t>
+          <t>OKVED_E_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin2</t>
+          <t>OKVED_38_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin3</t>
+          <t>OKVED_38_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin1</t>
+          <t>OKVED_F_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin2</t>
+          <t>OKVED_41_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin3</t>
+          <t>OKVED_43_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
         <is>
-          <t>OKVED_01_Velch</t>
+          <t>OKVED_43_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
         <is>
-          <t>OKVED_11_Velch</t>
+          <t>OKVED_G_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>OKVED_32_Velch</t>
+          <t>OKVED_46_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
         <is>
-          <t>OKVED_33_Velch</t>
+          <t>OKVED_47_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
         <is>
-          <t>OKVED_E_Velch</t>
+          <t>OKVED_H_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
         <is>
-          <t>OKVED_38_Velch</t>
+          <t>OKVED_49_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
         <is>
-          <t>OKVED_F_Velch</t>
+          <t>OKVED_49_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>OKVED_41_Velch</t>
+          <t>OKVED_50_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
         <is>
-          <t>OKVED_42_Velch</t>
+          <t>OKVED_52_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>OKVED_43_Velch</t>
+          <t>OKVED_I_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>OKVED_47_Velch</t>
+          <t>OKVED_I_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>OKVED_49_Velch</t>
+          <t>OKVED_55_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>OKVED_I_Velch</t>
+          <t>OKVED_55_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>OKVED_56_Velch</t>
+          <t>OKVED_K_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>OKVED_J_Velch</t>
+          <t>OKVED_64_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>OKVED_63_Velch</t>
+          <t>OKVED_68_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>OKVED_L_Velch</t>
+          <t>OKVED_M_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>OKVED_68_Velch</t>
+          <t>OKVED_70_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>OKVED_M_Velch</t>
+          <t>OKVED_70_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
-          <t>OKVED_69_Velch</t>
+          <t>OKVED_70_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>OKVED_70_Velch</t>
+          <t>OKVED_70_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>OKVED_71_Velch</t>
+          <t>OKVED_71_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1696">
       <c r="A1696" t="inlineStr">
         <is>
-          <t>OKVED_N_Velch</t>
+          <t>OKVED_74_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1697">
       <c r="A1697" t="inlineStr">
         <is>
-          <t>OKVED_77_Velch</t>
+          <t>OKVED_74_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1698">
       <c r="A1698" t="inlineStr">
         <is>
-          <t>OKVED_79_Velch</t>
+          <t>OKVED_74_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1699">
       <c r="A1699" t="inlineStr">
         <is>
-          <t>OKVED_81_Velch</t>
+          <t>OKVED_74_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1700">
       <c r="A1700" t="inlineStr">
         <is>
-          <t>OKVED_82_Velch</t>
+          <t>OKVED_79_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1701">
       <c r="A1701" t="inlineStr">
         <is>
-          <t>OKVED_O_Velch</t>
+          <t>OKVED_79_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1702">
       <c r="A1702" t="inlineStr">
         <is>
-          <t>OKVED_84_Velch</t>
+          <t>OKVED_81_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1703">
       <c r="A1703" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_81_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1704">
       <c r="A1704" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_81_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1705">
       <c r="A1705" t="inlineStr">
         <is>
-          <t>OKVED_88_Velch</t>
+          <t>OKVED_81_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1706">
       <c r="A1706" t="inlineStr">
         <is>
-          <t>OKVED_R_Velch</t>
+          <t>OKVED_S_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1707">
       <c r="A1707" t="inlineStr">
         <is>
-          <t>OKVED_93_Velch</t>
+          <t>OKVED_S_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1708">
       <c r="A1708" t="inlineStr">
         <is>
-          <t>OKVED_S_Velch</t>
+          <t>OKVED_S_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1709">
       <c r="A1709" t="inlineStr">
         <is>
-          <t>OKVED_94_Velch</t>
+          <t>OKVED_94_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1710">
       <c r="A1710" t="inlineStr">
         <is>
-          <t>OKVED_96_Velch</t>
+          <t>OKVED_94_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1711">
       <c r="A1711" t="inlineStr">
         <is>
-          <t>OKVED_43_UstKap</t>
+          <t>OKVED_94_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1712">
       <c r="A1712" t="inlineStr">
         <is>
-          <t>OKVED_43_ChiAkt</t>
+          <t>OKVED_01_Velch</t>
         </is>
       </c>
     </row>
     <row r="1713">
       <c r="A1713" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap</t>
+          <t>OKVED_11_Velch</t>
         </is>
       </c>
     </row>
     <row r="1714">
       <c r="A1714" t="inlineStr">
         <is>
-          <t>OKVED_J_SebPro</t>
+          <t>OKVED_32_Velch</t>
         </is>
       </c>
     </row>
     <row r="1715">
       <c r="A1715" t="inlineStr">
         <is>
-          <t>OKVED_J_Pri(ubOtPro</t>
+          <t>OKVED_33_Velch</t>
         </is>
       </c>
     </row>
     <row r="1716">
       <c r="A1716" t="inlineStr">
         <is>
-          <t>OKVED_J_ChiPri(ubOtcPer</t>
+          <t>OKVED_E_Velch</t>
         </is>
       </c>
     </row>
     <row r="1717">
       <c r="A1717" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_38_Velch</t>
         </is>
       </c>
     </row>
     <row r="1718">
       <c r="A1718" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap</t>
+          <t>OKVED_F_Velch</t>
         </is>
       </c>
     </row>
     <row r="1719">
       <c r="A1719" t="inlineStr">
         <is>
-          <t>OKVED_63_SebPro</t>
+          <t>OKVED_41_Velch</t>
         </is>
       </c>
     </row>
     <row r="1720">
       <c r="A1720" t="inlineStr">
         <is>
-          <t>OKVED_63_Pri(ubOtPro</t>
+          <t>OKVED_42_Velch</t>
         </is>
       </c>
     </row>
     <row r="1721">
       <c r="A1721" t="inlineStr">
         <is>
-          <t>OKVED_63_ChiPri(ubOtcPer</t>
+          <t>OKVED_43_Velch</t>
         </is>
       </c>
     </row>
     <row r="1722">
       <c r="A1722" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_47_Velch</t>
         </is>
       </c>
     </row>
     <row r="1723">
       <c r="A1723" t="inlineStr">
         <is>
-          <t>OKVED_K_SebPro</t>
+          <t>OKVED_49_Velch</t>
         </is>
       </c>
     </row>
     <row r="1724">
       <c r="A1724" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap</t>
+          <t>OKVED_I_Velch</t>
         </is>
       </c>
     </row>
     <row r="1725">
       <c r="A1725" t="inlineStr">
         <is>
-          <t>OKVED_69_ChiAkt</t>
+          <t>OKVED_56_Velch</t>
         </is>
       </c>
     </row>
     <row r="1726">
       <c r="A1726" t="inlineStr">
         <is>
-          <t>OKVED_69_SebPro</t>
+          <t>OKVED_J_Velch</t>
         </is>
       </c>
     </row>
     <row r="1727">
       <c r="A1727" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap</t>
+          <t>OKVED_63_Velch</t>
         </is>
       </c>
     </row>
     <row r="1728">
       <c r="A1728" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap</t>
+          <t>OKVED_L_Velch</t>
         </is>
       </c>
     </row>
     <row r="1729">
       <c r="A1729" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap</t>
+          <t>OKVED_68_Velch</t>
         </is>
       </c>
     </row>
     <row r="1730">
       <c r="A1730" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap</t>
+          <t>OKVED_M_Velch</t>
         </is>
       </c>
     </row>
     <row r="1731">
       <c r="A1731" t="inlineStr">
         <is>
-          <t>OKVED_Q_SebPro</t>
+          <t>OKVED_69_Velch</t>
         </is>
       </c>
     </row>
     <row r="1732">
       <c r="A1732" t="inlineStr">
         <is>
-          <t>OKVED_Q_Pri(ubOtPro</t>
+          <t>OKVED_70_Velch</t>
         </is>
       </c>
     </row>
     <row r="1733">
       <c r="A1733" t="inlineStr">
         <is>
-          <t>OKVED_Q_ChiPri(ubOtcPer</t>
+          <t>OKVED_71_Velch</t>
         </is>
       </c>
     </row>
     <row r="1734">
       <c r="A1734" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_N_Velch</t>
         </is>
       </c>
     </row>
     <row r="1735">
       <c r="A1735" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap</t>
+          <t>OKVED_77_Velch</t>
         </is>
       </c>
     </row>
     <row r="1736">
       <c r="A1736" t="inlineStr">
         <is>
-          <t>OKVED_88_SebPro</t>
+          <t>OKVED_79_Velch</t>
         </is>
       </c>
     </row>
     <row r="1737">
       <c r="A1737" t="inlineStr">
         <is>
-          <t>OKVED_88_Pri(ubOtPro</t>
+          <t>OKVED_81_Velch</t>
         </is>
       </c>
     </row>
     <row r="1738">
       <c r="A1738" t="inlineStr">
         <is>
-          <t>OKVED_88_ChiPri(ubOtcPer</t>
+          <t>OKVED_82_Velch</t>
         </is>
       </c>
     </row>
     <row r="1739">
       <c r="A1739" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_O_Velch</t>
         </is>
       </c>
     </row>
     <row r="1740">
       <c r="A1740" t="inlineStr">
         <is>
-          <t>OKVED_R_SebPro</t>
+          <t>OKVED_84_Velch</t>
         </is>
       </c>
     </row>
     <row r="1741">
       <c r="A1741" t="inlineStr">
+        <is>
+          <t>OKVED_85_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>OKVED_85_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>OKVED_88_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>OKVED_R_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>OKVED_93_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>OKVED_S_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>OKVED_94_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>OKVED_96_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>OKVED_43_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>OKVED_43_ChiAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>OKVED_J_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>OKVED_J_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>OKVED_J_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>OKVED_J_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>OKVED_63_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>OKVED_63_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr">
+        <is>
+          <t>OKVED_63_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="inlineStr">
+        <is>
+          <t>OKVED_63_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="inlineStr">
+        <is>
+          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr">
+        <is>
+          <t>OKVED_K_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr">
+        <is>
+          <t>OKVED_69_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr">
+        <is>
+          <t>OKVED_69_ChiAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="inlineStr">
+        <is>
+          <t>OKVED_69_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="inlineStr">
+        <is>
+          <t>OKVED_O_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="inlineStr">
+        <is>
+          <t>OKVED_84_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="inlineStr">
+        <is>
+          <t>OKVED_Q_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="inlineStr">
+        <is>
+          <t>OKVED_Q_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="inlineStr">
+        <is>
+          <t>OKVED_Q_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr">
+        <is>
+          <t>OKVED_Q_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr">
+        <is>
+          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr">
+        <is>
+          <t>OKVED_88_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr">
+        <is>
+          <t>OKVED_88_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr">
+        <is>
+          <t>OKVED_88_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="inlineStr">
+        <is>
+          <t>OKVED_88_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="inlineStr">
+        <is>
+          <t>OKVED_88_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="inlineStr">
+        <is>
+          <t>OKVED_R_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="inlineStr">
         <is>
           <t>OKVED_93_SebPro</t>
         </is>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1779"/>
+  <dimension ref="A1:A1790"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6572,70 +6572,70 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>OKVED_B_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_B_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>OKVED_07_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_07_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>OKVED_33_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_33_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>OKVED_E_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_E_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>OKVED_36_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_36_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>OKVED_38_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_38_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>OKVED_42_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_42_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>OKVED_43_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_43_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>OKVED_49_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_49_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>OKVED_52_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_52_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
@@ -6649,6221 +6649,6298 @@
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>OKVED_56_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_56_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>OKVED_K_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_56_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>OKVED_K_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_K_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>OKVED_64_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_K_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>OKVED_64_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_64_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>OKVED_69_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_64_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>OKVED_69_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_69_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>OKVED_71_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_69_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>OKVED_74_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_71_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>OKVED_74_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_74_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>OKVED_79_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_74_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>OKVED_81_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_74_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>OKVED_81_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_79_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>OKVED_82_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_81_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>OKVED_82_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_81_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>OKVED_O_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_81_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>OKVED_O_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_82_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_82_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_82_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_O_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_O_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_O_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas</t>
+          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas</t>
+          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>OKVED_S_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>OKVED_94_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>OKVED_96_DohIRasPoObyVidDeyZaOtcPerVToChi</t>
+          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>OKVED_11_OtcGoPro</t>
+          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>OKVED_32_OtcGoTekNalNaPri</t>
+          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>OKVED_32_OtcGoOtlNalNaPri</t>
+          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>OKVED_33_OtcGoPro</t>
+          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoTekNalNaPri</t>
+          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoOtlNalNaPri</t>
+          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoPro</t>
+          <t>OKVED_S_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>OKVED_42_OtcGoPro</t>
+          <t>OKVED_94_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>OKVED_43_OtcGoPro</t>
+          <t>OKVED_96_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>OKVED_50_OtcGoTekNalNaPri</t>
+          <t>OKVED_11_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>OKVED_50_OtcGoPro</t>
+          <t>OKVED_32_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>OKVED_56_OtcGoTekNalNaPri</t>
+          <t>OKVED_32_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>OKVED_56_OtcGoOtlNalNaPri</t>
+          <t>OKVED_33_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoTekNalNaPri</t>
+          <t>OKVED_38_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoOtlNalNaPri</t>
+          <t>OKVED_38_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoPro</t>
+          <t>OKVED_38_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>OKVED_71_OtcGoTekNalNaPri</t>
+          <t>OKVED_42_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>OKVED_74_OtcGoTekNalNaPri</t>
+          <t>OKVED_43_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>OKVED_74_OtcGoPro</t>
+          <t>OKVED_50_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>OKVED_77_OtcGoPro</t>
+          <t>OKVED_50_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>OKVED_79_OtcGoTekNalNaPri</t>
+          <t>OKVED_56_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>OKVED_79_OtcGoPro</t>
+          <t>OKVED_56_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>OKVED_O_OtcGoOtlNalNaPri</t>
+          <t>OKVED_69_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>OKVED_O_OtcGoPro</t>
+          <t>OKVED_69_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>OKVED_84_OtcGoOtlNalNaPri</t>
+          <t>OKVED_69_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>OKVED_84_OtcGoPro</t>
+          <t>OKVED_71_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoTekNalNaPri</t>
+          <t>OKVED_74_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoPro</t>
+          <t>OKVED_74_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoTekNalNaPri</t>
+          <t>OKVED_77_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoPro</t>
+          <t>OKVED_79_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoSalProDohIRas</t>
+          <t>OKVED_79_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoTekNalNaPri</t>
+          <t>OKVED_O_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoOtlNalNaPri</t>
+          <t>OKVED_O_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoPro</t>
+          <t>OKVED_84_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoSalProDohIRas</t>
+          <t>OKVED_84_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoTekNalNaPri</t>
+          <t>OKVED_85_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoOtlNalNaPri</t>
+          <t>OKVED_85_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoPro</t>
+          <t>OKVED_85_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>OKVED_S_OtcGoPro</t>
+          <t>OKVED_85_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>OKVED_94_OtcGoPro</t>
+          <t>OKVED_R_OtcGoSalProDohIRas</t>
         </is>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>OKVED_96_OtcGoPro</t>
+          <t>OKVED_R_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>OKVED_01_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_R_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>OKVED_B_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_R_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>OKVED_B_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_93_OtcGoSalProDohIRas</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>OKVED_07_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_93_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>OKVED_07_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_93_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>OKVED_10_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_93_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>OKVED_11_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_S_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>OKVED_11_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_94_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>OKVED_32_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_96_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>OKVED_33_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_01_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>OKVED_33_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_B_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>OKVED_35_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_B_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>OKVED_35_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_07_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>OKVED_35_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_07_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>OKVED_35_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_10_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>OKVED_36_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_11_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>OKVED_36_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_11_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_32_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_33_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>OKVED_F_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_33_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>OKVED_41_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_35_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>OKVED_41_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_35_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>OKVED_42_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_35_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>OKVED_43_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_35_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>OKVED_43_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_36_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>OKVED_G_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_36_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>OKVED_G_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_38_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>OKVED_46_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_38_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>OKVED_46_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_F_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>OKVED_47_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_41_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>OKVED_47_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_41_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>OKVED_50_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_42_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>OKVED_50_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_43_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>OKVED_52_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_43_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>OKVED_52_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_G_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>OKVED_I_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_G_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>OKVED_I_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_46_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>OKVED_55_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_46_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>OKVED_55_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_47_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>OKVED_56_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_47_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>OKVED_56_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_50_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>OKVED_K_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_50_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>OKVED_K_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_52_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>OKVED_64_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_52_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>OKVED_64_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_I_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>OKVED_L_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_I_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>OKVED_L_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_55_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>OKVED_68_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_55_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>OKVED_68_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_56_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>OKVED_M_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_56_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>OKVED_M_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_K_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_K_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_64_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>OKVED_71_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_64_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>OKVED_71_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_L_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>OKVED_74_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_L_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>OKVED_74_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_68_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>OKVED_N_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_68_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>OKVED_N_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_M_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>OKVED_77_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_M_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>OKVED_77_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_69_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>OKVED_79_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_69_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>OKVED_79_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_71_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>OKVED_81_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_71_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>OKVED_81_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_74_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>OKVED_82_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_74_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>OKVED_82_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_N_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>OKVED_84_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_N_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>OKVED_84_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_77_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_77_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_79_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_79_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_81_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_81_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_82_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_82_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_84_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>OKVED_S_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_84_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>OKVED_S_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_85_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>OKVED_94_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_85_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>OKVED_94_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_85_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>OKVED_96_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_85_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>OKVED_96_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_R_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerVyr_1</t>
+          <t>OKVED_R_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerKomIUprRas_1</t>
+          <t>OKVED_93_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>MO_30851_OtcGoPro_1</t>
+          <t>OKVED_93_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>MO_30501_OtcGoOtlNalNaPri_1</t>
+          <t>OKVED_S_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>MO_30501_OtcGoPro_1</t>
+          <t>OKVED_S_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>MO_30510_OtcGoSalProDohIRas_1</t>
+          <t>OKVED_94_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>MO_30510_OtcGoTekNalNaPri_1</t>
+          <t>OKVED_94_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>MO_30510_OtcGoOtlNalNaPri_1</t>
+          <t>OKVED_96_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>MO_30510_OtcGoPro_1</t>
+          <t>OKVED_96_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>MO_30604_OtcGoPri(ubDoNal_1</t>
+          <t>MO_30851_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas_1</t>
         </is>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>MO_30604_OtcGoTekNalNaPri_1</t>
+          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas_1</t>
         </is>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>MO_30604_OtcGoOtlNalNaPri_1</t>
+          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas_1</t>
         </is>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>MO_30604_OtcGoPro_1</t>
+          <t>MO_30832_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas_1</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>MO_30832_OtcGoTekNalNaPri_1</t>
+          <t>MO_30851_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>MO_30832_OtcGoPro_1</t>
+          <t>MO_30501_OtcGoOtlNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>OKVED_11_OrgPolUbyKolOrgEdi</t>
+          <t>MO_30501_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>OKVED_11_OrgPolUbyV%KObsKol</t>
+          <t>MO_30510_OtcGoSalProDohIRas_1</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>OKVED_11_OrgPolUbyUby</t>
+          <t>MO_30510_OtcGoTekNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>OKVED_32_OrgPolUbyKolOrgEdi</t>
+          <t>MO_30510_OtcGoOtlNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>OKVED_32_OrgPolUbyV%KObsKol</t>
+          <t>MO_30510_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>OKVED_32_OrgPolUbyUby</t>
+          <t>MO_30604_OtcGoPri(ubDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>OKVED_42_OrgPolPriKolOrgEdi</t>
+          <t>MO_30604_OtcGoTekNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>OKVED_42_OrgPolPriV%KObsKol</t>
+          <t>MO_30604_OtcGoOtlNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>OKVED_42_OrgPolPriPriDoNal</t>
+          <t>MO_30604_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>OKVED_43_OrgPolUbyKolOrgEdi</t>
+          <t>MO_30832_OtcGoTekNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>OKVED_43_OrgPolUbyV%KObsKol</t>
+          <t>MO_30832_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>OKVED_43_OrgPolUbyUby</t>
+          <t>OKVED_11_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>OKVED_49_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_11_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>OKVED_49_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_11_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>OKVED_49_OrgPolUbyUby</t>
+          <t>OKVED_32_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>OKVED_51_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_32_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>OKVED_51_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_32_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>OKVED_51_OrgPolUbyUby</t>
+          <t>OKVED_42_OrgPolPriKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>OKVED_56_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_42_OrgPolPriV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>OKVED_56_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_42_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>OKVED_56_OrgPolUbyUby</t>
+          <t>OKVED_43_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-DoNal</t>
+          <t>OKVED_43_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>OKVED_J_OrgPolPriPriDoNal</t>
+          <t>OKVED_43_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>OKVED_J_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_49_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>OKVED_J_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_49_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>OKVED_J_OrgPolUbyUby</t>
+          <t>OKVED_49_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-DoNal</t>
+          <t>OKVED_51_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>OKVED_63_OrgPolPriPriDoNal</t>
+          <t>OKVED_51_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>OKVED_63_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_51_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>OKVED_63_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_56_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>OKVED_63_OrgPolUbyUby</t>
+          <t>OKVED_56_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>OKVED_69_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_56_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>OKVED_69_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_J_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>OKVED_69_OrgPolUbyUby</t>
+          <t>OKVED_J_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>OKVED_74_OrgPolPriKolOrgEdi</t>
+          <t>OKVED_J_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>OKVED_74_OrgPolPriV%KObsKol</t>
+          <t>OKVED_J_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>OKVED_74_OrgPolPriPriDoNal</t>
+          <t>OKVED_J_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>OKVED_79_OrgPolPriKolOrgEdi</t>
+          <t>OKVED_63_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>OKVED_79_OrgPolPriV%KObsKol</t>
+          <t>OKVED_63_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>OKVED_79_OrgPolPriPriDoNal</t>
+          <t>OKVED_63_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>OKVED_81_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_63_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>OKVED_81_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_63_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>OKVED_81_OrgPolUbyUby</t>
+          <t>OKVED_69_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>OKVED_O_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_69_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>OKVED_O_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_69_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>OKVED_O_OrgPolUbyUby</t>
+          <t>OKVED_74_OrgPolPriKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>OKVED_84_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_74_OrgPolPriV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>OKVED_84_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_74_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>OKVED_84_OrgPolUbyUby</t>
+          <t>OKVED_79_OrgPolPriKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_79_OrgPolPriV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_79_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyUby</t>
+          <t>OKVED_81_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_81_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_81_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyUby</t>
+          <t>OKVED_O_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-DoNal</t>
+          <t>OKVED_O_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>OKVED_Q_OrgPolPriPriDoNal</t>
+          <t>OKVED_O_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>OKVED_Q_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_84_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>OKVED_Q_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_84_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>OKVED_Q_OrgPolUbyUby</t>
+          <t>OKVED_84_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-DoNal</t>
+          <t>OKVED_85_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>OKVED_88_OrgPolPriPriDoNal</t>
+          <t>OKVED_85_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>OKVED_88_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_85_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>OKVED_88_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_85_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>OKVED_88_OrgPolUbyUby</t>
+          <t>OKVED_85_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>OKVED_93_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_85_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>OKVED_93_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_Q_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>OKVED_93_OrgPolUbyUby</t>
+          <t>OKVED_Q_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>OKVED_94_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_Q_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>OKVED_94_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_Q_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>OKVED_94_OrgPolUbyUby</t>
+          <t>OKVED_Q_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>OKVED_01_TeRosPriV%</t>
+          <t>OKVED_88_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>OKVED_10_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_88_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>OKVED_10_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_88_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>OKVED_11_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_88_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>OKVED_11_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_88_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>OKVED_11_TeRosUbyV%</t>
+          <t>OKVED_93_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>OKVED_32_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_93_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>OKVED_32_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_93_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>OKVED_32_TeRosUbyV%</t>
+          <t>OKVED_94_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>OKVED_38_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_94_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>OKVED_38_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_94_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>OKVED_F_TeRosPriV%</t>
+          <t>OKVED_01_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>OKVED_41_TeRosPriV%</t>
+          <t>OKVED_10_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>OKVED_41_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_10_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>OKVED_41_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_11_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>OKVED_42_TeRosPriV%</t>
+          <t>OKVED_11_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>OKVED_42_TeRosSumPriV%</t>
+          <t>OKVED_11_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>OKVED_43_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_32_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>OKVED_43_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_32_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>OKVED_43_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_32_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>OKVED_43_SumPriZaSooPerPreGo</t>
+          <t>OKVED_38_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>OKVED_43_TeRosUbyV%</t>
+          <t>OKVED_38_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>OKVED_49_TeRosUbyV%</t>
+          <t>OKVED_F_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>OKVED_50_TeRosPriV%</t>
+          <t>OKVED_41_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>OKVED_50_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_41_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>OKVED_50_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_41_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>OKVED_50_TeRosSumPriV%</t>
+          <t>OKVED_42_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>OKVED_51_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_42_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>OKVED_51_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_43_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>OKVED_51_TeRosUbyV%</t>
+          <t>OKVED_43_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>OKVED_I_TeRosPriV%</t>
+          <t>OKVED_43_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>OKVED_55_TeRosPriV%</t>
+          <t>OKVED_43_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>OKVED_55_SumPriZaSooPerPreGo</t>
+          <t>OKVED_43_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>OKVED_56_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_49_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>OKVED_56_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_50_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>OKVED_56_TeRosUbyV%</t>
+          <t>OKVED_50_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>OKVED_L_TeRosPriV%</t>
+          <t>OKVED_50_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>OKVED_68_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_50_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>OKVED_68_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_51_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>OKVED_68_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_51_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>OKVED_68_SumPriZaSooPerPreGo</t>
+          <t>OKVED_51_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>OKVED_68_TeRosUbyV%</t>
+          <t>OKVED_I_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>OKVED_M_TeRosPriV%</t>
+          <t>OKVED_55_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>OKVED_69_TeRosPriV%</t>
+          <t>OKVED_55_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>OKVED_70_TeRosPriV%</t>
+          <t>OKVED_56_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>OKVED_70_SumPriZaSooPerPreGo</t>
+          <t>OKVED_56_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>OKVED_70_TeRosSumPriV%</t>
+          <t>OKVED_56_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>OKVED_71_TeRosPriV%</t>
+          <t>OKVED_L_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>OKVED_74_TeRosPriV%</t>
+          <t>OKVED_68_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>OKVED_77_TeRosPriV%</t>
+          <t>OKVED_68_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>OKVED_77_SumPriZaSooPerPreGo</t>
+          <t>OKVED_68_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>OKVED_77_TeRosUbyV%</t>
+          <t>OKVED_68_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>OKVED_79_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_68_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>OKVED_79_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_M_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>OKVED_79_TeRosUbyV%</t>
+          <t>OKVED_69_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>OKVED_81_TeRosPriV%</t>
+          <t>OKVED_70_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>OKVED_81_SumPriZaSooPerPreGo</t>
+          <t>OKVED_70_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>OKVED_81_TeRosUbyV%</t>
+          <t>OKVED_70_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>OKVED_82_TeRosPriV%</t>
+          <t>OKVED_71_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>OKVED_82_SumPriZaSooPerPreGo</t>
+          <t>OKVED_74_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>OKVED_82_TeRosUbyV%</t>
+          <t>OKVED_77_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>OKVED_O_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_77_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>OKVED_O_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_77_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>OKVED_O_TeRosUbyV%</t>
+          <t>OKVED_79_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_79_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosPriV%</t>
+          <t>OKVED_79_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_81_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_81_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t>OKVED_85_SumPriZaSooPerPreGo</t>
+          <t>OKVED_81_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosUbyV%</t>
+          <t>OKVED_82_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosSumPriV%</t>
+          <t>OKVED_82_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_82_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosPriV%</t>
+          <t>OKVED_O_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_O_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_O_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>OKVED_85_SumPriZaSooPerPreGo</t>
+          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosUbyV%</t>
+          <t>OKVED_85_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosSumPriV%</t>
+          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>OKVED_93_TeRosUbyV%</t>
+          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>OKVED_S_TeRosPriV%</t>
+          <t>OKVED_85_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
-          <t>OKVED_94_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_85_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosPriV%</t>
+          <t>OKVED_85_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>OKVED_94_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t>OKVED_94_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_85_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>OKVED_94_SumPriZaSooPerPreGo</t>
+          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosUbyV%</t>
+          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosSumPriV%</t>
+          <t>OKVED_85_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>OKVED_96_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_85_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosPriV%</t>
+          <t>OKVED_85_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>OKVED_96_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_93_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>OKVED_96_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_S_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="inlineStr">
         <is>
-          <t>OKVED_96_SumPriZaSooPerPreGo</t>
+          <t>OKVED_94_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosUbyV%</t>
+          <t>OKVED_94_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosSumPriV%</t>
+          <t>OKVED_94_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="inlineStr">
         <is>
-          <t>MO_30851_OrgPolUbyKolOrgEdi_1</t>
+          <t>OKVED_94_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>MO_30851_OrgPolUbyV%KObsKol_1</t>
+          <t>OKVED_94_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>MO_30851_OrgPolUbyUby_1</t>
+          <t>OKVED_94_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>MO_30501_OrgPolPriKolOrgEdi_1</t>
+          <t>OKVED_94_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>MO_30501_OrgPolPriV%KObsKol_1</t>
+          <t>OKVED_96_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>MO_30501_OrgPolPriPriDoNal_1</t>
+          <t>OKVED_96_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>MO_30510_OrgPolPriPriDoNal_1</t>
+          <t>OKVED_96_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>MO_30604_PriUby(-DoNal_1</t>
+          <t>OKVED_96_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolPriPriDoNal_1</t>
+          <t>OKVED_96_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolUbyKolOrgEdi_1</t>
+          <t>OKVED_96_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolUbyV%KObsKol_1</t>
+          <t>OKVED_96_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolUbyUby_1</t>
+          <t>MO_30851_OrgPolUbyKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>MO_30851_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30851_OrgPolUbyV%KObsKol_1</t>
         </is>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>MO_30851_KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>MO_30851_OrgPolUbyUby_1</t>
         </is>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>MO_30851_TeRosUbyV%_1</t>
+          <t>MO_30501_OrgPolPriKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>MO_30501_TeRosPriV%_1</t>
+          <t>MO_30501_OrgPolPriV%KObsKol_1</t>
         </is>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>MO_30501_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30501_OrgPolPriPriDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>MO_30501_KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>MO_30510_OrgPolPriPriDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>MO_30501_TeRosSumPriV%_1</t>
+          <t>MO_30604_PriUby(-DoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>MO_30510_TeRosPriV%_1</t>
+          <t>MO_30604_OrgPolPriPriDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>MO_30510_SumPriZaSooPerPreGo_1</t>
+          <t>MO_30604_OrgPolUbyKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>MO_30510_TeRosSumPriV%_1</t>
+          <t>MO_30604_OrgPolUbyV%KObsKol_1</t>
         </is>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>MO_30604_PriUby(-DoNalZaAnaPerPreGo_1</t>
+          <t>MO_30604_OrgPolUbyUby_1</t>
         </is>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosPriV%_1</t>
+          <t>MO_30851_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>MO_30604_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30851_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>MO_30604_KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>MO_30851_TeRosUbyV%_1</t>
         </is>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>MO_30604_SumPriZaSooPerPreGo_1</t>
+          <t>MO_30501_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosUbyV%_1</t>
+          <t>MO_30501_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosSumPriV%_1</t>
+          <t>MO_30501_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>MO_30616_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30501_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>MO_30616_KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>MO_30510_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>MO_30619_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30510_SumPriZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>MO_30619_KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>MO_30510_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
         <is>
-          <t>MO_30832_TeRosPriV%_1</t>
+          <t>MO_30604_PriUby(-DoNalZaAnaPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>OPF_20200_OrgPolUbyKolOrgEdi_2</t>
+          <t>MO_30604_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>OPF_20200_OrgPolUbyV%KObsKol_2</t>
+          <t>MO_30604_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>OPF_20200_OrgPolUbyUby_2</t>
+          <t>MO_30604_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>OPF_20600_OrgPolUbyKolOrgEdi_2</t>
+          <t>MO_30604_SumPriZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>OPF_20600_OrgPolUbyV%KObsKol_2</t>
+          <t>MO_30604_TeRosUbyV%_1</t>
         </is>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>OPF_20600_OrgPolUbyUby_2</t>
+          <t>MO_30604_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>OPF_71400_OrgPolUbyKolOrgEdi_2</t>
+          <t>MO_30616_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>OPF_71400_OrgPolUbyV%KObsKol_2</t>
+          <t>MO_30616_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>OPF_71400_OrgPolUbyUby_2</t>
+          <t>MO_30619_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>OPF_75500_OrgPolUbyKolOrgEdi_2</t>
+          <t>MO_30619_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>OPF_75500_OrgPolUbyV%KObsKol_2</t>
+          <t>MO_30832_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>OPF_75500_OrgPolUbyUby_2</t>
+          <t>OPF_20200_OrgPolUbyKolOrgEdi_2</t>
         </is>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>OPF_14000_TeRosPriV%_2</t>
+          <t>OPF_20200_OrgPolUbyV%KObsKol_2</t>
         </is>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>OPF_14100_TeRosPriV%_2</t>
+          <t>OPF_20200_OrgPolUbyUby_2</t>
         </is>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>OPF_20200_TeRosUbyV%_2</t>
+          <t>OPF_20600_OrgPolUbyKolOrgEdi_2</t>
         </is>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>OPF_21200_TeRosPriV%_2</t>
+          <t>OPF_20600_OrgPolUbyV%KObsKol_2</t>
         </is>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>OPF_70000_SumUbyZaSooPerPreGo_2</t>
+          <t>OPF_20600_OrgPolUbyUby_2</t>
         </is>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>OPF_70000_KolOrgPolUbyZaPreGo(ed_2</t>
+          <t>OPF_71400_OrgPolUbyKolOrgEdi_2</t>
         </is>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>OPF_70400_SumUbyZaSooPerPreGo_2</t>
+          <t>OPF_71400_OrgPolUbyV%KObsKol_2</t>
         </is>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>OPF_70400_KolOrgPolUbyZaPreGo(ed_2</t>
+          <t>OPF_71400_OrgPolUbyUby_2</t>
         </is>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>OPF_71400_SumUbyZaSooPerPreGo_2</t>
+          <t>OPF_75500_OrgPolUbyKolOrgEdi_2</t>
         </is>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>OPF_71400_KolOrgPolUbyZaPreGo(ed_2</t>
+          <t>OPF_75500_OrgPolUbyV%KObsKol_2</t>
         </is>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>OPF_71400_TeRosUbyV%_2</t>
+          <t>OPF_75500_OrgPolUbyUby_2</t>
         </is>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>OPF_75500_SumUbyZaSooPerPreGo_2</t>
+          <t>OPF_14000_TeRosPriV%_2</t>
         </is>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>OPF_75500_KolOrgPolUbyZaPreGo(ed_2</t>
+          <t>OPF_14100_TeRosPriV%_2</t>
         </is>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>OPF_75500_TeRosUbyV%_2</t>
+          <t>OPF_20200_TeRosUbyV%_2</t>
         </is>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>FS_12_OrgPolPriKolOrgEdi_3</t>
+          <t>OPF_21200_TeRosPriV%_2</t>
         </is>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>FS_12_OrgPolPriV%KObsKol_3</t>
+          <t>OPF_70000_SumUbyZaSooPerPreGo_2</t>
         </is>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>FS_12_OrgPolPriPriDoNal_3</t>
+          <t>OPF_70000_KolOrgPolUbyZaPreGo(ed_2</t>
         </is>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>FS_15_OrgPolUbyKolOrgEdi_3</t>
+          <t>OPF_70400_SumUbyZaSooPerPreGo_2</t>
         </is>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>FS_15_OrgPolUbyV%KObsKol_3</t>
+          <t>OPF_70400_KolOrgPolUbyZaPreGo(ed_2</t>
         </is>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>FS_15_OrgPolUbyUby_3</t>
+          <t>OPF_71400_SumUbyZaSooPerPreGo_2</t>
         </is>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>FS_12_TeRosPriV%_3</t>
+          <t>OPF_71400_KolOrgPolUbyZaPreGo(ed_2</t>
         </is>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>FS_12_SumPriZaSooPerPreGo_3</t>
+          <t>OPF_71400_TeRosUbyV%_2</t>
         </is>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>FS_12_TeRosSumPriV%_3</t>
+          <t>OPF_75500_SumUbyZaSooPerPreGo_2</t>
         </is>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>FS_15_TeRosUbyV%_3</t>
+          <t>OPF_75500_KolOrgPolUbyZaPreGo(ed_2</t>
         </is>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>FS_17_SumUbyZaSooPerPreGo_3</t>
+          <t>OPF_75500_TeRosUbyV%_2</t>
         </is>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>FS_17_KolOrgPolUbyZaPreGo(ed_3</t>
+          <t>FS_12_OrgPolPriKolOrgEdi_3</t>
         </is>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>OKVED_56_VToChiKomIUprRas</t>
+          <t>FS_12_OrgPolPriV%KObsKol_3</t>
         </is>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-OtPro</t>
+          <t>FS_12_OrgPolPriPriDoNal_3</t>
         </is>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>OKVED_J_SebProSUchKomIUprRas</t>
+          <t>FS_15_OrgPolUbyKolOrgEdi_3</t>
         </is>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>OKVED_J_VToChiKomIUprRas</t>
+          <t>FS_15_OrgPolUbyV%KObsKol_3</t>
         </is>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>FS_15_OrgPolUbyUby_3</t>
         </is>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%KKomIUprRas</t>
+          <t>FS_12_TeRosPriV%_3</t>
         </is>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%KVyr</t>
+          <t>FS_12_SumPriZaSooPerPreGo_3</t>
         </is>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>FS_12_TeRosSumPriV%_3</t>
         </is>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-OtPro</t>
+          <t>FS_15_TeRosUbyV%_3</t>
         </is>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>OKVED_63_SebProSUchKomIUprRas</t>
+          <t>FS_17_SumUbyZaSooPerPreGo_3</t>
         </is>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>OKVED_63_VToChiKomIUprRas</t>
+          <t>FS_17_KolOrgPolUbyZaPreGo(ed_3</t>
         </is>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>OKVED_56_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%KKomIUprRas</t>
+          <t>OKVED_J_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%KVyr</t>
+          <t>OKVED_J_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>OKVED_J_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>OKVED_74_VToChiKomIUprRas</t>
+          <t>OKVED_J_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>OKVED_81_VToChiKomIUprRas</t>
+          <t>OKVED_J_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>OKVED_82_VToChiKomIUprRas</t>
+          <t>OKVED_J_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>OKVED_O_VToChiKomIUprRas</t>
+          <t>OKVED_J_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>OKVED_84_VToChiKomIUprRas</t>
+          <t>OKVED_63_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>OKVED_85_VToChiKomIUprRas</t>
+          <t>OKVED_63_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-OtPro</t>
+          <t>OKVED_63_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>OKVED_Q_SebProSUchKomIUprRas</t>
+          <t>OKVED_63_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>OKVED_Q_VToChiKomIUprRas</t>
+          <t>OKVED_63_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>OKVED_63_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%KKomIUprRas</t>
+          <t>OKVED_63_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%KVyr</t>
+          <t>OKVED_74_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>OKVED_81_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-OtPro</t>
+          <t>OKVED_82_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>OKVED_88_SebProSUchKomIUprRas</t>
+          <t>OKVED_O_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>OKVED_88_VToChiKomIUprRas</t>
+          <t>OKVED_84_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>OKVED_85_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%KKomIUprRas</t>
+          <t>OKVED_Q_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%KVyr</t>
+          <t>OKVED_Q_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>OKVED_Q_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>OKVED_R_SebProSUchKomIUprRas</t>
+          <t>OKVED_Q_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>OKVED_R_VToChiKomIUprRas</t>
+          <t>OKVED_Q_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>OKVED_93_SebProSUchKomIUprRas</t>
+          <t>OKVED_Q_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>OKVED_93_VToChiKomIUprRas</t>
+          <t>OKVED_Q_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>OKVED_56_OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OKVED_88_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>OKVED_O_OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OKVED_88_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>OKVED_84_OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OKVED_88_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>OKVED_11_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_88_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>OKVED_43_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_88_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>OKVED_49_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_88_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>OKVED_56_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_88_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>OKVED_56_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_R_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>OKVED_69_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_R_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>OKVED_69_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_93_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>OKVED_74_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_93_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>OKVED_81_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_56_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>OKVED_81_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_O_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>OKVED_82_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_84_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>OKVED_82_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_11_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>OKVED_O_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_43_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>OKVED_O_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_49_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_56_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_56_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_69_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_69_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>OKVED_R_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_74_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>OKVED_R_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_81_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>OKVED_93_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_81_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>OKVED_93_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_82_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>OKVED_94_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_82_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>OKVED_96_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_O_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_O_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10DebZad</t>
+          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_R_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_R_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>OKVED_70_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_93_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>OKVED_70_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_93_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>OKVED_R_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_94_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>OKVED_R_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_96_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>OKVED_93_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>OKVED_93_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>OKVED_94_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>OKVED_94_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>OKVED_96_KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10DebZad</t>
         </is>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>OKVED_96_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsKol</t>
+          <t>OKVED_70_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20DebZad</t>
+          <t>OKVED_70_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZad</t>
+          <t>OKVED_R_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KreZad</t>
+          <t>OKVED_R_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZadKre</t>
+          <t>OKVED_93_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20DenSreIDenEkv</t>
+          <t>OKVED_93_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
+          <t>OKVED_94_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeTekLikOt&gt;=20DebZad</t>
+          <t>OKVED_94_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeTekLikOt&gt;=20V%KObsZad</t>
+          <t>OKVED_96_KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>OKVED_01_ArendPlDeVsego</t>
+          <t>OKVED_96_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>OKVED_32_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>OKVED_E_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>OKVED_36_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>OKVED_38_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>OKVED_41_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KreZad</t>
         </is>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>OKVED_43_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>OKVED_49_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>OKVED_50_ArendPlDeVsego</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>OKVED_I_ArendPlDeVsego</t>
+          <t>OKVED_69_KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>OKVED_55_ArendPlDeVsego</t>
+          <t>OKVED_69_KoeTekLikOt&gt;=20V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>OKVED_56_ArendPlDeVsego</t>
+          <t>OKVED_01_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>OKVED_J_OtProdDeVsego</t>
+          <t>OKVED_32_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>OKVED_J_ArendPlDeVsego</t>
+          <t>OKVED_E_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>OKVED_63_OtProdDeVsego</t>
+          <t>OKVED_36_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>OKVED_63_ArendPlDeVsego</t>
+          <t>OKVED_38_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>OKVED_64_ArendPlDeVsego</t>
+          <t>OKVED_41_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>OKVED_69_ArendPlDeVsego</t>
+          <t>OKVED_43_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>OKVED_79_ArendPlDeVsego</t>
+          <t>OKVED_49_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>OKVED_81_ArendPlDeVsego</t>
+          <t>OKVED_50_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>OKVED_82_ArendPlDeVsego</t>
+          <t>OKVED_I_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>OKVED_O_ArendPlDeVsego</t>
+          <t>OKVED_55_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>OKVED_84_ArendPlDeVsego</t>
+          <t>OKVED_56_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_J_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_J_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>OKVED_88_OtProdDeVsego</t>
+          <t>OKVED_63_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>OKVED_88_ArendPlDeVsego</t>
+          <t>OKVED_63_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>OKVED_R_OtProdDeVsego</t>
+          <t>OKVED_64_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>OKVED_R_ArendPlDeVsego</t>
+          <t>OKVED_69_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>OKVED_93_OtProdDeVsego</t>
+          <t>OKVED_79_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>OKVED_93_ArendPlDeVsego</t>
+          <t>OKVED_81_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>OKVED_S_ArendPlDeVsego</t>
+          <t>OKVED_82_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>OKVED_94_ArendPlDeVsego</t>
+          <t>OKVED_O_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>OKVED_96_ArendPlDeVsego</t>
+          <t>OKVED_84_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcPoDolgObyaz</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>OKVED_32_ProcPoDolgObyaz</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>OKVED_32_NalogNaPri</t>
+          <t>OKVED_88_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>OKVED_33_NalogNaPri</t>
+          <t>OKVED_88_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcPoDolgObyaz</t>
+          <t>OKVED_R_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>OKVED_38_NalogNaPri</t>
+          <t>OKVED_R_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcPoDolgObyaz</t>
+          <t>OKVED_93_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>OKVED_56_ProcPoDolgObyaz</t>
+          <t>OKVED_93_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>OKVED_56_NalogNaPri</t>
+          <t>OKVED_S_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>OKVED_J_ProcPoDolgObyaz</t>
+          <t>OKVED_94_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>OKVED_J_NalogNaPri</t>
+          <t>OKVED_96_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>OKVED_63_ProcPoDolgObyaz</t>
+          <t>OKVED_11_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>OKVED_63_NalogNaPri</t>
+          <t>OKVED_32_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>OKVED_M_ProcPoDolgObyaz</t>
+          <t>OKVED_32_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>OKVED_69_ProcPoDolgObyaz</t>
+          <t>OKVED_33_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>OKVED_69_NalogNaPri</t>
+          <t>OKVED_36_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>OKVED_71_ProcPoDolgObyaz</t>
+          <t>OKVED_38_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>OKVED_71_NalogNaPri</t>
+          <t>OKVED_49_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>OKVED_74_ProcPoDolgObyaz</t>
+          <t>OKVED_56_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcPoDolgObyaz</t>
+          <t>OKVED_56_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>OKVED_79_NalogNaPri</t>
+          <t>OKVED_J_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>OKVED_81_NalogNaPri</t>
+          <t>OKVED_J_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_63_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>OKVED_O_VSvyaziSOplTrudRab</t>
+          <t>OKVED_63_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>OKVED_O_ProcPoDolgObyaz</t>
+          <t>OKVED_M_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_69_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>OKVED_84_VSvyaziSOplTrudRab</t>
+          <t>OKVED_69_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>OKVED_84_ProcPoDolgObyaz</t>
+          <t>OKVED_71_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_71_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_74_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_77_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_79_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>OKVED_Q_ProcPoDolgObyaz</t>
+          <t>OKVED_81_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>OKVED_Q_NalogNaPri</t>
+          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_O_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>OKVED_R_VSvyaziSOplTrudRab</t>
+          <t>OKVED_O_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>OKVED_R_ProcPoDolgObyaz</t>
+          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>OKVED_R_NalogNaPri</t>
+          <t>OKVED_84_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_84_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>OKVED_93_VSvyaziSOplTrudRab</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>OKVED_93_ProcPoDolgObyaz</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>OKVED_93_NalogNaPri</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>OKVED_96_ProcPoDolgObyaz</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>OKVED_96_NalogNaPri</t>
+          <t>OKVED_Q_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_Q_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdAkcOrgDolUch</t>
+          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>OKVED_01_DivProcDolgFinVlozh</t>
+          <t>OKVED_R_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>OKVED_B_OtProdAkcOrgDolUch</t>
+          <t>OKVED_R_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>OKVED_07_OtProdAkcOrgDolUch</t>
+          <t>OKVED_R_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>OKVED_C_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>OKVED_10_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_93_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdFinVlozh</t>
+          <t>OKVED_96_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_96_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdFinVlozh</t>
+          <t>OKVED_01_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>OKVED_E_DivProcDolgFinVlozh</t>
+          <t>OKVED_B_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdAkcOrgDolUch</t>
+          <t>OKVED_07_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdFinVlozh</t>
+          <t>OKVED_C_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>OKVED_36_DivProcDolgFinVlozh</t>
+          <t>OKVED_10_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdAkcOrgDolUch</t>
+          <t>OKVED_11_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdFinVlozh</t>
+          <t>OKVED_11_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>OKVED_38_DivProcDolgFinVlozh</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdAkcOrgDolUch</t>
+          <t>OKVED_E_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_E_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdAkcOrgDolUch</t>
+          <t>OKVED_E_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_36_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdAkcOrgDolUch</t>
+          <t>OKVED_36_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdFinVlozh</t>
+          <t>OKVED_36_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>OKVED_G_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>OKVED_46_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>OKVED_47_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>OKVED_H_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdAkcOrgDolUch</t>
+          <t>OKVED_F_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>OKVED_49_DivProcDolgFinVlozh</t>
+          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>OKVED_52_OtProdAkcOrgDolUch</t>
+          <t>OKVED_41_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_43_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdAkcOrgDolUch</t>
+          <t>OKVED_G_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_46_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdAkcOrgDolUch</t>
+          <t>OKVED_47_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_H_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdAkcOrgDolUch</t>
+          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>OKVED_L_OtProdAkcOrgDolUch</t>
+          <t>OKVED_49_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_49_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdAkcOrgDolUch</t>
+          <t>OKVED_52_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdAkcOrgDolUch</t>
+          <t>OKVED_I_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdAkcOrgDolUch</t>
+          <t>OKVED_55_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>OKVED_71_DivProcDolgFinVlozh</t>
+          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdAkcOrgDolUch</t>
+          <t>OKVED_K_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdFinVlozh</t>
+          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdAkcOrgDolUch</t>
+          <t>OKVED_64_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdFinVlozh</t>
+          <t>OKVED_L_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdAkcOrgDolUch</t>
+          <t>OKVED_M_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>OKVED_S_DivProcDolgFinVlozh</t>
+          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_70_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdAkcOrgDolUch</t>
+          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>OKVED_94_DivProcDolgFinVlozh</t>
+          <t>OKVED_71_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>OKVED_01_DolUch</t>
+          <t>OKVED_71_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_N_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>OKVED_B_DolUch</t>
+          <t>OKVED_N_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_77_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>OKVED_C_DolUch</t>
+          <t>OKVED_77_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>OKVED_10_DolUch</t>
+          <t>OKVED_S_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_S_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>OKVED_11_DolUch</t>
+          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>OKVED_11_PrCenBum</t>
+          <t>OKVED_94_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_94_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>OKVED_33_DolUch</t>
+          <t>OKVED_01_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_01_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>OKVED_E_DolUch</t>
+          <t>OKVED_B_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>OKVED_E_PrCenBum</t>
+          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_C_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>OKVED_36_DolUch</t>
+          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>OKVED_36_PrCenBum</t>
+          <t>OKVED_10_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>OKVED_F_DolUch</t>
+          <t>OKVED_11_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_11_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>OKVED_41_DolUch</t>
+          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_33_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>OKVED_42_DolUch</t>
+          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_E_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>OKVED_43_DolUch</t>
+          <t>OKVED_E_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>OKVED_43_PrCenBum</t>
+          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_36_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>OKVED_47_DolUch</t>
+          <t>OKVED_36_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>OKVED_H_DolUch</t>
+          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_F_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>OKVED_49_DolUch</t>
+          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_41_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>OKVED_50_DolUch</t>
+          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>OKVED_50_PrCenBum</t>
+          <t>OKVED_42_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>OKVED_52_DolUch</t>
+          <t>OKVED_43_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_43_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_47_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>OKVED_K_DolUch</t>
+          <t>OKVED_H_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>OKVED_M_DolUch</t>
+          <t>OKVED_49_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>OKVED_71_DolUch</t>
+          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>OKVED_N_DolUch</t>
+          <t>OKVED_50_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>OKVED_N_PrCenBum</t>
+          <t>OKVED_50_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>OKVED_79_DolUch</t>
+          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>OKVED_79_PrCenBum</t>
+          <t>OKVED_52_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>OKVED_S_Modern</t>
+          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>OKVED_S_DolUch</t>
+          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>OKVED_94_Modern</t>
+          <t>OKVED_K_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>OKVED_94_DolUch</t>
+          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_M_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>OKVED_01_PostDeyt1</t>
+          <t>OKVED_71_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>OKVED_01_DrPost</t>
+          <t>OKVED_N_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt</t>
+          <t>OKVED_N_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt1</t>
+          <t>OKVED_79_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt</t>
+          <t>OKVED_79_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt1</t>
+          <t>OKVED_S_Modern</t>
         </is>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>OKVED_C_PostDeyt1</t>
+          <t>OKVED_S_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>OKVED_10_PostDeyt1</t>
+          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>OKVED_32_PlCredit</t>
+          <t>OKVED_94_Modern</t>
         </is>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt</t>
+          <t>OKVED_94_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt1</t>
+          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt</t>
+          <t>OKVED_01_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt1</t>
+          <t>OKVED_01_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>OKVED_33_DrPost</t>
+          <t>OKVED_B_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_B_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_07_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>OKVED_38_PostDeyt1</t>
+          <t>OKVED_07_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>OKVED_38_DrPost</t>
+          <t>OKVED_C_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>OKVED_F_PostDeyt1</t>
+          <t>OKVED_10_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt</t>
+          <t>OKVED_32_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt1</t>
+          <t>OKVED_32_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt</t>
+          <t>OKVED_32_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt1</t>
+          <t>OKVED_33_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>OKVED_42_DrPost</t>
+          <t>OKVED_33_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>OKVED_43_PostDeyt1</t>
+          <t>OKVED_33_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>OKVED_43_DrPost</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt1</t>
+          <t>OKVED_38_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt</t>
+          <t>OKVED_38_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt1</t>
+          <t>OKVED_F_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt</t>
+          <t>OKVED_41_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt1</t>
+          <t>OKVED_41_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>OKVED_H_PostDeyt1</t>
+          <t>OKVED_42_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt</t>
+          <t>OKVED_42_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt1</t>
+          <t>OKVED_42_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>OKVED_50_DrPost</t>
+          <t>OKVED_43_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt</t>
+          <t>OKVED_43_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt1</t>
+          <t>OKVED_G_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>OKVED_51_DrPost</t>
+          <t>OKVED_G_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>OKVED_52_PostDeyt1</t>
+          <t>OKVED_46_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>OKVED_I_PostDeyt1</t>
+          <t>OKVED_46_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>OKVED_I_DrPost</t>
+          <t>OKVED_47_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>OKVED_55_PostDeyt1</t>
+          <t>OKVED_47_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>OKVED_55_DrPost</t>
+          <t>OKVED_H_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt</t>
+          <t>OKVED_50_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt1</t>
+          <t>OKVED_50_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>OKVED_K_DrPost</t>
+          <t>OKVED_50_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt</t>
+          <t>OKVED_51_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt1</t>
+          <t>OKVED_51_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>OKVED_64_DrPost</t>
+          <t>OKVED_51_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>OKVED_L_PostDeyt1</t>
+          <t>OKVED_52_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>OKVED_68_PostDeyt1</t>
+          <t>OKVED_I_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>OKVED_70_PlCredit</t>
+          <t>OKVED_I_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>OKVED_70_PostDeyt</t>
+          <t>OKVED_55_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>OKVED_71_PostDeyt</t>
+          <t>OKVED_55_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt</t>
+          <t>OKVED_K_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt1</t>
+          <t>OKVED_K_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>OKVED_74_DrPost</t>
+          <t>OKVED_K_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt</t>
+          <t>OKVED_64_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt1</t>
+          <t>OKVED_64_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt</t>
+          <t>OKVED_64_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt1</t>
+          <t>OKVED_L_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>OKVED_79_DrPost</t>
+          <t>OKVED_68_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
         <is>
-          <t>OKVED_81_PlCredit</t>
+          <t>OKVED_70_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt</t>
+          <t>OKVED_70_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt1</t>
+          <t>OKVED_71_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
         <is>
-          <t>OKVED_S_PlCredit</t>
+          <t>OKVED_74_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
         <is>
-          <t>OKVED_S_PostDeyt1</t>
+          <t>OKVED_74_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
         <is>
-          <t>OKVED_94_PlCredit</t>
+          <t>OKVED_74_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
         <is>
-          <t>OKVED_94_PostDeyt1</t>
+          <t>OKVED_N_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin1</t>
+          <t>OKVED_N_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin2</t>
+          <t>OKVED_79_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
         <is>
-          <t>OKVED_B_PlPoFin1</t>
+          <t>OKVED_79_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
         <is>
-          <t>OKVED_07_PlPoFin1</t>
+          <t>OKVED_79_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin</t>
+          <t>OKVED_81_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin1</t>
+          <t>OKVED_81_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin2</t>
+          <t>OKVED_81_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin3</t>
+          <t>OKVED_S_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_S_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_94_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin1</t>
+          <t>OKVED_94_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin2</t>
+          <t>OKVED_01_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin1</t>
+          <t>OKVED_01_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin2</t>
+          <t>OKVED_B_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>OKVED_F_PlPoFin1</t>
+          <t>OKVED_07_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>OKVED_41_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
         <is>
-          <t>OKVED_G_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>OKVED_46_PlPoFin1</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
         <is>
-          <t>OKVED_47_PlPoFin1</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
         <is>
-          <t>OKVED_H_PlPoFin1</t>
+          <t>OKVED_E_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin1</t>
+          <t>OKVED_E_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin2</t>
+          <t>OKVED_38_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoFin1</t>
+          <t>OKVED_38_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
         <is>
-          <t>OKVED_52_PlPoFin1</t>
+          <t>OKVED_F_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin1</t>
+          <t>OKVED_41_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin2</t>
+          <t>OKVED_43_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin1</t>
+          <t>OKVED_43_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin2</t>
+          <t>OKVED_G_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoFin1</t>
+          <t>OKVED_46_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoFin1</t>
+          <t>OKVED_47_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>OKVED_68_PlPoFin1</t>
+          <t>OKVED_H_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>OKVED_M_PlPoFin1</t>
+          <t>OKVED_49_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin</t>
+          <t>OKVED_49_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin1</t>
+          <t>OKVED_50_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin2</t>
+          <t>OKVED_52_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin3</t>
+          <t>OKVED_I_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>OKVED_71_PlPoFin1</t>
+          <t>OKVED_I_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1696">
       <c r="A1696" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin1</t>
+          <t>OKVED_55_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1697">
       <c r="A1697" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin2</t>
+          <t>OKVED_55_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1698">
       <c r="A1698" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin3</t>
+          <t>OKVED_K_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1699">
       <c r="A1699" t="inlineStr">
         <is>
-          <t>OKVED_74_SaldoDenPot</t>
+          <t>OKVED_64_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1700">
       <c r="A1700" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin1</t>
+          <t>OKVED_68_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1701">
       <c r="A1701" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin2</t>
+          <t>OKVED_M_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1702">
       <c r="A1702" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin1</t>
+          <t>OKVED_70_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1703">
       <c r="A1703" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin2</t>
+          <t>OKVED_70_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1704">
       <c r="A1704" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin3</t>
+          <t>OKVED_70_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1705">
       <c r="A1705" t="inlineStr">
         <is>
-          <t>OKVED_81_SaldoDenPot</t>
+          <t>OKVED_70_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1706">
       <c r="A1706" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin1</t>
+          <t>OKVED_71_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1707">
       <c r="A1707" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin2</t>
+          <t>OKVED_74_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1708">
       <c r="A1708" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin3</t>
+          <t>OKVED_74_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1709">
       <c r="A1709" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin1</t>
+          <t>OKVED_74_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1710">
       <c r="A1710" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin2</t>
+          <t>OKVED_74_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1711">
       <c r="A1711" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin3</t>
+          <t>OKVED_79_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1712">
       <c r="A1712" t="inlineStr">
         <is>
-          <t>OKVED_01_Velch</t>
+          <t>OKVED_79_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1713">
       <c r="A1713" t="inlineStr">
         <is>
-          <t>OKVED_11_Velch</t>
+          <t>OKVED_81_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1714">
       <c r="A1714" t="inlineStr">
         <is>
-          <t>OKVED_32_Velch</t>
+          <t>OKVED_81_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1715">
       <c r="A1715" t="inlineStr">
         <is>
-          <t>OKVED_33_Velch</t>
+          <t>OKVED_81_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1716">
       <c r="A1716" t="inlineStr">
         <is>
-          <t>OKVED_E_Velch</t>
+          <t>OKVED_81_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1717">
       <c r="A1717" t="inlineStr">
         <is>
-          <t>OKVED_38_Velch</t>
+          <t>OKVED_S_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1718">
       <c r="A1718" t="inlineStr">
         <is>
-          <t>OKVED_F_Velch</t>
+          <t>OKVED_S_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1719">
       <c r="A1719" t="inlineStr">
         <is>
-          <t>OKVED_41_Velch</t>
+          <t>OKVED_S_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1720">
       <c r="A1720" t="inlineStr">
         <is>
-          <t>OKVED_42_Velch</t>
+          <t>OKVED_94_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1721">
       <c r="A1721" t="inlineStr">
         <is>
-          <t>OKVED_43_Velch</t>
+          <t>OKVED_94_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1722">
       <c r="A1722" t="inlineStr">
         <is>
-          <t>OKVED_47_Velch</t>
+          <t>OKVED_94_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1723">
       <c r="A1723" t="inlineStr">
         <is>
-          <t>OKVED_49_Velch</t>
+          <t>OKVED_01_Velch</t>
         </is>
       </c>
     </row>
     <row r="1724">
       <c r="A1724" t="inlineStr">
         <is>
-          <t>OKVED_I_Velch</t>
+          <t>OKVED_11_Velch</t>
         </is>
       </c>
     </row>
     <row r="1725">
       <c r="A1725" t="inlineStr">
         <is>
-          <t>OKVED_56_Velch</t>
+          <t>OKVED_32_Velch</t>
         </is>
       </c>
     </row>
     <row r="1726">
       <c r="A1726" t="inlineStr">
         <is>
-          <t>OKVED_J_Velch</t>
+          <t>OKVED_33_Velch</t>
         </is>
       </c>
     </row>
     <row r="1727">
       <c r="A1727" t="inlineStr">
         <is>
-          <t>OKVED_63_Velch</t>
+          <t>OKVED_E_Velch</t>
         </is>
       </c>
     </row>
     <row r="1728">
       <c r="A1728" t="inlineStr">
         <is>
-          <t>OKVED_L_Velch</t>
+          <t>OKVED_38_Velch</t>
         </is>
       </c>
     </row>
     <row r="1729">
       <c r="A1729" t="inlineStr">
         <is>
-          <t>OKVED_68_Velch</t>
+          <t>OKVED_F_Velch</t>
         </is>
       </c>
     </row>
     <row r="1730">
       <c r="A1730" t="inlineStr">
         <is>
-          <t>OKVED_M_Velch</t>
+          <t>OKVED_41_Velch</t>
         </is>
       </c>
     </row>
     <row r="1731">
       <c r="A1731" t="inlineStr">
         <is>
-          <t>OKVED_69_Velch</t>
+          <t>OKVED_42_Velch</t>
         </is>
       </c>
     </row>
     <row r="1732">
       <c r="A1732" t="inlineStr">
         <is>
-          <t>OKVED_70_Velch</t>
+          <t>OKVED_43_Velch</t>
         </is>
       </c>
     </row>
     <row r="1733">
       <c r="A1733" t="inlineStr">
         <is>
-          <t>OKVED_71_Velch</t>
+          <t>OKVED_47_Velch</t>
         </is>
       </c>
     </row>
     <row r="1734">
       <c r="A1734" t="inlineStr">
         <is>
-          <t>OKVED_N_Velch</t>
+          <t>OKVED_49_Velch</t>
         </is>
       </c>
     </row>
     <row r="1735">
       <c r="A1735" t="inlineStr">
         <is>
-          <t>OKVED_77_Velch</t>
+          <t>OKVED_I_Velch</t>
         </is>
       </c>
     </row>
     <row r="1736">
       <c r="A1736" t="inlineStr">
         <is>
-          <t>OKVED_79_Velch</t>
+          <t>OKVED_56_Velch</t>
         </is>
       </c>
     </row>
     <row r="1737">
       <c r="A1737" t="inlineStr">
         <is>
-          <t>OKVED_81_Velch</t>
+          <t>OKVED_J_Velch</t>
         </is>
       </c>
     </row>
     <row r="1738">
       <c r="A1738" t="inlineStr">
         <is>
-          <t>OKVED_82_Velch</t>
+          <t>OKVED_63_Velch</t>
         </is>
       </c>
     </row>
     <row r="1739">
       <c r="A1739" t="inlineStr">
         <is>
-          <t>OKVED_O_Velch</t>
+          <t>OKVED_L_Velch</t>
         </is>
       </c>
     </row>
     <row r="1740">
       <c r="A1740" t="inlineStr">
         <is>
-          <t>OKVED_84_Velch</t>
+          <t>OKVED_68_Velch</t>
         </is>
       </c>
     </row>
     <row r="1741">
       <c r="A1741" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_M_Velch</t>
         </is>
       </c>
     </row>
     <row r="1742">
       <c r="A1742" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_69_Velch</t>
         </is>
       </c>
     </row>
     <row r="1743">
       <c r="A1743" t="inlineStr">
         <is>
-          <t>OKVED_88_Velch</t>
+          <t>OKVED_70_Velch</t>
         </is>
       </c>
     </row>
     <row r="1744">
       <c r="A1744" t="inlineStr">
         <is>
-          <t>OKVED_R_Velch</t>
+          <t>OKVED_71_Velch</t>
         </is>
       </c>
     </row>
     <row r="1745">
       <c r="A1745" t="inlineStr">
         <is>
-          <t>OKVED_93_Velch</t>
+          <t>OKVED_N_Velch</t>
         </is>
       </c>
     </row>
     <row r="1746">
       <c r="A1746" t="inlineStr">
         <is>
-          <t>OKVED_S_Velch</t>
+          <t>OKVED_77_Velch</t>
         </is>
       </c>
     </row>
     <row r="1747">
       <c r="A1747" t="inlineStr">
         <is>
-          <t>OKVED_94_Velch</t>
+          <t>OKVED_79_Velch</t>
         </is>
       </c>
     </row>
     <row r="1748">
       <c r="A1748" t="inlineStr">
         <is>
-          <t>OKVED_96_Velch</t>
+          <t>OKVED_81_Velch</t>
         </is>
       </c>
     </row>
     <row r="1749">
       <c r="A1749" t="inlineStr">
         <is>
-          <t>OKVED_43_UstKap</t>
+          <t>OKVED_82_Velch</t>
         </is>
       </c>
     </row>
     <row r="1750">
       <c r="A1750" t="inlineStr">
         <is>
-          <t>OKVED_43_ChiAkt</t>
+          <t>OKVED_O_Velch</t>
         </is>
       </c>
     </row>
     <row r="1751">
       <c r="A1751" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap</t>
+          <t>OKVED_84_Velch</t>
         </is>
       </c>
     </row>
     <row r="1752">
       <c r="A1752" t="inlineStr">
         <is>
-          <t>OKVED_J_SebPro</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1753">
       <c r="A1753" t="inlineStr">
         <is>
-          <t>OKVED_J_Pri(ubOtPro</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1754">
       <c r="A1754" t="inlineStr">
         <is>
-          <t>OKVED_J_ChiPri(ubOtcPer</t>
+          <t>OKVED_88_Velch</t>
         </is>
       </c>
     </row>
     <row r="1755">
       <c r="A1755" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_R_Velch</t>
         </is>
       </c>
     </row>
     <row r="1756">
       <c r="A1756" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap</t>
+          <t>OKVED_93_Velch</t>
         </is>
       </c>
     </row>
     <row r="1757">
       <c r="A1757" t="inlineStr">
         <is>
-          <t>OKVED_63_SebPro</t>
+          <t>OKVED_S_Velch</t>
         </is>
       </c>
     </row>
     <row r="1758">
       <c r="A1758" t="inlineStr">
         <is>
-          <t>OKVED_63_Pri(ubOtPro</t>
+          <t>OKVED_94_Velch</t>
         </is>
       </c>
     </row>
     <row r="1759">
       <c r="A1759" t="inlineStr">
         <is>
-          <t>OKVED_63_ChiPri(ubOtcPer</t>
+          <t>OKVED_96_Velch</t>
         </is>
       </c>
     </row>
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_43_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1761">
       <c r="A1761" t="inlineStr">
         <is>
-          <t>OKVED_K_SebPro</t>
+          <t>OKVED_43_ChiAkt</t>
         </is>
       </c>
     </row>
     <row r="1762">
       <c r="A1762" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap</t>
+          <t>OKVED_J_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1763">
       <c r="A1763" t="inlineStr">
         <is>
-          <t>OKVED_69_ChiAkt</t>
+          <t>OKVED_J_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1764">
       <c r="A1764" t="inlineStr">
         <is>
-          <t>OKVED_69_SebPro</t>
+          <t>OKVED_J_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1765">
       <c r="A1765" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap</t>
+          <t>OKVED_J_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1766">
       <c r="A1766" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap</t>
+          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1767">
       <c r="A1767" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap</t>
+          <t>OKVED_63_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1768">
       <c r="A1768" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap</t>
+          <t>OKVED_63_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1769">
       <c r="A1769" t="inlineStr">
         <is>
-          <t>OKVED_Q_SebPro</t>
+          <t>OKVED_63_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1770">
       <c r="A1770" t="inlineStr">
         <is>
-          <t>OKVED_Q_Pri(ubOtPro</t>
+          <t>OKVED_63_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1771">
       <c r="A1771" t="inlineStr">
         <is>
-          <t>OKVED_Q_ChiPri(ubOtcPer</t>
+          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1772">
       <c r="A1772" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_K_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1773">
       <c r="A1773" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap</t>
+          <t>OKVED_69_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1774">
       <c r="A1774" t="inlineStr">
         <is>
-          <t>OKVED_88_SebPro</t>
+          <t>OKVED_69_ChiAkt</t>
         </is>
       </c>
     </row>
     <row r="1775">
       <c r="A1775" t="inlineStr">
         <is>
-          <t>OKVED_88_Pri(ubOtPro</t>
+          <t>OKVED_69_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1776">
       <c r="A1776" t="inlineStr">
         <is>
-          <t>OKVED_88_ChiPri(ubOtcPer</t>
+          <t>OKVED_O_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1777">
       <c r="A1777" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-DoNalKChiAktV%</t>
+          <t>OKVED_84_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1778">
       <c r="A1778" t="inlineStr">
         <is>
-          <t>OKVED_R_SebPro</t>
+          <t>OKVED_85_UstKap</t>
         </is>
       </c>
     </row>
     <row r="1779">
       <c r="A1779" t="inlineStr">
+        <is>
+          <t>OKVED_Q_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="inlineStr">
+        <is>
+          <t>OKVED_Q_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="inlineStr">
+        <is>
+          <t>OKVED_Q_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="inlineStr">
+        <is>
+          <t>OKVED_Q_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="inlineStr">
+        <is>
+          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="inlineStr">
+        <is>
+          <t>OKVED_88_UstKap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="inlineStr">
+        <is>
+          <t>OKVED_88_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="inlineStr">
+        <is>
+          <t>OKVED_88_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="inlineStr">
+        <is>
+          <t>OKVED_88_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="inlineStr">
+        <is>
+          <t>OKVED_88_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="inlineStr">
+        <is>
+          <t>OKVED_R_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="inlineStr">
         <is>
           <t>OKVED_93_SebPro</t>
         </is>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1878"/>
+  <dimension ref="A1:A1880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7916,2345 +7916,2345 @@
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas_1</t>
+          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerVyr_1</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas_1</t>
+          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerKomIUprRas_1</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>MO_30832_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas_1</t>
+          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas_1</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>MO_30851_OtcGoPro_1</t>
+          <t>MO_30510_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas_1</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>MO_30501_OtcGoOtlNalNaPri_1</t>
+          <t>MO_30832_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas_1</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>MO_30501_OtcGoPro_1</t>
+          <t>MO_30851_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>MO_30510_OtcGoSalProDohIRas_1</t>
+          <t>MO_30501_OtcGoOtlNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>MO_30510_OtcGoTekNalNaPri_1</t>
+          <t>MO_30501_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>MO_30510_OtcGoOtlNalNaPri_1</t>
+          <t>MO_30510_OtcGoSalProDohIRas_1</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>MO_30510_OtcGoPro_1</t>
+          <t>MO_30510_OtcGoTekNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>MO_30604_OtcGoPri(ubDoNal_1</t>
+          <t>MO_30510_OtcGoOtlNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>MO_30604_OtcGoTekNalNaPri_1</t>
+          <t>MO_30510_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>MO_30604_OtcGoOtlNalNaPri_1</t>
+          <t>MO_30604_OtcGoPri(ubDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>MO_30604_OtcGoPro_1</t>
+          <t>MO_30604_OtcGoTekNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>MO_30832_OtcGoTekNalNaPri_1</t>
+          <t>MO_30604_OtcGoOtlNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>MO_30832_OtcGoPro_1</t>
+          <t>MO_30604_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>OKVED_11_OrgPolUbyKolOrgEdi</t>
+          <t>MO_30832_OtcGoTekNalNaPri_1</t>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>OKVED_11_OrgPolUbyV%KObsKol</t>
+          <t>MO_30832_OtcGoPro_1</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>OKVED_11_OrgPolUbyUby</t>
+          <t>OKVED_11_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>OKVED_32_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_11_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>OKVED_32_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_11_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>OKVED_32_OrgPolUbyUby</t>
+          <t>OKVED_32_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>OKVED_42_OrgPolPriKolOrgEdi</t>
+          <t>OKVED_32_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>OKVED_42_OrgPolPriV%KObsKol</t>
+          <t>OKVED_32_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>OKVED_42_OrgPolPriPriDoNal</t>
+          <t>OKVED_42_OrgPolPriKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>OKVED_43_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_42_OrgPolPriV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>OKVED_43_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_42_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>OKVED_43_OrgPolUbyUby</t>
+          <t>OKVED_43_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>OKVED_49_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_43_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>OKVED_49_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_43_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>OKVED_49_OrgPolUbyUby</t>
+          <t>OKVED_49_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>OKVED_50_OrgPolPriKolOrgEdi</t>
+          <t>OKVED_49_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>OKVED_50_OrgPolPriV%KObsKol</t>
+          <t>OKVED_49_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>OKVED_50_OrgPolPriPriDoNal</t>
+          <t>OKVED_50_OrgPolPriKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>OKVED_51_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_50_OrgPolPriV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>OKVED_51_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_50_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>OKVED_51_OrgPolUbyUby</t>
+          <t>OKVED_51_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>OKVED_56_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_51_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>OKVED_56_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_51_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>OKVED_56_OrgPolUbyUby</t>
+          <t>OKVED_56_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-DoNal</t>
+          <t>OKVED_56_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>OKVED_J_OrgPolPriPriDoNal</t>
+          <t>OKVED_56_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>OKVED_J_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_J_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>OKVED_J_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_J_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>OKVED_J_OrgPolUbyUby</t>
+          <t>OKVED_J_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-DoNal</t>
+          <t>OKVED_J_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>OKVED_63_OrgPolPriPriDoNal</t>
+          <t>OKVED_J_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>OKVED_63_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_63_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>OKVED_63_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_63_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>OKVED_63_OrgPolUbyUby</t>
+          <t>OKVED_63_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>OKVED_69_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_63_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>OKVED_69_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_63_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>OKVED_69_OrgPolUbyUby</t>
+          <t>OKVED_69_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>OKVED_74_OrgPolPriKolOrgEdi</t>
+          <t>OKVED_69_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>OKVED_74_OrgPolPriV%KObsKol</t>
+          <t>OKVED_69_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>OKVED_74_OrgPolPriPriDoNal</t>
+          <t>OKVED_74_OrgPolPriKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>OKVED_79_OrgPolPriKolOrgEdi</t>
+          <t>OKVED_74_OrgPolPriV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>OKVED_79_OrgPolPriV%KObsKol</t>
+          <t>OKVED_74_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>OKVED_79_OrgPolPriPriDoNal</t>
+          <t>OKVED_79_OrgPolPriKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>OKVED_81_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_79_OrgPolPriV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>OKVED_81_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_79_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>OKVED_81_OrgPolUbyUby</t>
+          <t>OKVED_81_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>OKVED_82_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_81_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>OKVED_82_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_81_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>OKVED_82_OrgPolUbyUby</t>
+          <t>OKVED_82_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>OKVED_O_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_82_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>OKVED_O_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_82_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>OKVED_O_OrgPolUbyUby</t>
+          <t>OKVED_O_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>OKVED_84_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_O_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>OKVED_84_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_O_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>OKVED_84_OrgPolUbyUby</t>
+          <t>OKVED_84_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_84_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_84_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyUby</t>
+          <t>OKVED_85_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_85_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_85_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>OKVED_85_OrgPolUbyUby</t>
+          <t>OKVED_85_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-DoNal</t>
+          <t>OKVED_85_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>OKVED_Q_OrgPolPriPriDoNal</t>
+          <t>OKVED_85_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>OKVED_Q_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_Q_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>OKVED_Q_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_Q_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>OKVED_Q_OrgPolUbyUby</t>
+          <t>OKVED_Q_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-DoNal</t>
+          <t>OKVED_Q_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>OKVED_88_OrgPolPriPriDoNal</t>
+          <t>OKVED_Q_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>OKVED_88_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_88_PriUby(-DoNal</t>
         </is>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>OKVED_88_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_88_OrgPolPriPriDoNal</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>OKVED_88_OrgPolUbyUby</t>
+          <t>OKVED_88_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>OKVED_R_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_88_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>OKVED_R_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_88_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>OKVED_R_OrgPolUbyUby</t>
+          <t>OKVED_R_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>OKVED_93_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_R_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>OKVED_93_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_R_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>OKVED_93_OrgPolUbyUby</t>
+          <t>OKVED_93_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>OKVED_94_OrgPolUbyKolOrgEdi</t>
+          <t>OKVED_93_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>OKVED_94_OrgPolUbyV%KObsKol</t>
+          <t>OKVED_93_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>OKVED_94_OrgPolUbyUby</t>
+          <t>OKVED_94_OrgPolUbyKolOrgEdi</t>
         </is>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>OKVED_01_TeRosPriV%</t>
+          <t>OKVED_94_OrgPolUbyV%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>OKVED_10_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_94_OrgPolUbyUby</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>OKVED_10_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_01_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>OKVED_11_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_10_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>OKVED_11_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_10_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>OKVED_11_TeRosUbyV%</t>
+          <t>OKVED_11_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>OKVED_32_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_11_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>OKVED_32_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_11_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>OKVED_32_TeRosUbyV%</t>
+          <t>OKVED_32_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>OKVED_38_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_32_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>OKVED_38_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_32_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>OKVED_F_TeRosPriV%</t>
+          <t>OKVED_38_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>OKVED_41_TeRosPriV%</t>
+          <t>OKVED_38_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>OKVED_41_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_F_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>OKVED_41_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_41_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>OKVED_42_TeRosPriV%</t>
+          <t>OKVED_41_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>OKVED_42_TeRosSumPriV%</t>
+          <t>OKVED_41_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>OKVED_43_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_42_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>OKVED_43_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_42_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>OKVED_43_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_43_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>OKVED_43_SumPriZaSooPerPreGo</t>
+          <t>OKVED_43_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>OKVED_43_TeRosUbyV%</t>
+          <t>OKVED_43_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>OKVED_49_TeRosUbyV%</t>
+          <t>OKVED_43_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>OKVED_50_TeRosPriV%</t>
+          <t>OKVED_43_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>OKVED_50_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_49_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>OKVED_50_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_50_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>OKVED_50_TeRosSumPriV%</t>
+          <t>OKVED_50_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>OKVED_51_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_50_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>OKVED_51_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_50_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>OKVED_51_TeRosUbyV%</t>
+          <t>OKVED_51_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>OKVED_I_TeRosPriV%</t>
+          <t>OKVED_51_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>OKVED_55_TeRosPriV%</t>
+          <t>OKVED_51_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>OKVED_55_SumPriZaSooPerPreGo</t>
+          <t>OKVED_I_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t>OKVED_56_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_55_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t>OKVED_56_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_55_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t>OKVED_56_TeRosUbyV%</t>
+          <t>OKVED_56_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>OKVED_L_TeRosPriV%</t>
+          <t>OKVED_56_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t>OKVED_68_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_56_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>OKVED_68_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_L_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>OKVED_68_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_68_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>OKVED_68_SumPriZaSooPerPreGo</t>
+          <t>OKVED_68_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t>OKVED_68_TeRosUbyV%</t>
+          <t>OKVED_68_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>OKVED_M_TeRosPriV%</t>
+          <t>OKVED_68_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>OKVED_69_TeRosPriV%</t>
+          <t>OKVED_68_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>OKVED_70_TeRosPriV%</t>
+          <t>OKVED_M_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
-          <t>OKVED_70_SumPriZaSooPerPreGo</t>
+          <t>OKVED_69_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>OKVED_70_TeRosSumPriV%</t>
+          <t>OKVED_70_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>OKVED_71_TeRosPriV%</t>
+          <t>OKVED_70_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t>OKVED_74_TeRosPriV%</t>
+          <t>OKVED_70_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>OKVED_N_TeRosPriV%</t>
+          <t>OKVED_71_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>OKVED_N_SumPriZaSooPerPreGo</t>
+          <t>OKVED_74_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>OKVED_N_TeRosSumPriV%</t>
+          <t>OKVED_N_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>OKVED_77_TeRosPriV%</t>
+          <t>OKVED_N_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>OKVED_77_SumPriZaSooPerPreGo</t>
+          <t>OKVED_N_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>OKVED_77_TeRosUbyV%</t>
+          <t>OKVED_77_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>OKVED_79_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_77_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="inlineStr">
         <is>
-          <t>OKVED_79_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_77_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
         <is>
-          <t>OKVED_79_TeRosUbyV%</t>
+          <t>OKVED_79_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>OKVED_81_TeRosPriV%</t>
+          <t>OKVED_79_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="inlineStr">
         <is>
-          <t>OKVED_81_SumPriZaSooPerPreGo</t>
+          <t>OKVED_79_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>OKVED_81_TeRosUbyV%</t>
+          <t>OKVED_81_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>OKVED_82_TeRosPriV%</t>
+          <t>OKVED_81_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>OKVED_82_SumPriZaSooPerPreGo</t>
+          <t>OKVED_81_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>OKVED_82_TeRosUbyV%</t>
+          <t>OKVED_82_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>OKVED_O_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_82_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>OKVED_O_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_82_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>OKVED_O_TeRosUbyV%</t>
+          <t>OKVED_O_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>OKVED_84_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_O_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>OKVED_84_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_O_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>OKVED_84_TeRosUbyV%</t>
+          <t>OKVED_84_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_84_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosPriV%</t>
+          <t>OKVED_84_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_85_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>OKVED_85_SumPriZaSooPerPreGo</t>
+          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosUbyV%</t>
+          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosSumPriV%</t>
+          <t>OKVED_85_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_85_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosPriV%</t>
+          <t>OKVED_85_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_85_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_85_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>OKVED_85_SumPriZaSooPerPreGo</t>
+          <t>OKVED_85_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosUbyV%</t>
+          <t>OKVED_85_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>OKVED_85_TeRosSumPriV%</t>
+          <t>OKVED_85_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>OKVED_93_TeRosUbyV%</t>
+          <t>OKVED_85_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>OKVED_S_TeRosPriV%</t>
+          <t>OKVED_85_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="inlineStr">
         <is>
-          <t>OKVED_94_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_93_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosPriV%</t>
+          <t>OKVED_S_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>OKVED_94_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_94_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>OKVED_94_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_94_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>OKVED_94_SumPriZaSooPerPreGo</t>
+          <t>OKVED_94_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosUbyV%</t>
+          <t>OKVED_94_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
         <is>
-          <t>OKVED_94_TeRosSumPriV%</t>
+          <t>OKVED_94_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>OKVED_96_PriUby(-DoNalZaAnaPerPreGo</t>
+          <t>OKVED_94_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosPriV%</t>
+          <t>OKVED_94_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>OKVED_96_SumUbyZaSooPerPreGo</t>
+          <t>OKVED_96_PriUby(-DoNalZaAnaPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>OKVED_96_KolOrgPolUbyZaPreGo(ed</t>
+          <t>OKVED_96_TeRosPriV%</t>
         </is>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>OKVED_96_SumPriZaSooPerPreGo</t>
+          <t>OKVED_96_SumUbyZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosUbyV%</t>
+          <t>OKVED_96_KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>OKVED_96_TeRosSumPriV%</t>
+          <t>OKVED_96_SumPriZaSooPerPreGo</t>
         </is>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>MO_30851_OrgPolUbyKolOrgEdi_1</t>
+          <t>OKVED_96_TeRosUbyV%</t>
         </is>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>MO_30851_OrgPolUbyV%KObsKol_1</t>
+          <t>OKVED_96_TeRosSumPriV%</t>
         </is>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>MO_30851_OrgPolUbyUby_1</t>
+          <t>MO_30851_OrgPolUbyKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>MO_30501_OrgPolPriKolOrgEdi_1</t>
+          <t>MO_30851_OrgPolUbyV%KObsKol_1</t>
         </is>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>MO_30501_OrgPolPriV%KObsKol_1</t>
+          <t>MO_30851_OrgPolUbyUby_1</t>
         </is>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>MO_30501_OrgPolPriPriDoNal_1</t>
+          <t>MO_30501_OrgPolPriKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>MO_30510_OrgPolPriPriDoNal_1</t>
+          <t>MO_30501_OrgPolPriV%KObsKol_1</t>
         </is>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>MO_30604_PriUby(-DoNal_1</t>
+          <t>MO_30501_OrgPolPriPriDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolPriPriDoNal_1</t>
+          <t>MO_30510_OrgPolPriPriDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolUbyKolOrgEdi_1</t>
+          <t>MO_30604_PriUby(-DoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolUbyV%KObsKol_1</t>
+          <t>MO_30604_OrgPolPriPriDoNal_1</t>
         </is>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>MO_30604_OrgPolUbyUby_1</t>
+          <t>MO_30604_OrgPolUbyKolOrgEdi_1</t>
         </is>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>MO_30851_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30604_OrgPolUbyV%KObsKol_1</t>
         </is>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>MO_30851_KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>MO_30604_OrgPolUbyUby_1</t>
         </is>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>MO_30851_TeRosUbyV%_1</t>
+          <t>MO_30851_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>MO_30501_TeRosPriV%_1</t>
+          <t>MO_30851_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>MO_30501_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30851_TeRosUbyV%_1</t>
         </is>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>MO_30501_KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>MO_30501_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>MO_30501_TeRosSumPriV%_1</t>
+          <t>MO_30501_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>MO_30510_TeRosPriV%_1</t>
+          <t>MO_30501_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>MO_30510_SumPriZaSooPerPreGo_1</t>
+          <t>MO_30501_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>MO_30510_TeRosSumPriV%_1</t>
+          <t>MO_30510_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>MO_30604_PriUby(-DoNalZaAnaPerPreGo_1</t>
+          <t>MO_30510_SumPriZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosPriV%_1</t>
+          <t>MO_30510_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>MO_30604_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30604_PriUby(-DoNalZaAnaPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>MO_30604_KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>MO_30604_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>MO_30604_SumPriZaSooPerPreGo_1</t>
+          <t>MO_30604_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosUbyV%_1</t>
+          <t>MO_30604_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>MO_30604_TeRosSumPriV%_1</t>
+          <t>MO_30604_SumPriZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>MO_30616_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30604_TeRosUbyV%_1</t>
         </is>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>MO_30616_KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>MO_30604_TeRosSumPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>MO_30619_SumUbyZaSooPerPreGo_1</t>
+          <t>MO_30616_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>MO_30619_KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>MO_30616_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>MO_30832_TeRosPriV%_1</t>
+          <t>MO_30619_SumUbyZaSooPerPreGo_1</t>
         </is>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>OPF_20200_OrgPolUbyKolOrgEdi_2</t>
+          <t>MO_30619_KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>OPF_20200_OrgPolUbyV%KObsKol_2</t>
+          <t>MO_30832_TeRosPriV%_1</t>
         </is>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>OPF_20200_OrgPolUbyUby_2</t>
+          <t>OPF_20200_OrgPolUbyKolOrgEdi_2</t>
         </is>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>OPF_20600_OrgPolUbyKolOrgEdi_2</t>
+          <t>OPF_20200_OrgPolUbyV%KObsKol_2</t>
         </is>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>OPF_20600_OrgPolUbyV%KObsKol_2</t>
+          <t>OPF_20200_OrgPolUbyUby_2</t>
         </is>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>OPF_20600_OrgPolUbyUby_2</t>
+          <t>OPF_20600_OrgPolUbyKolOrgEdi_2</t>
         </is>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>OPF_71400_OrgPolUbyKolOrgEdi_2</t>
+          <t>OPF_20600_OrgPolUbyV%KObsKol_2</t>
         </is>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>OPF_71400_OrgPolUbyV%KObsKol_2</t>
+          <t>OPF_20600_OrgPolUbyUby_2</t>
         </is>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>OPF_71400_OrgPolUbyUby_2</t>
+          <t>OPF_71400_OrgPolUbyKolOrgEdi_2</t>
         </is>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>OPF_75500_OrgPolUbyKolOrgEdi_2</t>
+          <t>OPF_71400_OrgPolUbyV%KObsKol_2</t>
         </is>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>OPF_75500_OrgPolUbyV%KObsKol_2</t>
+          <t>OPF_71400_OrgPolUbyUby_2</t>
         </is>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>OPF_75500_OrgPolUbyUby_2</t>
+          <t>OPF_75500_OrgPolUbyKolOrgEdi_2</t>
         </is>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>OPF_14000_TeRosPriV%_2</t>
+          <t>OPF_75500_OrgPolUbyV%KObsKol_2</t>
         </is>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>OPF_14100_TeRosPriV%_2</t>
+          <t>OPF_75500_OrgPolUbyUby_2</t>
         </is>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>OPF_20200_TeRosUbyV%_2</t>
+          <t>OPF_14000_TeRosPriV%_2</t>
         </is>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>OPF_20600_SumUbyZaSooPerPreGo_2</t>
+          <t>OPF_14100_TeRosPriV%_2</t>
         </is>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>OPF_20600_KolOrgPolUbyZaPreGo(ed_2</t>
+          <t>OPF_20200_TeRosUbyV%_2</t>
         </is>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>OPF_20600_TeRosUbyV%_2</t>
+          <t>OPF_20600_SumUbyZaSooPerPreGo_2</t>
         </is>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>OPF_21200_TeRosPriV%_2</t>
+          <t>OPF_20600_KolOrgPolUbyZaPreGo(ed_2</t>
         </is>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>OPF_70000_SumUbyZaSooPerPreGo_2</t>
+          <t>OPF_20600_TeRosUbyV%_2</t>
         </is>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>OPF_70000_KolOrgPolUbyZaPreGo(ed_2</t>
+          <t>OPF_21200_TeRosPriV%_2</t>
         </is>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>OPF_70400_SumUbyZaSooPerPreGo_2</t>
+          <t>OPF_70000_SumUbyZaSooPerPreGo_2</t>
         </is>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>OPF_70400_KolOrgPolUbyZaPreGo(ed_2</t>
+          <t>OPF_70000_KolOrgPolUbyZaPreGo(ed_2</t>
         </is>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>OPF_71400_SumUbyZaSooPerPreGo_2</t>
+          <t>OPF_70400_SumUbyZaSooPerPreGo_2</t>
         </is>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>OPF_71400_KolOrgPolUbyZaPreGo(ed_2</t>
+          <t>OPF_70400_KolOrgPolUbyZaPreGo(ed_2</t>
         </is>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>OPF_71400_TeRosUbyV%_2</t>
+          <t>OPF_71400_SumUbyZaSooPerPreGo_2</t>
         </is>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>OPF_75500_SumUbyZaSooPerPreGo_2</t>
+          <t>OPF_71400_KolOrgPolUbyZaPreGo(ed_2</t>
         </is>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>OPF_75500_KolOrgPolUbyZaPreGo(ed_2</t>
+          <t>OPF_71400_TeRosUbyV%_2</t>
         </is>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>OPF_75500_TeRosUbyV%_2</t>
+          <t>OPF_75500_SumUbyZaSooPerPreGo_2</t>
         </is>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>FS_12_OrgPolPriKolOrgEdi_3</t>
+          <t>OPF_75500_KolOrgPolUbyZaPreGo(ed_2</t>
         </is>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>FS_12_OrgPolPriV%KObsKol_3</t>
+          <t>OPF_75500_TeRosUbyV%_2</t>
         </is>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>FS_12_OrgPolPriPriDoNal_3</t>
+          <t>FS_12_OrgPolPriKolOrgEdi_3</t>
         </is>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>FS_15_OrgPolUbyKolOrgEdi_3</t>
+          <t>FS_12_OrgPolPriV%KObsKol_3</t>
         </is>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>FS_15_OrgPolUbyV%KObsKol_3</t>
+          <t>FS_12_OrgPolPriPriDoNal_3</t>
         </is>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>FS_15_OrgPolUbyUby_3</t>
+          <t>FS_15_OrgPolUbyKolOrgEdi_3</t>
         </is>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>FS_12_TeRosPriV%_3</t>
+          <t>FS_15_OrgPolUbyV%KObsKol_3</t>
         </is>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>FS_12_SumPriZaSooPerPreGo_3</t>
+          <t>FS_15_OrgPolUbyUby_3</t>
         </is>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>FS_12_TeRosSumPriV%_3</t>
+          <t>FS_12_TeRosPriV%_3</t>
         </is>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>FS_15_TeRosUbyV%_3</t>
+          <t>FS_12_SumPriZaSooPerPreGo_3</t>
         </is>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>FS_17_SumUbyZaSooPerPreGo_3</t>
+          <t>FS_12_TeRosSumPriV%_3</t>
         </is>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>FS_17_KolOrgPolUbyZaPreGo(ed_3</t>
+          <t>FS_15_TeRosUbyV%_3</t>
         </is>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>OKVED_56_VToChiKomIUprRas</t>
+          <t>FS_17_SumUbyZaSooPerPreGo_3</t>
         </is>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>OKVED_J_PriUby(-OtPro</t>
+          <t>FS_17_KolOrgPolUbyZaPreGo(ed_3</t>
         </is>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>OKVED_J_SebProSUchKomIUprRas</t>
+          <t>OKVED_56_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>OKVED_J_VToChiKomIUprRas</t>
+          <t>OKVED_J_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>OKVED_J_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%KKomIUprRas</t>
+          <t>OKVED_J_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%KVyr</t>
+          <t>OKVED_J_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>OKVED_J_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>OKVED_J_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>OKVED_63_PriUby(-OtPro</t>
+          <t>OKVED_J_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>OKVED_63_SebProSUchKomIUprRas</t>
+          <t>OKVED_J_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>OKVED_63_VToChiKomIUprRas</t>
+          <t>OKVED_63_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>OKVED_63_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%KKomIUprRas</t>
+          <t>OKVED_63_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%KVyr</t>
+          <t>OKVED_63_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>OKVED_63_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>OKVED_63_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>OKVED_74_VToChiKomIUprRas</t>
+          <t>OKVED_63_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>OKVED_81_VToChiKomIUprRas</t>
+          <t>OKVED_63_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>OKVED_82_VToChiKomIUprRas</t>
+          <t>OKVED_74_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>OKVED_O_VToChiKomIUprRas</t>
+          <t>OKVED_81_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>OKVED_84_VToChiKomIUprRas</t>
+          <t>OKVED_82_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>OKVED_85_VToChiKomIUprRas</t>
+          <t>OKVED_O_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>OKVED_85_VToChiKomIUprRas</t>
+          <t>OKVED_84_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>OKVED_Q_PriUby(-OtPro</t>
+          <t>OKVED_85_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>OKVED_Q_SebProSUchKomIUprRas</t>
+          <t>OKVED_85_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>OKVED_Q_VToChiKomIUprRas</t>
+          <t>OKVED_Q_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>OKVED_Q_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%KKomIUprRas</t>
+          <t>OKVED_Q_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%KVyr</t>
+          <t>OKVED_Q_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>OKVED_Q_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>OKVED_Q_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>OKVED_88_PriUby(-OtPro</t>
+          <t>OKVED_Q_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>OKVED_88_SebProSUchKomIUprRas</t>
+          <t>OKVED_Q_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>OKVED_88_VToChiKomIUprRas</t>
+          <t>OKVED_88_PriUby(-OtPro</t>
         </is>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>OKVED_88_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%KKomIUprRas</t>
+          <t>OKVED_88_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%KVyr</t>
+          <t>OKVED_88_UroRenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>OKVED_88_UroRenUby(-V%ChiPri(ubKVyr</t>
+          <t>OKVED_88_UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>OKVED_R_SebProSUchKomIUprRas</t>
+          <t>OKVED_88_UroRenUby(-V%KVyr</t>
         </is>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>OKVED_R_VToChiKomIUprRas</t>
+          <t>OKVED_88_UroRenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>OKVED_93_SebProSUchKomIUprRas</t>
+          <t>OKVED_R_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>OKVED_93_VToChiKomIUprRas</t>
+          <t>OKVED_R_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>OKVED_56_OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OKVED_93_SebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>OKVED_O_OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OKVED_93_VToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>OKVED_84_OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OKVED_56_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>OKVED_11_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_O_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>OKVED_32_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_84_OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>OKVED_32_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_11_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>OKVED_43_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_32_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>OKVED_49_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_32_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>OKVED_51_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_43_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>OKVED_56_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_49_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>OKVED_56_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_51_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>OKVED_69_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_56_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>OKVED_69_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_56_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>OKVED_74_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_69_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>OKVED_81_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_69_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>OKVED_81_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_74_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>OKVED_82_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_81_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>OKVED_82_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_81_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>OKVED_O_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_82_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>OKVED_O_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_82_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>OKVED_84_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_O_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>OKVED_84_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_O_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_84_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_84_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
@@ -10275,714 +10275,714 @@
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>OKVED_R_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_85_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>OKVED_R_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_85_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>OKVED_93_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_R_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>OKVED_93_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_R_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>OKVED_94_FinRezUbyOrgV%KItoAktUbyOrg</t>
+          <t>OKVED_93_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>OKVED_96_PriOtFinVloV%KoVsFinVlo</t>
+          <t>OKVED_93_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_94_FinRezUbyOrgV%KItoAktUbyOrg</t>
         </is>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_96_PriOtFinVloV%KoVsFinVlo</t>
         </is>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10DebZad</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10DebZad</t>
         </is>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>OKVED_70_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>OKVED_70_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>OKVED_R_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_70_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>OKVED_R_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_70_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>OKVED_93_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_R_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>OKVED_93_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_R_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>OKVED_94_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_93_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>OKVED_94_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_93_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>OKVED_96_KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>OKVED_94_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>OKVED_96_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>OKVED_94_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
+          <t>OKVED_96_KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsKol</t>
+          <t>OKVED_96_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20DebZad</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZad</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KreZad</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZadKre</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20DenSreIDenEkv</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KreZad</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeTekLikOt&gt;=20DebZad</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeTekLikOt&gt;=20V%KObsZad</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>OKVED_01_ArendPlDeVsego</t>
+          <t>OKVED_69_KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>OKVED_32_ArendPlDeVsego</t>
+          <t>OKVED_69_KoeTekLikOt&gt;=20V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>OKVED_E_ArendPlDeVsego</t>
+          <t>OKVED_01_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>OKVED_36_ArendPlDeVsego</t>
+          <t>OKVED_32_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>OKVED_38_ArendPlDeVsego</t>
+          <t>OKVED_E_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>OKVED_41_ArendPlDeVsego</t>
+          <t>OKVED_36_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>OKVED_43_ArendPlDeVsego</t>
+          <t>OKVED_38_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>OKVED_49_ArendPlDeVsego</t>
+          <t>OKVED_41_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>OKVED_50_ArendPlDeVsego</t>
+          <t>OKVED_43_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>OKVED_I_ArendPlDeVsego</t>
+          <t>OKVED_49_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>OKVED_55_ArendPlDeVsego</t>
+          <t>OKVED_50_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>OKVED_56_ArendPlDeVsego</t>
+          <t>OKVED_I_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>OKVED_J_OtProdDeVsego</t>
+          <t>OKVED_55_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>OKVED_J_ArendPlDeVsego</t>
+          <t>OKVED_56_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>OKVED_63_OtProdDeVsego</t>
+          <t>OKVED_J_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>OKVED_63_ArendPlDeVsego</t>
+          <t>OKVED_J_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>OKVED_K_ArendPlDeVsego</t>
+          <t>OKVED_63_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>OKVED_64_ArendPlDeVsego</t>
+          <t>OKVED_63_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>OKVED_69_ArendPlDeVsego</t>
+          <t>OKVED_K_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>OKVED_79_ArendPlDeVsego</t>
+          <t>OKVED_64_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>OKVED_81_ArendPlDeVsego</t>
+          <t>OKVED_69_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>OKVED_82_ArendPlDeVsego</t>
+          <t>OKVED_79_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>OKVED_O_ArendPlDeVsego</t>
+          <t>OKVED_81_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>OKVED_84_ArendPlDeVsego</t>
+          <t>OKVED_82_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_O_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_84_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>OKVED_Q_OtProdDeVsego</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>OKVED_Q_ArendPlDeVsego</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>OKVED_88_OtProdDeVsego</t>
+          <t>OKVED_Q_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>OKVED_88_ArendPlDeVsego</t>
+          <t>OKVED_Q_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>OKVED_R_OtProdDeVsego</t>
+          <t>OKVED_88_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>OKVED_R_ArendPlDeVsego</t>
+          <t>OKVED_88_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>OKVED_93_OtProdDeVsego</t>
+          <t>OKVED_R_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>OKVED_93_ArendPlDeVsego</t>
+          <t>OKVED_R_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>OKVED_S_ArendPlDeVsego</t>
+          <t>OKVED_93_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>OKVED_94_ArendPlDeVsego</t>
+          <t>OKVED_93_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>OKVED_96_ArendPlDeVsego</t>
+          <t>OKVED_S_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcPoDolgObyaz</t>
+          <t>OKVED_94_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>OKVED_32_ProcPoDolgObyaz</t>
+          <t>OKVED_96_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>OKVED_32_NalogNaPri</t>
+          <t>OKVED_11_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>OKVED_33_NalogNaPri</t>
+          <t>OKVED_32_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcPoDolgObyaz</t>
+          <t>OKVED_32_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>OKVED_38_NalogNaPri</t>
+          <t>OKVED_33_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcPoDolgObyaz</t>
+          <t>OKVED_36_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>OKVED_56_ProcPoDolgObyaz</t>
+          <t>OKVED_38_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>OKVED_56_NalogNaPri</t>
+          <t>OKVED_49_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>OKVED_J_ProcPoDolgObyaz</t>
+          <t>OKVED_56_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>OKVED_J_NalogNaPri</t>
+          <t>OKVED_56_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>OKVED_63_ProcPoDolgObyaz</t>
+          <t>OKVED_J_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>OKVED_63_NalogNaPri</t>
+          <t>OKVED_J_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>OKVED_M_ProcPoDolgObyaz</t>
+          <t>OKVED_63_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>OKVED_69_ProcPoDolgObyaz</t>
+          <t>OKVED_63_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>OKVED_69_NalogNaPri</t>
+          <t>OKVED_M_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>OKVED_70_ProcPoDolgObyaz</t>
+          <t>OKVED_69_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>OKVED_71_ProcPoDolgObyaz</t>
+          <t>OKVED_69_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>OKVED_71_NalogNaPri</t>
+          <t>OKVED_70_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>OKVED_74_ProcPoDolgObyaz</t>
+          <t>OKVED_71_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcPoDolgObyaz</t>
+          <t>OKVED_71_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>OKVED_79_NalogNaPri</t>
+          <t>OKVED_74_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>OKVED_81_NalogNaPri</t>
+          <t>OKVED_77_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>OKVED_82_ProcPoDolgObyaz</t>
+          <t>OKVED_79_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_81_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>OKVED_O_VSvyaziSOplTrudRab</t>
+          <t>OKVED_82_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>OKVED_O_ProcPoDolgObyaz</t>
+          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_O_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>OKVED_84_VSvyaziSOplTrudRab</t>
+          <t>OKVED_O_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>OKVED_84_ProcPoDolgObyaz</t>
+          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_84_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_84_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
@@ -11003,2506 +11003,2506 @@
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>OKVED_Q_ProcPoDolgObyaz</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>OKVED_Q_NalogNaPri</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>OKVED_86_PlatPoTekDeVsego</t>
+          <t>OKVED_Q_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>OKVED_86_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_Q_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>OKVED_86_VSvyaziSOplTrudRab</t>
+          <t>OKVED_86_PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>OKVED_86_ProcPoDolgObyaz</t>
+          <t>OKVED_86_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>OKVED_86_NalogNaPri</t>
+          <t>OKVED_86_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>OKVED_86_SaldoDenPotTekOper</t>
+          <t>OKVED_86_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_86_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>OKVED_R_VSvyaziSOplTrudRab</t>
+          <t>OKVED_86_SaldoDenPotTekOper</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>OKVED_R_ProcPoDolgObyaz</t>
+          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>OKVED_R_NalogNaPri</t>
+          <t>OKVED_R_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_R_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>OKVED_93_VSvyaziSOplTrudRab</t>
+          <t>OKVED_R_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>OKVED_93_ProcPoDolgObyaz</t>
+          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>OKVED_93_NalogNaPri</t>
+          <t>OKVED_93_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>OKVED_96_ProcPoDolgObyaz</t>
+          <t>OKVED_93_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>OKVED_96_NalogNaPri</t>
+          <t>OKVED_93_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_96_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdAkcOrgDolUch</t>
+          <t>OKVED_96_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>OKVED_01_DivProcDolgFinVlozh</t>
+          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>OKVED_B_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>OKVED_07_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>OKVED_C_OtProdAkcOrgDolUch</t>
+          <t>OKVED_B_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>OKVED_10_OtProdAkcOrgDolUch</t>
+          <t>OKVED_07_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_C_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdAkcOrgDolUch</t>
+          <t>OKVED_10_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdFinVlozh</t>
+          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>OKVED_33_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_11_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>OKVED_33_OtProdAkcOrgDolUch</t>
+          <t>OKVED_11_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>OKVED_33_DivProcDolgFinVlozh</t>
+          <t>OKVED_33_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_33_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_33_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdAkcOrgDolUch</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdFinVlozh</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>OKVED_E_DivProcDolgFinVlozh</t>
+          <t>OKVED_E_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdAkcOrgDolUch</t>
+          <t>OKVED_E_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdFinVlozh</t>
+          <t>OKVED_E_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>OKVED_36_DivProcDolgFinVlozh</t>
+          <t>OKVED_36_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_36_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdAkcOrgDolUch</t>
+          <t>OKVED_36_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdFinVlozh</t>
+          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>OKVED_38_DivProcDolgFinVlozh</t>
+          <t>OKVED_38_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_38_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdAkcOrgDolUch</t>
+          <t>OKVED_F_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>OKVED_42_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>OKVED_42_OtProdAkcOrgDolUch</t>
+          <t>OKVED_41_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_42_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdAkcOrgDolUch</t>
+          <t>OKVED_42_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdFinVlozh</t>
+          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>OKVED_G_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>OKVED_46_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>OKVED_47_OtProdAkcOrgDolUch</t>
+          <t>OKVED_G_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>OKVED_H_OtProdAkcOrgDolUch</t>
+          <t>OKVED_46_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_47_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdAkcOrgDolUch</t>
+          <t>OKVED_H_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>OKVED_49_DivProcDolgFinVlozh</t>
+          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>OKVED_51_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_49_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>OKVED_51_OtProdAkcOrgDolUch</t>
+          <t>OKVED_49_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>OKVED_52_OtProdAkcOrgDolUch</t>
+          <t>OKVED_51_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_51_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdAkcOrgDolUch</t>
+          <t>OKVED_52_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdAkcOrgDolUch</t>
+          <t>OKVED_I_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdAkcOrgDolUch</t>
+          <t>OKVED_55_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdAkcOrgDolUch</t>
+          <t>OKVED_K_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>OKVED_L_OtProdAkcOrgDolUch</t>
+          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>OKVED_68_OtProdAkcOrgDolUch</t>
+          <t>OKVED_64_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_L_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdAkcOrgDolUch</t>
+          <t>OKVED_68_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdAkcOrgDolUch</t>
+          <t>OKVED_M_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdAkcOrgDolUch</t>
+          <t>OKVED_70_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>OKVED_71_DivProcDolgFinVlozh</t>
+          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdAkcOrgDolUch</t>
+          <t>OKVED_71_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdFinVlozh</t>
+          <t>OKVED_71_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdAkcOrgDolUch</t>
+          <t>OKVED_N_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdFinVlozh</t>
+          <t>OKVED_N_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>OKVED_79_OtProdAkcOrgDolUch</t>
+          <t>OKVED_77_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>OKVED_79_OtProdFinVlozh</t>
+          <t>OKVED_77_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>OKVED_79_DivProcDolgFinVlozh</t>
+          <t>OKVED_79_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_79_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdAkcOrgDolUch</t>
+          <t>OKVED_79_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>OKVED_S_DivProcDolgFinVlozh</t>
+          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_S_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdAkcOrgDolUch</t>
+          <t>OKVED_S_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>OKVED_94_DivProcDolgFinVlozh</t>
+          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>OKVED_01_DolUch</t>
+          <t>OKVED_94_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_94_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>OKVED_B_DolUch</t>
+          <t>OKVED_01_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_01_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>OKVED_07_DolUch</t>
+          <t>OKVED_B_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>OKVED_07_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>OKVED_C_DolUch</t>
+          <t>OKVED_07_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_07_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>OKVED_10_DolUch</t>
+          <t>OKVED_C_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>OKVED_11_DolUch</t>
+          <t>OKVED_10_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>OKVED_11_PrCenBum</t>
+          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_11_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>OKVED_33_DolUch</t>
+          <t>OKVED_11_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>OKVED_E_DolUch</t>
+          <t>OKVED_33_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
         <is>
-          <t>OKVED_E_PrCenBum</t>
+          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_E_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>OKVED_36_DolUch</t>
+          <t>OKVED_E_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>OKVED_36_PrCenBum</t>
+          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_36_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>OKVED_38_DolUch</t>
+          <t>OKVED_36_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>OKVED_38_PrCenBum</t>
+          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>OKVED_38_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_38_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>OKVED_F_DolUch</t>
+          <t>OKVED_38_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_38_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>OKVED_41_DolUch</t>
+          <t>OKVED_F_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>OKVED_42_DolUch</t>
+          <t>OKVED_41_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
         <is>
-          <t>OKVED_43_DolUch</t>
+          <t>OKVED_42_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>OKVED_43_PrCenBum</t>
+          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_43_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>OKVED_46_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_43_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>OKVED_47_DolUch</t>
+          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>OKVED_H_DolUch</t>
+          <t>OKVED_46_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_47_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>OKVED_49_DolUch</t>
+          <t>OKVED_H_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>OKVED_50_DolUch</t>
+          <t>OKVED_49_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>OKVED_50_PrCenBum</t>
+          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
         <is>
-          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_50_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>OKVED_51_DolUch</t>
+          <t>OKVED_50_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>OKVED_51_PrCenBum</t>
+          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>OKVED_51_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_51_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
         <is>
-          <t>OKVED_52_DolUch</t>
+          <t>OKVED_51_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
         <is>
-          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_51_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_52_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
         <is>
-          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
         <is>
-          <t>OKVED_K_DolUch</t>
+          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
         <is>
-          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
         <is>
-          <t>OKVED_64_DolUch</t>
+          <t>OKVED_K_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
         <is>
-          <t>OKVED_64_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
         <is>
-          <t>OKVED_M_DolUch</t>
+          <t>OKVED_64_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
         <is>
-          <t>OKVED_70_DolUch</t>
+          <t>OKVED_64_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
         <is>
-          <t>OKVED_70_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_M_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
         <is>
-          <t>OKVED_71_DolUch</t>
+          <t>OKVED_70_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
         <is>
-          <t>OKVED_N_DolUch</t>
+          <t>OKVED_70_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
         <is>
-          <t>OKVED_N_PrCenBum</t>
+          <t>OKVED_71_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
         <is>
-          <t>OKVED_77_DolUch</t>
+          <t>OKVED_N_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
         <is>
-          <t>OKVED_77_PrCenBum</t>
+          <t>OKVED_N_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_77_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>OKVED_79_DolUch</t>
+          <t>OKVED_77_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
         <is>
-          <t>OKVED_79_PrCenBum</t>
+          <t>OKVED_77_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
         <is>
-          <t>OKVED_S_Modern</t>
+          <t>OKVED_79_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>OKVED_S_DolUch</t>
+          <t>OKVED_79_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_S_Modern</t>
         </is>
       </c>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>OKVED_94_Modern</t>
+          <t>OKVED_S_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>OKVED_94_DolUch</t>
+          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
         <is>
-          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_94_Modern</t>
         </is>
       </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
         <is>
-          <t>OKVED_01_PostDeyt1</t>
+          <t>OKVED_94_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>OKVED_01_DrPost</t>
+          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt</t>
+          <t>OKVED_01_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt1</t>
+          <t>OKVED_01_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt</t>
+          <t>OKVED_B_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt1</t>
+          <t>OKVED_B_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>OKVED_C_PostDeyt1</t>
+          <t>OKVED_07_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
         <is>
-          <t>OKVED_10_PostDeyt1</t>
+          <t>OKVED_07_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>OKVED_32_PlCredit</t>
+          <t>OKVED_C_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt</t>
+          <t>OKVED_10_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt1</t>
+          <t>OKVED_32_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt</t>
+          <t>OKVED_32_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt1</t>
+          <t>OKVED_32_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>OKVED_33_DrPost</t>
+          <t>OKVED_33_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_33_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_33_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>OKVED_E_PostDeyt1</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>OKVED_E_DrPost</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
-          <t>OKVED_38_PostDeyt1</t>
+          <t>OKVED_E_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>OKVED_38_DrPost</t>
+          <t>OKVED_E_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>OKVED_F_PostDeyt1</t>
+          <t>OKVED_38_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1696">
       <c r="A1696" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt</t>
+          <t>OKVED_38_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1697">
       <c r="A1697" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt1</t>
+          <t>OKVED_F_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1698">
       <c r="A1698" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt</t>
+          <t>OKVED_41_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1699">
       <c r="A1699" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt1</t>
+          <t>OKVED_41_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1700">
       <c r="A1700" t="inlineStr">
         <is>
-          <t>OKVED_42_DrPost</t>
+          <t>OKVED_42_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1701">
       <c r="A1701" t="inlineStr">
         <is>
-          <t>OKVED_43_PostDeyt1</t>
+          <t>OKVED_42_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1702">
       <c r="A1702" t="inlineStr">
         <is>
-          <t>OKVED_43_DrPost</t>
+          <t>OKVED_42_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1703">
       <c r="A1703" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt</t>
+          <t>OKVED_43_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1704">
       <c r="A1704" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt1</t>
+          <t>OKVED_43_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1705">
       <c r="A1705" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt</t>
+          <t>OKVED_G_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1706">
       <c r="A1706" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt1</t>
+          <t>OKVED_G_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1707">
       <c r="A1707" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt</t>
+          <t>OKVED_46_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1708">
       <c r="A1708" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt1</t>
+          <t>OKVED_46_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1709">
       <c r="A1709" t="inlineStr">
         <is>
-          <t>OKVED_H_PostDeyt1</t>
+          <t>OKVED_47_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1710">
       <c r="A1710" t="inlineStr">
         <is>
-          <t>OKVED_49_PostDeyt</t>
+          <t>OKVED_47_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1711">
       <c r="A1711" t="inlineStr">
         <is>
-          <t>OKVED_49_PostDeyt1</t>
+          <t>OKVED_H_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1712">
       <c r="A1712" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt</t>
+          <t>OKVED_49_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1713">
       <c r="A1713" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt1</t>
+          <t>OKVED_49_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1714">
       <c r="A1714" t="inlineStr">
         <is>
-          <t>OKVED_50_DrPost</t>
+          <t>OKVED_50_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1715">
       <c r="A1715" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt</t>
+          <t>OKVED_50_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1716">
       <c r="A1716" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt1</t>
+          <t>OKVED_50_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1717">
       <c r="A1717" t="inlineStr">
         <is>
-          <t>OKVED_51_DrPost</t>
+          <t>OKVED_51_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1718">
       <c r="A1718" t="inlineStr">
         <is>
-          <t>OKVED_52_PostDeyt1</t>
+          <t>OKVED_51_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1719">
       <c r="A1719" t="inlineStr">
         <is>
-          <t>OKVED_I_PostDeyt1</t>
+          <t>OKVED_51_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1720">
       <c r="A1720" t="inlineStr">
         <is>
-          <t>OKVED_I_DrPost</t>
+          <t>OKVED_52_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1721">
       <c r="A1721" t="inlineStr">
         <is>
-          <t>OKVED_55_PostDeyt1</t>
+          <t>OKVED_I_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1722">
       <c r="A1722" t="inlineStr">
         <is>
-          <t>OKVED_55_DrPost</t>
+          <t>OKVED_I_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1723">
       <c r="A1723" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt</t>
+          <t>OKVED_55_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1724">
       <c r="A1724" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt1</t>
+          <t>OKVED_55_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1725">
       <c r="A1725" t="inlineStr">
         <is>
-          <t>OKVED_K_DrPost</t>
+          <t>OKVED_K_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1726">
       <c r="A1726" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt</t>
+          <t>OKVED_K_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1727">
       <c r="A1727" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt1</t>
+          <t>OKVED_K_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1728">
       <c r="A1728" t="inlineStr">
         <is>
-          <t>OKVED_64_DrPost</t>
+          <t>OKVED_64_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1729">
       <c r="A1729" t="inlineStr">
         <is>
-          <t>OKVED_L_PostDeyt1</t>
+          <t>OKVED_64_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1730">
       <c r="A1730" t="inlineStr">
         <is>
-          <t>OKVED_68_PostDeyt1</t>
+          <t>OKVED_64_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1731">
       <c r="A1731" t="inlineStr">
         <is>
-          <t>OKVED_M_PostDeyt</t>
+          <t>OKVED_L_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1732">
       <c r="A1732" t="inlineStr">
         <is>
-          <t>OKVED_70_PlCredit</t>
+          <t>OKVED_68_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1733">
       <c r="A1733" t="inlineStr">
         <is>
-          <t>OKVED_70_PostDeyt</t>
+          <t>OKVED_M_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1734">
       <c r="A1734" t="inlineStr">
         <is>
-          <t>OKVED_71_PostDeyt</t>
+          <t>OKVED_70_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1735">
       <c r="A1735" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt</t>
+          <t>OKVED_70_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1736">
       <c r="A1736" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt1</t>
+          <t>OKVED_71_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1737">
       <c r="A1737" t="inlineStr">
         <is>
-          <t>OKVED_74_DrPost</t>
+          <t>OKVED_74_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1738">
       <c r="A1738" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt</t>
+          <t>OKVED_74_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1739">
       <c r="A1739" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt1</t>
+          <t>OKVED_74_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1740">
       <c r="A1740" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt</t>
+          <t>OKVED_N_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1741">
       <c r="A1741" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt1</t>
+          <t>OKVED_N_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1742">
       <c r="A1742" t="inlineStr">
         <is>
-          <t>OKVED_79_DrPost</t>
+          <t>OKVED_79_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1743">
       <c r="A1743" t="inlineStr">
         <is>
-          <t>OKVED_81_PlCredit</t>
+          <t>OKVED_79_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1744">
       <c r="A1744" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt</t>
+          <t>OKVED_79_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1745">
       <c r="A1745" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt1</t>
+          <t>OKVED_81_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1746">
       <c r="A1746" t="inlineStr">
         <is>
-          <t>OKVED_S_PlCredit</t>
+          <t>OKVED_81_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1747">
       <c r="A1747" t="inlineStr">
         <is>
-          <t>OKVED_S_PostDeyt1</t>
+          <t>OKVED_81_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1748">
       <c r="A1748" t="inlineStr">
         <is>
-          <t>OKVED_94_PlCredit</t>
+          <t>OKVED_S_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1749">
       <c r="A1749" t="inlineStr">
         <is>
-          <t>OKVED_94_PostDeyt1</t>
+          <t>OKVED_S_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1750">
       <c r="A1750" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin1</t>
+          <t>OKVED_94_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1751">
       <c r="A1751" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin2</t>
+          <t>OKVED_94_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1752">
       <c r="A1752" t="inlineStr">
         <is>
-          <t>OKVED_B_PlPoFin1</t>
+          <t>OKVED_01_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1753">
       <c r="A1753" t="inlineStr">
         <is>
-          <t>OKVED_07_PlPoFin1</t>
+          <t>OKVED_01_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1754">
       <c r="A1754" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin</t>
+          <t>OKVED_B_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1755">
       <c r="A1755" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin1</t>
+          <t>OKVED_07_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1756">
       <c r="A1756" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin2</t>
+          <t>OKVED_32_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1757">
       <c r="A1757" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin3</t>
+          <t>OKVED_32_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1758">
       <c r="A1758" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin</t>
+          <t>OKVED_32_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1759">
       <c r="A1759" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin1</t>
+          <t>OKVED_32_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1761">
       <c r="A1761" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin3</t>
+          <t>OKVED_33_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1762">
       <c r="A1762" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1763">
       <c r="A1763" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1764">
       <c r="A1764" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin1</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1765">
       <c r="A1765" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin2</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1766">
       <c r="A1766" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin1</t>
+          <t>OKVED_E_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1767">
       <c r="A1767" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin2</t>
+          <t>OKVED_E_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1768">
       <c r="A1768" t="inlineStr">
         <is>
-          <t>OKVED_F_PlPoFin1</t>
+          <t>OKVED_38_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1769">
       <c r="A1769" t="inlineStr">
         <is>
-          <t>OKVED_41_PlPoFin1</t>
+          <t>OKVED_38_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1770">
       <c r="A1770" t="inlineStr">
         <is>
-          <t>OKVED_42_PlPoFin1</t>
+          <t>OKVED_F_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1771">
       <c r="A1771" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin1</t>
+          <t>OKVED_41_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1772">
       <c r="A1772" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin2</t>
+          <t>OKVED_42_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1773">
       <c r="A1773" t="inlineStr">
         <is>
-          <t>OKVED_G_PlPoFin1</t>
+          <t>OKVED_43_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1774">
       <c r="A1774" t="inlineStr">
         <is>
-          <t>OKVED_46_PlPoFin1</t>
+          <t>OKVED_43_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1775">
       <c r="A1775" t="inlineStr">
         <is>
-          <t>OKVED_47_PlPoFin1</t>
+          <t>OKVED_G_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1776">
       <c r="A1776" t="inlineStr">
         <is>
-          <t>OKVED_H_PlPoFin1</t>
+          <t>OKVED_46_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1777">
       <c r="A1777" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin1</t>
+          <t>OKVED_47_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1778">
       <c r="A1778" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin2</t>
+          <t>OKVED_H_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1779">
       <c r="A1779" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoFin1</t>
+          <t>OKVED_49_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1780">
       <c r="A1780" t="inlineStr">
         <is>
-          <t>OKVED_51_PlPoFin1</t>
+          <t>OKVED_49_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1781">
       <c r="A1781" t="inlineStr">
         <is>
-          <t>OKVED_51_PlPoFin2</t>
+          <t>OKVED_50_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1782">
       <c r="A1782" t="inlineStr">
         <is>
-          <t>OKVED_52_PlPoFin1</t>
+          <t>OKVED_51_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1783">
       <c r="A1783" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin1</t>
+          <t>OKVED_51_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1784">
       <c r="A1784" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin2</t>
+          <t>OKVED_52_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1785">
       <c r="A1785" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin1</t>
+          <t>OKVED_I_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1786">
       <c r="A1786" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin2</t>
+          <t>OKVED_I_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1787">
       <c r="A1787" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoFin1</t>
+          <t>OKVED_55_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1788">
       <c r="A1788" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoFin1</t>
+          <t>OKVED_55_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1789">
       <c r="A1789" t="inlineStr">
         <is>
-          <t>OKVED_L_PlPoFin1</t>
+          <t>OKVED_K_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1790">
       <c r="A1790" t="inlineStr">
         <is>
-          <t>OKVED_68_PlPoFin1</t>
+          <t>OKVED_64_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1791">
       <c r="A1791" t="inlineStr">
         <is>
-          <t>OKVED_M_PlPoFin1</t>
+          <t>OKVED_L_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1792">
       <c r="A1792" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin</t>
+          <t>OKVED_68_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1793">
       <c r="A1793" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin1</t>
+          <t>OKVED_M_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1794">
       <c r="A1794" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin2</t>
+          <t>OKVED_70_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1795">
       <c r="A1795" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin3</t>
+          <t>OKVED_70_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1796">
       <c r="A1796" t="inlineStr">
         <is>
-          <t>OKVED_71_PlPoFin1</t>
+          <t>OKVED_70_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1797">
       <c r="A1797" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin1</t>
+          <t>OKVED_70_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1798">
       <c r="A1798" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin2</t>
+          <t>OKVED_71_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1799">
       <c r="A1799" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin3</t>
+          <t>OKVED_74_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1800">
       <c r="A1800" t="inlineStr">
         <is>
-          <t>OKVED_74_SaldoDenPot</t>
+          <t>OKVED_74_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1801">
       <c r="A1801" t="inlineStr">
         <is>
-          <t>OKVED_N_PlPoFin1</t>
+          <t>OKVED_74_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1802">
       <c r="A1802" t="inlineStr">
         <is>
-          <t>OKVED_N_PlPoFin2</t>
+          <t>OKVED_74_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1803">
       <c r="A1803" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin1</t>
+          <t>OKVED_N_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1804">
       <c r="A1804" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin2</t>
+          <t>OKVED_N_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1805">
       <c r="A1805" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin1</t>
+          <t>OKVED_79_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1806">
       <c r="A1806" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin2</t>
+          <t>OKVED_79_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1807">
       <c r="A1807" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin3</t>
+          <t>OKVED_81_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1808">
       <c r="A1808" t="inlineStr">
         <is>
-          <t>OKVED_81_SaldoDenPot</t>
+          <t>OKVED_81_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1809">
       <c r="A1809" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin1</t>
+          <t>OKVED_81_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1810">
       <c r="A1810" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin2</t>
+          <t>OKVED_81_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1811">
       <c r="A1811" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin3</t>
+          <t>OKVED_S_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1812">
       <c r="A1812" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin1</t>
+          <t>OKVED_S_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1813">
       <c r="A1813" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin2</t>
+          <t>OKVED_S_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1814">
       <c r="A1814" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin3</t>
+          <t>OKVED_94_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1815">
       <c r="A1815" t="inlineStr">
         <is>
-          <t>OKVED_01_Velch</t>
+          <t>OKVED_94_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1816">
       <c r="A1816" t="inlineStr">
         <is>
-          <t>OKVED_11_Velch</t>
+          <t>OKVED_94_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1817">
       <c r="A1817" t="inlineStr">
         <is>
-          <t>OKVED_32_Velch</t>
+          <t>OKVED_01_Velch</t>
         </is>
       </c>
     </row>
     <row r="1818">
       <c r="A1818" t="inlineStr">
         <is>
-          <t>OKVED_33_Velch</t>
+          <t>OKVED_11_Velch</t>
         </is>
       </c>
     </row>
     <row r="1819">
       <c r="A1819" t="inlineStr">
         <is>
-          <t>OKVED_E_Velch</t>
+          <t>OKVED_32_Velch</t>
         </is>
       </c>
     </row>
     <row r="1820">
       <c r="A1820" t="inlineStr">
         <is>
-          <t>OKVED_36_Velch</t>
+          <t>OKVED_33_Velch</t>
         </is>
       </c>
     </row>
     <row r="1821">
       <c r="A1821" t="inlineStr">
         <is>
-          <t>OKVED_38_Velch</t>
+          <t>OKVED_E_Velch</t>
         </is>
       </c>
     </row>
     <row r="1822">
       <c r="A1822" t="inlineStr">
         <is>
-          <t>OKVED_F_Velch</t>
+          <t>OKVED_36_Velch</t>
         </is>
       </c>
     </row>
     <row r="1823">
       <c r="A1823" t="inlineStr">
         <is>
-          <t>OKVED_41_Velch</t>
+          <t>OKVED_38_Velch</t>
         </is>
       </c>
     </row>
     <row r="1824">
       <c r="A1824" t="inlineStr">
         <is>
-          <t>OKVED_42_Velch</t>
+          <t>OKVED_F_Velch</t>
         </is>
       </c>
     </row>
     <row r="1825">
       <c r="A1825" t="inlineStr">
         <is>
-          <t>OKVED_43_Velch</t>
+          <t>OKVED_41_Velch</t>
         </is>
       </c>
     </row>
     <row r="1826">
       <c r="A1826" t="inlineStr">
         <is>
-          <t>OKVED_47_Velch</t>
+          <t>OKVED_42_Velch</t>
         </is>
       </c>
     </row>
     <row r="1827">
       <c r="A1827" t="inlineStr">
         <is>
-          <t>OKVED_49_Velch</t>
+          <t>OKVED_43_Velch</t>
         </is>
       </c>
     </row>
     <row r="1828">
       <c r="A1828" t="inlineStr">
         <is>
-          <t>OKVED_I_Velch</t>
+          <t>OKVED_47_Velch</t>
         </is>
       </c>
     </row>
     <row r="1829">
       <c r="A1829" t="inlineStr">
         <is>
-          <t>OKVED_55_Velch</t>
+          <t>OKVED_49_Velch</t>
         </is>
       </c>
     </row>
     <row r="1830">
       <c r="A1830" t="inlineStr">
         <is>
-          <t>OKVED_56_Velch</t>
+          <t>OKVED_I_Velch</t>
         </is>
       </c>
     </row>
     <row r="1831">
       <c r="A1831" t="inlineStr">
         <is>
-          <t>OKVED_J_Velch</t>
+          <t>OKVED_55_Velch</t>
         </is>
       </c>
     </row>
     <row r="1832">
       <c r="A1832" t="inlineStr">
         <is>
-          <t>OKVED_63_Velch</t>
+          <t>OKVED_56_Velch</t>
         </is>
       </c>
     </row>
     <row r="1833">
       <c r="A1833" t="inlineStr">
         <is>
-          <t>OKVED_L_Velch</t>
+          <t>OKVED_J_Velch</t>
         </is>
       </c>
     </row>
     <row r="1834">
       <c r="A1834" t="inlineStr">
         <is>
-          <t>OKVED_68_Velch</t>
+          <t>OKVED_63_Velch</t>
         </is>
       </c>
     </row>
     <row r="1835">
       <c r="A1835" t="inlineStr">
         <is>
-          <t>OKVED_M_Velch</t>
+          <t>OKVED_L_Velch</t>
         </is>
       </c>
     </row>
     <row r="1836">
       <c r="A1836" t="inlineStr">
         <is>
-          <t>OKVED_69_Velch</t>
+          <t>OKVED_68_Velch</t>
         </is>
       </c>
     </row>
     <row r="1837">
       <c r="A1837" t="inlineStr">
         <is>
-          <t>OKVED_70_Velch</t>
+          <t>OKVED_M_Velch</t>
         </is>
       </c>
     </row>
     <row r="1838">
       <c r="A1838" t="inlineStr">
         <is>
-          <t>OKVED_71_Velch</t>
+          <t>OKVED_69_Velch</t>
         </is>
       </c>
     </row>
     <row r="1839">
       <c r="A1839" t="inlineStr">
         <is>
-          <t>OKVED_74_Velch</t>
+          <t>OKVED_70_Velch</t>
         </is>
       </c>
     </row>
     <row r="1840">
       <c r="A1840" t="inlineStr">
         <is>
-          <t>OKVED_N_Velch</t>
+          <t>OKVED_71_Velch</t>
         </is>
       </c>
     </row>
     <row r="1841">
       <c r="A1841" t="inlineStr">
         <is>
-          <t>OKVED_77_Velch</t>
+          <t>OKVED_74_Velch</t>
         </is>
       </c>
     </row>
     <row r="1842">
       <c r="A1842" t="inlineStr">
         <is>
-          <t>OKVED_79_Velch</t>
+          <t>OKVED_N_Velch</t>
         </is>
       </c>
     </row>
     <row r="1843">
       <c r="A1843" t="inlineStr">
         <is>
-          <t>OKVED_81_Velch</t>
+          <t>OKVED_77_Velch</t>
         </is>
       </c>
     </row>
     <row r="1844">
       <c r="A1844" t="inlineStr">
         <is>
-          <t>OKVED_82_Velch</t>
+          <t>OKVED_79_Velch</t>
         </is>
       </c>
     </row>
     <row r="1845">
       <c r="A1845" t="inlineStr">
         <is>
-          <t>OKVED_O_Velch</t>
+          <t>OKVED_81_Velch</t>
         </is>
       </c>
     </row>
     <row r="1846">
       <c r="A1846" t="inlineStr">
         <is>
-          <t>OKVED_84_Velch</t>
+          <t>OKVED_82_Velch</t>
         </is>
       </c>
     </row>
     <row r="1847">
       <c r="A1847" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_O_Velch</t>
         </is>
       </c>
     </row>
     <row r="1848">
       <c r="A1848" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_84_Velch</t>
         </is>
       </c>
     </row>
     <row r="1849">
       <c r="A1849" t="inlineStr">
         <is>
-          <t>OKVED_Q_Velch</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1850">
       <c r="A1850" t="inlineStr">
         <is>
-          <t>OKVED_88_Velch</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1851">
       <c r="A1851" t="inlineStr">
         <is>
-          <t>OKVED_R_Velch</t>
+          <t>OKVED_Q_Velch</t>
         </is>
       </c>
     </row>
     <row r="1852">
       <c r="A1852" t="inlineStr">
         <is>
-          <t>OKVED_93_Velch</t>
+          <t>OKVED_88_Velch</t>
         </is>
       </c>
     </row>
     <row r="1853">
       <c r="A1853" t="inlineStr">
         <is>
-          <t>OKVED_S_Velch</t>
+          <t>OKVED_R_Velch</t>
         </is>
       </c>
     </row>
     <row r="1854">
       <c r="A1854" t="inlineStr">
         <is>
-          <t>OKVED_94_Velch</t>
+          <t>OKVED_93_Velch</t>
         </is>
       </c>
     </row>
     <row r="1855">
       <c r="A1855" t="inlineStr">
         <is>
-          <t>OKVED_96_Velch</t>
+          <t>OKVED_S_Velch</t>
         </is>
       </c>
     </row>
     <row r="1856">
       <c r="A1856" t="inlineStr">
         <is>
-          <t>OKVED_43_UstKap_23</t>
+          <t>OKVED_94_Velch</t>
         </is>
       </c>
     </row>
     <row r="1857">
       <c r="A1857" t="inlineStr">
         <is>
-          <t>OKVED_43_ChiAkt_23</t>
+          <t>OKVED_96_Velch</t>
         </is>
       </c>
     </row>
     <row r="1858">
       <c r="A1858" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap_23</t>
+          <t>OKVED_43_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1859">
       <c r="A1859" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap_24</t>
+          <t>OKVED_43_ChiAkt_23</t>
         </is>
       </c>
     </row>
     <row r="1860">
       <c r="A1860" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap_23</t>
+          <t>OKVED_J_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1861">
       <c r="A1861" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap_24</t>
+          <t>OKVED_J_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1862">
       <c r="A1862" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap_23</t>
+          <t>OKVED_63_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1863">
       <c r="A1863" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap_24</t>
+          <t>OKVED_63_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1864">
       <c r="A1864" t="inlineStr">
         <is>
-          <t>OKVED_69_ChiAkt_23</t>
+          <t>OKVED_69_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1865">
       <c r="A1865" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap_23</t>
+          <t>OKVED_69_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1866">
       <c r="A1866" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap_24</t>
+          <t>OKVED_69_ChiAkt_23</t>
         </is>
       </c>
     </row>
     <row r="1867">
       <c r="A1867" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap_23</t>
+          <t>OKVED_O_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1868">
       <c r="A1868" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap_24</t>
+          <t>OKVED_O_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1869">
       <c r="A1869" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_23</t>
+          <t>OKVED_84_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1870">
       <c r="A1870" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_24</t>
+          <t>OKVED_84_UstKap_24</t>
         </is>
       </c>
     </row>
@@ -13523,40 +13523,54 @@
     <row r="1873">
       <c r="A1873" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap_23</t>
+          <t>OKVED_85_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1874">
       <c r="A1874" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap_24</t>
+          <t>OKVED_85_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1875">
       <c r="A1875" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap_23</t>
+          <t>OKVED_Q_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1876">
       <c r="A1876" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap_24</t>
+          <t>OKVED_Q_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1877">
       <c r="A1877" t="inlineStr">
         <is>
-          <t>OKVED_R_UstKap_24</t>
+          <t>OKVED_88_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1878">
       <c r="A1878" t="inlineStr">
+        <is>
+          <t>OKVED_88_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="inlineStr">
+        <is>
+          <t>OKVED_R_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="inlineStr">
         <is>
           <t>OKVED_93_UstKap_24</t>
         </is>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1880"/>
+  <dimension ref="A1:A1881"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10331,14 +10331,14 @@
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>OKVED_10_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_10_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>OKVED_38_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10V%KObsZad</t>
         </is>
       </c>
     </row>
@@ -10380,315 +10380,315 @@
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>OKVED_70_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_38_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>OKVED_70_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_70_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>OKVED_R_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_70_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>OKVED_R_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_R_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>OKVED_93_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_R_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>OKVED_93_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_93_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>OKVED_94_KoeTekLikDo&lt;10KreZad</t>
+          <t>OKVED_93_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>OKVED_94_KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>OKVED_94_KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>OKVED_96_KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>OKVED_94_KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>OKVED_96_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>OKVED_96_KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
+          <t>OKVED_96_KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsKol</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20DebZad</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZad</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20KreZad</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZadKre</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20KreZad</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20DenSreIDenEkv</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>OKVED_42_KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeTekLikOt&gt;=20DebZad</t>
+          <t>OKVED_42_KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeTekLikOt&gt;=20V%KObsZad</t>
+          <t>OKVED_69_KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>OKVED_01_ArendPlDeVsego</t>
+          <t>OKVED_69_KoeTekLikOt&gt;=20V%KObsZad</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>OKVED_32_ArendPlDeVsego</t>
+          <t>OKVED_01_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>OKVED_E_ArendPlDeVsego</t>
+          <t>OKVED_32_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>OKVED_36_ArendPlDeVsego</t>
+          <t>OKVED_E_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>OKVED_38_ArendPlDeVsego</t>
+          <t>OKVED_36_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>OKVED_41_ArendPlDeVsego</t>
+          <t>OKVED_38_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>OKVED_43_ArendPlDeVsego</t>
+          <t>OKVED_41_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>OKVED_49_ArendPlDeVsego</t>
+          <t>OKVED_43_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>OKVED_50_ArendPlDeVsego</t>
+          <t>OKVED_49_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>OKVED_I_ArendPlDeVsego</t>
+          <t>OKVED_50_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>OKVED_55_ArendPlDeVsego</t>
+          <t>OKVED_I_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>OKVED_56_ArendPlDeVsego</t>
+          <t>OKVED_55_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>OKVED_J_OtProdDeVsego</t>
+          <t>OKVED_56_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>OKVED_J_ArendPlDeVsego</t>
+          <t>OKVED_J_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>OKVED_63_OtProdDeVsego</t>
+          <t>OKVED_J_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>OKVED_63_ArendPlDeVsego</t>
+          <t>OKVED_63_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>OKVED_K_ArendPlDeVsego</t>
+          <t>OKVED_63_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>OKVED_64_ArendPlDeVsego</t>
+          <t>OKVED_K_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>OKVED_69_ArendPlDeVsego</t>
+          <t>OKVED_64_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>OKVED_79_ArendPlDeVsego</t>
+          <t>OKVED_69_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>OKVED_81_ArendPlDeVsego</t>
+          <t>OKVED_79_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>OKVED_82_ArendPlDeVsego</t>
+          <t>OKVED_81_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>OKVED_O_ArendPlDeVsego</t>
+          <t>OKVED_82_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>OKVED_84_ArendPlDeVsego</t>
+          <t>OKVED_O_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_84_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
@@ -10702,539 +10702,539 @@
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>OKVED_Q_OtProdDeVsego</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>OKVED_Q_ArendPlDeVsego</t>
+          <t>OKVED_Q_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>OKVED_88_OtProdDeVsego</t>
+          <t>OKVED_Q_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>OKVED_88_ArendPlDeVsego</t>
+          <t>OKVED_88_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>OKVED_R_OtProdDeVsego</t>
+          <t>OKVED_88_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>OKVED_R_ArendPlDeVsego</t>
+          <t>OKVED_R_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>OKVED_93_OtProdDeVsego</t>
+          <t>OKVED_R_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>OKVED_93_ArendPlDeVsego</t>
+          <t>OKVED_93_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>OKVED_S_ArendPlDeVsego</t>
+          <t>OKVED_93_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>OKVED_94_ArendPlDeVsego</t>
+          <t>OKVED_S_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>OKVED_96_ArendPlDeVsego</t>
+          <t>OKVED_94_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcPoDolgObyaz</t>
+          <t>OKVED_96_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>OKVED_32_ProcPoDolgObyaz</t>
+          <t>OKVED_11_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>OKVED_32_NalogNaPri</t>
+          <t>OKVED_32_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>OKVED_33_NalogNaPri</t>
+          <t>OKVED_32_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcPoDolgObyaz</t>
+          <t>OKVED_33_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>OKVED_38_NalogNaPri</t>
+          <t>OKVED_36_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcPoDolgObyaz</t>
+          <t>OKVED_38_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>OKVED_56_ProcPoDolgObyaz</t>
+          <t>OKVED_49_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>OKVED_56_NalogNaPri</t>
+          <t>OKVED_56_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>OKVED_J_ProcPoDolgObyaz</t>
+          <t>OKVED_56_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>OKVED_J_NalogNaPri</t>
+          <t>OKVED_J_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>OKVED_63_ProcPoDolgObyaz</t>
+          <t>OKVED_J_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>OKVED_63_NalogNaPri</t>
+          <t>OKVED_63_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>OKVED_M_ProcPoDolgObyaz</t>
+          <t>OKVED_63_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>OKVED_69_ProcPoDolgObyaz</t>
+          <t>OKVED_M_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>OKVED_69_NalogNaPri</t>
+          <t>OKVED_69_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>OKVED_70_ProcPoDolgObyaz</t>
+          <t>OKVED_69_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>OKVED_71_ProcPoDolgObyaz</t>
+          <t>OKVED_70_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>OKVED_71_NalogNaPri</t>
+          <t>OKVED_71_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>OKVED_74_ProcPoDolgObyaz</t>
+          <t>OKVED_71_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcPoDolgObyaz</t>
+          <t>OKVED_74_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>OKVED_79_NalogNaPri</t>
+          <t>OKVED_77_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>OKVED_81_NalogNaPri</t>
+          <t>OKVED_79_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>OKVED_82_ProcPoDolgObyaz</t>
+          <t>OKVED_81_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_82_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>OKVED_O_VSvyaziSOplTrudRab</t>
+          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>OKVED_O_ProcPoDolgObyaz</t>
+          <t>OKVED_O_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_O_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>OKVED_84_VSvyaziSOplTrudRab</t>
+          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>OKVED_84_ProcPoDolgObyaz</t>
+          <t>OKVED_84_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_84_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>OKVED_Q_ProcPoDolgObyaz</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>OKVED_Q_NalogNaPri</t>
+          <t>OKVED_Q_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>OKVED_86_PlatPoTekDeVsego</t>
+          <t>OKVED_Q_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>OKVED_86_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_86_PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>OKVED_86_VSvyaziSOplTrudRab</t>
+          <t>OKVED_86_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>OKVED_86_ProcPoDolgObyaz</t>
+          <t>OKVED_86_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>OKVED_86_NalogNaPri</t>
+          <t>OKVED_86_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>OKVED_86_SaldoDenPotTekOper</t>
+          <t>OKVED_86_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_86_SaldoDenPotTekOper</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>OKVED_R_VSvyaziSOplTrudRab</t>
+          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>OKVED_R_ProcPoDolgObyaz</t>
+          <t>OKVED_R_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>OKVED_R_NalogNaPri</t>
+          <t>OKVED_R_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_R_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>OKVED_93_VSvyaziSOplTrudRab</t>
+          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>OKVED_93_ProcPoDolgObyaz</t>
+          <t>OKVED_93_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>OKVED_93_NalogNaPri</t>
+          <t>OKVED_93_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>OKVED_96_ProcPoDolgObyaz</t>
+          <t>OKVED_93_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>OKVED_96_NalogNaPri</t>
+          <t>OKVED_96_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_96_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>OKVED_01_DivProcDolgFinVlozh</t>
+          <t>OKVED_01_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>OKVED_B_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>OKVED_07_OtProdAkcOrgDolUch</t>
+          <t>OKVED_B_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>OKVED_C_OtProdAkcOrgDolUch</t>
+          <t>OKVED_07_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>OKVED_10_OtProdAkcOrgDolUch</t>
+          <t>OKVED_C_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_10_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdAkcOrgDolUch</t>
+          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdFinVlozh</t>
+          <t>OKVED_11_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>OKVED_33_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_11_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>OKVED_33_OtProdAkcOrgDolUch</t>
+          <t>OKVED_33_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>OKVED_33_DivProcDolgFinVlozh</t>
+          <t>OKVED_33_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_33_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
@@ -11248,1008 +11248,1008 @@
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdAkcOrgDolUch</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdFinVlozh</t>
+          <t>OKVED_E_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>OKVED_E_DivProcDolgFinVlozh</t>
+          <t>OKVED_E_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdAkcOrgDolUch</t>
+          <t>OKVED_E_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdFinVlozh</t>
+          <t>OKVED_36_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>OKVED_36_DivProcDolgFinVlozh</t>
+          <t>OKVED_36_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_36_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdFinVlozh</t>
+          <t>OKVED_38_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>OKVED_38_DivProcDolgFinVlozh</t>
+          <t>OKVED_38_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_38_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdAkcOrgDolUch</t>
+          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_F_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdAkcOrgDolUch</t>
+          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>OKVED_42_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_41_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>OKVED_42_OtProdAkcOrgDolUch</t>
+          <t>OKVED_42_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_42_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdFinVlozh</t>
+          <t>OKVED_43_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>OKVED_G_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>OKVED_46_OtProdAkcOrgDolUch</t>
+          <t>OKVED_G_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>OKVED_47_OtProdAkcOrgDolUch</t>
+          <t>OKVED_46_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>OKVED_H_OtProdAkcOrgDolUch</t>
+          <t>OKVED_47_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_H_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdAkcOrgDolUch</t>
+          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>OKVED_49_DivProcDolgFinVlozh</t>
+          <t>OKVED_49_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>OKVED_51_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_49_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>OKVED_51_OtProdAkcOrgDolUch</t>
+          <t>OKVED_51_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>OKVED_52_OtProdAkcOrgDolUch</t>
+          <t>OKVED_51_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_52_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdAkcOrgDolUch</t>
+          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_I_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdAkcOrgDolUch</t>
+          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_55_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdAkcOrgDolUch</t>
+          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_K_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdAkcOrgDolUch</t>
+          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>OKVED_L_OtProdAkcOrgDolUch</t>
+          <t>OKVED_64_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>OKVED_68_OtProdAkcOrgDolUch</t>
+          <t>OKVED_L_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_68_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdAkcOrgDolUch</t>
+          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_M_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdAkcOrgDolUch</t>
+          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_70_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdAkcOrgDolUch</t>
+          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>OKVED_71_DivProcDolgFinVlozh</t>
+          <t>OKVED_71_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdAkcOrgDolUch</t>
+          <t>OKVED_71_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdFinVlozh</t>
+          <t>OKVED_N_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdAkcOrgDolUch</t>
+          <t>OKVED_N_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdFinVlozh</t>
+          <t>OKVED_77_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>OKVED_79_OtProdAkcOrgDolUch</t>
+          <t>OKVED_77_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>OKVED_79_OtProdFinVlozh</t>
+          <t>OKVED_79_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>OKVED_79_DivProcDolgFinVlozh</t>
+          <t>OKVED_79_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_79_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdAkcOrgDolUch</t>
+          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>OKVED_S_DivProcDolgFinVlozh</t>
+          <t>OKVED_S_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_S_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdAkcOrgDolUch</t>
+          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>OKVED_94_DivProcDolgFinVlozh</t>
+          <t>OKVED_94_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>OKVED_01_DolUch</t>
+          <t>OKVED_94_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_01_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>OKVED_B_DolUch</t>
+          <t>OKVED_01_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_B_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>OKVED_07_DolUch</t>
+          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>OKVED_07_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_07_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>OKVED_C_DolUch</t>
+          <t>OKVED_07_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_C_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>OKVED_10_DolUch</t>
+          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_10_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>OKVED_11_DolUch</t>
+          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>OKVED_11_PrCenBum</t>
+          <t>OKVED_11_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_11_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>OKVED_33_DolUch</t>
+          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
         <is>
-          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_33_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>OKVED_E_DolUch</t>
+          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>OKVED_E_PrCenBum</t>
+          <t>OKVED_E_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_E_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>OKVED_36_DolUch</t>
+          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>OKVED_36_PrCenBum</t>
+          <t>OKVED_36_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_36_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>OKVED_38_DolUch</t>
+          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>OKVED_38_PrCenBum</t>
+          <t>OKVED_38_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>OKVED_38_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_38_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>OKVED_F_DolUch</t>
+          <t>OKVED_38_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_F_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>OKVED_41_DolUch</t>
+          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_41_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
         <is>
-          <t>OKVED_42_DolUch</t>
+          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_42_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>OKVED_43_DolUch</t>
+          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>OKVED_43_PrCenBum</t>
+          <t>OKVED_43_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_43_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>OKVED_46_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>OKVED_47_DolUch</t>
+          <t>OKVED_46_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>OKVED_H_DolUch</t>
+          <t>OKVED_47_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_H_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>OKVED_49_DolUch</t>
+          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_49_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
         <is>
-          <t>OKVED_50_DolUch</t>
+          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>OKVED_50_PrCenBum</t>
+          <t>OKVED_50_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_50_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>OKVED_51_DolUch</t>
+          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
         <is>
-          <t>OKVED_51_PrCenBum</t>
+          <t>OKVED_51_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
         <is>
-          <t>OKVED_51_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_51_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>OKVED_52_DolUch</t>
+          <t>OKVED_51_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
         <is>
-          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_52_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
         <is>
-          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
         <is>
-          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
         <is>
-          <t>OKVED_K_DolUch</t>
+          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
         <is>
-          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_K_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
         <is>
-          <t>OKVED_64_DolUch</t>
+          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
         <is>
-          <t>OKVED_64_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_64_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
         <is>
-          <t>OKVED_M_DolUch</t>
+          <t>OKVED_64_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
         <is>
-          <t>OKVED_70_DolUch</t>
+          <t>OKVED_M_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
         <is>
-          <t>OKVED_70_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_70_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
         <is>
-          <t>OKVED_71_DolUch</t>
+          <t>OKVED_70_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
         <is>
-          <t>OKVED_N_DolUch</t>
+          <t>OKVED_71_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
         <is>
-          <t>OKVED_N_PrCenBum</t>
+          <t>OKVED_N_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>OKVED_77_DolUch</t>
+          <t>OKVED_N_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>OKVED_77_PrCenBum</t>
+          <t>OKVED_77_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_77_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
         <is>
-          <t>OKVED_79_DolUch</t>
+          <t>OKVED_77_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>OKVED_79_PrCenBum</t>
+          <t>OKVED_79_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>OKVED_S_Modern</t>
+          <t>OKVED_79_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>OKVED_S_DolUch</t>
+          <t>OKVED_S_Modern</t>
         </is>
       </c>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_S_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
         <is>
-          <t>OKVED_94_Modern</t>
+          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
         <is>
-          <t>OKVED_94_DolUch</t>
+          <t>OKVED_94_Modern</t>
         </is>
       </c>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_94_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
         <is>
-          <t>OKVED_01_PostDeyt1</t>
+          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
         <is>
-          <t>OKVED_01_DrPost</t>
+          <t>OKVED_01_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt</t>
+          <t>OKVED_01_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt1</t>
+          <t>OKVED_B_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt</t>
+          <t>OKVED_B_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt1</t>
+          <t>OKVED_07_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>OKVED_C_PostDeyt1</t>
+          <t>OKVED_07_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>OKVED_10_PostDeyt1</t>
+          <t>OKVED_C_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>OKVED_32_PlCredit</t>
+          <t>OKVED_10_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt</t>
+          <t>OKVED_32_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt1</t>
+          <t>OKVED_32_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt</t>
+          <t>OKVED_32_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt1</t>
+          <t>OKVED_33_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>OKVED_33_DrPost</t>
+          <t>OKVED_33_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_33_DrPost</t>
         </is>
       </c>
     </row>
@@ -12263,504 +12263,504 @@
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
-          <t>OKVED_E_PostDeyt1</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>OKVED_E_DrPost</t>
+          <t>OKVED_E_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>OKVED_38_PostDeyt1</t>
+          <t>OKVED_E_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1696">
       <c r="A1696" t="inlineStr">
         <is>
-          <t>OKVED_38_DrPost</t>
+          <t>OKVED_38_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1697">
       <c r="A1697" t="inlineStr">
         <is>
-          <t>OKVED_F_PostDeyt1</t>
+          <t>OKVED_38_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1698">
       <c r="A1698" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt</t>
+          <t>OKVED_F_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1699">
       <c r="A1699" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt1</t>
+          <t>OKVED_41_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1700">
       <c r="A1700" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt</t>
+          <t>OKVED_41_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1701">
       <c r="A1701" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt1</t>
+          <t>OKVED_42_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1702">
       <c r="A1702" t="inlineStr">
         <is>
-          <t>OKVED_42_DrPost</t>
+          <t>OKVED_42_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1703">
       <c r="A1703" t="inlineStr">
         <is>
-          <t>OKVED_43_PostDeyt1</t>
+          <t>OKVED_42_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1704">
       <c r="A1704" t="inlineStr">
         <is>
-          <t>OKVED_43_DrPost</t>
+          <t>OKVED_43_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1705">
       <c r="A1705" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt</t>
+          <t>OKVED_43_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1706">
       <c r="A1706" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt1</t>
+          <t>OKVED_G_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1707">
       <c r="A1707" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt</t>
+          <t>OKVED_G_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1708">
       <c r="A1708" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt1</t>
+          <t>OKVED_46_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1709">
       <c r="A1709" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt</t>
+          <t>OKVED_46_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1710">
       <c r="A1710" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt1</t>
+          <t>OKVED_47_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1711">
       <c r="A1711" t="inlineStr">
         <is>
-          <t>OKVED_H_PostDeyt1</t>
+          <t>OKVED_47_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1712">
       <c r="A1712" t="inlineStr">
         <is>
-          <t>OKVED_49_PostDeyt</t>
+          <t>OKVED_H_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1713">
       <c r="A1713" t="inlineStr">
         <is>
-          <t>OKVED_49_PostDeyt1</t>
+          <t>OKVED_49_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1714">
       <c r="A1714" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt</t>
+          <t>OKVED_49_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1715">
       <c r="A1715" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt1</t>
+          <t>OKVED_50_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1716">
       <c r="A1716" t="inlineStr">
         <is>
-          <t>OKVED_50_DrPost</t>
+          <t>OKVED_50_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1717">
       <c r="A1717" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt</t>
+          <t>OKVED_50_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1718">
       <c r="A1718" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt1</t>
+          <t>OKVED_51_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1719">
       <c r="A1719" t="inlineStr">
         <is>
-          <t>OKVED_51_DrPost</t>
+          <t>OKVED_51_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1720">
       <c r="A1720" t="inlineStr">
         <is>
-          <t>OKVED_52_PostDeyt1</t>
+          <t>OKVED_51_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1721">
       <c r="A1721" t="inlineStr">
         <is>
-          <t>OKVED_I_PostDeyt1</t>
+          <t>OKVED_52_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1722">
       <c r="A1722" t="inlineStr">
         <is>
-          <t>OKVED_I_DrPost</t>
+          <t>OKVED_I_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1723">
       <c r="A1723" t="inlineStr">
         <is>
-          <t>OKVED_55_PostDeyt1</t>
+          <t>OKVED_I_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1724">
       <c r="A1724" t="inlineStr">
         <is>
-          <t>OKVED_55_DrPost</t>
+          <t>OKVED_55_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1725">
       <c r="A1725" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt</t>
+          <t>OKVED_55_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1726">
       <c r="A1726" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt1</t>
+          <t>OKVED_K_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1727">
       <c r="A1727" t="inlineStr">
         <is>
-          <t>OKVED_K_DrPost</t>
+          <t>OKVED_K_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1728">
       <c r="A1728" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt</t>
+          <t>OKVED_K_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1729">
       <c r="A1729" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt1</t>
+          <t>OKVED_64_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1730">
       <c r="A1730" t="inlineStr">
         <is>
-          <t>OKVED_64_DrPost</t>
+          <t>OKVED_64_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1731">
       <c r="A1731" t="inlineStr">
         <is>
-          <t>OKVED_L_PostDeyt1</t>
+          <t>OKVED_64_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1732">
       <c r="A1732" t="inlineStr">
         <is>
-          <t>OKVED_68_PostDeyt1</t>
+          <t>OKVED_L_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1733">
       <c r="A1733" t="inlineStr">
         <is>
-          <t>OKVED_M_PostDeyt</t>
+          <t>OKVED_68_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1734">
       <c r="A1734" t="inlineStr">
         <is>
-          <t>OKVED_70_PlCredit</t>
+          <t>OKVED_M_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1735">
       <c r="A1735" t="inlineStr">
         <is>
-          <t>OKVED_70_PostDeyt</t>
+          <t>OKVED_70_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1736">
       <c r="A1736" t="inlineStr">
         <is>
-          <t>OKVED_71_PostDeyt</t>
+          <t>OKVED_70_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1737">
       <c r="A1737" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt</t>
+          <t>OKVED_71_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1738">
       <c r="A1738" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt1</t>
+          <t>OKVED_74_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1739">
       <c r="A1739" t="inlineStr">
         <is>
-          <t>OKVED_74_DrPost</t>
+          <t>OKVED_74_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1740">
       <c r="A1740" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt</t>
+          <t>OKVED_74_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1741">
       <c r="A1741" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt1</t>
+          <t>OKVED_N_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1742">
       <c r="A1742" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt</t>
+          <t>OKVED_N_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1743">
       <c r="A1743" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt1</t>
+          <t>OKVED_79_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1744">
       <c r="A1744" t="inlineStr">
         <is>
-          <t>OKVED_79_DrPost</t>
+          <t>OKVED_79_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1745">
       <c r="A1745" t="inlineStr">
         <is>
-          <t>OKVED_81_PlCredit</t>
+          <t>OKVED_79_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1746">
       <c r="A1746" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt</t>
+          <t>OKVED_81_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1747">
       <c r="A1747" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt1</t>
+          <t>OKVED_81_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1748">
       <c r="A1748" t="inlineStr">
         <is>
-          <t>OKVED_S_PlCredit</t>
+          <t>OKVED_81_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1749">
       <c r="A1749" t="inlineStr">
         <is>
-          <t>OKVED_S_PostDeyt1</t>
+          <t>OKVED_S_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1750">
       <c r="A1750" t="inlineStr">
         <is>
-          <t>OKVED_94_PlCredit</t>
+          <t>OKVED_S_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1751">
       <c r="A1751" t="inlineStr">
         <is>
-          <t>OKVED_94_PostDeyt1</t>
+          <t>OKVED_94_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1752">
       <c r="A1752" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin1</t>
+          <t>OKVED_94_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1753">
       <c r="A1753" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin2</t>
+          <t>OKVED_01_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1754">
       <c r="A1754" t="inlineStr">
         <is>
-          <t>OKVED_B_PlPoFin1</t>
+          <t>OKVED_01_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1755">
       <c r="A1755" t="inlineStr">
         <is>
-          <t>OKVED_07_PlPoFin1</t>
+          <t>OKVED_B_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1756">
       <c r="A1756" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin</t>
+          <t>OKVED_07_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1757">
       <c r="A1757" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin1</t>
+          <t>OKVED_32_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1758">
       <c r="A1758" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin2</t>
+          <t>OKVED_32_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1759">
       <c r="A1759" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin3</t>
+          <t>OKVED_32_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin</t>
+          <t>OKVED_32_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1761">
       <c r="A1761" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1762">
       <c r="A1762" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1763">
       <c r="A1763" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin3</t>
+          <t>OKVED_33_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1764">
       <c r="A1764" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_33_PlPoFin3</t>
         </is>
       </c>
     </row>
@@ -12774,588 +12774,588 @@
     <row r="1766">
       <c r="A1766" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin1</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1767">
       <c r="A1767" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin2</t>
+          <t>OKVED_E_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1768">
       <c r="A1768" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin1</t>
+          <t>OKVED_E_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1769">
       <c r="A1769" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin2</t>
+          <t>OKVED_38_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1770">
       <c r="A1770" t="inlineStr">
         <is>
-          <t>OKVED_F_PlPoFin1</t>
+          <t>OKVED_38_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1771">
       <c r="A1771" t="inlineStr">
         <is>
-          <t>OKVED_41_PlPoFin1</t>
+          <t>OKVED_F_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1772">
       <c r="A1772" t="inlineStr">
         <is>
-          <t>OKVED_42_PlPoFin1</t>
+          <t>OKVED_41_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1773">
       <c r="A1773" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin1</t>
+          <t>OKVED_42_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1774">
       <c r="A1774" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin2</t>
+          <t>OKVED_43_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1775">
       <c r="A1775" t="inlineStr">
         <is>
-          <t>OKVED_G_PlPoFin1</t>
+          <t>OKVED_43_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1776">
       <c r="A1776" t="inlineStr">
         <is>
-          <t>OKVED_46_PlPoFin1</t>
+          <t>OKVED_G_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1777">
       <c r="A1777" t="inlineStr">
         <is>
-          <t>OKVED_47_PlPoFin1</t>
+          <t>OKVED_46_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1778">
       <c r="A1778" t="inlineStr">
         <is>
-          <t>OKVED_H_PlPoFin1</t>
+          <t>OKVED_47_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1779">
       <c r="A1779" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin1</t>
+          <t>OKVED_H_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1780">
       <c r="A1780" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin2</t>
+          <t>OKVED_49_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1781">
       <c r="A1781" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoFin1</t>
+          <t>OKVED_49_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1782">
       <c r="A1782" t="inlineStr">
         <is>
-          <t>OKVED_51_PlPoFin1</t>
+          <t>OKVED_50_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1783">
       <c r="A1783" t="inlineStr">
         <is>
-          <t>OKVED_51_PlPoFin2</t>
+          <t>OKVED_51_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1784">
       <c r="A1784" t="inlineStr">
         <is>
-          <t>OKVED_52_PlPoFin1</t>
+          <t>OKVED_51_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1785">
       <c r="A1785" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin1</t>
+          <t>OKVED_52_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1786">
       <c r="A1786" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin2</t>
+          <t>OKVED_I_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1787">
       <c r="A1787" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin1</t>
+          <t>OKVED_I_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1788">
       <c r="A1788" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin2</t>
+          <t>OKVED_55_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1789">
       <c r="A1789" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoFin1</t>
+          <t>OKVED_55_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1790">
       <c r="A1790" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoFin1</t>
+          <t>OKVED_K_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1791">
       <c r="A1791" t="inlineStr">
         <is>
-          <t>OKVED_L_PlPoFin1</t>
+          <t>OKVED_64_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1792">
       <c r="A1792" t="inlineStr">
         <is>
-          <t>OKVED_68_PlPoFin1</t>
+          <t>OKVED_L_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1793">
       <c r="A1793" t="inlineStr">
         <is>
-          <t>OKVED_M_PlPoFin1</t>
+          <t>OKVED_68_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1794">
       <c r="A1794" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin</t>
+          <t>OKVED_M_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1795">
       <c r="A1795" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin1</t>
+          <t>OKVED_70_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1796">
       <c r="A1796" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin2</t>
+          <t>OKVED_70_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1797">
       <c r="A1797" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin3</t>
+          <t>OKVED_70_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1798">
       <c r="A1798" t="inlineStr">
         <is>
-          <t>OKVED_71_PlPoFin1</t>
+          <t>OKVED_70_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1799">
       <c r="A1799" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin1</t>
+          <t>OKVED_71_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1800">
       <c r="A1800" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin2</t>
+          <t>OKVED_74_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1801">
       <c r="A1801" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin3</t>
+          <t>OKVED_74_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1802">
       <c r="A1802" t="inlineStr">
         <is>
-          <t>OKVED_74_SaldoDenPot</t>
+          <t>OKVED_74_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1803">
       <c r="A1803" t="inlineStr">
         <is>
-          <t>OKVED_N_PlPoFin1</t>
+          <t>OKVED_74_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1804">
       <c r="A1804" t="inlineStr">
         <is>
-          <t>OKVED_N_PlPoFin2</t>
+          <t>OKVED_N_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1805">
       <c r="A1805" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin1</t>
+          <t>OKVED_N_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1806">
       <c r="A1806" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin2</t>
+          <t>OKVED_79_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1807">
       <c r="A1807" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin1</t>
+          <t>OKVED_79_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1808">
       <c r="A1808" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin2</t>
+          <t>OKVED_81_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1809">
       <c r="A1809" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin3</t>
+          <t>OKVED_81_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1810">
       <c r="A1810" t="inlineStr">
         <is>
-          <t>OKVED_81_SaldoDenPot</t>
+          <t>OKVED_81_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1811">
       <c r="A1811" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin1</t>
+          <t>OKVED_81_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1812">
       <c r="A1812" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin2</t>
+          <t>OKVED_S_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1813">
       <c r="A1813" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin3</t>
+          <t>OKVED_S_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1814">
       <c r="A1814" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin1</t>
+          <t>OKVED_S_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1815">
       <c r="A1815" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin2</t>
+          <t>OKVED_94_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1816">
       <c r="A1816" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin3</t>
+          <t>OKVED_94_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1817">
       <c r="A1817" t="inlineStr">
         <is>
-          <t>OKVED_01_Velch</t>
+          <t>OKVED_94_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1818">
       <c r="A1818" t="inlineStr">
         <is>
-          <t>OKVED_11_Velch</t>
+          <t>OKVED_01_Velch</t>
         </is>
       </c>
     </row>
     <row r="1819">
       <c r="A1819" t="inlineStr">
         <is>
-          <t>OKVED_32_Velch</t>
+          <t>OKVED_11_Velch</t>
         </is>
       </c>
     </row>
     <row r="1820">
       <c r="A1820" t="inlineStr">
         <is>
-          <t>OKVED_33_Velch</t>
+          <t>OKVED_32_Velch</t>
         </is>
       </c>
     </row>
     <row r="1821">
       <c r="A1821" t="inlineStr">
         <is>
-          <t>OKVED_E_Velch</t>
+          <t>OKVED_33_Velch</t>
         </is>
       </c>
     </row>
     <row r="1822">
       <c r="A1822" t="inlineStr">
         <is>
-          <t>OKVED_36_Velch</t>
+          <t>OKVED_E_Velch</t>
         </is>
       </c>
     </row>
     <row r="1823">
       <c r="A1823" t="inlineStr">
         <is>
-          <t>OKVED_38_Velch</t>
+          <t>OKVED_36_Velch</t>
         </is>
       </c>
     </row>
     <row r="1824">
       <c r="A1824" t="inlineStr">
         <is>
-          <t>OKVED_F_Velch</t>
+          <t>OKVED_38_Velch</t>
         </is>
       </c>
     </row>
     <row r="1825">
       <c r="A1825" t="inlineStr">
         <is>
-          <t>OKVED_41_Velch</t>
+          <t>OKVED_F_Velch</t>
         </is>
       </c>
     </row>
     <row r="1826">
       <c r="A1826" t="inlineStr">
         <is>
-          <t>OKVED_42_Velch</t>
+          <t>OKVED_41_Velch</t>
         </is>
       </c>
     </row>
     <row r="1827">
       <c r="A1827" t="inlineStr">
         <is>
-          <t>OKVED_43_Velch</t>
+          <t>OKVED_42_Velch</t>
         </is>
       </c>
     </row>
     <row r="1828">
       <c r="A1828" t="inlineStr">
         <is>
-          <t>OKVED_47_Velch</t>
+          <t>OKVED_43_Velch</t>
         </is>
       </c>
     </row>
     <row r="1829">
       <c r="A1829" t="inlineStr">
         <is>
-          <t>OKVED_49_Velch</t>
+          <t>OKVED_47_Velch</t>
         </is>
       </c>
     </row>
     <row r="1830">
       <c r="A1830" t="inlineStr">
         <is>
-          <t>OKVED_I_Velch</t>
+          <t>OKVED_49_Velch</t>
         </is>
       </c>
     </row>
     <row r="1831">
       <c r="A1831" t="inlineStr">
         <is>
-          <t>OKVED_55_Velch</t>
+          <t>OKVED_I_Velch</t>
         </is>
       </c>
     </row>
     <row r="1832">
       <c r="A1832" t="inlineStr">
         <is>
-          <t>OKVED_56_Velch</t>
+          <t>OKVED_55_Velch</t>
         </is>
       </c>
     </row>
     <row r="1833">
       <c r="A1833" t="inlineStr">
         <is>
-          <t>OKVED_J_Velch</t>
+          <t>OKVED_56_Velch</t>
         </is>
       </c>
     </row>
     <row r="1834">
       <c r="A1834" t="inlineStr">
         <is>
-          <t>OKVED_63_Velch</t>
+          <t>OKVED_J_Velch</t>
         </is>
       </c>
     </row>
     <row r="1835">
       <c r="A1835" t="inlineStr">
         <is>
-          <t>OKVED_L_Velch</t>
+          <t>OKVED_63_Velch</t>
         </is>
       </c>
     </row>
     <row r="1836">
       <c r="A1836" t="inlineStr">
         <is>
-          <t>OKVED_68_Velch</t>
+          <t>OKVED_L_Velch</t>
         </is>
       </c>
     </row>
     <row r="1837">
       <c r="A1837" t="inlineStr">
         <is>
-          <t>OKVED_M_Velch</t>
+          <t>OKVED_68_Velch</t>
         </is>
       </c>
     </row>
     <row r="1838">
       <c r="A1838" t="inlineStr">
         <is>
-          <t>OKVED_69_Velch</t>
+          <t>OKVED_M_Velch</t>
         </is>
       </c>
     </row>
     <row r="1839">
       <c r="A1839" t="inlineStr">
         <is>
-          <t>OKVED_70_Velch</t>
+          <t>OKVED_69_Velch</t>
         </is>
       </c>
     </row>
     <row r="1840">
       <c r="A1840" t="inlineStr">
         <is>
-          <t>OKVED_71_Velch</t>
+          <t>OKVED_70_Velch</t>
         </is>
       </c>
     </row>
     <row r="1841">
       <c r="A1841" t="inlineStr">
         <is>
-          <t>OKVED_74_Velch</t>
+          <t>OKVED_71_Velch</t>
         </is>
       </c>
     </row>
     <row r="1842">
       <c r="A1842" t="inlineStr">
         <is>
-          <t>OKVED_N_Velch</t>
+          <t>OKVED_74_Velch</t>
         </is>
       </c>
     </row>
     <row r="1843">
       <c r="A1843" t="inlineStr">
         <is>
-          <t>OKVED_77_Velch</t>
+          <t>OKVED_N_Velch</t>
         </is>
       </c>
     </row>
     <row r="1844">
       <c r="A1844" t="inlineStr">
         <is>
-          <t>OKVED_79_Velch</t>
+          <t>OKVED_77_Velch</t>
         </is>
       </c>
     </row>
     <row r="1845">
       <c r="A1845" t="inlineStr">
         <is>
-          <t>OKVED_81_Velch</t>
+          <t>OKVED_79_Velch</t>
         </is>
       </c>
     </row>
     <row r="1846">
       <c r="A1846" t="inlineStr">
         <is>
-          <t>OKVED_82_Velch</t>
+          <t>OKVED_81_Velch</t>
         </is>
       </c>
     </row>
     <row r="1847">
       <c r="A1847" t="inlineStr">
         <is>
-          <t>OKVED_O_Velch</t>
+          <t>OKVED_82_Velch</t>
         </is>
       </c>
     </row>
     <row r="1848">
       <c r="A1848" t="inlineStr">
         <is>
-          <t>OKVED_84_Velch</t>
+          <t>OKVED_O_Velch</t>
         </is>
       </c>
     </row>
     <row r="1849">
       <c r="A1849" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_84_Velch</t>
         </is>
       </c>
     </row>
@@ -13369,208 +13369,215 @@
     <row r="1851">
       <c r="A1851" t="inlineStr">
         <is>
-          <t>OKVED_Q_Velch</t>
+          <t>OKVED_85_Velch</t>
         </is>
       </c>
     </row>
     <row r="1852">
       <c r="A1852" t="inlineStr">
         <is>
-          <t>OKVED_88_Velch</t>
+          <t>OKVED_Q_Velch</t>
         </is>
       </c>
     </row>
     <row r="1853">
       <c r="A1853" t="inlineStr">
         <is>
-          <t>OKVED_R_Velch</t>
+          <t>OKVED_88_Velch</t>
         </is>
       </c>
     </row>
     <row r="1854">
       <c r="A1854" t="inlineStr">
         <is>
-          <t>OKVED_93_Velch</t>
+          <t>OKVED_R_Velch</t>
         </is>
       </c>
     </row>
     <row r="1855">
       <c r="A1855" t="inlineStr">
         <is>
-          <t>OKVED_S_Velch</t>
+          <t>OKVED_93_Velch</t>
         </is>
       </c>
     </row>
     <row r="1856">
       <c r="A1856" t="inlineStr">
         <is>
-          <t>OKVED_94_Velch</t>
+          <t>OKVED_S_Velch</t>
         </is>
       </c>
     </row>
     <row r="1857">
       <c r="A1857" t="inlineStr">
         <is>
-          <t>OKVED_96_Velch</t>
+          <t>OKVED_94_Velch</t>
         </is>
       </c>
     </row>
     <row r="1858">
       <c r="A1858" t="inlineStr">
         <is>
-          <t>OKVED_43_UstKap_23</t>
+          <t>OKVED_96_Velch</t>
         </is>
       </c>
     </row>
     <row r="1859">
       <c r="A1859" t="inlineStr">
         <is>
-          <t>OKVED_43_ChiAkt_23</t>
+          <t>OKVED_43_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1860">
       <c r="A1860" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap_23</t>
+          <t>OKVED_43_ChiAkt_23</t>
         </is>
       </c>
     </row>
     <row r="1861">
       <c r="A1861" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap_24</t>
+          <t>OKVED_J_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1862">
       <c r="A1862" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap_23</t>
+          <t>OKVED_J_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1863">
       <c r="A1863" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap_24</t>
+          <t>OKVED_63_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1864">
       <c r="A1864" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap_23</t>
+          <t>OKVED_63_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1865">
       <c r="A1865" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap_24</t>
+          <t>OKVED_69_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1866">
       <c r="A1866" t="inlineStr">
         <is>
-          <t>OKVED_69_ChiAkt_23</t>
+          <t>OKVED_69_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1867">
       <c r="A1867" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap_23</t>
+          <t>OKVED_69_ChiAkt_23</t>
         </is>
       </c>
     </row>
     <row r="1868">
       <c r="A1868" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap_24</t>
+          <t>OKVED_O_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1869">
       <c r="A1869" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap_23</t>
+          <t>OKVED_O_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1870">
       <c r="A1870" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap_24</t>
+          <t>OKVED_84_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1871">
       <c r="A1871" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_23</t>
+          <t>OKVED_84_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1872">
       <c r="A1872" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_24</t>
+          <t>OKVED_85_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1873">
       <c r="A1873" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_23</t>
+          <t>OKVED_85_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1874">
       <c r="A1874" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_24</t>
+          <t>OKVED_85_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1875">
       <c r="A1875" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap_23</t>
+          <t>OKVED_85_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1876">
       <c r="A1876" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap_24</t>
+          <t>OKVED_Q_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1877">
       <c r="A1877" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap_23</t>
+          <t>OKVED_Q_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1878">
       <c r="A1878" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap_24</t>
+          <t>OKVED_88_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1879">
       <c r="A1879" t="inlineStr">
         <is>
-          <t>OKVED_R_UstKap_24</t>
+          <t>OKVED_88_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1880">
       <c r="A1880" t="inlineStr">
+        <is>
+          <t>OKVED_R_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="inlineStr">
         <is>
           <t>OKVED_93_UstKap_24</t>
         </is>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1881"/>
+  <dimension ref="A1:A1946"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10681,2903 +10681,3358 @@
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>OKVED_O_ArendPlDeVsego</t>
+          <t>OKVED_82_PrTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>OKVED_84_ArendPlDeVsego</t>
+          <t>OKVED_O_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_O_PrTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>OKVED_85_ArendPlDeVsego</t>
+          <t>OKVED_84_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>OKVED_Q_OtProdDeVsego</t>
+          <t>OKVED_84_PrTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>OKVED_Q_ArendPlDeVsego</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>OKVED_88_OtProdDeVsego</t>
+          <t>OKVED_85_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>OKVED_88_ArendPlDeVsego</t>
+          <t>OKVED_Q_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>OKVED_R_OtProdDeVsego</t>
+          <t>OKVED_Q_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>OKVED_R_ArendPlDeVsego</t>
+          <t>OKVED_88_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>OKVED_93_OtProdDeVsego</t>
+          <t>OKVED_88_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>OKVED_93_ArendPlDeVsego</t>
+          <t>OKVED_R_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>OKVED_S_ArendPlDeVsego</t>
+          <t>OKVED_R_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>OKVED_94_ArendPlDeVsego</t>
+          <t>OKVED_93_OtProdDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>OKVED_96_ArendPlDeVsego</t>
+          <t>OKVED_93_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcPoDolgObyaz</t>
+          <t>OKVED_S_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>OKVED_32_ProcPoDolgObyaz</t>
+          <t>OKVED_94_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>OKVED_32_NalogNaPri</t>
+          <t>OKVED_96_ArendPlDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>OKVED_33_NalogNaPri</t>
+          <t>OKVED_11_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcPoDolgObyaz</t>
+          <t>OKVED_32_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>OKVED_38_NalogNaPri</t>
+          <t>OKVED_32_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcPoDolgObyaz</t>
+          <t>OKVED_33_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>OKVED_56_ProcPoDolgObyaz</t>
+          <t>OKVED_36_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>OKVED_56_NalogNaPri</t>
+          <t>OKVED_38_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>OKVED_J_ProcPoDolgObyaz</t>
+          <t>OKVED_49_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>OKVED_J_NalogNaPri</t>
+          <t>OKVED_56_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>OKVED_63_ProcPoDolgObyaz</t>
+          <t>OKVED_56_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>OKVED_63_NalogNaPri</t>
+          <t>OKVED_J_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>OKVED_M_ProcPoDolgObyaz</t>
+          <t>OKVED_J_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>OKVED_69_ProcPoDolgObyaz</t>
+          <t>OKVED_63_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>OKVED_69_NalogNaPri</t>
+          <t>OKVED_63_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>OKVED_70_ProcPoDolgObyaz</t>
+          <t>OKVED_M_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>OKVED_71_ProcPoDolgObyaz</t>
+          <t>OKVED_69_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>OKVED_71_NalogNaPri</t>
+          <t>OKVED_69_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>OKVED_74_ProcPoDolgObyaz</t>
+          <t>OKVED_70_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcPoDolgObyaz</t>
+          <t>OKVED_71_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>OKVED_79_NalogNaPri</t>
+          <t>OKVED_71_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>OKVED_81_NalogNaPri</t>
+          <t>OKVED_74_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>OKVED_82_ProcPoDolgObyaz</t>
+          <t>OKVED_77_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_79_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>OKVED_O_VSvyaziSOplTrudRab</t>
+          <t>OKVED_81_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>OKVED_O_ProcPoDolgObyaz</t>
+          <t>OKVED_82_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_O_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>OKVED_84_VSvyaziSOplTrudRab</t>
+          <t>OKVED_O_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>OKVED_84_ProcPoDolgObyaz</t>
+          <t>OKVED_O_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_O_ProchiePlatezhi</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_84_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>OKVED_85_ProcPoDolgObyaz</t>
+          <t>OKVED_84_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>OKVED_85_NalogNaPri</t>
+          <t>OKVED_84_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>OKVED_Q_ProcPoDolgObyaz</t>
+          <t>OKVED_84_ProchiePlatezhi</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>OKVED_Q_NalogNaPri</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>OKVED_86_PlatPoTekDeVsego</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>OKVED_86_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_85_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>OKVED_86_VSvyaziSOplTrudRab</t>
+          <t>OKVED_85_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>OKVED_86_ProcPoDolgObyaz</t>
+          <t>OKVED_Q_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>OKVED_86_NalogNaPri</t>
+          <t>OKVED_Q_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>OKVED_86_SaldoDenPotTekOper</t>
+          <t>OKVED_Q_ProchiePlatezhi</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_86_PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>OKVED_R_VSvyaziSOplTrudRab</t>
+          <t>OKVED_86_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>OKVED_R_ProcPoDolgObyaz</t>
+          <t>OKVED_86_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>OKVED_R_NalogNaPri</t>
+          <t>OKVED_86_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
+          <t>OKVED_86_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>OKVED_93_VSvyaziSOplTrudRab</t>
+          <t>OKVED_86_ProchiePlatezhi</t>
         </is>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>OKVED_93_ProcPoDolgObyaz</t>
+          <t>OKVED_86_SaldoDenPotTekOper</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>OKVED_93_NalogNaPri</t>
+          <t>OKVED_R_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>OKVED_96_ProcPoDolgObyaz</t>
+          <t>OKVED_R_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>OKVED_96_NalogNaPri</t>
+          <t>OKVED_R_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_R_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>OKVED_01_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_PostavPoSyrMatRabUsl</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>OKVED_01_DivProcDolgFinVlozh</t>
+          <t>OKVED_93_VSvyaziSOplTrudRab</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>OKVED_B_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>OKVED_07_OtProdAkcOrgDolUch</t>
+          <t>OKVED_93_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>OKVED_C_OtProdAkcOrgDolUch</t>
+          <t>OKVED_96_ProcPoDolgObyaz</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>OKVED_10_OtProdAkcOrgDolUch</t>
+          <t>OKVED_96_NalogNaPri</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_01_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdAkcOrgDolUch</t>
+          <t>OKVED_01_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>OKVED_11_OtProdFinVlozh</t>
+          <t>OKVED_01_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>OKVED_33_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_01_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>OKVED_33_OtProdAkcOrgDolUch</t>
+          <t>OKVED_B_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>OKVED_33_DivProcDolgFinVlozh</t>
+          <t>OKVED_B_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_07_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>OKVED_35_OtProdAkcOrgDolUch</t>
+          <t>OKVED_07_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdAkcOrgDolUch</t>
+          <t>OKVED_C_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>OKVED_E_OtProdFinVlozh</t>
+          <t>OKVED_10_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>OKVED_E_DivProcDolgFinVlozh</t>
+          <t>OKVED_11_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdAkcOrgDolUch</t>
+          <t>OKVED_11_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>OKVED_36_OtProdFinVlozh</t>
+          <t>OKVED_11_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>OKVED_36_DivProcDolgFinVlozh</t>
+          <t>OKVED_11_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_33_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdAkcOrgDolUch</t>
+          <t>OKVED_33_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>OKVED_38_OtProdFinVlozh</t>
+          <t>OKVED_33_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>OKVED_38_DivProcDolgFinVlozh</t>
+          <t>OKVED_33_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>OKVED_F_OtProdAkcOrgDolUch</t>
+          <t>OKVED_35_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_35_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>OKVED_41_OtProdAkcOrgDolUch</t>
+          <t>OKVED_35_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>OKVED_42_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_E_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>OKVED_42_OtProdAkcOrgDolUch</t>
+          <t>OKVED_E_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_E_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdAkcOrgDolUch</t>
+          <t>OKVED_36_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>OKVED_43_OtProdFinVlozh</t>
+          <t>OKVED_36_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>OKVED_G_OtProdAkcOrgDolUch</t>
+          <t>OKVED_36_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>OKVED_46_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>OKVED_47_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>OKVED_H_OtProdAkcOrgDolUch</t>
+          <t>OKVED_38_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_38_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>OKVED_49_OtProdAkcOrgDolUch</t>
+          <t>OKVED_F_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>OKVED_49_DivProcDolgFinVlozh</t>
+          <t>OKVED_F_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>OKVED_51_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_41_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>OKVED_51_OtProdAkcOrgDolUch</t>
+          <t>OKVED_41_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>OKVED_52_OtProdAkcOrgDolUch</t>
+          <t>OKVED_42_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_42_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>OKVED_I_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_43_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>OKVED_55_OtProdAkcOrgDolUch</t>
+          <t>OKVED_43_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_43_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>OKVED_K_OtProdAkcOrgDolUch</t>
+          <t>OKVED_G_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_G_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>OKVED_64_OtProdAkcOrgDolUch</t>
+          <t>OKVED_46_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>OKVED_L_OtProdAkcOrgDolUch</t>
+          <t>OKVED_46_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>OKVED_68_OtProdAkcOrgDolUch</t>
+          <t>OKVED_47_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_47_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>OKVED_M_OtProdAkcOrgDolUch</t>
+          <t>OKVED_H_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_H_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>OKVED_70_OtProdAkcOrgDolUch</t>
+          <t>OKVED_49_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_49_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>OKVED_71_OtProdAkcOrgDolUch</t>
+          <t>OKVED_49_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>OKVED_71_DivProcDolgFinVlozh</t>
+          <t>OKVED_49_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdAkcOrgDolUch</t>
+          <t>OKVED_51_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>OKVED_N_OtProdFinVlozh</t>
+          <t>OKVED_51_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdAkcOrgDolUch</t>
+          <t>OKVED_51_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>OKVED_77_OtProdFinVlozh</t>
+          <t>OKVED_52_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>OKVED_79_OtProdAkcOrgDolUch</t>
+          <t>OKVED_52_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>OKVED_79_OtProdFinVlozh</t>
+          <t>OKVED_I_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>OKVED_79_DivProcDolgFinVlozh</t>
+          <t>OKVED_I_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_55_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>OKVED_S_OtProdAkcOrgDolUch</t>
+          <t>OKVED_55_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>OKVED_S_DivProcDolgFinVlozh</t>
+          <t>OKVED_K_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
+          <t>OKVED_K_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>OKVED_94_OtProdAkcOrgDolUch</t>
+          <t>OKVED_K_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>OKVED_94_DivProcDolgFinVlozh</t>
+          <t>OKVED_64_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>OKVED_01_DolUch</t>
+          <t>OKVED_64_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>OKVED_01_PrCenBum</t>
+          <t>OKVED_64_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>OKVED_B_DolUch</t>
+          <t>OKVED_L_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_68_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>OKVED_07_DolUch</t>
+          <t>OKVED_M_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>OKVED_07_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_M_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>OKVED_C_DolUch</t>
+          <t>OKVED_M_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_70_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>OKVED_10_DolUch</t>
+          <t>OKVED_70_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_70_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>OKVED_11_DolUch</t>
+          <t>OKVED_71_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>OKVED_11_PrCenBum</t>
+          <t>OKVED_71_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_71_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
         <is>
-          <t>OKVED_33_DolUch</t>
+          <t>OKVED_71_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_N_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>OKVED_E_DolUch</t>
+          <t>OKVED_N_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>OKVED_E_PrCenBum</t>
+          <t>OKVED_77_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_77_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>OKVED_36_DolUch</t>
+          <t>OKVED_77_PrPostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>OKVED_36_PrCenBum</t>
+          <t>OKVED_79_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_79_OtProdFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>OKVED_38_DolUch</t>
+          <t>OKVED_79_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>OKVED_38_PrCenBum</t>
+          <t>OKVED_S_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>OKVED_38_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_S_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>OKVED_F_DolUch</t>
+          <t>OKVED_S_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_94_OtProdVneObAktKromeFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>OKVED_41_DolUch</t>
+          <t>OKVED_94_OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
         <is>
-          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_94_DivProcDolgFinVlozh</t>
         </is>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>OKVED_42_DolUch</t>
+          <t>OKVED_01_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_01_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>OKVED_43_DolUch</t>
+          <t>OKVED_01_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>OKVED_43_PrCenBum</t>
+          <t>OKVED_B_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_B_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>OKVED_46_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_B_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>OKVED_47_DolUch</t>
+          <t>OKVED_07_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>OKVED_H_DolUch</t>
+          <t>OKVED_07_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_07_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>OKVED_49_DolUch</t>
+          <t>OKVED_C_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
         <is>
-          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_C_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>OKVED_50_DolUch</t>
+          <t>OKVED_10_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>OKVED_50_PrCenBum</t>
+          <t>OKVED_10_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_11_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
         <is>
-          <t>OKVED_51_DolUch</t>
+          <t>OKVED_11_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
         <is>
-          <t>OKVED_51_PrCenBum</t>
+          <t>OKVED_11_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>OKVED_51_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_11_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
         <is>
-          <t>OKVED_52_DolUch</t>
+          <t>OKVED_33_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
         <is>
-          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_33_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
         <is>
-          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_33_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
         <is>
-          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_35_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
         <is>
-          <t>OKVED_K_DolUch</t>
+          <t>OKVED_35_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
         <is>
-          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_E_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
         <is>
-          <t>OKVED_64_DolUch</t>
+          <t>OKVED_E_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
         <is>
-          <t>OKVED_64_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_E_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
         <is>
-          <t>OKVED_M_DolUch</t>
+          <t>OKVED_E_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
         <is>
-          <t>OKVED_70_DolUch</t>
+          <t>OKVED_36_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
         <is>
-          <t>OKVED_70_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_36_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
         <is>
-          <t>OKVED_71_DolUch</t>
+          <t>OKVED_36_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
         <is>
-          <t>OKVED_N_DolUch</t>
+          <t>OKVED_36_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>OKVED_N_PrCenBum</t>
+          <t>OKVED_38_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>OKVED_77_DolUch</t>
+          <t>OKVED_38_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
         <is>
-          <t>OKVED_77_PrCenBum</t>
+          <t>OKVED_38_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
         <is>
-          <t>OKVED_77_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_38_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>OKVED_79_DolUch</t>
+          <t>OKVED_F_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>OKVED_79_PrCenBum</t>
+          <t>OKVED_F_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>OKVED_S_Modern</t>
+          <t>OKVED_F_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>OKVED_S_DolUch</t>
+          <t>OKVED_41_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
         <is>
-          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_41_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
         <is>
-          <t>OKVED_94_Modern</t>
+          <t>OKVED_41_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>OKVED_94_DolUch</t>
+          <t>OKVED_42_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
         <is>
-          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
+          <t>OKVED_42_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
         <is>
-          <t>OKVED_01_PostDeyt1</t>
+          <t>OKVED_42_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
         <is>
-          <t>OKVED_01_DrPost</t>
+          <t>OKVED_43_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt</t>
+          <t>OKVED_43_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>OKVED_B_PostDeyt1</t>
+          <t>OKVED_43_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt</t>
+          <t>OKVED_43_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>OKVED_07_PostDeyt1</t>
+          <t>OKVED_G_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>OKVED_C_PostDeyt1</t>
+          <t>OKVED_46_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>OKVED_10_PostDeyt1</t>
+          <t>OKVED_46_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>OKVED_32_PlCredit</t>
+          <t>OKVED_47_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt</t>
+          <t>OKVED_47_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>OKVED_32_PostDeyt1</t>
+          <t>OKVED_H_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt</t>
+          <t>OKVED_H_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>OKVED_33_PostDeyt1</t>
+          <t>OKVED_H_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>OKVED_33_DrPost</t>
+          <t>OKVED_49_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_49_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
-          <t>OKVED_35_PostDeyt1</t>
+          <t>OKVED_49_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>OKVED_E_PostDeyt1</t>
+          <t>OKVED_50_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>OKVED_E_DrPost</t>
+          <t>OKVED_50_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1696">
       <c r="A1696" t="inlineStr">
         <is>
-          <t>OKVED_38_PostDeyt1</t>
+          <t>OKVED_50_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1697">
       <c r="A1697" t="inlineStr">
         <is>
-          <t>OKVED_38_DrPost</t>
+          <t>OKVED_50_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1698">
       <c r="A1698" t="inlineStr">
         <is>
-          <t>OKVED_F_PostDeyt1</t>
+          <t>OKVED_51_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1699">
       <c r="A1699" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt</t>
+          <t>OKVED_51_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1700">
       <c r="A1700" t="inlineStr">
         <is>
-          <t>OKVED_41_PostDeyt1</t>
+          <t>OKVED_51_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1701">
       <c r="A1701" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt</t>
+          <t>OKVED_51_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1702">
       <c r="A1702" t="inlineStr">
         <is>
-          <t>OKVED_42_PostDeyt1</t>
+          <t>OKVED_52_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1703">
       <c r="A1703" t="inlineStr">
         <is>
-          <t>OKVED_42_DrPost</t>
+          <t>OKVED_52_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1704">
       <c r="A1704" t="inlineStr">
         <is>
-          <t>OKVED_43_PostDeyt1</t>
+          <t>OKVED_52_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1705">
       <c r="A1705" t="inlineStr">
         <is>
-          <t>OKVED_43_DrPost</t>
+          <t>OKVED_I_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1706">
       <c r="A1706" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt</t>
+          <t>OKVED_55_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1707">
       <c r="A1707" t="inlineStr">
         <is>
-          <t>OKVED_G_PostDeyt1</t>
+          <t>OKVED_K_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1708">
       <c r="A1708" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt</t>
+          <t>OKVED_K_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1709">
       <c r="A1709" t="inlineStr">
         <is>
-          <t>OKVED_46_PostDeyt1</t>
+          <t>OKVED_K_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1710">
       <c r="A1710" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt</t>
+          <t>OKVED_64_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1711">
       <c r="A1711" t="inlineStr">
         <is>
-          <t>OKVED_47_PostDeyt1</t>
+          <t>OKVED_64_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1712">
       <c r="A1712" t="inlineStr">
         <is>
-          <t>OKVED_H_PostDeyt1</t>
+          <t>OKVED_64_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1713">
       <c r="A1713" t="inlineStr">
         <is>
-          <t>OKVED_49_PostDeyt</t>
+          <t>OKVED_M_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1714">
       <c r="A1714" t="inlineStr">
         <is>
-          <t>OKVED_49_PostDeyt1</t>
+          <t>OKVED_70_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1715">
       <c r="A1715" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt</t>
+          <t>OKVED_70_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1716">
       <c r="A1716" t="inlineStr">
         <is>
-          <t>OKVED_50_PostDeyt1</t>
+          <t>OKVED_71_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1717">
       <c r="A1717" t="inlineStr">
         <is>
-          <t>OKVED_50_DrPost</t>
+          <t>OKVED_71_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1718">
       <c r="A1718" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt</t>
+          <t>OKVED_N_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1719">
       <c r="A1719" t="inlineStr">
         <is>
-          <t>OKVED_51_PostDeyt1</t>
+          <t>OKVED_N_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1720">
       <c r="A1720" t="inlineStr">
         <is>
-          <t>OKVED_51_DrPost</t>
+          <t>OKVED_77_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1721">
       <c r="A1721" t="inlineStr">
         <is>
-          <t>OKVED_52_PostDeyt1</t>
+          <t>OKVED_77_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1722">
       <c r="A1722" t="inlineStr">
         <is>
-          <t>OKVED_I_PostDeyt1</t>
+          <t>OKVED_77_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1723">
       <c r="A1723" t="inlineStr">
         <is>
-          <t>OKVED_I_DrPost</t>
+          <t>OKVED_79_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1724">
       <c r="A1724" t="inlineStr">
         <is>
-          <t>OKVED_55_PostDeyt1</t>
+          <t>OKVED_79_PrCenBum</t>
         </is>
       </c>
     </row>
     <row r="1725">
       <c r="A1725" t="inlineStr">
         <is>
-          <t>OKVED_55_DrPost</t>
+          <t>OKVED_79_PrPl</t>
         </is>
       </c>
     </row>
     <row r="1726">
       <c r="A1726" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt</t>
+          <t>OKVED_S_Modern</t>
         </is>
       </c>
     </row>
     <row r="1727">
       <c r="A1727" t="inlineStr">
         <is>
-          <t>OKVED_K_PostDeyt1</t>
+          <t>OKVED_S_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1728">
       <c r="A1728" t="inlineStr">
         <is>
-          <t>OKVED_K_DrPost</t>
+          <t>OKVED_S_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1729">
       <c r="A1729" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt</t>
+          <t>OKVED_94_Modern</t>
         </is>
       </c>
     </row>
     <row r="1730">
       <c r="A1730" t="inlineStr">
         <is>
-          <t>OKVED_64_PostDeyt1</t>
+          <t>OKVED_94_DolUch</t>
         </is>
       </c>
     </row>
     <row r="1731">
       <c r="A1731" t="inlineStr">
         <is>
-          <t>OKVED_64_DrPost</t>
+          <t>OKVED_94_ProcDolgObyazVklInvAkt</t>
         </is>
       </c>
     </row>
     <row r="1732">
       <c r="A1732" t="inlineStr">
         <is>
-          <t>OKVED_L_PostDeyt1</t>
+          <t>OKVED_01_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1733">
       <c r="A1733" t="inlineStr">
         <is>
-          <t>OKVED_68_PostDeyt1</t>
+          <t>OKVED_01_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1734">
       <c r="A1734" t="inlineStr">
         <is>
-          <t>OKVED_M_PostDeyt</t>
+          <t>OKVED_B_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1735">
       <c r="A1735" t="inlineStr">
         <is>
-          <t>OKVED_70_PlCredit</t>
+          <t>OKVED_B_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1736">
       <c r="A1736" t="inlineStr">
         <is>
-          <t>OKVED_70_PostDeyt</t>
+          <t>OKVED_07_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1737">
       <c r="A1737" t="inlineStr">
         <is>
-          <t>OKVED_71_PostDeyt</t>
+          <t>OKVED_07_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1738">
       <c r="A1738" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt</t>
+          <t>OKVED_C_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1739">
       <c r="A1739" t="inlineStr">
         <is>
-          <t>OKVED_74_PostDeyt1</t>
+          <t>OKVED_10_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1740">
       <c r="A1740" t="inlineStr">
         <is>
-          <t>OKVED_74_DrPost</t>
+          <t>OKVED_32_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1741">
       <c r="A1741" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt</t>
+          <t>OKVED_32_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1742">
       <c r="A1742" t="inlineStr">
         <is>
-          <t>OKVED_N_PostDeyt1</t>
+          <t>OKVED_32_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1743">
       <c r="A1743" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt</t>
+          <t>OKVED_33_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1744">
       <c r="A1744" t="inlineStr">
         <is>
-          <t>OKVED_79_PostDeyt1</t>
+          <t>OKVED_33_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1745">
       <c r="A1745" t="inlineStr">
         <is>
-          <t>OKVED_79_DrPost</t>
+          <t>OKVED_33_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1746">
       <c r="A1746" t="inlineStr">
         <is>
-          <t>OKVED_81_PlCredit</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1747">
       <c r="A1747" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt</t>
+          <t>OKVED_35_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1748">
       <c r="A1748" t="inlineStr">
         <is>
-          <t>OKVED_81_PostDeyt1</t>
+          <t>OKVED_E_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1749">
       <c r="A1749" t="inlineStr">
         <is>
-          <t>OKVED_S_PlCredit</t>
+          <t>OKVED_E_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1750">
       <c r="A1750" t="inlineStr">
         <is>
-          <t>OKVED_S_PostDeyt1</t>
+          <t>OKVED_38_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1751">
       <c r="A1751" t="inlineStr">
         <is>
-          <t>OKVED_94_PlCredit</t>
+          <t>OKVED_38_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1752">
       <c r="A1752" t="inlineStr">
         <is>
-          <t>OKVED_94_PostDeyt1</t>
+          <t>OKVED_F_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1753">
       <c r="A1753" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin1</t>
+          <t>OKVED_41_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1754">
       <c r="A1754" t="inlineStr">
         <is>
-          <t>OKVED_01_PlPoFin2</t>
+          <t>OKVED_41_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1755">
       <c r="A1755" t="inlineStr">
         <is>
-          <t>OKVED_B_PlPoFin1</t>
+          <t>OKVED_42_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1756">
       <c r="A1756" t="inlineStr">
         <is>
-          <t>OKVED_07_PlPoFin1</t>
+          <t>OKVED_42_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1757">
       <c r="A1757" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin</t>
+          <t>OKVED_42_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1758">
       <c r="A1758" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin1</t>
+          <t>OKVED_43_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1759">
       <c r="A1759" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin2</t>
+          <t>OKVED_43_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>OKVED_32_PlPoFin3</t>
+          <t>OKVED_G_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1761">
       <c r="A1761" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin</t>
+          <t>OKVED_G_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1762">
       <c r="A1762" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin1</t>
+          <t>OKVED_46_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1763">
       <c r="A1763" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin2</t>
+          <t>OKVED_46_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1764">
       <c r="A1764" t="inlineStr">
         <is>
-          <t>OKVED_33_PlPoFin3</t>
+          <t>OKVED_47_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1765">
       <c r="A1765" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_47_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1766">
       <c r="A1766" t="inlineStr">
         <is>
-          <t>OKVED_35_PlPoFin1</t>
+          <t>OKVED_H_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1767">
       <c r="A1767" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin1</t>
+          <t>OKVED_49_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1768">
       <c r="A1768" t="inlineStr">
         <is>
-          <t>OKVED_E_PlPoFin2</t>
+          <t>OKVED_49_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1769">
       <c r="A1769" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin1</t>
+          <t>OKVED_50_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1770">
       <c r="A1770" t="inlineStr">
         <is>
-          <t>OKVED_38_PlPoFin2</t>
+          <t>OKVED_50_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1771">
       <c r="A1771" t="inlineStr">
         <is>
-          <t>OKVED_F_PlPoFin1</t>
+          <t>OKVED_50_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1772">
       <c r="A1772" t="inlineStr">
         <is>
-          <t>OKVED_41_PlPoFin1</t>
+          <t>OKVED_51_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1773">
       <c r="A1773" t="inlineStr">
         <is>
-          <t>OKVED_42_PlPoFin1</t>
+          <t>OKVED_51_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1774">
       <c r="A1774" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin1</t>
+          <t>OKVED_51_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1775">
       <c r="A1775" t="inlineStr">
         <is>
-          <t>OKVED_43_PlPoFin2</t>
+          <t>OKVED_52_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1776">
       <c r="A1776" t="inlineStr">
         <is>
-          <t>OKVED_G_PlPoFin1</t>
+          <t>OKVED_I_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1777">
       <c r="A1777" t="inlineStr">
         <is>
-          <t>OKVED_46_PlPoFin1</t>
+          <t>OKVED_I_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1778">
       <c r="A1778" t="inlineStr">
         <is>
-          <t>OKVED_47_PlPoFin1</t>
+          <t>OKVED_55_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1779">
       <c r="A1779" t="inlineStr">
         <is>
-          <t>OKVED_H_PlPoFin1</t>
+          <t>OKVED_55_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1780">
       <c r="A1780" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin1</t>
+          <t>OKVED_K_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1781">
       <c r="A1781" t="inlineStr">
         <is>
-          <t>OKVED_49_PlPoFin2</t>
+          <t>OKVED_K_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1782">
       <c r="A1782" t="inlineStr">
         <is>
-          <t>OKVED_50_PlPoFin1</t>
+          <t>OKVED_K_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1783">
       <c r="A1783" t="inlineStr">
         <is>
-          <t>OKVED_51_PlPoFin1</t>
+          <t>OKVED_64_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1784">
       <c r="A1784" t="inlineStr">
         <is>
-          <t>OKVED_51_PlPoFin2</t>
+          <t>OKVED_64_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1785">
       <c r="A1785" t="inlineStr">
         <is>
-          <t>OKVED_52_PlPoFin1</t>
+          <t>OKVED_64_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1786">
       <c r="A1786" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin1</t>
+          <t>OKVED_L_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1787">
       <c r="A1787" t="inlineStr">
         <is>
-          <t>OKVED_I_PlPoFin2</t>
+          <t>OKVED_68_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1788">
       <c r="A1788" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin1</t>
+          <t>OKVED_M_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1789">
       <c r="A1789" t="inlineStr">
         <is>
-          <t>OKVED_55_PlPoFin2</t>
+          <t>OKVED_70_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1790">
       <c r="A1790" t="inlineStr">
         <is>
-          <t>OKVED_K_PlPoFin1</t>
+          <t>OKVED_70_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1791">
       <c r="A1791" t="inlineStr">
         <is>
-          <t>OKVED_64_PlPoFin1</t>
+          <t>OKVED_71_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1792">
       <c r="A1792" t="inlineStr">
         <is>
-          <t>OKVED_L_PlPoFin1</t>
+          <t>OKVED_74_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1793">
       <c r="A1793" t="inlineStr">
         <is>
-          <t>OKVED_68_PlPoFin1</t>
+          <t>OKVED_74_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1794">
       <c r="A1794" t="inlineStr">
         <is>
-          <t>OKVED_M_PlPoFin1</t>
+          <t>OKVED_74_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1795">
       <c r="A1795" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin</t>
+          <t>OKVED_N_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1796">
       <c r="A1796" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin1</t>
+          <t>OKVED_N_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1797">
       <c r="A1797" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin2</t>
+          <t>OKVED_79_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1798">
       <c r="A1798" t="inlineStr">
         <is>
-          <t>OKVED_70_PlPoFin3</t>
+          <t>OKVED_79_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1799">
       <c r="A1799" t="inlineStr">
         <is>
-          <t>OKVED_71_PlPoFin1</t>
+          <t>OKVED_79_DrPost</t>
         </is>
       </c>
     </row>
     <row r="1800">
       <c r="A1800" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin1</t>
+          <t>OKVED_81_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1801">
       <c r="A1801" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin2</t>
+          <t>OKVED_81_PostDeyt</t>
         </is>
       </c>
     </row>
     <row r="1802">
       <c r="A1802" t="inlineStr">
         <is>
-          <t>OKVED_74_PlPoFin3</t>
+          <t>OKVED_81_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1803">
       <c r="A1803" t="inlineStr">
         <is>
-          <t>OKVED_74_SaldoDenPot</t>
+          <t>OKVED_S_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1804">
       <c r="A1804" t="inlineStr">
         <is>
-          <t>OKVED_N_PlPoFin1</t>
+          <t>OKVED_S_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1805">
       <c r="A1805" t="inlineStr">
         <is>
-          <t>OKVED_N_PlPoFin2</t>
+          <t>OKVED_94_PlCredit</t>
         </is>
       </c>
     </row>
     <row r="1806">
       <c r="A1806" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin1</t>
+          <t>OKVED_94_PostDeyt1</t>
         </is>
       </c>
     </row>
     <row r="1807">
       <c r="A1807" t="inlineStr">
         <is>
-          <t>OKVED_79_PlPoFin2</t>
+          <t>OKVED_01_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1808">
       <c r="A1808" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin1</t>
+          <t>OKVED_01_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1809">
       <c r="A1809" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin2</t>
+          <t>OKVED_B_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1810">
       <c r="A1810" t="inlineStr">
         <is>
-          <t>OKVED_81_PlPoFin3</t>
+          <t>OKVED_07_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1811">
       <c r="A1811" t="inlineStr">
         <is>
-          <t>OKVED_81_SaldoDenPot</t>
+          <t>OKVED_32_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1812">
       <c r="A1812" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin1</t>
+          <t>OKVED_32_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1813">
       <c r="A1813" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin2</t>
+          <t>OKVED_32_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1814">
       <c r="A1814" t="inlineStr">
         <is>
-          <t>OKVED_S_PlPoFin3</t>
+          <t>OKVED_32_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1815">
       <c r="A1815" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin1</t>
+          <t>OKVED_32_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1816">
       <c r="A1816" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin2</t>
+          <t>OKVED_33_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1817">
       <c r="A1817" t="inlineStr">
         <is>
-          <t>OKVED_94_PlPoFin3</t>
+          <t>OKVED_33_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1818">
       <c r="A1818" t="inlineStr">
         <is>
-          <t>OKVED_01_Velch</t>
+          <t>OKVED_33_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1819">
       <c r="A1819" t="inlineStr">
         <is>
-          <t>OKVED_11_Velch</t>
+          <t>OKVED_33_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1820">
       <c r="A1820" t="inlineStr">
         <is>
-          <t>OKVED_32_Velch</t>
+          <t>OKVED_33_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1821">
       <c r="A1821" t="inlineStr">
         <is>
-          <t>OKVED_33_Velch</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1822">
       <c r="A1822" t="inlineStr">
         <is>
-          <t>OKVED_E_Velch</t>
+          <t>OKVED_35_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1823">
       <c r="A1823" t="inlineStr">
         <is>
-          <t>OKVED_36_Velch</t>
+          <t>OKVED_E_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1824">
       <c r="A1824" t="inlineStr">
         <is>
-          <t>OKVED_38_Velch</t>
+          <t>OKVED_E_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1825">
       <c r="A1825" t="inlineStr">
         <is>
-          <t>OKVED_F_Velch</t>
+          <t>OKVED_38_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1826">
       <c r="A1826" t="inlineStr">
         <is>
-          <t>OKVED_41_Velch</t>
+          <t>OKVED_38_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1827">
       <c r="A1827" t="inlineStr">
         <is>
-          <t>OKVED_42_Velch</t>
+          <t>OKVED_F_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1828">
       <c r="A1828" t="inlineStr">
         <is>
-          <t>OKVED_43_Velch</t>
+          <t>OKVED_41_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1829">
       <c r="A1829" t="inlineStr">
         <is>
-          <t>OKVED_47_Velch</t>
+          <t>OKVED_42_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1830">
       <c r="A1830" t="inlineStr">
         <is>
-          <t>OKVED_49_Velch</t>
+          <t>OKVED_43_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1831">
       <c r="A1831" t="inlineStr">
         <is>
-          <t>OKVED_I_Velch</t>
+          <t>OKVED_43_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1832">
       <c r="A1832" t="inlineStr">
         <is>
-          <t>OKVED_55_Velch</t>
+          <t>OKVED_43_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1833">
       <c r="A1833" t="inlineStr">
         <is>
-          <t>OKVED_56_Velch</t>
+          <t>OKVED_G_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1834">
       <c r="A1834" t="inlineStr">
         <is>
-          <t>OKVED_J_Velch</t>
+          <t>OKVED_46_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1835">
       <c r="A1835" t="inlineStr">
         <is>
-          <t>OKVED_63_Velch</t>
+          <t>OKVED_47_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1836">
       <c r="A1836" t="inlineStr">
         <is>
-          <t>OKVED_L_Velch</t>
+          <t>OKVED_H_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1837">
       <c r="A1837" t="inlineStr">
         <is>
-          <t>OKVED_68_Velch</t>
+          <t>OKVED_49_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1838">
       <c r="A1838" t="inlineStr">
         <is>
-          <t>OKVED_M_Velch</t>
+          <t>OKVED_49_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1839">
       <c r="A1839" t="inlineStr">
         <is>
-          <t>OKVED_69_Velch</t>
+          <t>OKVED_49_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1840">
       <c r="A1840" t="inlineStr">
         <is>
-          <t>OKVED_70_Velch</t>
+          <t>OKVED_50_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1841">
       <c r="A1841" t="inlineStr">
         <is>
-          <t>OKVED_71_Velch</t>
+          <t>OKVED_50_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1842">
       <c r="A1842" t="inlineStr">
         <is>
-          <t>OKVED_74_Velch</t>
+          <t>OKVED_51_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1843">
       <c r="A1843" t="inlineStr">
         <is>
-          <t>OKVED_N_Velch</t>
+          <t>OKVED_51_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1844">
       <c r="A1844" t="inlineStr">
         <is>
-          <t>OKVED_77_Velch</t>
+          <t>OKVED_52_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1845">
       <c r="A1845" t="inlineStr">
         <is>
-          <t>OKVED_79_Velch</t>
+          <t>OKVED_I_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1846">
       <c r="A1846" t="inlineStr">
         <is>
-          <t>OKVED_81_Velch</t>
+          <t>OKVED_I_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1847">
       <c r="A1847" t="inlineStr">
         <is>
-          <t>OKVED_82_Velch</t>
+          <t>OKVED_I_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1848">
       <c r="A1848" t="inlineStr">
         <is>
-          <t>OKVED_O_Velch</t>
+          <t>OKVED_55_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1849">
       <c r="A1849" t="inlineStr">
         <is>
-          <t>OKVED_84_Velch</t>
+          <t>OKVED_55_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1850">
       <c r="A1850" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_55_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1851">
       <c r="A1851" t="inlineStr">
         <is>
-          <t>OKVED_85_Velch</t>
+          <t>OKVED_K_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1852">
       <c r="A1852" t="inlineStr">
         <is>
-          <t>OKVED_Q_Velch</t>
+          <t>OKVED_K_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1853">
       <c r="A1853" t="inlineStr">
         <is>
-          <t>OKVED_88_Velch</t>
+          <t>OKVED_64_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1854">
       <c r="A1854" t="inlineStr">
         <is>
-          <t>OKVED_R_Velch</t>
+          <t>OKVED_64_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1855">
       <c r="A1855" t="inlineStr">
         <is>
-          <t>OKVED_93_Velch</t>
+          <t>OKVED_L_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1856">
       <c r="A1856" t="inlineStr">
         <is>
-          <t>OKVED_S_Velch</t>
+          <t>OKVED_68_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1857">
       <c r="A1857" t="inlineStr">
         <is>
-          <t>OKVED_94_Velch</t>
+          <t>OKVED_M_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1858">
       <c r="A1858" t="inlineStr">
         <is>
-          <t>OKVED_96_Velch</t>
+          <t>OKVED_70_PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="1859">
       <c r="A1859" t="inlineStr">
         <is>
-          <t>OKVED_43_UstKap_23</t>
+          <t>OKVED_70_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1860">
       <c r="A1860" t="inlineStr">
         <is>
-          <t>OKVED_43_ChiAkt_23</t>
+          <t>OKVED_70_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1861">
       <c r="A1861" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap_23</t>
+          <t>OKVED_70_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1862">
       <c r="A1862" t="inlineStr">
         <is>
-          <t>OKVED_J_UstKap_24</t>
+          <t>OKVED_70_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1863">
       <c r="A1863" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap_23</t>
+          <t>OKVED_71_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1864">
       <c r="A1864" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap_24</t>
+          <t>OKVED_74_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1865">
       <c r="A1865" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap_23</t>
+          <t>OKVED_74_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1866">
       <c r="A1866" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap_24</t>
+          <t>OKVED_74_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1867">
       <c r="A1867" t="inlineStr">
         <is>
-          <t>OKVED_69_ChiAkt_23</t>
+          <t>OKVED_74_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1868">
       <c r="A1868" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap_23</t>
+          <t>OKVED_N_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1869">
       <c r="A1869" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap_24</t>
+          <t>OKVED_N_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1870">
       <c r="A1870" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap_23</t>
+          <t>OKVED_79_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1871">
       <c r="A1871" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap_24</t>
+          <t>OKVED_79_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1872">
       <c r="A1872" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_23</t>
+          <t>OKVED_79_PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="1873">
       <c r="A1873" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_24</t>
+          <t>OKVED_81_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1874">
       <c r="A1874" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_23</t>
+          <t>OKVED_81_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1875">
       <c r="A1875" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_24</t>
+          <t>OKVED_81_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1876">
       <c r="A1876" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap_23</t>
+          <t>OKVED_81_SaldoDenPot</t>
         </is>
       </c>
     </row>
     <row r="1877">
       <c r="A1877" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap_24</t>
+          <t>OKVED_S_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1878">
       <c r="A1878" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap_23</t>
+          <t>OKVED_S_PlPoFin2</t>
         </is>
       </c>
     </row>
     <row r="1879">
       <c r="A1879" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap_24</t>
+          <t>OKVED_S_PlPoFin3</t>
         </is>
       </c>
     </row>
     <row r="1880">
       <c r="A1880" t="inlineStr">
         <is>
-          <t>OKVED_R_UstKap_24</t>
+          <t>OKVED_94_PlPoFin1</t>
         </is>
       </c>
     </row>
     <row r="1881">
       <c r="A1881" t="inlineStr">
+        <is>
+          <t>OKVED_94_PlPoFin2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="inlineStr">
+        <is>
+          <t>OKVED_94_PlPoFin3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="inlineStr">
+        <is>
+          <t>OKVED_01_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="inlineStr">
+        <is>
+          <t>OKVED_11_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="inlineStr">
+        <is>
+          <t>OKVED_32_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="inlineStr">
+        <is>
+          <t>OKVED_33_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="inlineStr">
+        <is>
+          <t>OKVED_E_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="inlineStr">
+        <is>
+          <t>OKVED_36_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="inlineStr">
+        <is>
+          <t>OKVED_38_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="inlineStr">
+        <is>
+          <t>OKVED_F_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="inlineStr">
+        <is>
+          <t>OKVED_41_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="inlineStr">
+        <is>
+          <t>OKVED_42_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="inlineStr">
+        <is>
+          <t>OKVED_43_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="inlineStr">
+        <is>
+          <t>OKVED_47_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="inlineStr">
+        <is>
+          <t>OKVED_49_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="inlineStr">
+        <is>
+          <t>OKVED_I_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="inlineStr">
+        <is>
+          <t>OKVED_55_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="inlineStr">
+        <is>
+          <t>OKVED_56_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="inlineStr">
+        <is>
+          <t>OKVED_J_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="inlineStr">
+        <is>
+          <t>OKVED_63_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="inlineStr">
+        <is>
+          <t>OKVED_L_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="inlineStr">
+        <is>
+          <t>OKVED_68_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="inlineStr">
+        <is>
+          <t>OKVED_M_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="inlineStr">
+        <is>
+          <t>OKVED_69_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr">
+        <is>
+          <t>OKVED_70_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="inlineStr">
+        <is>
+          <t>OKVED_71_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="inlineStr">
+        <is>
+          <t>OKVED_74_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="inlineStr">
+        <is>
+          <t>OKVED_N_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="inlineStr">
+        <is>
+          <t>OKVED_77_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="inlineStr">
+        <is>
+          <t>OKVED_79_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="inlineStr">
+        <is>
+          <t>OKVED_81_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="inlineStr">
+        <is>
+          <t>OKVED_82_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="inlineStr">
+        <is>
+          <t>OKVED_O_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="inlineStr">
+        <is>
+          <t>OKVED_84_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="inlineStr">
+        <is>
+          <t>OKVED_85_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="inlineStr">
+        <is>
+          <t>OKVED_85_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="inlineStr">
+        <is>
+          <t>OKVED_Q_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="inlineStr">
+        <is>
+          <t>OKVED_88_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="inlineStr">
+        <is>
+          <t>OKVED_R_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="inlineStr">
+        <is>
+          <t>OKVED_93_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="inlineStr">
+        <is>
+          <t>OKVED_S_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="inlineStr">
+        <is>
+          <t>OKVED_94_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
+        <is>
+          <t>OKVED_96_Velch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="inlineStr">
+        <is>
+          <t>OKVED_43_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
+        <is>
+          <t>OKVED_43_ChiAkt_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
+        <is>
+          <t>OKVED_J_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
+        <is>
+          <t>OKVED_J_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
+        <is>
+          <t>OKVED_63_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
+        <is>
+          <t>OKVED_63_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr">
+        <is>
+          <t>OKVED_69_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
+        <is>
+          <t>OKVED_69_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>OKVED_69_ChiAkt_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="inlineStr">
+        <is>
+          <t>OKVED_O_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
+        <is>
+          <t>OKVED_O_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>OKVED_84_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
+        <is>
+          <t>OKVED_84_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
+        <is>
+          <t>OKVED_Q_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
+        <is>
+          <t>OKVED_Q_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
+        <is>
+          <t>OKVED_88_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
+        <is>
+          <t>OKVED_88_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
+        <is>
+          <t>OKVED_R_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
         <is>
           <t>OKVED_93_UstKap_24</t>
         </is>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1946"/>
+  <dimension ref="A1:A1967"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13908,133 +13908,280 @@
     <row r="1928">
       <c r="A1928" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap_23</t>
+          <t>OKVED_J_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1929">
       <c r="A1929" t="inlineStr">
         <is>
-          <t>OKVED_63_UstKap_24</t>
+          <t>OKVED_J_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1930">
       <c r="A1930" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap_23</t>
+          <t>OKVED_J_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1931">
       <c r="A1931" t="inlineStr">
         <is>
-          <t>OKVED_69_UstKap_24</t>
+          <t>OKVED_J_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1932">
       <c r="A1932" t="inlineStr">
         <is>
-          <t>OKVED_69_ChiAkt_23</t>
+          <t>OKVED_63_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1933">
       <c r="A1933" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap_23</t>
+          <t>OKVED_63_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1934">
       <c r="A1934" t="inlineStr">
         <is>
-          <t>OKVED_O_UstKap_24</t>
+          <t>OKVED_63_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1935">
       <c r="A1935" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap_23</t>
+          <t>OKVED_63_Pri(ubOtPro</t>
         </is>
       </c>
     </row>
     <row r="1936">
       <c r="A1936" t="inlineStr">
         <is>
-          <t>OKVED_84_UstKap_24</t>
+          <t>OKVED_63_ChiPri(ubOtcPer</t>
         </is>
       </c>
     </row>
     <row r="1937">
       <c r="A1937" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_23</t>
+          <t>OKVED_63_PriUby(-DoNalKChiAktV%</t>
         </is>
       </c>
     </row>
     <row r="1938">
       <c r="A1938" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_24</t>
+          <t>OKVED_K_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1939">
       <c r="A1939" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_23</t>
+          <t>OKVED_64_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1940">
       <c r="A1940" t="inlineStr">
         <is>
-          <t>OKVED_85_UstKap_24</t>
+          <t>OKVED_69_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1941">
       <c r="A1941" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap_23</t>
+          <t>OKVED_69_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1942">
       <c r="A1942" t="inlineStr">
         <is>
-          <t>OKVED_Q_UstKap_24</t>
+          <t>OKVED_69_ChiAkt_23</t>
         </is>
       </c>
     </row>
     <row r="1943">
       <c r="A1943" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap_23</t>
+          <t>OKVED_69_SebPro</t>
         </is>
       </c>
     </row>
     <row r="1944">
       <c r="A1944" t="inlineStr">
         <is>
-          <t>OKVED_88_UstKap_24</t>
+          <t>OKVED_O_UstKap_23</t>
         </is>
       </c>
     </row>
     <row r="1945">
       <c r="A1945" t="inlineStr">
         <is>
-          <t>OKVED_R_UstKap_24</t>
+          <t>OKVED_O_UstKap_24</t>
         </is>
       </c>
     </row>
     <row r="1946">
       <c r="A1946" t="inlineStr">
         <is>
+          <t>OKVED_84_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
+        <is>
+          <t>OKVED_84_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
+        <is>
+          <t>OKVED_85_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
+        <is>
+          <t>OKVED_Q_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
+        <is>
+          <t>OKVED_Q_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
+        <is>
+          <t>OKVED_Q_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
+        <is>
+          <t>OKVED_Q_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
+        <is>
+          <t>OKVED_Q_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
+        <is>
+          <t>OKVED_Q_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
+        <is>
+          <t>OKVED_88_UstKap_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
+        <is>
+          <t>OKVED_88_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
+        <is>
+          <t>OKVED_88_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
+        <is>
+          <t>OKVED_88_Pri(ubOtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
+        <is>
+          <t>OKVED_88_ChiPri(ubOtcPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
+        <is>
+          <t>OKVED_88_PriUby(-DoNalKChiAktV%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
+        <is>
+          <t>OKVED_R_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
+        <is>
+          <t>OKVED_R_SebPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
+        <is>
           <t>OKVED_93_UstKap_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
+        <is>
+          <t>OKVED_93_SebPro</t>
         </is>
       </c>
     </row>

--- a/output/unfilled_tags.xlsx
+++ b/output/unfilled_tags.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1967"/>
+  <dimension ref="A1:A1968"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6250,3724 +6250,3724 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>OKVED_43_KoeObeSobOboSre_23</t>
+          <t>OKVED_32_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>OKVED_43_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_43_KoeObeSobOboSre_23</t>
         </is>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>OKVED_43_DolIstFin(isSobSreIDolObyVValBal_23</t>
+          <t>OKVED_43_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>OKVED_43_SooSobIZaeSre_23</t>
+          <t>OKVED_43_DolIstFin(isSobSreIDolObyVValBal_23</t>
         </is>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>OKVED_56_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_43_SooSobIZaeSre_23</t>
         </is>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>OKVED_56_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_56_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>OKVED_J_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_56_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>OKVED_J_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_J_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>OKVED_63_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_J_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>OKVED_63_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_63_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeObeSobOboSre_23</t>
+          <t>OKVED_63_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>OKVED_69_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_69_KoeObeSobOboSre_23</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>OKVED_69_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_69_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>OKVED_69_DolIstFin(isSobSreIDolObyVValBal_23</t>
+          <t>OKVED_69_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>OKVED_69_SooSobIZaeSre_23</t>
+          <t>OKVED_69_DolIstFin(isSobSreIDolObyVValBal_23</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>OKVED_81_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_69_SooSobIZaeSre_23</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>OKVED_82_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_81_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>OKVED_82_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_82_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>OKVED_O_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_82_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>OKVED_84_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_O_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>OKVED_85_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_84_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>OKVED_85_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_85_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>OKVED_85_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_85_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>OKVED_85_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_85_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>OKVED_Q_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_85_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>OKVED_Q_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_Q_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>OKVED_88_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_Q_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>OKVED_88_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_88_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>OKVED_R_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_88_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>OKVED_R_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_R_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>OKVED_93_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_R_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>OKVED_93_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_93_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>OKVED_96_DolDolObyKIstSobSreIDolOby_23</t>
+          <t>OKVED_93_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>OKVED_96_DolDolObyKIstSobSreIDolOby_24</t>
+          <t>OKVED_96_DolDolObyKIstSobSreIDolOby_23</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>OKVED_43_KoeAbsLik(noOgr20%)_23</t>
+          <t>OKVED_96_DolDolObyKIstSobSreIDolOby_24</t>
         </is>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>OKVED_43_KoeLik(noOgr80%)_23</t>
+          <t>OKVED_43_KoeAbsLik(noOgr20%)_23</t>
         </is>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>OKVED_43_KoeTekLik(po(noOgr20%)_23</t>
+          <t>OKVED_43_KoeLik(noOgr80%)_23</t>
         </is>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeAbsLik(noOgr20%)_23</t>
+          <t>OKVED_43_KoeTekLik(po(noOgr20%)_23</t>
         </is>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeLik(noOgr80%)_23</t>
+          <t>OKVED_69_KoeAbsLik(noOgr20%)_23</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>OKVED_69_KoeTekLik(po(noOgr20%)_23</t>
+          <t>OKVED_69_KoeLik(noOgr80%)_23</t>
         </is>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>MO_30510_SooZaeISobSre(noOgrMenLiRav100_1_24</t>
+          <t>OKVED_69_KoeTekLik(po(noOgr20%)_23</t>
         </is>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>MO_30501_DolDolObyKIstSobSreIDolOby_1_23</t>
+          <t>MO_30510_SooZaeISobSre(noOgrMenLiRav100_1_24</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>MO_30501_DolDolObyKIstSobSreIDolOby_1_24</t>
+          <t>MO_30501_DolDolObyKIstSobSreIDolOby_1_23</t>
         </is>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>MO_30510_DolDolObyKIstSobSreIDolOby_1_23</t>
+          <t>MO_30501_DolDolObyKIstSobSreIDolOby_1_24</t>
         </is>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>MO_30510_DolDolObyKIstSobSreIDolOby_1_24</t>
+          <t>MO_30510_DolDolObyKIstSobSreIDolOby_1_23</t>
         </is>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>MO_30604_DolDolObyKIstSobSreIDolOby_1_23</t>
+          <t>MO_30510_DolDolObyKIstSobSreIDolOby_1_24</t>
         </is>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>MO_30604_DolDolObyKIstSobSreIDolOby_1_24</t>
+          <t>MO_30604_DolDolObyKIstSobSreIDolOby_1_23</t>
         </is>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>OKVED_B_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>MO_30604_DolDolObyKIstSobSreIDolOby_1_24</t>
         </is>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>OKVED_07_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_B_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>OKVED_32_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_07_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>OKVED_33_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_32_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>OKVED_E_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_33_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>OKVED_36_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_E_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>OKVED_38_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_36_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>OKVED_42_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_38_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>OKVED_43_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_42_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>OKVED_49_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_43_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>OKVED_52_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_49_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>OKVED_56_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_52_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>OKVED_56_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_56_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>OKVED_56_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
+          <t>OKVED_56_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>OKVED_K_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_56_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>OKVED_K_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_K_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>OKVED_64_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_K_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>OKVED_64_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_64_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>OKVED_69_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_64_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>OKVED_69_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_69_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>OKVED_71_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_69_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>OKVED_74_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_71_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>OKVED_74_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_74_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>OKVED_74_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
+          <t>OKVED_74_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>OKVED_79_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_74_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>OKVED_81_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_79_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>OKVED_81_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_81_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>OKVED_81_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
+          <t>OKVED_81_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>OKVED_82_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_81_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>OKVED_82_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_82_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>OKVED_82_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
+          <t>OKVED_82_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>OKVED_O_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_82_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>OKVED_O_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_O_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>OKVED_O_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
+          <t>OKVED_O_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>OKVED_84_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_O_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>OKVED_84_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_84_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>OKVED_84_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
+          <t>OKVED_84_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_84_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
+          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
+          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_85_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
+          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas</t>
+          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
+          <t>OKVED_R_DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
+          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerSebPro</t>
         </is>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
+          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas</t>
+          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerVToChiUprRas</t>
         </is>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>OKVED_S_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_93_DohIRasPoObyVidDeyZaOtcPerSebProSUchKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>OKVED_94_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_S_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>OKVED_96_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
+          <t>OKVED_94_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>OKVED_11_OtcGoPro</t>
+          <t>OKVED_96_DohIRasPoObyVidDeyZaOtcPerVToChiKomRas</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>OKVED_32_OtcGoTekNalNaPri</t>
+          <t>OKVED_11_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>OKVED_32_OtcGoOtlNalNaPri</t>
+          <t>OKVED_32_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>OKVED_33_OtcGoPro</t>
+          <t>OKVED_32_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoTekNalNaPri</t>
+          <t>OKVED_33_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoOtlNalNaPri</t>
+          <t>OKVED_38_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoPro</t>
+          <t>OKVED_38_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>OKVED_42_OtcGoPro</t>
+          <t>OKVED_38_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>OKVED_43_OtcGoPro</t>
+          <t>OKVED_42_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>OKVED_50_OtcGoTekNalNaPri</t>
+          <t>OKVED_43_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>OKVED_50_OtcGoPro</t>
+          <t>OKVED_50_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>OKVED_56_OtcGoTekNalNaPri</t>
+          <t>OKVED_50_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>OKVED_56_OtcGoOtlNalNaPri</t>
+          <t>OKVED_56_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoTekNalNaPri</t>
+          <t>OKVED_56_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoOtlNalNaPri</t>
+          <t>OKVED_69_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoPro</t>
+          <t>OKVED_69_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>OKVED_71_OtcGoTekNalNaPri</t>
+          <t>OKVED_69_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>OKVED_74_OtcGoTekNalNaPri</t>
+          <t>OKVED_71_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>OKVED_74_OtcGoPro</t>
+          <t>OKVED_74_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>OKVED_77_OtcGoPro</t>
+          <t>OKVED_74_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>OKVED_79_OtcGoTekNalNaPri</t>
+          <t>OKVED_77_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>OKVED_79_OtcGoPro</t>
+          <t>OKVED_79_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>OKVED_82_OtcGoOtlNalNaPri</t>
+          <t>OKVED_79_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>OKVED_82_OtcGoPro</t>
+          <t>OKVED_82_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>OKVED_O_OtcGoOtlNalNaPri</t>
+          <t>OKVED_82_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>OKVED_O_OtcGoPro</t>
+          <t>OKVED_O_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>OKVED_84_OtcGoOtlNalNaPri</t>
+          <t>OKVED_O_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>OKVED_84_OtcGoPro</t>
+          <t>OKVED_84_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoTekNalNaPri</t>
+          <t>OKVED_84_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoPro</t>
+          <t>OKVED_85_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoTekNalNaPri</t>
+          <t>OKVED_85_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>OKVED_85_OtcGoPro</t>
+          <t>OKVED_85_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoSalProDohIRas</t>
+          <t>OKVED_85_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoTekNalNaPri</t>
+          <t>OKVED_R_OtcGoSalProDohIRas</t>
         </is>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoOtlNalNaPri</t>
+          <t>OKVED_R_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>OKVED_R_OtcGoPro</t>
+          <t>OKVED_R_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoSalProDohIRas</t>
+          <t>OKVED_R_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoTekNalNaPri</t>
+          <t>OKVED_93_OtcGoSalProDohIRas</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoOtlNalNaPri</t>
+          <t>OKVED_93_OtcGoTekNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>OKVED_93_OtcGoPro</t>
+          <t>OKVED_93_OtcGoOtlNalNaPri</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>OKVED_S_OtcGoPro</t>
+          <t>OKVED_93_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>OKVED_94_OtcGoPro</t>
+          <t>OKVED_S_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>OKVED_96_OtcGoPro</t>
+          <t>OKVED_94_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>OKVED_01_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_96_OtcGoPro</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>OKVED_B_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_01_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>OKVED_B_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_B_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>OKVED_07_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_B_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>OKVED_07_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_07_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>OKVED_10_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_07_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>OKVED_11_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_10_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>OKVED_11_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_11_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>OKVED_32_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_11_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>OKVED_33_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_32_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>OKVED_33_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_33_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>OKVED_35_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_33_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>OKVED_35_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_35_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>OKVED_35_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_35_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>OKVED_35_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_35_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>OKVED_E_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_35_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>OKVED_E_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_E_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>OKVED_36_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_E_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>OKVED_36_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_36_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_36_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>OKVED_38_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_38_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>OKVED_F_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_38_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>OKVED_41_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_F_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>OKVED_41_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_41_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>OKVED_42_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_41_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>OKVED_43_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_42_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>OKVED_43_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_43_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>OKVED_G_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_43_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>OKVED_G_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_G_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>OKVED_46_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_G_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>OKVED_46_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_46_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>OKVED_47_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_46_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>OKVED_47_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_47_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>OKVED_50_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_47_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>OKVED_50_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_50_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>OKVED_51_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_50_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>OKVED_51_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_51_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>OKVED_52_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_51_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>OKVED_52_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_52_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>OKVED_I_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_52_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>OKVED_I_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_I_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>OKVED_55_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_I_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>OKVED_55_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_55_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>OKVED_56_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_55_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>OKVED_56_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_56_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>OKVED_K_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_56_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>OKVED_K_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_K_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>OKVED_64_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_K_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>OKVED_64_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_64_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>OKVED_L_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_64_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>OKVED_L_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_L_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>OKVED_68_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_L_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>OKVED_68_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_68_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>OKVED_M_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_68_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>OKVED_M_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_M_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_M_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>OKVED_69_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_69_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>OKVED_70_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_69_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>OKVED_70_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_70_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>OKVED_71_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_70_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>OKVED_71_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_71_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>OKVED_74_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_71_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>OKVED_74_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_74_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>OKVED_N_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_74_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>OKVED_N_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_N_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>OKVED_77_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_N_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>OKVED_77_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_77_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>OKVED_79_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_77_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>OKVED_79_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
+          <t>OKVED_79_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>OKVED_81_OtcGoRezOtPerVneAktNeVklVChiPri(ubPer</t>
+          <t>OKVED_79_OtcGoRezOtProOpeNeVklVChiPri(ubPer</t>
         </is>
       </c>
     </row>
   